--- a/Inventarios.xlsx
+++ b/Inventarios.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheets>
-    <sheet name="Inventarios" sheetId="1" r:id="R9f09cf109d1c4d91"/>
+    <sheet name="Inventarios" sheetId="1" r:id="Rd4d7bed7317c44e2"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="214" xml:space="preserve">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="277" xml:space="preserve">
   <si>
     <t>codigo_articulo</t>
   </si>
@@ -43,10 +43,10 @@
     <t>consecutivo</t>
   </si>
   <si>
-    <t>141102</t>
-  </si>
-  <si>
-    <t>BARRA DE PROTEINA MUESTRA 3-4 GR ARANDANO CAJA X 250</t>
+    <t>110322</t>
+  </si>
+  <si>
+    <t>HUEVO L X 30 CARTON VERDE AMARRADO - VENTA INTERNA</t>
   </si>
   <si>
     <t>VT1</t>
@@ -58,124 +58,424 @@
     <t>UN</t>
   </si>
   <si>
+    <t>HU</t>
+  </si>
+  <si>
+    <t>112268</t>
+  </si>
+  <si>
+    <t>HUEVO XL X 15 PET CAJA X 300.</t>
+  </si>
+  <si>
+    <t>112357</t>
+  </si>
+  <si>
+    <t>HUEVO L X 12 PET CAJA X 120</t>
+  </si>
+  <si>
+    <t>112379</t>
+  </si>
+  <si>
+    <t>HUEVO L X 30 PET CAJA X 300</t>
+  </si>
+  <si>
+    <t>114268</t>
+  </si>
+  <si>
+    <t>HUEVO XL X 15 PET CAJA X 300 PV.</t>
+  </si>
+  <si>
+    <t>114357</t>
+  </si>
+  <si>
+    <t>HUEVO L X 12 PET CAJA X 120 PV.</t>
+  </si>
+  <si>
+    <t>114379</t>
+  </si>
+  <si>
+    <t>HUEVO L X 30 PET CAJA X 300 PV.</t>
+  </si>
+  <si>
+    <t>2110327</t>
+  </si>
+  <si>
+    <t>HUEVO L X 30 CARTON VERDE CANASTA - BGA</t>
+  </si>
+  <si>
+    <t>2110427</t>
+  </si>
+  <si>
+    <t>HUEVO M X 30 CARTON VERDE CANASTA - BGA</t>
+  </si>
+  <si>
+    <t>2112207</t>
+  </si>
+  <si>
+    <t>HUEVO XL X 15 PET CANASTA</t>
+  </si>
+  <si>
+    <t>2114158</t>
+  </si>
+  <si>
+    <t>HUEVO XXL X 10 PET CANASTA X 100 PV</t>
+  </si>
+  <si>
+    <t>2114268</t>
+  </si>
+  <si>
+    <t>HUEVO XL X 15 PET CANASTA X 180 PV</t>
+  </si>
+  <si>
+    <t>2114357</t>
+  </si>
+  <si>
+    <t>HUEVO L X 12 PET CANASTA X 144 PV</t>
+  </si>
+  <si>
+    <t>2114379</t>
+  </si>
+  <si>
+    <t>HUEVO L X 30 PET CANASTA X 180 PV</t>
+  </si>
+  <si>
+    <t>AFCA022</t>
+  </si>
+  <si>
+    <t>CANASTA KIKES 63  X 32 X  23</t>
+  </si>
+  <si>
+    <t>AF</t>
+  </si>
+  <si>
+    <t>AFES013</t>
+  </si>
+  <si>
+    <t>ESTIBAS OVOID 124CM X 65CM</t>
+  </si>
+  <si>
+    <t>2010102</t>
+  </si>
+  <si>
+    <t>HUEVO YUMBO X20 CARTON VERDE CANASTA.</t>
+  </si>
+  <si>
+    <t>VT23</t>
+  </si>
+  <si>
+    <t>TAT POPAYAN - INVENTARIO TRANSITO</t>
+  </si>
+  <si>
+    <t>2110202</t>
+  </si>
+  <si>
+    <t>HUEVO XL X 30 CARTON VERDE CANASTA</t>
+  </si>
+  <si>
+    <t>2110217</t>
+  </si>
+  <si>
+    <t>HUEVO XL X 30 CARTON VERDE AMARRADO SIN ETIQUETA CANASTA</t>
+  </si>
+  <si>
+    <t>2110302</t>
+  </si>
+  <si>
+    <t>HUEVO L X 30 CARTON VERDE CANASTA</t>
+  </si>
+  <si>
+    <t>2110317</t>
+  </si>
+  <si>
+    <t>HUEVO L X 30 CARTON VERDE AMARRADO SIN ETIQUETA CANASTA</t>
+  </si>
+  <si>
+    <t>2110402</t>
+  </si>
+  <si>
+    <t>HUEVO M X 30 CARTON VERDE CANASTA</t>
+  </si>
+  <si>
+    <t>2152388</t>
+  </si>
+  <si>
+    <t>HUEVO L X 15 PAGUE 14 PET EN CANASTA.</t>
+  </si>
+  <si>
+    <t>AFSE003</t>
+  </si>
+  <si>
+    <t>SEPARADORES OVOID DE 124CM X 66CM</t>
+  </si>
+  <si>
+    <t>112271</t>
+  </si>
+  <si>
+    <t>HUEVO XL X 15 PET CAJA X 300 - TAT</t>
+  </si>
+  <si>
+    <t>VT3</t>
+  </si>
+  <si>
+    <t>TAT MEDELLIN - INVENTARIO TRANSITO</t>
+  </si>
+  <si>
+    <t>152384</t>
+  </si>
+  <si>
+    <t>HUEVO L X 15 PAGUE 14 PET CAJA X 300.</t>
+  </si>
+  <si>
+    <t>MDGA105</t>
+  </si>
+  <si>
+    <t>GANGHO METÁLICO LAMINA CAL14 COLD ROLLED BRAZOS 5.2CM P/CANASTA OVOID</t>
+  </si>
+  <si>
+    <t>MD</t>
+  </si>
+  <si>
+    <t>110316</t>
+  </si>
+  <si>
+    <t>HUEVO L X30 CARTON VERDE CON ETIQUETA</t>
+  </si>
+  <si>
+    <t>VT36</t>
+  </si>
+  <si>
+    <t>PEREIRA - INVENTARIO TRANSITO OPERADOR</t>
+  </si>
+  <si>
+    <t>152281</t>
+  </si>
+  <si>
+    <t>HUEVO XL X 15 PAGUE 14 PET CAJA X 300</t>
+  </si>
+  <si>
+    <t>152382</t>
+  </si>
+  <si>
+    <t>HUEVO L X 30 PAGUE 28 PET CAJA X 300</t>
+  </si>
+  <si>
+    <t>VT4</t>
+  </si>
+  <si>
+    <t>TAT BARRANQUILLA - INVENTARIO TRANSITO</t>
+  </si>
+  <si>
+    <t>VT41</t>
+  </si>
+  <si>
+    <t>TAT CARTAGENA - INVENTARIO TRANSITO</t>
+  </si>
+  <si>
+    <t>VT42</t>
+  </si>
+  <si>
+    <t>TAT SANTAMARTA - INVENTARIO TRANSITO</t>
+  </si>
+  <si>
+    <t>VT45</t>
+  </si>
+  <si>
+    <t>TAT SINCELEJO - INVENTARIO TRANSITO</t>
+  </si>
+  <si>
+    <t>VT52</t>
+  </si>
+  <si>
+    <t>TAT BOGOTA - VT52</t>
+  </si>
+  <si>
+    <t>114365</t>
+  </si>
+  <si>
+    <t>HUEVO L X 15 PET CAJA X 300 PV.</t>
+  </si>
+  <si>
+    <t>13560</t>
+  </si>
+  <si>
+    <t>HUEVO B X 300 BANDEJA GRIS CAJA AMARRADO - OLIMPICA</t>
+  </si>
+  <si>
+    <t>142121</t>
+  </si>
+  <si>
+    <t>BARRA DE PROTEINA 50 GR ARANDANO DISPLAY X 12 CAJA X 48</t>
+  </si>
+  <si>
     <t>BP</t>
   </si>
   <si>
-    <t>141202</t>
-  </si>
-  <si>
-    <t>BARRA DE PROTEINA MUESTRA 3-4 GR CHOCOLATE CAJA X 250</t>
-  </si>
-  <si>
-    <t>142111</t>
-  </si>
-  <si>
-    <t>BARRA DE PROTEINA 50 GR ARANDANO DISPLAY X 4 CAJA X 48</t>
-  </si>
-  <si>
-    <t>142121</t>
-  </si>
-  <si>
-    <t>BARRA DE PROTEINA 50 GR ARANDANO DISPLAY X 12 CAJA X 48</t>
-  </si>
-  <si>
-    <t>110480</t>
-  </si>
-  <si>
-    <t>HUEVO M X30 CARTON VERDE CAJA X 360 CON ETIQUETA</t>
-  </si>
-  <si>
-    <t>VT4</t>
-  </si>
-  <si>
-    <t>TAT BARRANQUILLA - INVENTARIO TRANSITO</t>
-  </si>
-  <si>
-    <t>HU</t>
-  </si>
-  <si>
-    <t>112268</t>
-  </si>
-  <si>
-    <t>HUEVO XL X 15 PET CAJA X 300.</t>
-  </si>
-  <si>
-    <t>114268</t>
-  </si>
-  <si>
-    <t>HUEVO XL X 15 PET CAJA X 300 PV.</t>
-  </si>
-  <si>
-    <t>114357</t>
-  </si>
-  <si>
-    <t>HUEVO L X 12 PET CAJA X 120 PV.</t>
-  </si>
-  <si>
-    <t>114379</t>
-  </si>
-  <si>
-    <t>HUEVO L X 30 PET CAJA X 300 PV.</t>
-  </si>
-  <si>
-    <t>2110302</t>
-  </si>
-  <si>
-    <t>HUEVO L X 30 CARTON VERDE CANASTA</t>
-  </si>
-  <si>
-    <t>2110402</t>
-  </si>
-  <si>
-    <t>HUEVO M X 30 CARTON VERDE CANASTA</t>
-  </si>
-  <si>
-    <t>2152388</t>
-  </si>
-  <si>
-    <t>HUEVO L X 15 PAGUE 14 PET EN CANASTA.</t>
-  </si>
-  <si>
-    <t>AFCA022</t>
-  </si>
-  <si>
-    <t>CANASTA KIKES 63  X 32 X  23</t>
-  </si>
-  <si>
-    <t>AF</t>
-  </si>
-  <si>
-    <t>AFES013</t>
-  </si>
-  <si>
-    <t>ESTIBAS OVOID 124CM X 65CM</t>
-  </si>
-  <si>
-    <t>AFSE003</t>
-  </si>
-  <si>
-    <t>SEPARADORES OVOID DE 124CM X 66CM</t>
-  </si>
-  <si>
-    <t>MDGA105</t>
-  </si>
-  <si>
-    <t>GANGHO METÁLICO LAMINA CAL14 COLD ROLLED BRAZOS 5.2CM P/CANASTA OVOID</t>
-  </si>
-  <si>
-    <t>MD</t>
-  </si>
-  <si>
-    <t>VT41</t>
-  </si>
-  <si>
-    <t>TAT CARTAGENA - INVENTARIO TRANSITO</t>
-  </si>
-  <si>
-    <t>13561</t>
-  </si>
-  <si>
-    <t>HUEVO B X 30 BAND GRIS AMARRADO - OLIMPICA</t>
+    <t>143231</t>
+  </si>
+  <si>
+    <t>BARRA DE PROTEINA 30 GR CHOCOLATE DISPLAY X 18 CAJA X 72</t>
+  </si>
+  <si>
+    <t>VT59</t>
+  </si>
+  <si>
+    <t>TAT BOGOTA - VT59</t>
+  </si>
+  <si>
+    <t>VT6</t>
+  </si>
+  <si>
+    <t>TAT PASTO - INVENTARIO TRANSITO</t>
+  </si>
+  <si>
+    <t>EECA006</t>
+  </si>
+  <si>
+    <t>CAJA REGULAR X300 EMPAQUE PET</t>
+  </si>
+  <si>
+    <t>VTAL06</t>
+  </si>
+  <si>
+    <t>EMPAQUES ALKA 1 TRANSITO</t>
+  </si>
+  <si>
+    <t>EE</t>
+  </si>
+  <si>
+    <t>EMET014</t>
+  </si>
+  <si>
+    <t>ETIQUETA COD  BARRA HUEVO A ROJO X 30 D1</t>
+  </si>
+  <si>
+    <t>EM</t>
+  </si>
+  <si>
+    <t>EMET02</t>
+  </si>
+  <si>
+    <t>ETIQUETA COD DE BARRA HUEVO L X 30 - K</t>
+  </si>
+  <si>
+    <t>PTEM029</t>
+  </si>
+  <si>
+    <t>EMPAQUE PET X 30 UNIDADES BASE ACEBRI</t>
+  </si>
+  <si>
+    <t>PT</t>
+  </si>
+  <si>
+    <t>PTEM030</t>
+  </si>
+  <si>
+    <t>EMPAQUE PET X 30 UNIDADES TAPA ACEBRI</t>
+  </si>
+  <si>
+    <t>PTEM034</t>
+  </si>
+  <si>
+    <t>EMPAQUE PET X 15 TRANSPARENTE ACEBRI</t>
+  </si>
+  <si>
+    <t>PTEM048</t>
+  </si>
+  <si>
+    <t>EMPAQUE PETX12 - ACEBRI</t>
+  </si>
+  <si>
+    <t>EMCA019</t>
+  </si>
+  <si>
+    <t>CAJA DOCENERA SOL NACIENTE NEGRA</t>
+  </si>
+  <si>
+    <t>VTALBKA2</t>
+  </si>
+  <si>
+    <t>EMPAQUES ALKA 2 TRANSITO</t>
+  </si>
+  <si>
+    <t>EMCI001</t>
+  </si>
+  <si>
+    <t>CINTA CAJA  ROLLO X 1000 MTS</t>
+  </si>
+  <si>
+    <t>RL</t>
+  </si>
+  <si>
+    <t>EMES005</t>
+  </si>
+  <si>
+    <t>ESQUINERO DE CARTON 85 X 14 CM</t>
+  </si>
+  <si>
+    <t>EMET010</t>
+  </si>
+  <si>
+    <t>ETIQUETA COD BARRA HUEVO A ROJO X 30 ALAT</t>
+  </si>
+  <si>
+    <t>EMLA001</t>
+  </si>
+  <si>
+    <t>LAMINA DE CARTON CORRUGADO 88 X 119 CM</t>
+  </si>
+  <si>
+    <t>EMPA007</t>
+  </si>
+  <si>
+    <t>PLASTICO SUPER STRECH 45X10X450 MT SIN CONO</t>
+  </si>
+  <si>
+    <t>PTEM051</t>
+  </si>
+  <si>
+    <t>EMPAQUE PET X 30 L ETIQUETADO</t>
+  </si>
+  <si>
+    <t>PTEM054</t>
+  </si>
+  <si>
+    <t>EMPAQUE PET X 15 L ETIQUETADO</t>
+  </si>
+  <si>
+    <t>VTALKA</t>
+  </si>
+  <si>
+    <t>KIKES - EGIPTO - INVENTARIO TRANSITO</t>
+  </si>
+  <si>
+    <t>VTALKA2</t>
+  </si>
+  <si>
+    <t>EGIPTO - INVENTARIO TRANSITO ALKA2</t>
+  </si>
+  <si>
+    <t>VTBE</t>
+  </si>
+  <si>
+    <t>BODEGA BELLAVISTA - INVENTARIO TRANSITO</t>
+  </si>
+  <si>
+    <t>2010301</t>
+  </si>
+  <si>
+    <t>HUEVO AA X30 CARTON GRIS CANASTA.</t>
+  </si>
+  <si>
+    <t>VTBO</t>
+  </si>
+  <si>
+    <t>CENTRO DE EMPAQUES BOGOTA -INVENTARIO TRANSITO</t>
+  </si>
+  <si>
+    <t>2410401</t>
+  </si>
+  <si>
+    <t>HUEVO CE X 30 CARTON GRIS CANASTA</t>
   </si>
   <si>
     <t>13358</t>
@@ -184,10 +484,190 @@
     <t>HUEVO AA ROJO X 288 CARTON GRIS CAJA-EN DOCENERA-SOL NACIENT.</t>
   </si>
   <si>
-    <t>VT43</t>
-  </si>
-  <si>
-    <t>TAT VALLEDUPAR - INVENTARIO TRANSITO</t>
+    <t>VTBQ</t>
+  </si>
+  <si>
+    <t>BARRANQUILLA - INVENTARIO TRANSITO</t>
+  </si>
+  <si>
+    <t>2010401</t>
+  </si>
+  <si>
+    <t>HUEVO A X30 CARTON GRIS CANASTA.</t>
+  </si>
+  <si>
+    <t>2010501</t>
+  </si>
+  <si>
+    <t>HUEVO B X30 CARTON GRIS CANASTA.</t>
+  </si>
+  <si>
+    <t>13324</t>
+  </si>
+  <si>
+    <t>HUEVO AA X 30 BAND GRIS AMARRADO TAPA VERDE ALAT - ESTIBADO</t>
+  </si>
+  <si>
+    <t>VTCA</t>
+  </si>
+  <si>
+    <t>CENTRO DE EMPAQUES CALI-INVENTARIO TRANSITO</t>
+  </si>
+  <si>
+    <t>13420</t>
+  </si>
+  <si>
+    <t>HUEVO A X 30 BAND GRIS AMARRADO SOL NACIENTE - ESTIBADO</t>
+  </si>
+  <si>
+    <t>EMBA008</t>
+  </si>
+  <si>
+    <t>BANDEJA HUEVO X 30 EXTRA VERDE</t>
+  </si>
+  <si>
+    <t>VTEM03</t>
+  </si>
+  <si>
+    <t>EMPAQUES MEDELLIN TRANSITO</t>
+  </si>
+  <si>
+    <t>EMTB001</t>
+  </si>
+  <si>
+    <t>TAPA PARA BANDEJA GRIS</t>
+  </si>
+  <si>
+    <t>EMTB002</t>
+  </si>
+  <si>
+    <t>TAPA PARA BANDEJA VERDE KIKES</t>
+  </si>
+  <si>
+    <t>VTEMBQ</t>
+  </si>
+  <si>
+    <t>EMPAQUES BARRANQUILLA TRANSITO</t>
+  </si>
+  <si>
+    <t>EMET01</t>
+  </si>
+  <si>
+    <t>ETIQUETA COD DE BARRA HUEVO M X 30 - K</t>
+  </si>
+  <si>
+    <t>EMET031</t>
+  </si>
+  <si>
+    <t>ETIQUETA ADHESIVA BLANCA 100 MM X 50 MM - ZEBRA</t>
+  </si>
+  <si>
+    <t>EMLA002</t>
+  </si>
+  <si>
+    <t>LAMINA CARTON 60X90</t>
+  </si>
+  <si>
+    <t>VTEMT3</t>
+  </si>
+  <si>
+    <t>VIRTUAL EMPAQUE TAT MEDELLIN</t>
+  </si>
+  <si>
+    <t>EMBA010</t>
+  </si>
+  <si>
+    <t>BANDEJA HUEVO X 30 SPCCO VERDE</t>
+  </si>
+  <si>
+    <t>VTEMT41</t>
+  </si>
+  <si>
+    <t>VIRTUAL EMPAQUE TAT CARTAGENA</t>
+  </si>
+  <si>
+    <t>EMSU001</t>
+  </si>
+  <si>
+    <t>SUJETADOR PLASTIFLECHA 8MM NYLON DOBLE TT CAJA X 10.000 UNID</t>
+  </si>
+  <si>
+    <t>VTEMT42</t>
+  </si>
+  <si>
+    <t>VIRTUAL EMPAQUE TAT SANTAMARTA</t>
+  </si>
+  <si>
+    <t>DOCL002</t>
+  </si>
+  <si>
+    <t>CAMISETA LANILLA VERDE TALLA M</t>
+  </si>
+  <si>
+    <t>VTEMT6</t>
+  </si>
+  <si>
+    <t>VIRTUAL EMPAQUE TAT PASTO</t>
+  </si>
+  <si>
+    <t>DO</t>
+  </si>
+  <si>
+    <t>DOCP003</t>
+  </si>
+  <si>
+    <t>CAMISETA POLO VERDE TALLA L</t>
+  </si>
+  <si>
+    <t>DOPJ003</t>
+  </si>
+  <si>
+    <t>PANTALON JEAN CABALLERO TALLA 32</t>
+  </si>
+  <si>
+    <t>VTKI</t>
+  </si>
+  <si>
+    <t>BODEGA KIKES - INVENTARIO TRANSITO</t>
+  </si>
+  <si>
+    <t>AFES00</t>
+  </si>
+  <si>
+    <t>ESTIBA DE MADERA 120 CM X100 CM   X 9 TACOS</t>
+  </si>
+  <si>
+    <t>ENES014</t>
+  </si>
+  <si>
+    <t>ESTIBA TIPO EXPORTACION 120 CMS X 100CMS</t>
+  </si>
+  <si>
+    <t>EN</t>
+  </si>
+  <si>
+    <t>MDES002</t>
+  </si>
+  <si>
+    <t>ESTIBAS PLASTICAS</t>
+  </si>
+  <si>
+    <t>13322</t>
+  </si>
+  <si>
+    <t>HUEVO AA X 30 BAND GRIS AMARRADO TAPA VERDE ALAT.</t>
+  </si>
+  <si>
+    <t>VTKIGT</t>
+  </si>
+  <si>
+    <t>BODEGA EVENTUALIDAD ALMACENAMIENTO- INVENTARIO TRA</t>
+  </si>
+  <si>
+    <t>13419</t>
+  </si>
+  <si>
+    <t>HUEVO A X 30 CARTON GRIS AMARRADO SOL NACIENTE.</t>
   </si>
   <si>
     <t>13457</t>
@@ -202,253 +682,106 @@
     <t>HUEVO B X 240 BANDEJA GRIS CAJA AMARRADO BUENASOS.</t>
   </si>
   <si>
-    <t>110472</t>
-  </si>
-  <si>
-    <t>HUEVO M X30 CARTON VERDE CAJA  X 60</t>
-  </si>
-  <si>
-    <t>VT52</t>
-  </si>
-  <si>
-    <t>TAT BOGOTA - VT52</t>
-  </si>
-  <si>
-    <t>112271</t>
-  </si>
-  <si>
-    <t>HUEVO XL X 15 PET CAJA X 300 - TAT</t>
-  </si>
-  <si>
-    <t>112357</t>
-  </si>
-  <si>
-    <t>HUEVO L X 12 PET CAJA X 120</t>
-  </si>
-  <si>
-    <t>112379</t>
-  </si>
-  <si>
-    <t>HUEVO L X 30 PET CAJA X 300</t>
-  </si>
-  <si>
-    <t>114365</t>
-  </si>
-  <si>
-    <t>HUEVO L X 15 PET CAJA X 300 PV.</t>
-  </si>
-  <si>
-    <t>13560</t>
-  </si>
-  <si>
-    <t>HUEVO B X 300 BANDEJA GRIS CAJA AMARRADO - OLIMPICA</t>
-  </si>
-  <si>
-    <t>143231</t>
-  </si>
-  <si>
-    <t>BARRA DE PROTEINA 30 GR CHOCOLATE DISPLAY X 18 CAJA X 72</t>
-  </si>
-  <si>
-    <t>152382</t>
-  </si>
-  <si>
-    <t>HUEVO L X 30 PAGUE 28 PET CAJA X 300</t>
-  </si>
-  <si>
-    <t>152384</t>
-  </si>
-  <si>
-    <t>HUEVO L X 15 PAGUE 14 PET CAJA X 300.</t>
-  </si>
-  <si>
-    <t>2010102</t>
-  </si>
-  <si>
-    <t>HUEVO YUMBO X20 CARTON VERDE CANASTA.</t>
-  </si>
-  <si>
-    <t>2110202</t>
-  </si>
-  <si>
-    <t>HUEVO XL X 30 CARTON VERDE CANASTA</t>
-  </si>
-  <si>
-    <t>2110217</t>
-  </si>
-  <si>
-    <t>HUEVO XL X 30 CARTON VERDE AMARRADO SIN ETIQUETA CANASTA</t>
-  </si>
-  <si>
-    <t>2110317</t>
-  </si>
-  <si>
-    <t>HUEVO L X 30 CARTON VERDE AMARRADO SIN ETIQUETA CANASTA</t>
-  </si>
-  <si>
-    <t>2112207</t>
-  </si>
-  <si>
-    <t>HUEVO XL X 15 PET CANASTA</t>
-  </si>
-  <si>
-    <t>74001</t>
-  </si>
-  <si>
-    <t>HUEVO DE BAJA ROTACION</t>
-  </si>
-  <si>
-    <t>VT59</t>
-  </si>
-  <si>
-    <t>TAT BOGOTA - VT59</t>
-  </si>
-  <si>
-    <t>VT6</t>
-  </si>
-  <si>
-    <t>TAT PASTO - INVENTARIO TRANSITO</t>
-  </si>
-  <si>
-    <t>VT7</t>
-  </si>
-  <si>
-    <t>TAT CUCUTA - INVENTARIO TRANSITO</t>
-  </si>
-  <si>
-    <t>VTBO</t>
-  </si>
-  <si>
-    <t>CENTRO DE EMPAQUES BOGOTA -INVENTARIO TRANSITO</t>
-  </si>
-  <si>
-    <t>2410401</t>
-  </si>
-  <si>
-    <t>HUEVO CE X 30 CARTON GRIS CANASTA</t>
-  </si>
-  <si>
-    <t>2010301</t>
-  </si>
-  <si>
-    <t>HUEVO AA X30 CARTON GRIS CANASTA.</t>
-  </si>
-  <si>
-    <t>VTBQ</t>
-  </si>
-  <si>
-    <t>BARRANQUILLA - INVENTARIO TRANSITO</t>
-  </si>
-  <si>
-    <t>2010501</t>
-  </si>
-  <si>
-    <t>HUEVO B X30 CARTON GRIS CANASTA.</t>
-  </si>
-  <si>
-    <t>13420</t>
-  </si>
-  <si>
-    <t>HUEVO A X 30 BAND GRIS AMARRADO SOL NACIENTE - ESTIBADO</t>
-  </si>
-  <si>
-    <t>VTCA</t>
-  </si>
-  <si>
-    <t>CENTRO DE EMPAQUES CALI-INVENTARIO TRANSITO</t>
-  </si>
-  <si>
-    <t>EMBA006</t>
-  </si>
-  <si>
-    <t>BANDEJA HUEVO X 30 SUPERIOR O UNIVERSAL GRIS</t>
-  </si>
-  <si>
-    <t>VTEM02</t>
-  </si>
-  <si>
-    <t>EMPAQUES CALI TRANSITO</t>
-  </si>
-  <si>
-    <t>EM</t>
-  </si>
-  <si>
-    <t>EMBA008</t>
-  </si>
-  <si>
-    <t>BANDEJA HUEVO X 30 EXTRA VERDE</t>
-  </si>
-  <si>
-    <t>EMBA001</t>
-  </si>
-  <si>
-    <t>BANDEJA HUEVO X 30 SPCCO GRIS</t>
-  </si>
-  <si>
-    <t>VTEM03</t>
-  </si>
-  <si>
-    <t>EMPAQUES MEDELLIN TRANSITO</t>
-  </si>
-  <si>
-    <t>EMES005</t>
-  </si>
-  <si>
-    <t>ESQUINERO DE CARTON 85 X 14 CM</t>
-  </si>
-  <si>
-    <t>EMTB001</t>
-  </si>
-  <si>
-    <t>TAPA PARA BANDEJA GRIS</t>
-  </si>
-  <si>
-    <t>EMTB002</t>
-  </si>
-  <si>
-    <t>TAPA PARA BANDEJA VERDE KIKES</t>
-  </si>
-  <si>
-    <t>EMLA002</t>
-  </si>
-  <si>
-    <t>LAMINA CARTON 60X90</t>
-  </si>
-  <si>
-    <t>VTEMT3</t>
-  </si>
-  <si>
-    <t>VIRTUAL EMPAQUE TAT MEDELLIN</t>
-  </si>
-  <si>
-    <t>EMBA010</t>
-  </si>
-  <si>
-    <t>BANDEJA HUEVO X 30 SPCCO VERDE</t>
-  </si>
-  <si>
-    <t>VTEMT41</t>
-  </si>
-  <si>
-    <t>VIRTUAL EMPAQUE TAT CARTAGENA</t>
-  </si>
-  <si>
-    <t>EMSU001</t>
-  </si>
-  <si>
-    <t>SUJETADOR PLASTIFLECHA 8MM NYLON DOBLE TT CAJA X 10.000 UNID</t>
-  </si>
-  <si>
-    <t>EMET02</t>
-  </si>
-  <si>
-    <t>ETIQUETA COD DE BARRA HUEVO L X 30 - K</t>
-  </si>
-  <si>
-    <t>VTEMT52</t>
-  </si>
-  <si>
-    <t>VIRTUAL EMPAQUE TAT BOGOTA NORTE</t>
+    <t>2013322</t>
+  </si>
+  <si>
+    <t>HUEVO AA X 30 BAND GRIS AMARRADO TAPA VERDE ALAT CANASTA</t>
+  </si>
+  <si>
+    <t>2013419</t>
+  </si>
+  <si>
+    <t>HUEVO A X 30 CARTON GRIS AMARRADO SOL NACIENTE CANASTA.</t>
+  </si>
+  <si>
+    <t>VTME</t>
+  </si>
+  <si>
+    <t>CENTRO DE EMPAQUES MEDELLIN -INVENTARIO TRANSITO</t>
+  </si>
+  <si>
+    <t>VTPALM</t>
+  </si>
+  <si>
+    <t>EGIPTO - INVENTARIO TRANSITO PALMA</t>
+  </si>
+  <si>
+    <t>MA0101</t>
+  </si>
+  <si>
+    <t>DESTILADO DE MAIZ (DDGS)</t>
+  </si>
+  <si>
+    <t>VTPBA</t>
+  </si>
+  <si>
+    <t>TRANSITO VIRTUAL PUERTO BARRANQUILLA</t>
+  </si>
+  <si>
+    <t>KG</t>
+  </si>
+  <si>
+    <t>MI</t>
+  </si>
+  <si>
+    <t>MA0001</t>
+  </si>
+  <si>
+    <t>MAIZ AMARILLO AMERICANO</t>
+  </si>
+  <si>
+    <t>VTPBU</t>
+  </si>
+  <si>
+    <t>TRANSITO VIRTUAL PUERTO BUENAVENTURA</t>
+  </si>
+  <si>
+    <t>MA0041</t>
+  </si>
+  <si>
+    <t>TORTA DE SOYA AMERICANA</t>
+  </si>
+  <si>
+    <t>MA0056</t>
+  </si>
+  <si>
+    <t>FRIJOL SOYA AMERICANO CRUDO</t>
+  </si>
+  <si>
+    <t>MI0502</t>
+  </si>
+  <si>
+    <t>FOSFATO MONOCALCICO MCP PHOSPHEA</t>
+  </si>
+  <si>
+    <t>MDKI027</t>
+  </si>
+  <si>
+    <t>KIT-71 ANILLOS INTERMEDIO HIDROLAVADORA  WS-171/ W-913 / W-9</t>
+  </si>
+  <si>
+    <t>VTPL01</t>
+  </si>
+  <si>
+    <t>ALMACEN - PALMAS TRANSITO</t>
+  </si>
+  <si>
+    <t>KI</t>
+  </si>
+  <si>
+    <t>UPTA25</t>
+  </si>
+  <si>
+    <t>TALON. RECIBOS DE CAJA MENOR</t>
+  </si>
+  <si>
+    <t>UP</t>
+  </si>
+  <si>
+    <t>VTPL06</t>
+  </si>
+  <si>
+    <t>EMPAQUES PALMAS TRANSITO</t>
   </si>
   <si>
     <t>EMET03</t>
@@ -457,178 +790,34 @@
     <t>ETIQUETA COD DE BARRA HUEVO XL X 30 - K</t>
   </si>
   <si>
-    <t>DOCL002</t>
-  </si>
-  <si>
-    <t>CAMISETA LANILLA VERDE TALLA M</t>
-  </si>
-  <si>
-    <t>VTEMT6</t>
-  </si>
-  <si>
-    <t>VIRTUAL EMPAQUE TAT PASTO</t>
-  </si>
-  <si>
-    <t>DO</t>
-  </si>
-  <si>
-    <t>DOCP003</t>
-  </si>
-  <si>
-    <t>CAMISETA POLO VERDE TALLA L</t>
-  </si>
-  <si>
-    <t>DOPJ003</t>
-  </si>
-  <si>
-    <t>PANTALON JEAN CABALLERO TALLA 32</t>
-  </si>
-  <si>
-    <t>100</t>
-  </si>
-  <si>
-    <t>HUEVO SIN CLASIFICAR ROJO</t>
-  </si>
-  <si>
-    <t>VTGRA</t>
-  </si>
-  <si>
-    <t>BODEGA VIRTUAL DE HUEVO EN TRANSITO</t>
-  </si>
-  <si>
-    <t>13324</t>
-  </si>
-  <si>
-    <t>HUEVO AA X 30 BAND GRIS AMARRADO TAPA VERDE ALAT - ESTIBADO</t>
-  </si>
-  <si>
-    <t>VTKI</t>
-  </si>
-  <si>
-    <t>BODEGA KIKES - INVENTARIO TRANSITO</t>
-  </si>
-  <si>
-    <t>AFES00</t>
-  </si>
-  <si>
-    <t>ESTIBA DE MADERA 120 CM X100 CM   X 9 TACOS</t>
-  </si>
-  <si>
-    <t>ENES014</t>
-  </si>
-  <si>
-    <t>ESTIBA TIPO EXPORTACION 120 CMS X 100CMS</t>
-  </si>
-  <si>
-    <t>EN</t>
-  </si>
-  <si>
-    <t>MDES002</t>
-  </si>
-  <si>
-    <t>ESTIBAS PLASTICAS</t>
-  </si>
-  <si>
-    <t>13322</t>
-  </si>
-  <si>
-    <t>HUEVO AA X 30 BAND GRIS AMARRADO TAPA VERDE ALAT.</t>
-  </si>
-  <si>
-    <t>VTKIGT</t>
-  </si>
-  <si>
-    <t>BODEGA EVENTUALIDAD ALMACENAMIENTO- INVENTARIO TRA</t>
-  </si>
-  <si>
-    <t>13419</t>
-  </si>
-  <si>
-    <t>HUEVO A X 30 CARTON GRIS AMARRADO SOL NACIENTE.</t>
-  </si>
-  <si>
-    <t>VTME</t>
-  </si>
-  <si>
-    <t>CENTRO DE EMPAQUES MEDELLIN -INVENTARIO TRANSITO</t>
-  </si>
-  <si>
-    <t>MA0101</t>
-  </si>
-  <si>
-    <t>DESTILADO DE MAIZ (DDGS)</t>
-  </si>
-  <si>
-    <t>VTPBA</t>
-  </si>
-  <si>
-    <t>TRANSITO VIRTUAL PUERTO BARRANQUILLA</t>
-  </si>
-  <si>
-    <t>KG</t>
-  </si>
-  <si>
-    <t>MI</t>
-  </si>
-  <si>
-    <t>MA0001</t>
-  </si>
-  <si>
-    <t>MAIZ AMARILLO AMERICANO</t>
-  </si>
-  <si>
-    <t>VTPBU</t>
-  </si>
-  <si>
-    <t>TRANSITO VIRTUAL PUERTO BUENAVENTURA</t>
-  </si>
-  <si>
-    <t>MA0041</t>
-  </si>
-  <si>
-    <t>TORTA DE SOYA AMERICANA</t>
-  </si>
-  <si>
-    <t>MA0056</t>
-  </si>
-  <si>
-    <t>FRIJOL SOYA AMERICANO CRUDO</t>
-  </si>
-  <si>
-    <t>MI0502</t>
-  </si>
-  <si>
-    <t>FOSFATO MONOCALCICO MCP PHOSPHEA</t>
-  </si>
-  <si>
-    <t>MDKI027</t>
-  </si>
-  <si>
-    <t>KIT-71 ANILLOS INTERMEDIO HIDROLAVADORA  WS-171/ W-913 / W-9</t>
-  </si>
-  <si>
-    <t>VTPL01</t>
-  </si>
-  <si>
-    <t>ALMACEN - PALMAS TRANSITO</t>
-  </si>
-  <si>
-    <t>KI</t>
-  </si>
-  <si>
-    <t>UPTA25</t>
-  </si>
-  <si>
-    <t>TALON. RECIBOS DE CAJA MENOR</t>
-  </si>
-  <si>
-    <t>UP</t>
+    <t>PTEM050</t>
+  </si>
+  <si>
+    <t>EMPAQUE PET X 15 L PAGUE 14 ETIQUETADO</t>
+  </si>
+  <si>
+    <t>PTEM067</t>
+  </si>
+  <si>
+    <t>EMPAQUE PET X 15 XL PAGUE 14 ETIQUETADO.</t>
   </si>
   <si>
     <t>VTPSM</t>
   </si>
   <si>
     <t>TRANSITO VIRTUAL PUERTO SANTA MARTA</t>
+  </si>
+  <si>
+    <t>79103</t>
+  </si>
+  <si>
+    <t>HUEVO ROTO GT</t>
+  </si>
+  <si>
+    <t>VTPULV</t>
+  </si>
+  <si>
+    <t>BODEGA TRANSITO HUEVO ROTO PARA PULVERIZADO</t>
   </si>
   <si>
     <t>81151</t>
@@ -754,13 +943,13 @@
         <v>13</v>
       </c>
       <c r="D2">
-        <v>1750</v>
+        <v>750</v>
       </c>
       <c r="E2" t="s">
         <v>14</v>
       </c>
       <c r="F2" s="2">
-        <v>46265.501307870371</v>
+        <v>46266</v>
       </c>
       <c r="G2" t="s">
         <v>15</v>
@@ -772,7 +961,7 @@
       <c r="J2"/>
       <c r="K2"/>
       <c r="L2">
-        <v>33</v>
+        <v>97</v>
       </c>
     </row>
     <row r="3">
@@ -786,13 +975,13 @@
         <v>13</v>
       </c>
       <c r="D3">
-        <v>1750</v>
+        <v>300</v>
       </c>
       <c r="E3" t="s">
         <v>14</v>
       </c>
       <c r="F3" s="2">
-        <v>46265.501307870371</v>
+        <v>46267.381990740738</v>
       </c>
       <c r="G3" t="s">
         <v>15</v>
@@ -804,7 +993,7 @@
       <c r="J3"/>
       <c r="K3"/>
       <c r="L3">
-        <v>25</v>
+        <v>2489</v>
       </c>
     </row>
     <row r="4">
@@ -818,13 +1007,13 @@
         <v>13</v>
       </c>
       <c r="D4">
-        <v>480</v>
+        <v>120</v>
       </c>
       <c r="E4" t="s">
         <v>14</v>
       </c>
       <c r="F4" s="2">
-        <v>46265.501307870371</v>
+        <v>46267.381990740738</v>
       </c>
       <c r="G4" t="s">
         <v>15</v>
@@ -836,7 +1025,7 @@
       <c r="J4"/>
       <c r="K4"/>
       <c r="L4">
-        <v>15</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="5">
@@ -850,13 +1039,13 @@
         <v>13</v>
       </c>
       <c r="D5">
-        <v>2064</v>
+        <v>300</v>
       </c>
       <c r="E5" t="s">
         <v>14</v>
       </c>
       <c r="F5" s="2">
-        <v>46265.501307870371</v>
+        <v>46267.381990740738</v>
       </c>
       <c r="G5" t="s">
         <v>15</v>
@@ -868,7 +1057,7 @@
       <c r="J5"/>
       <c r="K5"/>
       <c r="L5">
-        <v>59</v>
+        <v>2789</v>
       </c>
     </row>
     <row r="6">
@@ -879,1108 +1068,1100 @@
         <v>24</v>
       </c>
       <c r="C6" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D6">
-        <v>33480</v>
+        <v>600</v>
       </c>
       <c r="E6" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="F6" s="2">
-        <v>46265.881678240738</v>
+        <v>46267.379988425921</v>
       </c>
       <c r="G6" t="s">
         <v>15</v>
       </c>
       <c r="H6" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="I6"/>
       <c r="J6"/>
       <c r="K6"/>
       <c r="L6">
-        <v>175</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B7" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D7">
-        <v>300</v>
+        <v>360</v>
       </c>
       <c r="E7" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="F7" s="2">
-        <v>46265.881678240738</v>
+        <v>46267.38077546296</v>
       </c>
       <c r="G7" t="s">
         <v>15</v>
       </c>
       <c r="H7" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="I7"/>
       <c r="J7"/>
       <c r="K7"/>
       <c r="L7">
-        <v>635</v>
+        <v>592</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B8" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C8" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D8">
-        <v>2100</v>
+        <v>1800</v>
       </c>
       <c r="E8" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="F8" s="2">
-        <v>46265.880752314813</v>
+        <v>46267.38077546296</v>
       </c>
       <c r="G8" t="s">
         <v>15</v>
       </c>
       <c r="H8" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="I8"/>
       <c r="J8"/>
       <c r="K8"/>
       <c r="L8">
-        <v>1276</v>
+        <v>1372</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B9" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C9" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D9">
-        <v>360</v>
+        <v>46080</v>
       </c>
       <c r="E9" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="F9" s="2">
-        <v>46265.880752314813</v>
+        <v>46267.381990740738</v>
       </c>
       <c r="G9" t="s">
         <v>15</v>
       </c>
       <c r="H9" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="I9"/>
       <c r="J9"/>
       <c r="K9"/>
       <c r="L9">
-        <v>533</v>
+        <v>831</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B10" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C10" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D10">
-        <v>4200</v>
+        <v>11520</v>
       </c>
       <c r="E10" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="F10" s="2">
-        <v>46265.880752314813</v>
+        <v>46267.381990740738</v>
       </c>
       <c r="G10" t="s">
         <v>15</v>
       </c>
       <c r="H10" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="I10"/>
       <c r="J10"/>
       <c r="K10"/>
       <c r="L10">
-        <v>1296</v>
+        <v>829</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B11" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C11" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D11">
-        <v>95040</v>
+        <v>180</v>
       </c>
       <c r="E11" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="F11" s="2">
-        <v>46265.881678240738</v>
+        <v>46267.381990740738</v>
       </c>
       <c r="G11" t="s">
         <v>15</v>
       </c>
       <c r="H11" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="I11"/>
       <c r="J11"/>
       <c r="K11"/>
       <c r="L11">
-        <v>2036</v>
+        <v>89</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="B12" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C12" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D12">
-        <v>165120</v>
+        <v>500</v>
       </c>
       <c r="E12" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="F12" s="2">
-        <v>46265.881678240738</v>
+        <v>46267.379988425921</v>
       </c>
       <c r="G12" t="s">
         <v>15</v>
       </c>
       <c r="H12" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="I12"/>
       <c r="J12"/>
       <c r="K12"/>
       <c r="L12">
-        <v>2729</v>
+        <v>65</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B13" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C13" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D13">
-        <v>7920</v>
+        <v>540</v>
       </c>
       <c r="E13" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="F13" s="2">
-        <v>46265.881678240738</v>
+        <v>46267.379988425921</v>
       </c>
       <c r="G13" t="s">
         <v>15</v>
       </c>
       <c r="H13" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="I13"/>
       <c r="J13"/>
       <c r="K13"/>
       <c r="L13">
-        <v>476</v>
+        <v>219</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B14" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C14" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D14">
-        <v>1128</v>
+        <v>432</v>
       </c>
       <c r="E14" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="F14" s="2">
-        <v>46265.881678240738</v>
+        <v>46267.379988425921</v>
       </c>
       <c r="G14" t="s">
         <v>15</v>
       </c>
       <c r="H14" t="s">
-        <v>44</v>
-      </c>
-      <c r="I14">
-        <v>440</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="I14"/>
       <c r="J14"/>
       <c r="K14"/>
       <c r="L14">
-        <v>3395</v>
+        <v>213</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B15" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C15" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D15">
-        <v>144</v>
+        <v>1440</v>
       </c>
       <c r="E15" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="F15" s="2">
-        <v>46265.881678240738</v>
+        <v>46267.379988425921</v>
       </c>
       <c r="G15" t="s">
         <v>15</v>
       </c>
       <c r="H15" t="s">
-        <v>44</v>
-      </c>
-      <c r="I15">
-        <v>250</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="I15"/>
       <c r="J15"/>
       <c r="K15"/>
       <c r="L15">
-        <v>2660</v>
+        <v>243</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B16" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C16" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D16">
-        <v>72</v>
+        <v>260</v>
       </c>
       <c r="E16" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="F16" s="2">
-        <v>46265.881678240738</v>
+        <v>46267.381990740738</v>
       </c>
       <c r="G16" t="s">
         <v>15</v>
       </c>
       <c r="H16" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I16">
-        <v>250</v>
+        <v>440</v>
       </c>
       <c r="J16"/>
       <c r="K16"/>
       <c r="L16">
-        <v>2023</v>
+        <v>2401</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B17" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C17" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D17">
-        <v>72</v>
+        <v>9</v>
       </c>
       <c r="E17" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="F17" s="2">
-        <v>46265.881678240738</v>
+        <v>46267.381990740738</v>
       </c>
       <c r="G17" t="s">
         <v>15</v>
       </c>
       <c r="H17" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="I17">
-        <v>5000</v>
+        <v>250</v>
       </c>
       <c r="J17"/>
       <c r="K17"/>
       <c r="L17">
-        <v>2123</v>
+        <v>1699</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="B18" t="s">
-        <v>31</v>
+        <v>49</v>
       </c>
       <c r="C18" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D18">
-        <v>1800</v>
+        <v>750</v>
       </c>
       <c r="E18" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="F18" s="2">
-        <v>46265.935983796291</v>
+        <v>46267.400925925926</v>
       </c>
       <c r="G18" t="s">
         <v>15</v>
       </c>
       <c r="H18" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="I18"/>
       <c r="J18"/>
       <c r="K18"/>
       <c r="L18">
-        <v>1014</v>
+        <v>257</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="B19" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="C19" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D19">
-        <v>480</v>
+        <v>31680</v>
       </c>
       <c r="E19" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="F19" s="2">
-        <v>46265.935983796291</v>
+        <v>46267.400925925926</v>
       </c>
       <c r="G19" t="s">
         <v>15</v>
       </c>
       <c r="H19" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="I19"/>
       <c r="J19"/>
       <c r="K19"/>
       <c r="L19">
-        <v>606</v>
+        <v>833</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="B20" t="s">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="C20" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D20">
-        <v>4800</v>
+        <v>1800</v>
       </c>
       <c r="E20" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="F20" s="2">
-        <v>46265.935983796291</v>
+        <v>46267.400925925926</v>
       </c>
       <c r="G20" t="s">
         <v>15</v>
       </c>
       <c r="H20" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="I20"/>
       <c r="J20"/>
       <c r="K20"/>
       <c r="L20">
-        <v>1023</v>
+        <v>405</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B21" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C21" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D21">
-        <v>149400</v>
+        <v>287520</v>
       </c>
       <c r="E21" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="F21" s="2">
-        <v>46265.801111111112</v>
+        <v>46267.400925925926</v>
       </c>
       <c r="G21" t="s">
         <v>15</v>
       </c>
       <c r="H21" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="I21"/>
       <c r="J21"/>
       <c r="K21"/>
       <c r="L21">
-        <v>67</v>
+        <v>2167</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="B22" t="s">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="C22" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D22">
-        <v>188160</v>
+        <v>3960</v>
       </c>
       <c r="E22" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="F22" s="2">
-        <v>46265.821030092593</v>
+        <v>46267.400925925926</v>
       </c>
       <c r="G22" t="s">
         <v>15</v>
       </c>
       <c r="H22" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="I22"/>
       <c r="J22"/>
       <c r="K22"/>
       <c r="L22">
-        <v>3170</v>
+        <v>545</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="B23" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="C23" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D23">
-        <v>784</v>
+        <v>42240</v>
       </c>
       <c r="E23" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="F23" s="2">
-        <v>46265.823715277773</v>
+        <v>46267.400925925926</v>
       </c>
       <c r="G23" t="s">
         <v>15</v>
       </c>
       <c r="H23" t="s">
-        <v>44</v>
-      </c>
-      <c r="I23">
-        <v>440</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="I23"/>
       <c r="J23"/>
       <c r="K23"/>
       <c r="L23">
-        <v>3996</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="B24" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="C24" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D24">
-        <v>40</v>
+        <v>1800</v>
       </c>
       <c r="E24" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="F24" s="2">
-        <v>46265.823715277773</v>
+        <v>46267.400925925926</v>
       </c>
       <c r="G24" t="s">
         <v>15</v>
       </c>
       <c r="H24" t="s">
-        <v>44</v>
-      </c>
-      <c r="I24">
-        <v>250</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="I24"/>
       <c r="J24"/>
       <c r="K24"/>
       <c r="L24">
-        <v>3088</v>
+        <v>157</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="B25" t="s">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="C25" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D25">
-        <v>16</v>
+        <v>7920</v>
       </c>
       <c r="E25" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="F25" s="2">
-        <v>46265.821030092593</v>
+        <v>46267.400925925926</v>
       </c>
       <c r="G25" t="s">
         <v>15</v>
       </c>
       <c r="H25" t="s">
-        <v>44</v>
-      </c>
-      <c r="I25">
-        <v>250</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="I25"/>
       <c r="J25"/>
       <c r="K25"/>
       <c r="L25">
-        <v>1750</v>
+        <v>309</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B26" t="s">
+        <v>44</v>
+      </c>
+      <c r="C26" t="s">
         <v>50</v>
       </c>
-      <c r="C26" t="s">
-        <v>52</v>
-      </c>
       <c r="D26">
-        <v>70</v>
+        <v>1648</v>
       </c>
       <c r="E26" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="F26" s="2">
-        <v>46265.820196759254</v>
+        <v>46267.400925925926</v>
       </c>
       <c r="G26" t="s">
         <v>15</v>
       </c>
       <c r="H26" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="I26">
-        <v>5000</v>
+        <v>440</v>
       </c>
       <c r="J26"/>
       <c r="K26"/>
       <c r="L26">
-        <v>2120</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="B27" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="C27" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="D27">
-        <v>288</v>
+        <v>88</v>
       </c>
       <c r="E27" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="F27" s="2">
-        <v>46265.722152777773</v>
+        <v>46267.400925925926</v>
       </c>
       <c r="G27" t="s">
         <v>15</v>
       </c>
       <c r="H27" t="s">
-        <v>27</v>
-      </c>
-      <c r="I27"/>
+        <v>45</v>
+      </c>
+      <c r="I27">
+        <v>250</v>
+      </c>
       <c r="J27"/>
       <c r="K27"/>
       <c r="L27">
-        <v>795</v>
+        <v>2240</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="B28" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="C28" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="D28">
-        <v>720</v>
+        <v>40</v>
       </c>
       <c r="E28" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="F28" s="2">
-        <v>46265.722152777773</v>
+        <v>46267.400925925926</v>
       </c>
       <c r="G28" t="s">
         <v>15</v>
       </c>
       <c r="H28" t="s">
-        <v>27</v>
-      </c>
-      <c r="I28"/>
+        <v>45</v>
+      </c>
+      <c r="I28">
+        <v>250</v>
+      </c>
       <c r="J28"/>
       <c r="K28"/>
       <c r="L28">
-        <v>1</v>
+        <v>201</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="B29" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="C29" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="D29">
-        <v>240</v>
+        <v>12000</v>
       </c>
       <c r="E29" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="F29" s="2">
-        <v>46265.722152777773</v>
+        <v>46267.108935185184</v>
       </c>
       <c r="G29" t="s">
         <v>15</v>
       </c>
       <c r="H29" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="I29"/>
       <c r="J29"/>
       <c r="K29"/>
       <c r="L29">
-        <v>1053</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="B30" t="s">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="C30" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="D30">
-        <v>215520</v>
+        <v>18000</v>
       </c>
       <c r="E30" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="F30" s="2">
-        <v>46265.883472222224</v>
+        <v>46267.108935185184</v>
       </c>
       <c r="G30" t="s">
         <v>15</v>
       </c>
       <c r="H30" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="I30"/>
       <c r="J30"/>
       <c r="K30"/>
       <c r="L30">
-        <v>1335</v>
+        <v>2695</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="B31" t="s">
-        <v>41</v>
+        <v>71</v>
       </c>
       <c r="C31" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="D31">
-        <v>2700</v>
+        <v>3000</v>
       </c>
       <c r="E31" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="F31" s="2">
-        <v>46265.883472222224</v>
+        <v>46267.108935185184</v>
       </c>
       <c r="G31" t="s">
         <v>15</v>
       </c>
       <c r="H31" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="I31"/>
       <c r="J31"/>
       <c r="K31"/>
       <c r="L31">
-        <v>225</v>
+        <v>1619</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="B32" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="C32" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="D32">
-        <v>913</v>
+        <v>4800</v>
       </c>
       <c r="E32" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="F32" s="2">
-        <v>46265.883472222224</v>
+        <v>46267.108935185184</v>
       </c>
       <c r="G32" t="s">
         <v>15</v>
       </c>
       <c r="H32" t="s">
-        <v>44</v>
-      </c>
-      <c r="I32">
-        <v>440</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="I32"/>
       <c r="J32"/>
       <c r="K32"/>
       <c r="L32">
-        <v>1441</v>
+        <v>501</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B33" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="C33" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="D33">
-        <v>48</v>
+        <v>261000</v>
       </c>
       <c r="E33" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="F33" s="2">
-        <v>46265.883472222224</v>
+        <v>46267.108935185184</v>
       </c>
       <c r="G33" t="s">
         <v>15</v>
       </c>
       <c r="H33" t="s">
-        <v>44</v>
-      </c>
-      <c r="I33">
-        <v>250</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="I33"/>
       <c r="J33"/>
       <c r="K33"/>
       <c r="L33">
-        <v>1220</v>
+        <v>2861</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B34" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="C34" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="D34">
-        <v>24</v>
+        <v>10560</v>
       </c>
       <c r="E34" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="F34" s="2">
-        <v>46265.883472222224</v>
+        <v>46267.108935185184</v>
       </c>
       <c r="G34" t="s">
         <v>15</v>
       </c>
       <c r="H34" t="s">
-        <v>44</v>
-      </c>
-      <c r="I34">
-        <v>250</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="I34"/>
       <c r="J34"/>
       <c r="K34"/>
       <c r="L34">
-        <v>153</v>
+        <v>807</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="B35" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="C35" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="D35">
-        <v>48</v>
+        <v>218640</v>
       </c>
       <c r="E35" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="F35" s="2">
-        <v>46265.883472222224</v>
+        <v>46267.108935185184</v>
       </c>
       <c r="G35" t="s">
         <v>15</v>
       </c>
       <c r="H35" t="s">
-        <v>51</v>
-      </c>
-      <c r="I35">
-        <v>5000</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="I35"/>
       <c r="J35"/>
       <c r="K35"/>
       <c r="L35">
-        <v>879</v>
+        <v>2386</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="B36" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="C36" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D36">
-        <v>6360</v>
+        <v>5280</v>
       </c>
       <c r="E36" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F36" s="2">
-        <v>46265.791180555556</v>
+        <v>46267.108935185184</v>
       </c>
       <c r="G36" t="s">
         <v>15</v>
       </c>
       <c r="H36" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="I36"/>
       <c r="J36"/>
       <c r="K36"/>
       <c r="L36">
-        <v>937</v>
+        <v>1617</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="B37" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="C37" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D37">
-        <v>2700</v>
+        <v>2511</v>
       </c>
       <c r="E37" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F37" s="2">
-        <v>46265.426747685182</v>
+        <v>46267.108935185184</v>
       </c>
       <c r="G37" t="s">
         <v>15</v>
       </c>
       <c r="H37" t="s">
-        <v>27</v>
-      </c>
-      <c r="I37"/>
+        <v>45</v>
+      </c>
+      <c r="I37">
+        <v>440</v>
+      </c>
       <c r="J37"/>
       <c r="K37"/>
       <c r="L37">
-        <v>3708</v>
+        <v>4156</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
+        <v>46</v>
+      </c>
+      <c r="B38" t="s">
+        <v>47</v>
+      </c>
+      <c r="C38" t="s">
         <v>68</v>
       </c>
-      <c r="B38" t="s">
+      <c r="D38">
+        <v>110</v>
+      </c>
+      <c r="E38" t="s">
         <v>69</v>
       </c>
-      <c r="C38" t="s">
-        <v>66</v>
-      </c>
-      <c r="D38">
-        <v>6000</v>
-      </c>
-      <c r="E38" t="s">
-        <v>67</v>
-      </c>
       <c r="F38" s="2">
-        <v>46265.83211805555</v>
+        <v>46267.108935185184</v>
       </c>
       <c r="G38" t="s">
         <v>15</v>
       </c>
       <c r="H38" t="s">
-        <v>27</v>
-      </c>
-      <c r="I38"/>
+        <v>45</v>
+      </c>
+      <c r="I38">
+        <v>250</v>
+      </c>
       <c r="J38"/>
       <c r="K38"/>
       <c r="L38">
-        <v>1023</v>
+        <v>3618</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="B39" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="C39" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D39">
-        <v>1320</v>
+        <v>40</v>
       </c>
       <c r="E39" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F39" s="2">
-        <v>46265.791180555556</v>
+        <v>46267.108935185184</v>
       </c>
       <c r="G39" t="s">
         <v>15</v>
       </c>
       <c r="H39" t="s">
-        <v>27</v>
-      </c>
-      <c r="I39"/>
+        <v>45</v>
+      </c>
+      <c r="I39">
+        <v>250</v>
+      </c>
       <c r="J39"/>
       <c r="K39"/>
       <c r="L39">
-        <v>2370</v>
+        <v>2435</v>
       </c>
     </row>
     <row r="40">
@@ -1991,112 +2172,114 @@
         <v>73</v>
       </c>
       <c r="C40" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D40">
-        <v>13200</v>
+        <v>32</v>
       </c>
       <c r="E40" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F40" s="2">
-        <v>46265.83211805555</v>
+        <v>46266.834074074075</v>
       </c>
       <c r="G40" t="s">
         <v>15</v>
       </c>
       <c r="H40" t="s">
-        <v>27</v>
-      </c>
-      <c r="I40"/>
+        <v>74</v>
+      </c>
+      <c r="I40">
+        <v>5000</v>
+      </c>
       <c r="J40"/>
       <c r="K40"/>
       <c r="L40">
-        <v>4706</v>
+        <v>2497</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B41" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C41" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="D41">
-        <v>300</v>
+        <v>6000</v>
       </c>
       <c r="E41" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="F41" s="2">
-        <v>46264.768113425926</v>
+        <v>46266.749097222222</v>
       </c>
       <c r="G41" t="s">
         <v>15</v>
       </c>
       <c r="H41" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="I41"/>
       <c r="J41"/>
       <c r="K41"/>
       <c r="L41">
-        <v>9</v>
+        <v>692</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="B42" t="s">
+        <v>80</v>
+      </c>
+      <c r="C42" t="s">
         <v>77</v>
       </c>
-      <c r="C42" t="s">
-        <v>66</v>
-      </c>
       <c r="D42">
-        <v>300</v>
+        <v>1500</v>
       </c>
       <c r="E42" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="F42" s="2">
-        <v>46265.79105324074</v>
+        <v>46266.749097222222</v>
       </c>
       <c r="G42" t="s">
         <v>15</v>
       </c>
       <c r="H42" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="I42"/>
       <c r="J42"/>
       <c r="K42"/>
       <c r="L42">
-        <v>25</v>
+        <v>169</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>21</v>
+        <v>81</v>
       </c>
       <c r="B43" t="s">
-        <v>22</v>
+        <v>82</v>
       </c>
       <c r="C43" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="D43">
-        <v>2208</v>
+        <v>3000</v>
       </c>
       <c r="E43" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="F43" s="2">
-        <v>46265.876111111109</v>
+        <v>46266.749097222222</v>
       </c>
       <c r="G43" t="s">
         <v>15</v>
@@ -2108,27 +2291,27 @@
       <c r="J43"/>
       <c r="K43"/>
       <c r="L43">
-        <v>5</v>
+        <v>217</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>78</v>
+        <v>23</v>
       </c>
       <c r="B44" t="s">
-        <v>79</v>
+        <v>24</v>
       </c>
       <c r="C44" t="s">
-        <v>66</v>
+        <v>83</v>
       </c>
       <c r="D44">
-        <v>2304</v>
+        <v>2400</v>
       </c>
       <c r="E44" t="s">
-        <v>67</v>
+        <v>84</v>
       </c>
       <c r="F44" s="2">
-        <v>46265.876111111109</v>
+        <v>46267.288958333331</v>
       </c>
       <c r="G44" t="s">
         <v>15</v>
@@ -2140,1007 +2323,1017 @@
       <c r="J44"/>
       <c r="K44"/>
       <c r="L44">
-        <v>9</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>80</v>
+        <v>25</v>
       </c>
       <c r="B45" t="s">
-        <v>81</v>
+        <v>26</v>
       </c>
       <c r="C45" t="s">
-        <v>66</v>
+        <v>83</v>
       </c>
       <c r="D45">
-        <v>21000</v>
+        <v>720</v>
       </c>
       <c r="E45" t="s">
-        <v>67</v>
+        <v>84</v>
       </c>
       <c r="F45" s="2">
-        <v>46265.83211805555</v>
+        <v>46267.288634259254</v>
       </c>
       <c r="G45" t="s">
         <v>15</v>
       </c>
       <c r="H45" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="I45"/>
       <c r="J45"/>
       <c r="K45"/>
       <c r="L45">
-        <v>610</v>
+        <v>537</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>82</v>
+        <v>27</v>
       </c>
       <c r="B46" t="s">
+        <v>28</v>
+      </c>
+      <c r="C46" t="s">
         <v>83</v>
       </c>
-      <c r="C46" t="s">
-        <v>66</v>
-      </c>
       <c r="D46">
-        <v>9000</v>
+        <v>6600</v>
       </c>
       <c r="E46" t="s">
-        <v>67</v>
+        <v>84</v>
       </c>
       <c r="F46" s="2">
-        <v>46265.83211805555</v>
+        <v>46267.288958333331</v>
       </c>
       <c r="G46" t="s">
         <v>15</v>
       </c>
       <c r="H46" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="I46"/>
       <c r="J46"/>
       <c r="K46"/>
       <c r="L46">
-        <v>2115</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
+        <v>56</v>
+      </c>
+      <c r="B47" t="s">
+        <v>57</v>
+      </c>
+      <c r="C47" t="s">
+        <v>83</v>
+      </c>
+      <c r="D47">
+        <v>307680</v>
+      </c>
+      <c r="E47" t="s">
         <v>84</v>
       </c>
-      <c r="B47" t="s">
-        <v>85</v>
-      </c>
-      <c r="C47" t="s">
-        <v>66</v>
-      </c>
-      <c r="D47">
-        <v>1478</v>
-      </c>
-      <c r="E47" t="s">
-        <v>67</v>
-      </c>
       <c r="F47" s="2">
-        <v>46265.758229166662</v>
+        <v>46267.288356481477</v>
       </c>
       <c r="G47" t="s">
         <v>15</v>
       </c>
       <c r="H47" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="I47"/>
       <c r="J47"/>
       <c r="K47"/>
       <c r="L47">
-        <v>1601</v>
+        <v>2041</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
       <c r="B48" t="s">
-        <v>87</v>
+        <v>59</v>
       </c>
       <c r="C48" t="s">
-        <v>66</v>
+        <v>83</v>
       </c>
       <c r="D48">
-        <v>246420</v>
+        <v>3960</v>
       </c>
       <c r="E48" t="s">
-        <v>67</v>
+        <v>84</v>
       </c>
       <c r="F48" s="2">
-        <v>46266.068622685183</v>
+        <v>46266.691412037035</v>
       </c>
       <c r="G48" t="s">
         <v>15</v>
       </c>
       <c r="H48" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="I48"/>
       <c r="J48"/>
       <c r="K48"/>
       <c r="L48">
-        <v>3702</v>
+        <v>429</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>88</v>
+        <v>60</v>
       </c>
       <c r="B49" t="s">
-        <v>89</v>
+        <v>61</v>
       </c>
       <c r="C49" t="s">
-        <v>66</v>
+        <v>83</v>
       </c>
       <c r="D49">
-        <v>84480</v>
+        <v>342240</v>
       </c>
       <c r="E49" t="s">
-        <v>67</v>
+        <v>84</v>
       </c>
       <c r="F49" s="2">
-        <v>46265.83211805555</v>
+        <v>46267.288356481477</v>
       </c>
       <c r="G49" t="s">
         <v>15</v>
       </c>
       <c r="H49" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="I49"/>
       <c r="J49"/>
       <c r="K49"/>
       <c r="L49">
-        <v>1186</v>
+        <v>2732</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>36</v>
+        <v>62</v>
       </c>
       <c r="B50" t="s">
-        <v>37</v>
+        <v>63</v>
       </c>
       <c r="C50" t="s">
-        <v>66</v>
+        <v>83</v>
       </c>
       <c r="D50">
-        <v>70800</v>
+        <v>11880</v>
       </c>
       <c r="E50" t="s">
-        <v>67</v>
+        <v>84</v>
       </c>
       <c r="F50" s="2">
-        <v>46265.758229166662</v>
+        <v>46267.288356481477</v>
       </c>
       <c r="G50" t="s">
         <v>15</v>
       </c>
       <c r="H50" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="I50"/>
       <c r="J50"/>
       <c r="K50"/>
       <c r="L50">
-        <v>2815</v>
+        <v>478</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>90</v>
+        <v>43</v>
       </c>
       <c r="B51" t="s">
-        <v>91</v>
+        <v>44</v>
       </c>
       <c r="C51" t="s">
-        <v>66</v>
+        <v>83</v>
       </c>
       <c r="D51">
-        <v>3960</v>
+        <v>2796</v>
       </c>
       <c r="E51" t="s">
-        <v>67</v>
+        <v>84</v>
       </c>
       <c r="F51" s="2">
-        <v>46265.83211805555</v>
+        <v>46267.288356481477</v>
       </c>
       <c r="G51" t="s">
         <v>15</v>
       </c>
       <c r="H51" t="s">
-        <v>27</v>
-      </c>
-      <c r="I51"/>
+        <v>45</v>
+      </c>
+      <c r="I51">
+        <v>440</v>
+      </c>
       <c r="J51"/>
       <c r="K51"/>
       <c r="L51">
-        <v>825</v>
+        <v>3401</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="B52" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="C52" t="s">
-        <v>66</v>
+        <v>83</v>
       </c>
       <c r="D52">
-        <v>10560</v>
+        <v>201</v>
       </c>
       <c r="E52" t="s">
-        <v>67</v>
+        <v>84</v>
       </c>
       <c r="F52" s="2">
-        <v>46265.83211805555</v>
+        <v>46267.288356481477</v>
       </c>
       <c r="G52" t="s">
         <v>15</v>
       </c>
       <c r="H52" t="s">
-        <v>27</v>
-      </c>
-      <c r="I52"/>
+        <v>45</v>
+      </c>
+      <c r="I52">
+        <v>250</v>
+      </c>
       <c r="J52"/>
       <c r="K52"/>
       <c r="L52">
-        <v>1101</v>
+        <v>2665</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>92</v>
+        <v>64</v>
       </c>
       <c r="B53" t="s">
-        <v>93</v>
+        <v>65</v>
       </c>
       <c r="C53" t="s">
-        <v>66</v>
+        <v>83</v>
       </c>
       <c r="D53">
-        <v>900</v>
+        <v>72</v>
       </c>
       <c r="E53" t="s">
-        <v>67</v>
+        <v>84</v>
       </c>
       <c r="F53" s="2">
-        <v>46265.83211805555</v>
+        <v>46267.288356481477</v>
       </c>
       <c r="G53" t="s">
         <v>15</v>
       </c>
       <c r="H53" t="s">
-        <v>27</v>
-      </c>
-      <c r="I53"/>
+        <v>45</v>
+      </c>
+      <c r="I53">
+        <v>250</v>
+      </c>
       <c r="J53"/>
       <c r="K53"/>
       <c r="L53">
-        <v>197</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="B54" t="s">
-        <v>95</v>
+        <v>73</v>
       </c>
       <c r="C54" t="s">
-        <v>66</v>
+        <v>83</v>
       </c>
       <c r="D54">
-        <v>6049</v>
+        <v>86</v>
       </c>
       <c r="E54" t="s">
-        <v>67</v>
+        <v>84</v>
       </c>
       <c r="F54" s="2">
-        <v>46266.323368055557</v>
+        <v>46267.288356481477</v>
       </c>
       <c r="G54" t="s">
         <v>15</v>
       </c>
       <c r="H54" t="s">
-        <v>27</v>
-      </c>
-      <c r="I54"/>
+        <v>74</v>
+      </c>
+      <c r="I54">
+        <v>5000</v>
+      </c>
       <c r="J54"/>
       <c r="K54"/>
       <c r="L54">
-        <v>13</v>
+        <v>2127</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>42</v>
+        <v>23</v>
       </c>
       <c r="B55" t="s">
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="C55" t="s">
-        <v>66</v>
+        <v>85</v>
       </c>
       <c r="D55">
-        <v>2486</v>
+        <v>1800</v>
       </c>
       <c r="E55" t="s">
-        <v>67</v>
+        <v>86</v>
       </c>
       <c r="F55" s="2">
-        <v>46266.323368055557</v>
+        <v>46265.935983796291</v>
       </c>
       <c r="G55" t="s">
         <v>15</v>
       </c>
       <c r="H55" t="s">
-        <v>44</v>
-      </c>
-      <c r="I55">
-        <v>440</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="I55"/>
       <c r="J55"/>
       <c r="K55"/>
       <c r="L55">
-        <v>5376</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="B56" t="s">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="C56" t="s">
-        <v>66</v>
+        <v>85</v>
       </c>
       <c r="D56">
-        <v>154</v>
+        <v>480</v>
       </c>
       <c r="E56" t="s">
-        <v>67</v>
+        <v>86</v>
       </c>
       <c r="F56" s="2">
-        <v>46266.323368055557</v>
+        <v>46265.935983796291</v>
       </c>
       <c r="G56" t="s">
         <v>15</v>
       </c>
       <c r="H56" t="s">
-        <v>44</v>
-      </c>
-      <c r="I56">
-        <v>250</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="I56"/>
       <c r="J56"/>
       <c r="K56"/>
       <c r="L56">
-        <v>4679</v>
+        <v>606</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c r="B57" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="C57" t="s">
-        <v>66</v>
+        <v>85</v>
       </c>
       <c r="D57">
-        <v>88</v>
+        <v>4800</v>
       </c>
       <c r="E57" t="s">
-        <v>67</v>
+        <v>86</v>
       </c>
       <c r="F57" s="2">
-        <v>46266.068622685183</v>
+        <v>46265.935983796291</v>
       </c>
       <c r="G57" t="s">
         <v>15</v>
       </c>
       <c r="H57" t="s">
-        <v>44</v>
-      </c>
-      <c r="I57">
-        <v>250</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="I57"/>
       <c r="J57"/>
       <c r="K57"/>
       <c r="L57">
-        <v>2653</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="B58" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="C58" t="s">
-        <v>66</v>
+        <v>85</v>
       </c>
       <c r="D58">
-        <v>19</v>
+        <v>188160</v>
       </c>
       <c r="E58" t="s">
-        <v>67</v>
+        <v>86</v>
       </c>
       <c r="F58" s="2">
-        <v>46266.323368055557</v>
+        <v>46265.821030092593</v>
       </c>
       <c r="G58" t="s">
         <v>15</v>
       </c>
       <c r="H58" t="s">
-        <v>51</v>
-      </c>
-      <c r="I58">
-        <v>5000</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="I58"/>
       <c r="J58"/>
       <c r="K58"/>
       <c r="L58">
-        <v>3598</v>
+        <v>3170</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>68</v>
+        <v>43</v>
       </c>
       <c r="B59" t="s">
-        <v>69</v>
+        <v>44</v>
       </c>
       <c r="C59" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="D59">
-        <v>3000</v>
+        <v>784</v>
       </c>
       <c r="E59" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="F59" s="2">
-        <v>46265.84574074074</v>
+        <v>46265.823715277773</v>
       </c>
       <c r="G59" t="s">
         <v>15</v>
       </c>
       <c r="H59" t="s">
-        <v>27</v>
-      </c>
-      <c r="I59"/>
+        <v>45</v>
+      </c>
+      <c r="I59">
+        <v>440</v>
+      </c>
       <c r="J59"/>
       <c r="K59"/>
       <c r="L59">
-        <v>177</v>
+        <v>3996</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>82</v>
+        <v>46</v>
       </c>
       <c r="B60" t="s">
-        <v>83</v>
+        <v>47</v>
       </c>
       <c r="C60" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="D60">
-        <v>3000</v>
+        <v>40</v>
       </c>
       <c r="E60" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="F60" s="2">
-        <v>46265.84574074074</v>
+        <v>46265.823715277773</v>
       </c>
       <c r="G60" t="s">
         <v>15</v>
       </c>
       <c r="H60" t="s">
-        <v>27</v>
-      </c>
-      <c r="I60"/>
+        <v>45</v>
+      </c>
+      <c r="I60">
+        <v>250</v>
+      </c>
       <c r="J60"/>
       <c r="K60"/>
       <c r="L60">
-        <v>813</v>
+        <v>3088</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s">
+        <v>64</v>
+      </c>
+      <c r="B61" t="s">
+        <v>65</v>
+      </c>
+      <c r="C61" t="s">
+        <v>85</v>
+      </c>
+      <c r="D61">
+        <v>16</v>
+      </c>
+      <c r="E61" t="s">
         <v>86</v>
       </c>
-      <c r="B61" t="s">
-        <v>87</v>
-      </c>
-      <c r="C61" t="s">
-        <v>96</v>
-      </c>
-      <c r="D61">
-        <v>31680</v>
-      </c>
-      <c r="E61" t="s">
-        <v>97</v>
-      </c>
       <c r="F61" s="2">
-        <v>46265.84574074074</v>
+        <v>46265.821030092593</v>
       </c>
       <c r="G61" t="s">
         <v>15</v>
       </c>
       <c r="H61" t="s">
-        <v>27</v>
-      </c>
-      <c r="I61"/>
+        <v>45</v>
+      </c>
+      <c r="I61">
+        <v>250</v>
+      </c>
       <c r="J61"/>
       <c r="K61"/>
       <c r="L61">
-        <v>1149</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>88</v>
+        <v>72</v>
       </c>
       <c r="B62" t="s">
-        <v>89</v>
+        <v>73</v>
       </c>
       <c r="C62" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="D62">
-        <v>10560</v>
+        <v>70</v>
       </c>
       <c r="E62" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="F62" s="2">
-        <v>46265.84574074074</v>
+        <v>46265.820196759254</v>
       </c>
       <c r="G62" t="s">
         <v>15</v>
       </c>
       <c r="H62" t="s">
-        <v>27</v>
-      </c>
-      <c r="I62"/>
+        <v>74</v>
+      </c>
+      <c r="I62">
+        <v>5000</v>
+      </c>
       <c r="J62"/>
       <c r="K62"/>
       <c r="L62">
-        <v>649</v>
+        <v>2120</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="B63" t="s">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="C63" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="D63">
-        <v>21120</v>
+        <v>600</v>
       </c>
       <c r="E63" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="F63" s="2">
-        <v>46265.84574074074</v>
+        <v>46266.839502314811</v>
       </c>
       <c r="G63" t="s">
         <v>15</v>
       </c>
       <c r="H63" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="I63"/>
       <c r="J63"/>
       <c r="K63"/>
       <c r="L63">
-        <v>967</v>
+        <v>417</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="B64" t="s">
-        <v>43</v>
+        <v>22</v>
       </c>
       <c r="C64" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="D64">
-        <v>352</v>
+        <v>600</v>
       </c>
       <c r="E64" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="F64" s="2">
-        <v>46265.84574074074</v>
+        <v>46266.839502314811</v>
       </c>
       <c r="G64" t="s">
         <v>15</v>
       </c>
       <c r="H64" t="s">
-        <v>44</v>
-      </c>
-      <c r="I64">
-        <v>440</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="I64"/>
       <c r="J64"/>
       <c r="K64"/>
       <c r="L64">
-        <v>1373</v>
+        <v>413</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>45</v>
+        <v>70</v>
       </c>
       <c r="B65" t="s">
-        <v>46</v>
+        <v>71</v>
       </c>
       <c r="C65" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="D65">
-        <v>86</v>
+        <v>900</v>
       </c>
       <c r="E65" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="F65" s="2">
-        <v>46265.84574074074</v>
+        <v>46266.839502314811</v>
       </c>
       <c r="G65" t="s">
         <v>15</v>
       </c>
       <c r="H65" t="s">
-        <v>44</v>
-      </c>
-      <c r="I65">
-        <v>250</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="I65"/>
       <c r="J65"/>
       <c r="K65"/>
       <c r="L65">
-        <v>1091</v>
+        <v>917</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="B66" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="C66" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="D66">
-        <v>44</v>
+        <v>25920</v>
       </c>
       <c r="E66" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="F66" s="2">
-        <v>46265.84574074074</v>
+        <v>46266.839502314811</v>
       </c>
       <c r="G66" t="s">
         <v>15</v>
       </c>
       <c r="H66" t="s">
-        <v>44</v>
-      </c>
-      <c r="I66">
-        <v>250</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="I66"/>
       <c r="J66"/>
       <c r="K66"/>
       <c r="L66">
-        <v>697</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="B67" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="C67" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="D67">
-        <v>1200</v>
+        <v>148341</v>
       </c>
       <c r="E67" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="F67" s="2">
-        <v>46265.792858796296</v>
+        <v>46266.839502314811</v>
       </c>
       <c r="G67" t="s">
         <v>15</v>
       </c>
       <c r="H67" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="I67"/>
       <c r="J67"/>
       <c r="K67"/>
       <c r="L67">
-        <v>127</v>
+        <v>1729</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>82</v>
+        <v>62</v>
       </c>
       <c r="B68" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="C68" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="D68">
-        <v>6000</v>
+        <v>3240</v>
       </c>
       <c r="E68" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="F68" s="2">
-        <v>46265.792858796296</v>
+        <v>46266.839502314811</v>
       </c>
       <c r="G68" t="s">
         <v>15</v>
       </c>
       <c r="H68" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="I68"/>
       <c r="J68"/>
       <c r="K68"/>
       <c r="L68">
-        <v>1032</v>
+        <v>241</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>86</v>
+        <v>43</v>
       </c>
       <c r="B69" t="s">
+        <v>44</v>
+      </c>
+      <c r="C69" t="s">
         <v>87</v>
       </c>
-      <c r="C69" t="s">
-        <v>98</v>
-      </c>
       <c r="D69">
-        <v>31680</v>
+        <v>745</v>
       </c>
       <c r="E69" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="F69" s="2">
-        <v>46265.648333333331</v>
+        <v>46266.839502314811</v>
       </c>
       <c r="G69" t="s">
         <v>15</v>
       </c>
       <c r="H69" t="s">
-        <v>27</v>
-      </c>
-      <c r="I69"/>
+        <v>45</v>
+      </c>
+      <c r="I69">
+        <v>440</v>
+      </c>
       <c r="J69"/>
       <c r="K69"/>
       <c r="L69">
-        <v>1151</v>
+        <v>2053</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s">
+        <v>46</v>
+      </c>
+      <c r="B70" t="s">
+        <v>47</v>
+      </c>
+      <c r="C70" t="s">
+        <v>87</v>
+      </c>
+      <c r="D70">
+        <v>34</v>
+      </c>
+      <c r="E70" t="s">
         <v>88</v>
       </c>
-      <c r="B70" t="s">
-        <v>89</v>
-      </c>
-      <c r="C70" t="s">
-        <v>98</v>
-      </c>
-      <c r="D70">
-        <v>960</v>
-      </c>
-      <c r="E70" t="s">
-        <v>99</v>
-      </c>
       <c r="F70" s="2">
-        <v>46265.792858796296</v>
+        <v>46266.839502314811</v>
       </c>
       <c r="G70" t="s">
         <v>15</v>
       </c>
       <c r="H70" t="s">
-        <v>27</v>
-      </c>
-      <c r="I70"/>
+        <v>45</v>
+      </c>
+      <c r="I70">
+        <v>250</v>
+      </c>
       <c r="J70"/>
       <c r="K70"/>
       <c r="L70">
-        <v>59</v>
+        <v>1715</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>36</v>
+        <v>64</v>
       </c>
       <c r="B71" t="s">
-        <v>37</v>
+        <v>65</v>
       </c>
       <c r="C71" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="D71">
-        <v>555360</v>
+        <v>10</v>
       </c>
       <c r="E71" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="F71" s="2">
-        <v>46265.946967592594</v>
+        <v>46266.839502314811</v>
       </c>
       <c r="G71" t="s">
         <v>15</v>
       </c>
       <c r="H71" t="s">
-        <v>27</v>
-      </c>
-      <c r="I71"/>
+        <v>45</v>
+      </c>
+      <c r="I71">
+        <v>250</v>
+      </c>
       <c r="J71"/>
       <c r="K71"/>
       <c r="L71">
-        <v>2818</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>38</v>
+        <v>72</v>
       </c>
       <c r="B72" t="s">
-        <v>39</v>
+        <v>73</v>
       </c>
       <c r="C72" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="D72">
-        <v>2400</v>
+        <v>32</v>
       </c>
       <c r="E72" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="F72" s="2">
-        <v>46265.792858796296</v>
+        <v>46266.839502314811</v>
       </c>
       <c r="G72" t="s">
         <v>15</v>
       </c>
       <c r="H72" t="s">
-        <v>27</v>
-      </c>
-      <c r="I72"/>
+        <v>74</v>
+      </c>
+      <c r="I72">
+        <v>5000</v>
+      </c>
       <c r="J72"/>
       <c r="K72"/>
       <c r="L72">
-        <v>792</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>92</v>
+        <v>56</v>
       </c>
       <c r="B73" t="s">
-        <v>93</v>
+        <v>57</v>
       </c>
       <c r="C73" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="D73">
-        <v>1800</v>
+        <v>31680</v>
       </c>
       <c r="E73" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="F73" s="2">
-        <v>46265.792858796296</v>
+        <v>46267.391469907408</v>
       </c>
       <c r="G73" t="s">
         <v>15</v>
       </c>
       <c r="H73" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="I73"/>
       <c r="J73"/>
       <c r="K73"/>
       <c r="L73">
-        <v>151</v>
+        <v>387</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="B74" t="s">
-        <v>41</v>
+        <v>61</v>
       </c>
       <c r="C74" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="D74">
-        <v>3960</v>
+        <v>25920</v>
       </c>
       <c r="E74" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="F74" s="2">
-        <v>46265.792858796296</v>
+        <v>46267.391469907408</v>
       </c>
       <c r="G74" t="s">
         <v>15</v>
       </c>
       <c r="H74" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="I74"/>
       <c r="J74"/>
       <c r="K74"/>
       <c r="L74">
-        <v>199</v>
+        <v>379</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B75" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C75" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="D75">
-        <v>2637</v>
+        <v>240</v>
       </c>
       <c r="E75" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="F75" s="2">
-        <v>46265.946967592594</v>
+        <v>46267.391469907408</v>
       </c>
       <c r="G75" t="s">
         <v>15</v>
       </c>
       <c r="H75" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I75">
         <v>440</v>
@@ -3148,33 +3341,33 @@
       <c r="J75"/>
       <c r="K75"/>
       <c r="L75">
-        <v>3065</v>
+        <v>413</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s">
+        <v>46</v>
+      </c>
+      <c r="B76" t="s">
+        <v>47</v>
+      </c>
+      <c r="C76" t="s">
+        <v>89</v>
+      </c>
+      <c r="D76">
+        <v>10</v>
+      </c>
+      <c r="E76" t="s">
+        <v>90</v>
+      </c>
+      <c r="F76" s="2">
+        <v>46267.391469907408</v>
+      </c>
+      <c r="G76" t="s">
+        <v>15</v>
+      </c>
+      <c r="H76" t="s">
         <v>45</v>
-      </c>
-      <c r="B76" t="s">
-        <v>46</v>
-      </c>
-      <c r="C76" t="s">
-        <v>98</v>
-      </c>
-      <c r="D76">
-        <v>157</v>
-      </c>
-      <c r="E76" t="s">
-        <v>99</v>
-      </c>
-      <c r="F76" s="2">
-        <v>46265.946967592594</v>
-      </c>
-      <c r="G76" t="s">
-        <v>15</v>
-      </c>
-      <c r="H76" t="s">
-        <v>44</v>
       </c>
       <c r="I76">
         <v>250</v>
@@ -3182,623 +3375,613 @@
       <c r="J76"/>
       <c r="K76"/>
       <c r="L76">
-        <v>2784</v>
+        <v>371</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>47</v>
+        <v>72</v>
       </c>
       <c r="B77" t="s">
-        <v>48</v>
+        <v>73</v>
       </c>
       <c r="C77" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="D77">
-        <v>79</v>
+        <v>10</v>
       </c>
       <c r="E77" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="F77" s="2">
-        <v>46265.946967592594</v>
+        <v>46267.391469907408</v>
       </c>
       <c r="G77" t="s">
         <v>15</v>
       </c>
       <c r="H77" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="I77">
-        <v>250</v>
+        <v>5000</v>
       </c>
       <c r="J77"/>
       <c r="K77"/>
       <c r="L77">
-        <v>336</v>
+        <v>303</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>82</v>
+        <v>17</v>
       </c>
       <c r="B78" t="s">
-        <v>83</v>
+        <v>18</v>
       </c>
       <c r="C78" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="D78">
-        <v>1800</v>
+        <v>11700</v>
       </c>
       <c r="E78" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="F78" s="2">
-        <v>46265.901134259257</v>
+        <v>46266.884675925925</v>
       </c>
       <c r="G78" t="s">
         <v>15</v>
       </c>
       <c r="H78" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="I78"/>
       <c r="J78"/>
       <c r="K78"/>
       <c r="L78">
-        <v>955</v>
+        <v>3709</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>36</v>
+        <v>66</v>
       </c>
       <c r="B79" t="s">
-        <v>37</v>
+        <v>67</v>
       </c>
       <c r="C79" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="D79">
-        <v>103680</v>
+        <v>21000</v>
       </c>
       <c r="E79" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="F79" s="2">
-        <v>46265.901134259257</v>
+        <v>46266.884675925925</v>
       </c>
       <c r="G79" t="s">
         <v>15</v>
       </c>
       <c r="H79" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="I79"/>
       <c r="J79"/>
       <c r="K79"/>
       <c r="L79">
-        <v>1645</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>90</v>
+        <v>19</v>
       </c>
       <c r="B80" t="s">
+        <v>20</v>
+      </c>
+      <c r="C80" t="s">
         <v>91</v>
       </c>
-      <c r="C80" t="s">
-        <v>100</v>
-      </c>
       <c r="D80">
-        <v>9720</v>
+        <v>3480</v>
       </c>
       <c r="E80" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="F80" s="2">
-        <v>46265.901134259257</v>
+        <v>46267.041493055556</v>
       </c>
       <c r="G80" t="s">
         <v>15</v>
       </c>
       <c r="H80" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="I80"/>
       <c r="J80"/>
       <c r="K80"/>
       <c r="L80">
-        <v>663</v>
+        <v>2372</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="B81" t="s">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="C81" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="D81">
-        <v>34560</v>
+        <v>4200</v>
       </c>
       <c r="E81" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="F81" s="2">
-        <v>46265.901134259257</v>
+        <v>46266.822754629626</v>
       </c>
       <c r="G81" t="s">
         <v>15</v>
       </c>
       <c r="H81" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="I81"/>
       <c r="J81"/>
       <c r="K81"/>
       <c r="L81">
-        <v>1441</v>
+        <v>4707</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s">
+        <v>93</v>
+      </c>
+      <c r="B82" t="s">
+        <v>94</v>
+      </c>
+      <c r="C82" t="s">
+        <v>91</v>
+      </c>
+      <c r="D82">
+        <v>300</v>
+      </c>
+      <c r="E82" t="s">
         <v>92</v>
       </c>
-      <c r="B82" t="s">
-        <v>93</v>
-      </c>
-      <c r="C82" t="s">
-        <v>100</v>
-      </c>
-      <c r="D82">
-        <v>900</v>
-      </c>
-      <c r="E82" t="s">
-        <v>101</v>
-      </c>
       <c r="F82" s="2">
-        <v>46265.901134259257</v>
+        <v>46264.768113425926</v>
       </c>
       <c r="G82" t="s">
         <v>15</v>
       </c>
       <c r="H82" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="I82"/>
       <c r="J82"/>
       <c r="K82"/>
       <c r="L82">
-        <v>221</v>
+        <v>9</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="B83" t="s">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="C83" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="D83">
-        <v>2640</v>
+        <v>9900</v>
       </c>
       <c r="E83" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="F83" s="2">
-        <v>46265.901134259257</v>
+        <v>46266.855219907404</v>
       </c>
       <c r="G83" t="s">
         <v>15</v>
       </c>
       <c r="H83" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="I83"/>
       <c r="J83"/>
       <c r="K83"/>
       <c r="L83">
-        <v>341</v>
+        <v>1807</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>42</v>
+        <v>95</v>
       </c>
       <c r="B84" t="s">
-        <v>43</v>
+        <v>96</v>
       </c>
       <c r="C84" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="D84">
-        <v>650</v>
+        <v>300</v>
       </c>
       <c r="E84" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="F84" s="2">
-        <v>46265.901134259257</v>
+        <v>46265.79105324074</v>
       </c>
       <c r="G84" t="s">
         <v>15</v>
       </c>
       <c r="H84" t="s">
-        <v>44</v>
-      </c>
-      <c r="I84">
-        <v>440</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="I84"/>
       <c r="J84"/>
       <c r="K84"/>
       <c r="L84">
-        <v>2295</v>
+        <v>25</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>45</v>
+        <v>97</v>
       </c>
       <c r="B85" t="s">
-        <v>46</v>
+        <v>98</v>
       </c>
       <c r="C85" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="D85">
-        <v>18</v>
+        <v>2208</v>
       </c>
       <c r="E85" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="F85" s="2">
-        <v>46265.901134259257</v>
+        <v>46265.876111111109</v>
       </c>
       <c r="G85" t="s">
         <v>15</v>
       </c>
       <c r="H85" t="s">
-        <v>44</v>
-      </c>
-      <c r="I85">
-        <v>250</v>
-      </c>
+        <v>99</v>
+      </c>
+      <c r="I85"/>
       <c r="J85"/>
       <c r="K85"/>
       <c r="L85">
-        <v>1863</v>
+        <v>5</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>56</v>
+        <v>100</v>
       </c>
       <c r="B86" t="s">
-        <v>57</v>
+        <v>101</v>
       </c>
       <c r="C86" t="s">
-        <v>102</v>
+        <v>91</v>
       </c>
       <c r="D86">
-        <v>73152</v>
+        <v>2304</v>
       </c>
       <c r="E86" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="F86" s="2">
-        <v>46265.752893518518</v>
+        <v>46265.876111111109</v>
       </c>
       <c r="G86" t="s">
         <v>15</v>
       </c>
       <c r="H86" t="s">
-        <v>27</v>
+        <v>99</v>
       </c>
       <c r="I86"/>
       <c r="J86"/>
       <c r="K86"/>
       <c r="L86">
-        <v>1478</v>
+        <v>9</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>104</v>
+        <v>70</v>
       </c>
       <c r="B87" t="s">
-        <v>105</v>
+        <v>71</v>
       </c>
       <c r="C87" t="s">
-        <v>102</v>
+        <v>91</v>
       </c>
       <c r="D87">
-        <v>364800</v>
+        <v>9000</v>
       </c>
       <c r="E87" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="F87" s="2">
-        <v>46265.847939814812</v>
+        <v>46266.860717592594</v>
       </c>
       <c r="G87" t="s">
         <v>15</v>
       </c>
       <c r="H87" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="I87"/>
       <c r="J87"/>
       <c r="K87"/>
       <c r="L87">
-        <v>172</v>
+        <v>2117</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="B88" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="C88" t="s">
-        <v>102</v>
+        <v>91</v>
       </c>
       <c r="D88">
-        <v>1520</v>
+        <v>10023</v>
       </c>
       <c r="E88" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="F88" s="2">
-        <v>46265.847939814812</v>
+        <v>46266.884675925925</v>
       </c>
       <c r="G88" t="s">
         <v>15</v>
       </c>
       <c r="H88" t="s">
-        <v>44</v>
-      </c>
-      <c r="I88">
-        <v>440</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="I88"/>
       <c r="J88"/>
       <c r="K88"/>
       <c r="L88">
-        <v>4312</v>
+        <v>1604</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B89" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="C89" t="s">
-        <v>102</v>
+        <v>91</v>
       </c>
       <c r="D89">
-        <v>20</v>
+        <v>101520</v>
       </c>
       <c r="E89" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="F89" s="2">
-        <v>46265.752893518518</v>
+        <v>46267.040127314816</v>
       </c>
       <c r="G89" t="s">
         <v>15</v>
       </c>
       <c r="H89" t="s">
-        <v>44</v>
-      </c>
-      <c r="I89">
-        <v>250</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="I89"/>
       <c r="J89"/>
       <c r="K89"/>
       <c r="L89">
-        <v>4003</v>
+        <v>3705</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="s">
-        <v>106</v>
+        <v>54</v>
       </c>
       <c r="B90" t="s">
-        <v>107</v>
+        <v>55</v>
       </c>
       <c r="C90" t="s">
-        <v>108</v>
+        <v>91</v>
       </c>
       <c r="D90">
-        <v>153600</v>
+        <v>79200</v>
       </c>
       <c r="E90" t="s">
-        <v>109</v>
+        <v>92</v>
       </c>
       <c r="F90" s="2">
-        <v>46265.882118055553</v>
+        <v>46266.884675925925</v>
       </c>
       <c r="G90" t="s">
         <v>15</v>
       </c>
       <c r="H90" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="I90"/>
       <c r="J90"/>
       <c r="K90"/>
       <c r="L90">
-        <v>1318</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>110</v>
+        <v>56</v>
       </c>
       <c r="B91" t="s">
-        <v>111</v>
+        <v>57</v>
       </c>
       <c r="C91" t="s">
-        <v>108</v>
+        <v>91</v>
       </c>
       <c r="D91">
-        <v>259200</v>
+        <v>49920</v>
       </c>
       <c r="E91" t="s">
-        <v>109</v>
+        <v>92</v>
       </c>
       <c r="F91" s="2">
-        <v>46265.927256944444</v>
+        <v>46266.860717592594</v>
       </c>
       <c r="G91" t="s">
         <v>15</v>
       </c>
       <c r="H91" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="I91"/>
       <c r="J91"/>
       <c r="K91"/>
       <c r="L91">
-        <v>5113</v>
+        <v>2817</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s">
-        <v>104</v>
+        <v>60</v>
       </c>
       <c r="B92" t="s">
-        <v>105</v>
+        <v>61</v>
       </c>
       <c r="C92" t="s">
-        <v>108</v>
+        <v>91</v>
       </c>
       <c r="D92">
-        <v>105600</v>
+        <v>5280</v>
       </c>
       <c r="E92" t="s">
-        <v>109</v>
+        <v>92</v>
       </c>
       <c r="F92" s="2">
-        <v>46265.92759259259</v>
+        <v>46266.860717592594</v>
       </c>
       <c r="G92" t="s">
         <v>15</v>
       </c>
       <c r="H92" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="I92"/>
       <c r="J92"/>
       <c r="K92"/>
       <c r="L92">
-        <v>97</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="B93" t="s">
-        <v>43</v>
+        <v>63</v>
       </c>
       <c r="C93" t="s">
-        <v>108</v>
+        <v>91</v>
       </c>
       <c r="D93">
-        <v>2160</v>
+        <v>3960</v>
       </c>
       <c r="E93" t="s">
-        <v>109</v>
+        <v>92</v>
       </c>
       <c r="F93" s="2">
-        <v>46265.92759259259</v>
+        <v>46266.860717592594</v>
       </c>
       <c r="G93" t="s">
         <v>15</v>
       </c>
       <c r="H93" t="s">
-        <v>44</v>
-      </c>
-      <c r="I93">
-        <v>440</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="I93"/>
       <c r="J93"/>
       <c r="K93"/>
       <c r="L93">
-        <v>9067</v>
+        <v>187</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s">
+        <v>43</v>
+      </c>
+      <c r="B94" t="s">
+        <v>44</v>
+      </c>
+      <c r="C94" t="s">
+        <v>91</v>
+      </c>
+      <c r="D94">
+        <v>1560</v>
+      </c>
+      <c r="E94" t="s">
+        <v>92</v>
+      </c>
+      <c r="F94" s="2">
+        <v>46267.188877314809</v>
+      </c>
+      <c r="G94" t="s">
+        <v>15</v>
+      </c>
+      <c r="H94" t="s">
         <v>45</v>
       </c>
-      <c r="B94" t="s">
-        <v>46</v>
-      </c>
-      <c r="C94" t="s">
-        <v>108</v>
-      </c>
-      <c r="D94">
-        <v>20</v>
-      </c>
-      <c r="E94" t="s">
-        <v>109</v>
-      </c>
-      <c r="F94" s="2">
-        <v>46265.92759259259</v>
-      </c>
-      <c r="G94" t="s">
-        <v>15</v>
-      </c>
-      <c r="H94" t="s">
-        <v>44</v>
-      </c>
       <c r="I94">
-        <v>250</v>
+        <v>440</v>
       </c>
       <c r="J94"/>
       <c r="K94"/>
       <c r="L94">
-        <v>6361</v>
+        <v>5383</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="s">
+        <v>46</v>
+      </c>
+      <c r="B95" t="s">
         <v>47</v>
       </c>
-      <c r="B95" t="s">
-        <v>48</v>
-      </c>
       <c r="C95" t="s">
-        <v>108</v>
+        <v>91</v>
       </c>
       <c r="D95">
-        <v>10</v>
+        <v>98</v>
       </c>
       <c r="E95" t="s">
-        <v>109</v>
+        <v>92</v>
       </c>
       <c r="F95" s="2">
-        <v>46265.927256944444</v>
+        <v>46267.188877314809</v>
       </c>
       <c r="G95" t="s">
         <v>15</v>
       </c>
       <c r="H95" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I95">
         <v>250</v>
@@ -3806,1512 +3989,4074 @@
       <c r="J95"/>
       <c r="K95"/>
       <c r="L95">
-        <v>5165</v>
+        <v>4686</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="s">
-        <v>112</v>
+        <v>64</v>
       </c>
       <c r="B96" t="s">
-        <v>113</v>
+        <v>65</v>
       </c>
       <c r="C96" t="s">
-        <v>114</v>
+        <v>91</v>
       </c>
       <c r="D96">
-        <v>900</v>
+        <v>44</v>
       </c>
       <c r="E96" t="s">
-        <v>115</v>
+        <v>92</v>
       </c>
       <c r="F96" s="2">
-        <v>46265.835532407407</v>
+        <v>46267.040127314816</v>
       </c>
       <c r="G96" t="s">
         <v>15</v>
       </c>
       <c r="H96" t="s">
-        <v>27</v>
-      </c>
-      <c r="I96"/>
+        <v>45</v>
+      </c>
+      <c r="I96">
+        <v>250</v>
+      </c>
       <c r="J96"/>
       <c r="K96"/>
       <c r="L96">
-        <v>1425</v>
+        <v>2658</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="s">
-        <v>116</v>
+        <v>72</v>
       </c>
       <c r="B97" t="s">
-        <v>117</v>
+        <v>73</v>
       </c>
       <c r="C97" t="s">
-        <v>118</v>
+        <v>91</v>
       </c>
       <c r="D97">
-        <v>560</v>
+        <v>93</v>
       </c>
       <c r="E97" t="s">
-        <v>119</v>
+        <v>92</v>
       </c>
       <c r="F97" s="2">
-        <v>46265.839085648149</v>
+        <v>46267.188877314809</v>
       </c>
       <c r="G97" t="s">
         <v>15</v>
       </c>
       <c r="H97" t="s">
-        <v>120</v>
+        <v>74</v>
       </c>
       <c r="I97">
-        <v>13440</v>
+        <v>5000</v>
       </c>
       <c r="J97"/>
       <c r="K97"/>
       <c r="L97">
-        <v>97</v>
+        <v>3601</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s">
-        <v>121</v>
+        <v>66</v>
       </c>
       <c r="B98" t="s">
-        <v>122</v>
+        <v>67</v>
       </c>
       <c r="C98" t="s">
-        <v>118</v>
+        <v>102</v>
       </c>
       <c r="D98">
-        <v>600</v>
+        <v>6000</v>
       </c>
       <c r="E98" t="s">
-        <v>119</v>
+        <v>103</v>
       </c>
       <c r="F98" s="2">
-        <v>46265.839085648149</v>
+        <v>46267.351400462961</v>
       </c>
       <c r="G98" t="s">
         <v>15</v>
       </c>
       <c r="H98" t="s">
-        <v>120</v>
-      </c>
-      <c r="I98">
-        <v>13440</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="I98"/>
       <c r="J98"/>
       <c r="K98"/>
       <c r="L98">
-        <v>376</v>
+        <v>179</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s">
-        <v>123</v>
+        <v>48</v>
       </c>
       <c r="B99" t="s">
-        <v>124</v>
+        <v>49</v>
       </c>
       <c r="C99" t="s">
-        <v>125</v>
+        <v>102</v>
       </c>
       <c r="D99">
-        <v>2240</v>
+        <v>8640</v>
       </c>
       <c r="E99" t="s">
-        <v>126</v>
+        <v>103</v>
       </c>
       <c r="F99" s="2">
-        <v>46265.787905092591</v>
+        <v>46266.849386574075</v>
       </c>
       <c r="G99" t="s">
         <v>15</v>
       </c>
       <c r="H99" t="s">
-        <v>120</v>
-      </c>
-      <c r="I99">
-        <v>10080</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="I99"/>
       <c r="J99"/>
       <c r="K99"/>
       <c r="L99">
-        <v>870</v>
+        <v>669</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="s">
-        <v>121</v>
+        <v>52</v>
       </c>
       <c r="B100" t="s">
-        <v>122</v>
+        <v>53</v>
       </c>
       <c r="C100" t="s">
-        <v>125</v>
+        <v>102</v>
       </c>
       <c r="D100">
-        <v>960</v>
+        <v>36720</v>
       </c>
       <c r="E100" t="s">
-        <v>126</v>
+        <v>103</v>
       </c>
       <c r="F100" s="2">
-        <v>46265.787905092591</v>
+        <v>46267.351400462961</v>
       </c>
       <c r="G100" t="s">
         <v>15</v>
       </c>
       <c r="H100" t="s">
-        <v>120</v>
-      </c>
-      <c r="I100">
-        <v>13440</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="I100"/>
       <c r="J100"/>
       <c r="K100"/>
       <c r="L100">
-        <v>363</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="s">
-        <v>127</v>
+        <v>54</v>
       </c>
       <c r="B101" t="s">
-        <v>128</v>
+        <v>55</v>
       </c>
       <c r="C101" t="s">
-        <v>125</v>
+        <v>102</v>
       </c>
       <c r="D101">
-        <v>800</v>
+        <v>10560</v>
       </c>
       <c r="E101" t="s">
-        <v>126</v>
+        <v>103</v>
       </c>
       <c r="F101" s="2">
-        <v>46265.787905092591</v>
+        <v>46267.351400462961</v>
       </c>
       <c r="G101" t="s">
         <v>15</v>
       </c>
       <c r="H101" t="s">
-        <v>120</v>
-      </c>
-      <c r="I101">
-        <v>995</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="I101"/>
       <c r="J101"/>
       <c r="K101"/>
       <c r="L101">
-        <v>375</v>
+        <v>651</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="s">
-        <v>129</v>
+        <v>56</v>
       </c>
       <c r="B102" t="s">
-        <v>130</v>
+        <v>57</v>
       </c>
       <c r="C102" t="s">
-        <v>125</v>
+        <v>102</v>
       </c>
       <c r="D102">
-        <v>4480</v>
+        <v>26880</v>
       </c>
       <c r="E102" t="s">
-        <v>126</v>
+        <v>103</v>
       </c>
       <c r="F102" s="2">
-        <v>46265.787905092591</v>
+        <v>46267.351400462961</v>
       </c>
       <c r="G102" t="s">
         <v>15</v>
       </c>
       <c r="H102" t="s">
-        <v>120</v>
-      </c>
-      <c r="I102">
-        <v>15120</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="I102"/>
       <c r="J102"/>
       <c r="K102"/>
       <c r="L102">
-        <v>2122</v>
+        <v>969</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="s">
-        <v>131</v>
+        <v>43</v>
       </c>
       <c r="B103" t="s">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="C103" t="s">
-        <v>125</v>
+        <v>102</v>
       </c>
       <c r="D103">
-        <v>4480</v>
+        <v>476</v>
       </c>
       <c r="E103" t="s">
-        <v>126</v>
+        <v>103</v>
       </c>
       <c r="F103" s="2">
-        <v>46265.787905092591</v>
+        <v>46267.351400462961</v>
       </c>
       <c r="G103" t="s">
         <v>15</v>
       </c>
       <c r="H103" t="s">
-        <v>120</v>
+        <v>45</v>
       </c>
       <c r="I103">
-        <v>15120</v>
+        <v>440</v>
       </c>
       <c r="J103"/>
       <c r="K103"/>
       <c r="L103">
-        <v>588</v>
+        <v>1375</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="s">
-        <v>133</v>
+        <v>46</v>
       </c>
       <c r="B104" t="s">
-        <v>134</v>
+        <v>47</v>
       </c>
       <c r="C104" t="s">
-        <v>135</v>
+        <v>102</v>
       </c>
       <c r="D104">
-        <v>400</v>
+        <v>84</v>
       </c>
       <c r="E104" t="s">
-        <v>136</v>
+        <v>103</v>
       </c>
       <c r="F104" s="2">
-        <v>45185</v>
+        <v>46267.351400462961</v>
       </c>
       <c r="G104" t="s">
         <v>15</v>
       </c>
       <c r="H104" t="s">
-        <v>120</v>
+        <v>45</v>
       </c>
       <c r="I104">
-        <v>173</v>
+        <v>250</v>
       </c>
       <c r="J104"/>
       <c r="K104"/>
       <c r="L104">
-        <v>1</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="s">
-        <v>137</v>
+        <v>64</v>
       </c>
       <c r="B105" t="s">
-        <v>138</v>
+        <v>65</v>
       </c>
       <c r="C105" t="s">
-        <v>139</v>
+        <v>102</v>
       </c>
       <c r="D105">
-        <v>3220</v>
+        <v>42</v>
       </c>
       <c r="E105" t="s">
-        <v>140</v>
+        <v>103</v>
       </c>
       <c r="F105" s="2">
-        <v>46265.808981481481</v>
+        <v>46267.351400462961</v>
       </c>
       <c r="G105" t="s">
         <v>15</v>
       </c>
       <c r="H105" t="s">
-        <v>120</v>
+        <v>45</v>
       </c>
       <c r="I105">
-        <v>24920</v>
+        <v>250</v>
       </c>
       <c r="J105"/>
       <c r="K105"/>
       <c r="L105">
-        <v>254</v>
+        <v>699</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="s">
-        <v>141</v>
+        <v>72</v>
       </c>
       <c r="B106" t="s">
-        <v>142</v>
+        <v>73</v>
       </c>
       <c r="C106" t="s">
-        <v>139</v>
+        <v>102</v>
       </c>
       <c r="D106">
-        <v>30000</v>
+        <v>80</v>
       </c>
       <c r="E106" t="s">
-        <v>140</v>
+        <v>103</v>
       </c>
       <c r="F106" s="2">
-        <v>46265.808981481481</v>
+        <v>46266.849386574075</v>
       </c>
       <c r="G106" t="s">
         <v>15</v>
       </c>
       <c r="H106" t="s">
-        <v>120</v>
+        <v>74</v>
       </c>
       <c r="I106">
-        <v>200000</v>
+        <v>5000</v>
       </c>
       <c r="J106"/>
       <c r="K106"/>
       <c r="L106">
-        <v>100</v>
+        <v>737</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="s">
-        <v>143</v>
+        <v>66</v>
       </c>
       <c r="B107" t="s">
-        <v>144</v>
+        <v>67</v>
       </c>
       <c r="C107" t="s">
-        <v>145</v>
+        <v>104</v>
       </c>
       <c r="D107">
-        <v>8000</v>
+        <v>900</v>
       </c>
       <c r="E107" t="s">
-        <v>146</v>
+        <v>105</v>
       </c>
       <c r="F107" s="2">
-        <v>46265.760115740741</v>
+        <v>46266.9480324074</v>
       </c>
       <c r="G107" t="s">
         <v>15</v>
       </c>
       <c r="H107" t="s">
-        <v>120</v>
-      </c>
-      <c r="I107">
-        <v>10000</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="I107"/>
       <c r="J107"/>
       <c r="K107"/>
       <c r="L107">
-        <v>135</v>
+        <v>129</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="s">
-        <v>147</v>
+        <v>70</v>
       </c>
       <c r="B108" t="s">
-        <v>148</v>
+        <v>71</v>
       </c>
       <c r="C108" t="s">
-        <v>145</v>
+        <v>104</v>
       </c>
       <c r="D108">
-        <v>6880</v>
+        <v>9900</v>
       </c>
       <c r="E108" t="s">
-        <v>146</v>
+        <v>105</v>
       </c>
       <c r="F108" s="2">
-        <v>46265.760115740741</v>
+        <v>46266.9480324074</v>
       </c>
       <c r="G108" t="s">
         <v>15</v>
       </c>
       <c r="H108" t="s">
-        <v>120</v>
-      </c>
-      <c r="I108">
-        <v>10000</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="I108"/>
       <c r="J108"/>
       <c r="K108"/>
       <c r="L108">
-        <v>69</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="s">
-        <v>141</v>
+        <v>48</v>
       </c>
       <c r="B109" t="s">
-        <v>142</v>
+        <v>49</v>
       </c>
       <c r="C109" t="s">
-        <v>145</v>
+        <v>104</v>
       </c>
       <c r="D109">
-        <v>10000</v>
+        <v>6600</v>
       </c>
       <c r="E109" t="s">
-        <v>146</v>
+        <v>105</v>
       </c>
       <c r="F109" s="2">
-        <v>46265.760115740741</v>
+        <v>46266.9480324074</v>
       </c>
       <c r="G109" t="s">
         <v>15</v>
       </c>
       <c r="H109" t="s">
-        <v>120</v>
-      </c>
-      <c r="I109">
-        <v>200000</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="I109"/>
       <c r="J109"/>
       <c r="K109"/>
       <c r="L109">
-        <v>25</v>
+        <v>141</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="s">
-        <v>149</v>
+        <v>52</v>
       </c>
       <c r="B110" t="s">
-        <v>150</v>
+        <v>53</v>
       </c>
       <c r="C110" t="s">
-        <v>151</v>
+        <v>104</v>
       </c>
       <c r="D110">
-        <v>1</v>
+        <v>63360</v>
       </c>
       <c r="E110" t="s">
-        <v>152</v>
+        <v>105</v>
       </c>
       <c r="F110" s="2">
-        <v>46265.788981481477</v>
+        <v>46266.9480324074</v>
       </c>
       <c r="G110" t="s">
         <v>15</v>
       </c>
       <c r="H110" t="s">
-        <v>153</v>
-      </c>
-      <c r="I110">
-        <v>12</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="I110"/>
       <c r="J110"/>
       <c r="K110"/>
       <c r="L110">
-        <v>14</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="s">
-        <v>154</v>
+        <v>56</v>
       </c>
       <c r="B111" t="s">
-        <v>155</v>
+        <v>57</v>
       </c>
       <c r="C111" t="s">
-        <v>151</v>
+        <v>104</v>
       </c>
       <c r="D111">
-        <v>1</v>
+        <v>295680</v>
       </c>
       <c r="E111" t="s">
-        <v>152</v>
+        <v>105</v>
       </c>
       <c r="F111" s="2">
-        <v>46265.776967592588</v>
+        <v>46266.9480324074</v>
       </c>
       <c r="G111" t="s">
         <v>15</v>
       </c>
       <c r="H111" t="s">
-        <v>153</v>
-      </c>
-      <c r="I111">
-        <v>45</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="I111"/>
       <c r="J111"/>
       <c r="K111"/>
       <c r="L111">
-        <v>11</v>
+        <v>2823</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="s">
-        <v>156</v>
+        <v>58</v>
       </c>
       <c r="B112" t="s">
-        <v>157</v>
+        <v>59</v>
       </c>
       <c r="C112" t="s">
-        <v>151</v>
+        <v>104</v>
       </c>
       <c r="D112">
-        <v>1</v>
+        <v>1800</v>
       </c>
       <c r="E112" t="s">
-        <v>152</v>
+        <v>105</v>
       </c>
       <c r="F112" s="2">
-        <v>46265.788981481477</v>
+        <v>46266.9480324074</v>
       </c>
       <c r="G112" t="s">
         <v>15</v>
       </c>
       <c r="H112" t="s">
-        <v>153</v>
-      </c>
-      <c r="I112">
-        <v>60</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="I112"/>
       <c r="J112"/>
       <c r="K112"/>
       <c r="L112">
-        <v>19</v>
+        <v>427</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="s">
-        <v>137</v>
+        <v>60</v>
       </c>
       <c r="B113" t="s">
-        <v>138</v>
+        <v>61</v>
       </c>
       <c r="C113" t="s">
-        <v>151</v>
+        <v>104</v>
       </c>
       <c r="D113">
-        <v>280</v>
+        <v>1243</v>
       </c>
       <c r="E113" t="s">
-        <v>152</v>
+        <v>105</v>
       </c>
       <c r="F113" s="2">
-        <v>46261.786122685182</v>
+        <v>46266</v>
       </c>
       <c r="G113" t="s">
         <v>15</v>
       </c>
       <c r="H113" t="s">
-        <v>120</v>
-      </c>
-      <c r="I113">
-        <v>24920</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="I113"/>
       <c r="J113"/>
       <c r="K113"/>
       <c r="L113">
-        <v>167</v>
+        <v>796</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="s">
-        <v>158</v>
+        <v>62</v>
       </c>
       <c r="B114" t="s">
-        <v>159</v>
+        <v>63</v>
       </c>
       <c r="C114" t="s">
-        <v>160</v>
+        <v>104</v>
       </c>
       <c r="D114">
-        <v>206040</v>
+        <v>1800</v>
       </c>
       <c r="E114" t="s">
-        <v>161</v>
+        <v>105</v>
       </c>
       <c r="F114" s="2">
-        <v>46265</v>
+        <v>46266.9480324074</v>
       </c>
       <c r="G114" t="s">
         <v>15</v>
       </c>
       <c r="H114" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="I114"/>
       <c r="J114"/>
       <c r="K114"/>
       <c r="L114">
-        <v>1354</v>
+        <v>201</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="s">
-        <v>162</v>
+        <v>43</v>
       </c>
       <c r="B115" t="s">
-        <v>163</v>
+        <v>44</v>
       </c>
       <c r="C115" t="s">
-        <v>164</v>
+        <v>104</v>
       </c>
       <c r="D115">
-        <v>300</v>
+        <v>1664</v>
       </c>
       <c r="E115" t="s">
-        <v>165</v>
+        <v>105</v>
       </c>
       <c r="F115" s="2">
-        <v>46266.293368055551</v>
+        <v>46266.9480324074</v>
       </c>
       <c r="G115" t="s">
         <v>15</v>
       </c>
       <c r="H115" t="s">
-        <v>27</v>
-      </c>
-      <c r="I115"/>
+        <v>45</v>
+      </c>
+      <c r="I115">
+        <v>440</v>
+      </c>
       <c r="J115"/>
       <c r="K115"/>
       <c r="L115">
-        <v>275</v>
+        <v>3071</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="B116" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="C116" t="s">
-        <v>164</v>
+        <v>104</v>
       </c>
       <c r="D116">
-        <v>288</v>
+        <v>92</v>
       </c>
       <c r="E116" t="s">
-        <v>165</v>
+        <v>105</v>
       </c>
       <c r="F116" s="2">
-        <v>46266.293368055551</v>
+        <v>46266.9480324074</v>
       </c>
       <c r="G116" t="s">
         <v>15</v>
       </c>
       <c r="H116" t="s">
-        <v>27</v>
-      </c>
-      <c r="I116"/>
+        <v>45</v>
+      </c>
+      <c r="I116">
+        <v>250</v>
+      </c>
       <c r="J116"/>
       <c r="K116"/>
       <c r="L116">
-        <v>1520</v>
+        <v>2789</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="s">
-        <v>166</v>
+        <v>64</v>
       </c>
       <c r="B117" t="s">
-        <v>167</v>
+        <v>65</v>
       </c>
       <c r="C117" t="s">
-        <v>164</v>
+        <v>104</v>
       </c>
       <c r="D117">
-        <v>186</v>
+        <v>46</v>
       </c>
       <c r="E117" t="s">
-        <v>165</v>
+        <v>105</v>
       </c>
       <c r="F117" s="2">
-        <v>44946.553055555552</v>
+        <v>46266.9480324074</v>
       </c>
       <c r="G117" t="s">
         <v>15</v>
       </c>
       <c r="H117" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I117">
-        <v>20</v>
+        <v>250</v>
       </c>
       <c r="J117"/>
       <c r="K117"/>
       <c r="L117">
-        <v>2</v>
+        <v>341</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="s">
-        <v>168</v>
+        <v>106</v>
       </c>
       <c r="B118" t="s">
-        <v>169</v>
+        <v>107</v>
       </c>
       <c r="C118" t="s">
-        <v>164</v>
+        <v>108</v>
       </c>
       <c r="D118">
-        <v>93</v>
+        <v>500</v>
       </c>
       <c r="E118" t="s">
-        <v>165</v>
+        <v>109</v>
       </c>
       <c r="F118" s="2">
-        <v>45777.752291666664</v>
+        <v>46267.346643518518</v>
       </c>
       <c r="G118" t="s">
         <v>15</v>
       </c>
       <c r="H118" t="s">
-        <v>170</v>
+        <v>110</v>
       </c>
       <c r="I118">
-        <v>16</v>
+        <v>884</v>
       </c>
       <c r="J118"/>
       <c r="K118"/>
       <c r="L118">
-        <v>7</v>
+        <v>1860</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="s">
-        <v>171</v>
+        <v>111</v>
       </c>
       <c r="B119" t="s">
-        <v>172</v>
+        <v>112</v>
       </c>
       <c r="C119" t="s">
-        <v>164</v>
+        <v>108</v>
       </c>
       <c r="D119">
-        <v>55</v>
+        <v>10000</v>
       </c>
       <c r="E119" t="s">
-        <v>165</v>
+        <v>109</v>
       </c>
       <c r="F119" s="2">
-        <v>44426</v>
+        <v>46267.346643518518</v>
       </c>
       <c r="G119" t="s">
         <v>15</v>
       </c>
       <c r="H119" t="s">
-        <v>51</v>
+        <v>113</v>
       </c>
       <c r="I119">
-        <v>2</v>
+        <v>60000</v>
       </c>
       <c r="J119"/>
       <c r="K119"/>
       <c r="L119">
-        <v>5</v>
+        <v>864</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="s">
-        <v>173</v>
+        <v>114</v>
       </c>
       <c r="B120" t="s">
-        <v>174</v>
+        <v>115</v>
       </c>
       <c r="C120" t="s">
-        <v>175</v>
+        <v>108</v>
       </c>
       <c r="D120">
-        <v>2160</v>
+        <v>5200</v>
       </c>
       <c r="E120" t="s">
-        <v>176</v>
+        <v>109</v>
       </c>
       <c r="F120" s="2">
-        <v>46265.869062499994</v>
+        <v>46267.346643518518</v>
       </c>
       <c r="G120" t="s">
         <v>15</v>
       </c>
       <c r="H120" t="s">
-        <v>27</v>
-      </c>
-      <c r="I120"/>
+        <v>113</v>
+      </c>
+      <c r="I120">
+        <v>10000</v>
+      </c>
       <c r="J120"/>
       <c r="K120"/>
       <c r="L120">
-        <v>28</v>
+        <v>155</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="s">
-        <v>56</v>
+        <v>116</v>
       </c>
       <c r="B121" t="s">
-        <v>57</v>
+        <v>117</v>
       </c>
       <c r="C121" t="s">
-        <v>175</v>
+        <v>108</v>
       </c>
       <c r="D121">
-        <v>576</v>
+        <v>36960</v>
       </c>
       <c r="E121" t="s">
-        <v>176</v>
+        <v>109</v>
       </c>
       <c r="F121" s="2">
-        <v>46265.882777777777</v>
+        <v>46266.650312499994</v>
       </c>
       <c r="G121" t="s">
         <v>15</v>
       </c>
       <c r="H121" t="s">
-        <v>27</v>
-      </c>
-      <c r="I121"/>
+        <v>118</v>
+      </c>
+      <c r="I121">
+        <v>7200</v>
+      </c>
       <c r="J121"/>
       <c r="K121"/>
       <c r="L121">
-        <v>431</v>
+        <v>1877</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="s">
-        <v>177</v>
+        <v>119</v>
       </c>
       <c r="B122" t="s">
-        <v>178</v>
+        <v>120</v>
       </c>
       <c r="C122" t="s">
-        <v>175</v>
+        <v>108</v>
       </c>
       <c r="D122">
-        <v>4320</v>
+        <v>36960</v>
       </c>
       <c r="E122" t="s">
-        <v>176</v>
+        <v>109</v>
       </c>
       <c r="F122" s="2">
-        <v>46265.869062499994</v>
+        <v>46266.650312499994</v>
       </c>
       <c r="G122" t="s">
         <v>15</v>
       </c>
       <c r="H122" t="s">
-        <v>27</v>
-      </c>
-      <c r="I122"/>
+        <v>118</v>
+      </c>
+      <c r="I122">
+        <v>7200</v>
+      </c>
       <c r="J122"/>
       <c r="K122"/>
       <c r="L122">
-        <v>50</v>
+        <v>1876</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="B123" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="C123" t="s">
-        <v>175</v>
+        <v>108</v>
       </c>
       <c r="D123">
-        <v>300</v>
+        <v>36400</v>
       </c>
       <c r="E123" t="s">
-        <v>176</v>
+        <v>109</v>
       </c>
       <c r="F123" s="2">
-        <v>46265.692060185182</v>
+        <v>46266.650312499994</v>
       </c>
       <c r="G123" t="s">
         <v>15</v>
       </c>
       <c r="H123" t="s">
-        <v>27</v>
-      </c>
-      <c r="I123"/>
+        <v>118</v>
+      </c>
+      <c r="I123">
+        <v>36400</v>
+      </c>
       <c r="J123"/>
       <c r="K123"/>
       <c r="L123">
-        <v>529</v>
+        <v>1953</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="s">
-        <v>62</v>
+        <v>123</v>
       </c>
       <c r="B124" t="s">
-        <v>63</v>
+        <v>124</v>
       </c>
       <c r="C124" t="s">
-        <v>175</v>
+        <v>108</v>
       </c>
       <c r="D124">
-        <v>720</v>
+        <v>42000</v>
       </c>
       <c r="E124" t="s">
-        <v>176</v>
+        <v>109</v>
       </c>
       <c r="F124" s="2">
-        <v>46265.74722222222</v>
+        <v>46266.650312499994</v>
       </c>
       <c r="G124" t="s">
         <v>15</v>
       </c>
       <c r="H124" t="s">
-        <v>27</v>
-      </c>
-      <c r="I124"/>
+        <v>118</v>
+      </c>
+      <c r="I124">
+        <v>42000</v>
+      </c>
       <c r="J124"/>
       <c r="K124"/>
       <c r="L124">
-        <v>380</v>
+        <v>69</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="s">
-        <v>94</v>
+        <v>125</v>
       </c>
       <c r="B125" t="s">
-        <v>95</v>
+        <v>126</v>
       </c>
       <c r="C125" t="s">
-        <v>175</v>
+        <v>127</v>
       </c>
       <c r="D125">
-        <v>5880</v>
+        <v>500</v>
       </c>
       <c r="E125" t="s">
-        <v>176</v>
+        <v>128</v>
       </c>
       <c r="F125" s="2">
-        <v>46260.628460648149</v>
+        <v>46267.336666666662</v>
       </c>
       <c r="G125" t="s">
         <v>15</v>
       </c>
       <c r="H125" t="s">
-        <v>27</v>
-      </c>
-      <c r="I125"/>
+        <v>113</v>
+      </c>
+      <c r="I125">
+        <v>404</v>
+      </c>
       <c r="J125"/>
       <c r="K125"/>
       <c r="L125">
-        <v>60</v>
+        <v>93</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="s">
-        <v>106</v>
+        <v>129</v>
       </c>
       <c r="B126" t="s">
-        <v>107</v>
+        <v>130</v>
       </c>
       <c r="C126" t="s">
-        <v>179</v>
+        <v>127</v>
       </c>
       <c r="D126">
-        <v>262800</v>
+        <v>5</v>
       </c>
       <c r="E126" t="s">
-        <v>180</v>
+        <v>128</v>
       </c>
       <c r="F126" s="2">
-        <v>46265.834976851853</v>
+        <v>46267.336666666662</v>
       </c>
       <c r="G126" t="s">
-        <v>15</v>
+        <v>131</v>
       </c>
       <c r="H126" t="s">
-        <v>27</v>
-      </c>
-      <c r="I126"/>
+        <v>113</v>
+      </c>
+      <c r="I126">
+        <v>60</v>
+      </c>
       <c r="J126"/>
       <c r="K126"/>
       <c r="L126">
-        <v>1768</v>
+        <v>86</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="s">
-        <v>104</v>
+        <v>132</v>
       </c>
       <c r="B127" t="s">
-        <v>105</v>
+        <v>133</v>
       </c>
       <c r="C127" t="s">
-        <v>179</v>
+        <v>127</v>
       </c>
       <c r="D127">
-        <v>274560</v>
+        <v>623</v>
       </c>
       <c r="E127" t="s">
-        <v>180</v>
+        <v>128</v>
       </c>
       <c r="F127" s="2">
-        <v>46266.072499999995</v>
+        <v>46267.338124999995</v>
       </c>
       <c r="G127" t="s">
         <v>15</v>
       </c>
       <c r="H127" t="s">
-        <v>27</v>
-      </c>
-      <c r="I127"/>
+        <v>113</v>
+      </c>
+      <c r="I127">
+        <v>793</v>
+      </c>
       <c r="J127"/>
       <c r="K127"/>
       <c r="L127">
-        <v>191</v>
+        <v>87</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="s">
-        <v>42</v>
+        <v>134</v>
       </c>
       <c r="B128" t="s">
-        <v>43</v>
+        <v>135</v>
       </c>
       <c r="C128" t="s">
-        <v>179</v>
+        <v>127</v>
       </c>
       <c r="D128">
-        <v>2239</v>
+        <v>10000</v>
       </c>
       <c r="E128" t="s">
-        <v>180</v>
+        <v>128</v>
       </c>
       <c r="F128" s="2">
-        <v>46266.072499999995</v>
+        <v>46267.338124999995</v>
       </c>
       <c r="G128" t="s">
         <v>15</v>
       </c>
       <c r="H128" t="s">
-        <v>44</v>
+        <v>113</v>
       </c>
       <c r="I128">
-        <v>440</v>
+        <v>100000</v>
       </c>
       <c r="J128"/>
       <c r="K128"/>
       <c r="L128">
-        <v>4957</v>
+        <v>559</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="s">
-        <v>45</v>
+        <v>111</v>
       </c>
       <c r="B129" t="s">
-        <v>46</v>
+        <v>112</v>
       </c>
       <c r="C129" t="s">
-        <v>179</v>
+        <v>127</v>
       </c>
       <c r="D129">
-        <v>95</v>
+        <v>20000</v>
       </c>
       <c r="E129" t="s">
-        <v>180</v>
+        <v>128</v>
       </c>
       <c r="F129" s="2">
-        <v>46266.075173611112</v>
+        <v>46267.338124999995</v>
       </c>
       <c r="G129" t="s">
         <v>15</v>
       </c>
       <c r="H129" t="s">
-        <v>44</v>
+        <v>113</v>
       </c>
       <c r="I129">
-        <v>250</v>
+        <v>60000</v>
       </c>
       <c r="J129"/>
       <c r="K129"/>
       <c r="L129">
-        <v>4322</v>
+        <v>613</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="s">
-        <v>47</v>
+        <v>136</v>
       </c>
       <c r="B130" t="s">
-        <v>48</v>
+        <v>137</v>
       </c>
       <c r="C130" t="s">
-        <v>179</v>
+        <v>127</v>
       </c>
       <c r="D130">
-        <v>36</v>
+        <v>500</v>
       </c>
       <c r="E130" t="s">
-        <v>180</v>
+        <v>128</v>
       </c>
       <c r="F130" s="2">
-        <v>46266.072499999995</v>
+        <v>46267.338124999995</v>
       </c>
       <c r="G130" t="s">
         <v>15</v>
       </c>
       <c r="H130" t="s">
-        <v>44</v>
+        <v>113</v>
       </c>
       <c r="I130">
-        <v>250</v>
+        <v>7000</v>
       </c>
       <c r="J130"/>
       <c r="K130"/>
       <c r="L130">
-        <v>2468</v>
+        <v>248</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="s">
-        <v>181</v>
+        <v>138</v>
       </c>
       <c r="B131" t="s">
-        <v>182</v>
+        <v>139</v>
       </c>
       <c r="C131" t="s">
-        <v>183</v>
+        <v>127</v>
       </c>
       <c r="D131">
-        <v>1000000</v>
+        <v>8</v>
       </c>
       <c r="E131" t="s">
-        <v>184</v>
+        <v>128</v>
       </c>
       <c r="F131" s="2">
-        <v>46235</v>
+        <v>46267.338124999995</v>
       </c>
       <c r="G131" t="s">
-        <v>185</v>
+        <v>131</v>
       </c>
       <c r="H131" t="s">
-        <v>186</v>
+        <v>113</v>
       </c>
       <c r="I131">
-        <v>1000000</v>
+        <v>90</v>
       </c>
       <c r="J131"/>
       <c r="K131"/>
       <c r="L131">
-        <v>49</v>
+        <v>5</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="s">
-        <v>187</v>
+        <v>116</v>
       </c>
       <c r="B132" t="s">
-        <v>188</v>
+        <v>117</v>
       </c>
       <c r="C132" t="s">
-        <v>189</v>
+        <v>127</v>
       </c>
       <c r="D132">
-        <v>5060000</v>
+        <v>2880</v>
       </c>
       <c r="E132" t="s">
-        <v>190</v>
+        <v>128</v>
       </c>
       <c r="F132" s="2">
-        <v>46239</v>
+        <v>46267.338124999995</v>
       </c>
       <c r="G132" t="s">
-        <v>185</v>
+        <v>15</v>
       </c>
       <c r="H132" t="s">
-        <v>186</v>
+        <v>118</v>
       </c>
       <c r="I132">
-        <v>5060000</v>
+        <v>7200</v>
       </c>
       <c r="J132"/>
       <c r="K132"/>
       <c r="L132">
-        <v>157</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="s">
-        <v>191</v>
+        <v>140</v>
       </c>
       <c r="B133" t="s">
-        <v>192</v>
+        <v>141</v>
       </c>
       <c r="C133" t="s">
-        <v>189</v>
+        <v>127</v>
       </c>
       <c r="D133">
-        <v>2439100</v>
+        <v>2880</v>
       </c>
       <c r="E133" t="s">
-        <v>190</v>
+        <v>128</v>
       </c>
       <c r="F133" s="2">
-        <v>46235</v>
+        <v>46267.338124999995</v>
       </c>
       <c r="G133" t="s">
-        <v>185</v>
+        <v>15</v>
       </c>
       <c r="H133" t="s">
-        <v>186</v>
-      </c>
-      <c r="I133">
-        <v>800000</v>
-      </c>
+        <v>118</v>
+      </c>
+      <c r="I133"/>
       <c r="J133"/>
       <c r="K133"/>
       <c r="L133">
-        <v>54</v>
+        <v>43</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="s">
-        <v>193</v>
+        <v>142</v>
       </c>
       <c r="B134" t="s">
-        <v>194</v>
+        <v>143</v>
       </c>
       <c r="C134" t="s">
-        <v>189</v>
+        <v>127</v>
       </c>
       <c r="D134">
-        <v>880000</v>
+        <v>400</v>
       </c>
       <c r="E134" t="s">
-        <v>190</v>
+        <v>128</v>
       </c>
       <c r="F134" s="2">
-        <v>46235</v>
+        <v>46267.338124999995</v>
       </c>
       <c r="G134" t="s">
-        <v>185</v>
+        <v>15</v>
       </c>
       <c r="H134" t="s">
-        <v>186</v>
-      </c>
-      <c r="I134">
-        <v>880000</v>
-      </c>
+        <v>118</v>
+      </c>
+      <c r="I134"/>
       <c r="J134"/>
       <c r="K134"/>
       <c r="L134">
-        <v>43</v>
+        <v>35</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="s">
-        <v>195</v>
+        <v>43</v>
       </c>
       <c r="B135" t="s">
-        <v>196</v>
+        <v>44</v>
       </c>
       <c r="C135" t="s">
-        <v>189</v>
+        <v>144</v>
       </c>
       <c r="D135">
-        <v>104000</v>
+        <v>2304</v>
       </c>
       <c r="E135" t="s">
-        <v>190</v>
+        <v>145</v>
       </c>
       <c r="F135" s="2">
-        <v>46258</v>
+        <v>46267.375532407408</v>
       </c>
       <c r="G135" t="s">
-        <v>185</v>
+        <v>15</v>
       </c>
       <c r="H135" t="s">
-        <v>186</v>
+        <v>45</v>
       </c>
       <c r="I135">
-        <v>52000</v>
+        <v>440</v>
       </c>
       <c r="J135"/>
       <c r="K135"/>
       <c r="L135">
-        <v>53</v>
+        <v>5628</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="s">
-        <v>197</v>
+        <v>46</v>
       </c>
       <c r="B136" t="s">
-        <v>198</v>
+        <v>47</v>
       </c>
       <c r="C136" t="s">
-        <v>199</v>
+        <v>144</v>
       </c>
       <c r="D136">
-        <v>3</v>
+        <v>158</v>
       </c>
       <c r="E136" t="s">
-        <v>200</v>
+        <v>145</v>
       </c>
       <c r="F136" s="2">
-        <v>46262.311388888884</v>
+        <v>46267.375532407408</v>
       </c>
       <c r="G136" t="s">
-        <v>201</v>
+        <v>15</v>
       </c>
       <c r="H136" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="I136">
-        <v>2</v>
+        <v>250</v>
       </c>
       <c r="J136"/>
       <c r="K136"/>
       <c r="L136">
-        <v>1</v>
+        <v>5101</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="s">
-        <v>202</v>
+        <v>64</v>
       </c>
       <c r="B137" t="s">
-        <v>203</v>
+        <v>65</v>
       </c>
       <c r="C137" t="s">
-        <v>199</v>
+        <v>144</v>
       </c>
       <c r="D137">
-        <v>2</v>
+        <v>48</v>
       </c>
       <c r="E137" t="s">
-        <v>200</v>
+        <v>145</v>
       </c>
       <c r="F137" s="2">
-        <v>46261.675902777773</v>
+        <v>46267.375532407408</v>
       </c>
       <c r="G137" t="s">
         <v>15</v>
       </c>
       <c r="H137" t="s">
-        <v>204</v>
+        <v>45</v>
       </c>
       <c r="I137">
-        <v>20</v>
+        <v>250</v>
       </c>
       <c r="J137"/>
       <c r="K137"/>
       <c r="L137">
-        <v>3</v>
+        <v>2280</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="s">
-        <v>195</v>
+        <v>72</v>
       </c>
       <c r="B138" t="s">
-        <v>196</v>
+        <v>73</v>
       </c>
       <c r="C138" t="s">
-        <v>205</v>
+        <v>144</v>
       </c>
       <c r="D138">
-        <v>104000</v>
+        <v>80</v>
       </c>
       <c r="E138" t="s">
-        <v>206</v>
+        <v>145</v>
       </c>
       <c r="F138" s="2">
-        <v>46235</v>
+        <v>46267.375532407408</v>
       </c>
       <c r="G138" t="s">
-        <v>185</v>
+        <v>15</v>
       </c>
       <c r="H138" t="s">
-        <v>186</v>
+        <v>74</v>
       </c>
       <c r="I138">
-        <v>52000</v>
+        <v>5000</v>
       </c>
       <c r="J138"/>
       <c r="K138"/>
       <c r="L138">
-        <v>47</v>
+        <v>1591</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="s">
-        <v>207</v>
+        <v>43</v>
       </c>
       <c r="B139" t="s">
-        <v>208</v>
+        <v>44</v>
       </c>
       <c r="C139" t="s">
-        <v>209</v>
+        <v>146</v>
       </c>
       <c r="D139">
-        <v>520</v>
+        <v>5232</v>
       </c>
       <c r="E139" t="s">
-        <v>210</v>
+        <v>147</v>
       </c>
       <c r="F139" s="2">
-        <v>46265.37394675926</v>
+        <v>46267.371759259258</v>
       </c>
       <c r="G139" t="s">
-        <v>185</v>
+        <v>15</v>
       </c>
       <c r="H139" t="s">
-        <v>211</v>
+        <v>45</v>
       </c>
       <c r="I139">
-        <v>520</v>
+        <v>440</v>
       </c>
       <c r="J139"/>
       <c r="K139"/>
       <c r="L139">
-        <v>51</v>
+        <v>2695</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="s">
-        <v>212</v>
+        <v>46</v>
       </c>
       <c r="B140" t="s">
-        <v>213</v>
+        <v>47</v>
       </c>
       <c r="C140" t="s">
-        <v>209</v>
+        <v>146</v>
       </c>
       <c r="D140">
-        <v>5000</v>
+        <v>226</v>
       </c>
       <c r="E140" t="s">
-        <v>210</v>
+        <v>147</v>
       </c>
       <c r="F140" s="2">
-        <v>46265.37394675926</v>
+        <v>46267.371759259258</v>
       </c>
       <c r="G140" t="s">
-        <v>185</v>
+        <v>15</v>
       </c>
       <c r="H140" t="s">
-        <v>211</v>
+        <v>45</v>
       </c>
       <c r="I140">
-        <v>5000</v>
+        <v>250</v>
       </c>
       <c r="J140"/>
       <c r="K140"/>
       <c r="L140">
+        <v>2516</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="s">
+        <v>64</v>
+      </c>
+      <c r="B141" t="s">
+        <v>65</v>
+      </c>
+      <c r="C141" t="s">
+        <v>146</v>
+      </c>
+      <c r="D141">
+        <v>152</v>
+      </c>
+      <c r="E141" t="s">
+        <v>147</v>
+      </c>
+      <c r="F141" s="2">
+        <v>46267.371759259258</v>
+      </c>
+      <c r="G141" t="s">
+        <v>15</v>
+      </c>
+      <c r="H141" t="s">
+        <v>45</v>
+      </c>
+      <c r="I141">
+        <v>250</v>
+      </c>
+      <c r="J141"/>
+      <c r="K141"/>
+      <c r="L141">
+        <v>967</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="s">
+        <v>72</v>
+      </c>
+      <c r="B142" t="s">
+        <v>73</v>
+      </c>
+      <c r="C142" t="s">
+        <v>146</v>
+      </c>
+      <c r="D142">
+        <v>16</v>
+      </c>
+      <c r="E142" t="s">
+        <v>147</v>
+      </c>
+      <c r="F142" s="2">
+        <v>46267.371064814812</v>
+      </c>
+      <c r="G142" t="s">
+        <v>15</v>
+      </c>
+      <c r="H142" t="s">
+        <v>74</v>
+      </c>
+      <c r="I142">
+        <v>5000</v>
+      </c>
+      <c r="J142"/>
+      <c r="K142"/>
+      <c r="L142">
+        <v>1067</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="s">
+        <v>43</v>
+      </c>
+      <c r="B143" t="s">
+        <v>44</v>
+      </c>
+      <c r="C143" t="s">
+        <v>148</v>
+      </c>
+      <c r="D143">
+        <v>4912</v>
+      </c>
+      <c r="E143" t="s">
+        <v>149</v>
+      </c>
+      <c r="F143" s="2">
+        <v>46267.373518518514</v>
+      </c>
+      <c r="G143" t="s">
+        <v>15</v>
+      </c>
+      <c r="H143" t="s">
+        <v>45</v>
+      </c>
+      <c r="I143">
+        <v>440</v>
+      </c>
+      <c r="J143"/>
+      <c r="K143"/>
+      <c r="L143">
+        <v>4299</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="s">
+        <v>46</v>
+      </c>
+      <c r="B144" t="s">
+        <v>47</v>
+      </c>
+      <c r="C144" t="s">
+        <v>148</v>
+      </c>
+      <c r="D144">
+        <v>311</v>
+      </c>
+      <c r="E144" t="s">
+        <v>149</v>
+      </c>
+      <c r="F144" s="2">
+        <v>46267.373518518514</v>
+      </c>
+      <c r="G144" t="s">
+        <v>15</v>
+      </c>
+      <c r="H144" t="s">
+        <v>45</v>
+      </c>
+      <c r="I144">
+        <v>250</v>
+      </c>
+      <c r="J144"/>
+      <c r="K144"/>
+      <c r="L144">
+        <v>4126</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="s">
+        <v>64</v>
+      </c>
+      <c r="B145" t="s">
+        <v>65</v>
+      </c>
+      <c r="C145" t="s">
+        <v>148</v>
+      </c>
+      <c r="D145">
+        <v>122</v>
+      </c>
+      <c r="E145" t="s">
+        <v>149</v>
+      </c>
+      <c r="F145" s="2">
+        <v>46267.373518518514</v>
+      </c>
+      <c r="G145" t="s">
+        <v>15</v>
+      </c>
+      <c r="H145" t="s">
+        <v>45</v>
+      </c>
+      <c r="I145">
+        <v>250</v>
+      </c>
+      <c r="J145"/>
+      <c r="K145"/>
+      <c r="L145">
+        <v>2320</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="s">
+        <v>72</v>
+      </c>
+      <c r="B146" t="s">
+        <v>73</v>
+      </c>
+      <c r="C146" t="s">
+        <v>148</v>
+      </c>
+      <c r="D146">
+        <v>750</v>
+      </c>
+      <c r="E146" t="s">
+        <v>149</v>
+      </c>
+      <c r="F146" s="2">
+        <v>46267.373518518514</v>
+      </c>
+      <c r="G146" t="s">
+        <v>15</v>
+      </c>
+      <c r="H146" t="s">
+        <v>74</v>
+      </c>
+      <c r="I146">
+        <v>5000</v>
+      </c>
+      <c r="J146"/>
+      <c r="K146"/>
+      <c r="L146">
+        <v>1058</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="s">
+        <v>150</v>
+      </c>
+      <c r="B147" t="s">
+        <v>151</v>
+      </c>
+      <c r="C147" t="s">
+        <v>152</v>
+      </c>
+      <c r="D147">
+        <v>160080</v>
+      </c>
+      <c r="E147" t="s">
+        <v>153</v>
+      </c>
+      <c r="F147" s="2">
+        <v>46266.811215277776</v>
+      </c>
+      <c r="G147" t="s">
+        <v>15</v>
+      </c>
+      <c r="H147" t="s">
+        <v>16</v>
+      </c>
+      <c r="I147"/>
+      <c r="J147"/>
+      <c r="K147"/>
+      <c r="L147">
+        <v>1788</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="s">
+        <v>154</v>
+      </c>
+      <c r="B148" t="s">
+        <v>155</v>
+      </c>
+      <c r="C148" t="s">
+        <v>152</v>
+      </c>
+      <c r="D148">
+        <v>470400</v>
+      </c>
+      <c r="E148" t="s">
+        <v>153</v>
+      </c>
+      <c r="F148" s="2">
+        <v>46267.353402777779</v>
+      </c>
+      <c r="G148" t="s">
+        <v>15</v>
+      </c>
+      <c r="H148" t="s">
+        <v>16</v>
+      </c>
+      <c r="I148"/>
+      <c r="J148"/>
+      <c r="K148"/>
+      <c r="L148">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="s">
+        <v>43</v>
+      </c>
+      <c r="B149" t="s">
+        <v>44</v>
+      </c>
+      <c r="C149" t="s">
+        <v>152</v>
+      </c>
+      <c r="D149">
+        <v>2627</v>
+      </c>
+      <c r="E149" t="s">
+        <v>153</v>
+      </c>
+      <c r="F149" s="2">
+        <v>46267.353402777779</v>
+      </c>
+      <c r="G149" t="s">
+        <v>15</v>
+      </c>
+      <c r="H149" t="s">
+        <v>45</v>
+      </c>
+      <c r="I149">
+        <v>440</v>
+      </c>
+      <c r="J149"/>
+      <c r="K149"/>
+      <c r="L149">
+        <v>4318</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="s">
+        <v>46</v>
+      </c>
+      <c r="B150" t="s">
+        <v>47</v>
+      </c>
+      <c r="C150" t="s">
+        <v>152</v>
+      </c>
+      <c r="D150">
+        <v>34</v>
+      </c>
+      <c r="E150" t="s">
+        <v>153</v>
+      </c>
+      <c r="F150" s="2">
+        <v>46266.811215277776</v>
+      </c>
+      <c r="G150" t="s">
+        <v>15</v>
+      </c>
+      <c r="H150" t="s">
+        <v>45</v>
+      </c>
+      <c r="I150">
+        <v>250</v>
+      </c>
+      <c r="J150"/>
+      <c r="K150"/>
+      <c r="L150">
+        <v>4007</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="s">
+        <v>72</v>
+      </c>
+      <c r="B151" t="s">
+        <v>73</v>
+      </c>
+      <c r="C151" t="s">
+        <v>152</v>
+      </c>
+      <c r="D151">
+        <v>32</v>
+      </c>
+      <c r="E151" t="s">
+        <v>153</v>
+      </c>
+      <c r="F151" s="2">
+        <v>46266.736793981479</v>
+      </c>
+      <c r="G151" t="s">
+        <v>15</v>
+      </c>
+      <c r="H151" t="s">
+        <v>74</v>
+      </c>
+      <c r="I151">
+        <v>5000</v>
+      </c>
+      <c r="J151"/>
+      <c r="K151"/>
+      <c r="L151">
+        <v>2555</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="s">
+        <v>156</v>
+      </c>
+      <c r="B152" t="s">
+        <v>157</v>
+      </c>
+      <c r="C152" t="s">
+        <v>158</v>
+      </c>
+      <c r="D152">
+        <v>72864</v>
+      </c>
+      <c r="E152" t="s">
+        <v>159</v>
+      </c>
+      <c r="F152" s="2">
+        <v>46266.850347222222</v>
+      </c>
+      <c r="G152" t="s">
+        <v>15</v>
+      </c>
+      <c r="H152" t="s">
+        <v>16</v>
+      </c>
+      <c r="I152"/>
+      <c r="J152"/>
+      <c r="K152"/>
+      <c r="L152">
+        <v>1813</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="s">
+        <v>150</v>
+      </c>
+      <c r="B153" t="s">
+        <v>151</v>
+      </c>
+      <c r="C153" t="s">
+        <v>158</v>
+      </c>
+      <c r="D153">
+        <v>168960</v>
+      </c>
+      <c r="E153" t="s">
+        <v>159</v>
+      </c>
+      <c r="F153" s="2">
+        <v>46266.904409722221</v>
+      </c>
+      <c r="G153" t="s">
+        <v>15</v>
+      </c>
+      <c r="H153" t="s">
+        <v>16</v>
+      </c>
+      <c r="I153"/>
+      <c r="J153"/>
+      <c r="K153"/>
+      <c r="L153">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="s">
+        <v>160</v>
+      </c>
+      <c r="B154" t="s">
+        <v>161</v>
+      </c>
+      <c r="C154" t="s">
+        <v>158</v>
+      </c>
+      <c r="D154">
+        <v>51840</v>
+      </c>
+      <c r="E154" t="s">
+        <v>159</v>
+      </c>
+      <c r="F154" s="2">
+        <v>46266.850347222222</v>
+      </c>
+      <c r="G154" t="s">
+        <v>15</v>
+      </c>
+      <c r="H154" t="s">
+        <v>16</v>
+      </c>
+      <c r="I154"/>
+      <c r="J154"/>
+      <c r="K154"/>
+      <c r="L154">
+        <v>1875</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="s">
+        <v>162</v>
+      </c>
+      <c r="B155" t="s">
+        <v>163</v>
+      </c>
+      <c r="C155" t="s">
+        <v>158</v>
+      </c>
+      <c r="D155">
+        <v>364520</v>
+      </c>
+      <c r="E155" t="s">
+        <v>159</v>
+      </c>
+      <c r="F155" s="2">
+        <v>46266.80940972222</v>
+      </c>
+      <c r="G155" t="s">
+        <v>15</v>
+      </c>
+      <c r="H155" t="s">
+        <v>16</v>
+      </c>
+      <c r="I155"/>
+      <c r="J155"/>
+      <c r="K155"/>
+      <c r="L155">
+        <v>5115</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="s">
+        <v>154</v>
+      </c>
+      <c r="B156" t="s">
+        <v>155</v>
+      </c>
+      <c r="C156" t="s">
+        <v>158</v>
+      </c>
+      <c r="D156">
+        <v>211200</v>
+      </c>
+      <c r="E156" t="s">
+        <v>159</v>
+      </c>
+      <c r="F156" s="2">
+        <v>46266.904409722221</v>
+      </c>
+      <c r="G156" t="s">
+        <v>15</v>
+      </c>
+      <c r="H156" t="s">
+        <v>16</v>
+      </c>
+      <c r="I156"/>
+      <c r="J156"/>
+      <c r="K156"/>
+      <c r="L156">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="s">
+        <v>43</v>
+      </c>
+      <c r="B157" t="s">
+        <v>44</v>
+      </c>
+      <c r="C157" t="s">
+        <v>158</v>
+      </c>
+      <c r="D157">
+        <v>3319</v>
+      </c>
+      <c r="E157" t="s">
+        <v>159</v>
+      </c>
+      <c r="F157" s="2">
+        <v>46266.904409722221</v>
+      </c>
+      <c r="G157" t="s">
+        <v>15</v>
+      </c>
+      <c r="H157" t="s">
+        <v>45</v>
+      </c>
+      <c r="I157">
+        <v>440</v>
+      </c>
+      <c r="J157"/>
+      <c r="K157"/>
+      <c r="L157">
+        <v>9071</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="s">
+        <v>46</v>
+      </c>
+      <c r="B158" t="s">
+        <v>47</v>
+      </c>
+      <c r="C158" t="s">
+        <v>158</v>
+      </c>
+      <c r="D158">
+        <v>100</v>
+      </c>
+      <c r="E158" t="s">
+        <v>159</v>
+      </c>
+      <c r="F158" s="2">
+        <v>46266.80940972222</v>
+      </c>
+      <c r="G158" t="s">
+        <v>15</v>
+      </c>
+      <c r="H158" t="s">
+        <v>45</v>
+      </c>
+      <c r="I158">
+        <v>250</v>
+      </c>
+      <c r="J158"/>
+      <c r="K158"/>
+      <c r="L158">
+        <v>6362</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="s">
+        <v>64</v>
+      </c>
+      <c r="B159" t="s">
+        <v>65</v>
+      </c>
+      <c r="C159" t="s">
+        <v>158</v>
+      </c>
+      <c r="D159">
+        <v>50</v>
+      </c>
+      <c r="E159" t="s">
+        <v>159</v>
+      </c>
+      <c r="F159" s="2">
+        <v>46266.80940972222</v>
+      </c>
+      <c r="G159" t="s">
+        <v>15</v>
+      </c>
+      <c r="H159" t="s">
+        <v>45</v>
+      </c>
+      <c r="I159">
+        <v>250</v>
+      </c>
+      <c r="J159"/>
+      <c r="K159"/>
+      <c r="L159">
+        <v>5166</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="s">
+        <v>72</v>
+      </c>
+      <c r="B160" t="s">
+        <v>73</v>
+      </c>
+      <c r="C160" t="s">
+        <v>158</v>
+      </c>
+      <c r="D160">
+        <v>74</v>
+      </c>
+      <c r="E160" t="s">
+        <v>159</v>
+      </c>
+      <c r="F160" s="2">
+        <v>46266.80940972222</v>
+      </c>
+      <c r="G160" t="s">
+        <v>15</v>
+      </c>
+      <c r="H160" t="s">
+        <v>74</v>
+      </c>
+      <c r="I160">
+        <v>5000</v>
+      </c>
+      <c r="J160"/>
+      <c r="K160"/>
+      <c r="L160">
+        <v>2975</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="s">
+        <v>164</v>
+      </c>
+      <c r="B161" t="s">
+        <v>165</v>
+      </c>
+      <c r="C161" t="s">
+        <v>166</v>
+      </c>
+      <c r="D161">
+        <v>900</v>
+      </c>
+      <c r="E161" t="s">
+        <v>167</v>
+      </c>
+      <c r="F161" s="2">
+        <v>46266.768946759257</v>
+      </c>
+      <c r="G161" t="s">
+        <v>15</v>
+      </c>
+      <c r="H161" t="s">
+        <v>16</v>
+      </c>
+      <c r="I161"/>
+      <c r="J161"/>
+      <c r="K161"/>
+      <c r="L161">
+        <v>1001</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="s">
+        <v>168</v>
+      </c>
+      <c r="B162" t="s">
+        <v>169</v>
+      </c>
+      <c r="C162" t="s">
+        <v>166</v>
+      </c>
+      <c r="D162">
+        <v>900</v>
+      </c>
+      <c r="E162" t="s">
+        <v>167</v>
+      </c>
+      <c r="F162" s="2">
+        <v>46266.998935185184</v>
+      </c>
+      <c r="G162" t="s">
+        <v>15</v>
+      </c>
+      <c r="H162" t="s">
+        <v>16</v>
+      </c>
+      <c r="I162"/>
+      <c r="J162"/>
+      <c r="K162"/>
+      <c r="L162">
+        <v>1427</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="s">
+        <v>170</v>
+      </c>
+      <c r="B163" t="s">
+        <v>171</v>
+      </c>
+      <c r="C163" t="s">
+        <v>172</v>
+      </c>
+      <c r="D163">
+        <v>600</v>
+      </c>
+      <c r="E163" t="s">
+        <v>173</v>
+      </c>
+      <c r="F163" s="2">
+        <v>46266.953113425923</v>
+      </c>
+      <c r="G163" t="s">
+        <v>15</v>
+      </c>
+      <c r="H163" t="s">
+        <v>113</v>
+      </c>
+      <c r="I163">
+        <v>26880</v>
+      </c>
+      <c r="J163"/>
+      <c r="K163"/>
+      <c r="L163">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="s">
+        <v>132</v>
+      </c>
+      <c r="B164" t="s">
+        <v>133</v>
+      </c>
+      <c r="C164" t="s">
+        <v>172</v>
+      </c>
+      <c r="D164">
+        <v>800</v>
+      </c>
+      <c r="E164" t="s">
+        <v>173</v>
+      </c>
+      <c r="F164" s="2">
+        <v>46266.953113425923</v>
+      </c>
+      <c r="G164" t="s">
+        <v>15</v>
+      </c>
+      <c r="H164" t="s">
+        <v>113</v>
+      </c>
+      <c r="I164">
+        <v>793</v>
+      </c>
+      <c r="J164"/>
+      <c r="K164"/>
+      <c r="L164">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="s">
+        <v>174</v>
+      </c>
+      <c r="B165" t="s">
+        <v>175</v>
+      </c>
+      <c r="C165" t="s">
+        <v>172</v>
+      </c>
+      <c r="D165">
+        <v>6719</v>
+      </c>
+      <c r="E165" t="s">
+        <v>173</v>
+      </c>
+      <c r="F165" s="2">
+        <v>46266.953113425923</v>
+      </c>
+      <c r="G165" t="s">
+        <v>15</v>
+      </c>
+      <c r="H165" t="s">
+        <v>113</v>
+      </c>
+      <c r="I165">
+        <v>13440</v>
+      </c>
+      <c r="J165"/>
+      <c r="K165"/>
+      <c r="L165">
+        <v>2125</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="s">
+        <v>176</v>
+      </c>
+      <c r="B166" t="s">
+        <v>177</v>
+      </c>
+      <c r="C166" t="s">
+        <v>172</v>
+      </c>
+      <c r="D166">
+        <v>2240</v>
+      </c>
+      <c r="E166" t="s">
+        <v>173</v>
+      </c>
+      <c r="F166" s="2">
+        <v>46266.953113425923</v>
+      </c>
+      <c r="G166" t="s">
+        <v>15</v>
+      </c>
+      <c r="H166" t="s">
+        <v>113</v>
+      </c>
+      <c r="I166">
+        <v>13440</v>
+      </c>
+      <c r="J166"/>
+      <c r="K166"/>
+      <c r="L166">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="s">
+        <v>132</v>
+      </c>
+      <c r="B167" t="s">
+        <v>133</v>
+      </c>
+      <c r="C167" t="s">
+        <v>178</v>
+      </c>
+      <c r="D167">
+        <v>800</v>
+      </c>
+      <c r="E167" t="s">
+        <v>179</v>
+      </c>
+      <c r="F167" s="2">
+        <v>46266.728865740741</v>
+      </c>
+      <c r="G167" t="s">
+        <v>15</v>
+      </c>
+      <c r="H167" t="s">
+        <v>113</v>
+      </c>
+      <c r="I167">
+        <v>793</v>
+      </c>
+      <c r="J167"/>
+      <c r="K167"/>
+      <c r="L167">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="s">
+        <v>180</v>
+      </c>
+      <c r="B168" t="s">
+        <v>181</v>
+      </c>
+      <c r="C168" t="s">
+        <v>178</v>
+      </c>
+      <c r="D168">
+        <v>400</v>
+      </c>
+      <c r="E168" t="s">
+        <v>179</v>
+      </c>
+      <c r="F168" s="2">
+        <v>46266.802256944444</v>
+      </c>
+      <c r="G168" t="s">
+        <v>15</v>
+      </c>
+      <c r="H168" t="s">
+        <v>113</v>
+      </c>
+      <c r="I168">
+        <v>15000</v>
+      </c>
+      <c r="J168"/>
+      <c r="K168"/>
+      <c r="L168">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="s">
+        <v>182</v>
+      </c>
+      <c r="B169" t="s">
+        <v>183</v>
+      </c>
+      <c r="C169" t="s">
+        <v>178</v>
+      </c>
+      <c r="D169">
+        <v>2500</v>
+      </c>
+      <c r="E169" t="s">
+        <v>179</v>
+      </c>
+      <c r="F169" s="2">
+        <v>46266.802256944444</v>
+      </c>
+      <c r="G169" t="s">
+        <v>15</v>
+      </c>
+      <c r="H169" t="s">
+        <v>113</v>
+      </c>
+      <c r="I169">
+        <v>2500</v>
+      </c>
+      <c r="J169"/>
+      <c r="K169"/>
+      <c r="L169">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="s">
+        <v>184</v>
+      </c>
+      <c r="B170" t="s">
+        <v>185</v>
+      </c>
+      <c r="C170" t="s">
+        <v>186</v>
+      </c>
+      <c r="D170">
+        <v>400</v>
+      </c>
+      <c r="E170" t="s">
+        <v>187</v>
+      </c>
+      <c r="F170" s="2">
+        <v>45185</v>
+      </c>
+      <c r="G170" t="s">
+        <v>15</v>
+      </c>
+      <c r="H170" t="s">
+        <v>113</v>
+      </c>
+      <c r="I170">
+        <v>173</v>
+      </c>
+      <c r="J170"/>
+      <c r="K170"/>
+      <c r="L170">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="s">
+        <v>188</v>
+      </c>
+      <c r="B171" t="s">
+        <v>189</v>
+      </c>
+      <c r="C171" t="s">
+        <v>190</v>
+      </c>
+      <c r="D171">
+        <v>3220</v>
+      </c>
+      <c r="E171" t="s">
+        <v>191</v>
+      </c>
+      <c r="F171" s="2">
+        <v>46265.808981481481</v>
+      </c>
+      <c r="G171" t="s">
+        <v>15</v>
+      </c>
+      <c r="H171" t="s">
+        <v>113</v>
+      </c>
+      <c r="I171">
+        <v>49280</v>
+      </c>
+      <c r="J171"/>
+      <c r="K171"/>
+      <c r="L171">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="s">
+        <v>192</v>
+      </c>
+      <c r="B172" t="s">
+        <v>193</v>
+      </c>
+      <c r="C172" t="s">
+        <v>190</v>
+      </c>
+      <c r="D172">
+        <v>30000</v>
+      </c>
+      <c r="E172" t="s">
+        <v>191</v>
+      </c>
+      <c r="F172" s="2">
+        <v>46265.808981481481</v>
+      </c>
+      <c r="G172" t="s">
+        <v>15</v>
+      </c>
+      <c r="H172" t="s">
+        <v>113</v>
+      </c>
+      <c r="I172">
+        <v>290000</v>
+      </c>
+      <c r="J172"/>
+      <c r="K172"/>
+      <c r="L172">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="s">
+        <v>188</v>
+      </c>
+      <c r="B173" t="s">
+        <v>189</v>
+      </c>
+      <c r="C173" t="s">
+        <v>194</v>
+      </c>
+      <c r="D173">
+        <v>280</v>
+      </c>
+      <c r="E173" t="s">
+        <v>195</v>
+      </c>
+      <c r="F173" s="2">
+        <v>46266.840324074074</v>
+      </c>
+      <c r="G173" t="s">
+        <v>15</v>
+      </c>
+      <c r="H173" t="s">
+        <v>113</v>
+      </c>
+      <c r="I173">
+        <v>49280</v>
+      </c>
+      <c r="J173"/>
+      <c r="K173"/>
+      <c r="L173">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="s">
+        <v>196</v>
+      </c>
+      <c r="B174" t="s">
+        <v>197</v>
+      </c>
+      <c r="C174" t="s">
+        <v>198</v>
+      </c>
+      <c r="D174">
+        <v>1</v>
+      </c>
+      <c r="E174" t="s">
+        <v>199</v>
+      </c>
+      <c r="F174" s="2">
+        <v>46265.788981481477</v>
+      </c>
+      <c r="G174" t="s">
+        <v>15</v>
+      </c>
+      <c r="H174" t="s">
+        <v>200</v>
+      </c>
+      <c r="I174">
+        <v>12</v>
+      </c>
+      <c r="J174"/>
+      <c r="K174"/>
+      <c r="L174">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="s">
+        <v>201</v>
+      </c>
+      <c r="B175" t="s">
+        <v>202</v>
+      </c>
+      <c r="C175" t="s">
+        <v>198</v>
+      </c>
+      <c r="D175">
+        <v>1</v>
+      </c>
+      <c r="E175" t="s">
+        <v>199</v>
+      </c>
+      <c r="F175" s="2">
+        <v>46265.776967592588</v>
+      </c>
+      <c r="G175" t="s">
+        <v>15</v>
+      </c>
+      <c r="H175" t="s">
+        <v>200</v>
+      </c>
+      <c r="I175">
+        <v>45</v>
+      </c>
+      <c r="J175"/>
+      <c r="K175"/>
+      <c r="L175">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="s">
+        <v>203</v>
+      </c>
+      <c r="B176" t="s">
+        <v>204</v>
+      </c>
+      <c r="C176" t="s">
+        <v>198</v>
+      </c>
+      <c r="D176">
+        <v>1</v>
+      </c>
+      <c r="E176" t="s">
+        <v>199</v>
+      </c>
+      <c r="F176" s="2">
+        <v>46265.788981481477</v>
+      </c>
+      <c r="G176" t="s">
+        <v>15</v>
+      </c>
+      <c r="H176" t="s">
+        <v>200</v>
+      </c>
+      <c r="I176">
+        <v>60</v>
+      </c>
+      <c r="J176"/>
+      <c r="K176"/>
+      <c r="L176">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="s">
+        <v>188</v>
+      </c>
+      <c r="B177" t="s">
+        <v>189</v>
+      </c>
+      <c r="C177" t="s">
+        <v>198</v>
+      </c>
+      <c r="D177">
+        <v>280</v>
+      </c>
+      <c r="E177" t="s">
+        <v>199</v>
+      </c>
+      <c r="F177" s="2">
+        <v>46261.786122685182</v>
+      </c>
+      <c r="G177" t="s">
+        <v>15</v>
+      </c>
+      <c r="H177" t="s">
+        <v>113</v>
+      </c>
+      <c r="I177">
+        <v>49280</v>
+      </c>
+      <c r="J177"/>
+      <c r="K177"/>
+      <c r="L177">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="s">
+        <v>168</v>
+      </c>
+      <c r="B178" t="s">
+        <v>169</v>
+      </c>
+      <c r="C178" t="s">
+        <v>205</v>
+      </c>
+      <c r="D178">
+        <v>300</v>
+      </c>
+      <c r="E178" t="s">
+        <v>206</v>
+      </c>
+      <c r="F178" s="2">
+        <v>46267.281064814815</v>
+      </c>
+      <c r="G178" t="s">
+        <v>15</v>
+      </c>
+      <c r="H178" t="s">
+        <v>16</v>
+      </c>
+      <c r="I178"/>
+      <c r="J178"/>
+      <c r="K178"/>
+      <c r="L178">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="s">
+        <v>207</v>
+      </c>
+      <c r="B179" t="s">
+        <v>208</v>
+      </c>
+      <c r="C179" t="s">
+        <v>205</v>
+      </c>
+      <c r="D179">
+        <v>186</v>
+      </c>
+      <c r="E179" t="s">
+        <v>206</v>
+      </c>
+      <c r="F179" s="2">
+        <v>44946.553055555552</v>
+      </c>
+      <c r="G179" t="s">
+        <v>15</v>
+      </c>
+      <c r="H179" t="s">
+        <v>45</v>
+      </c>
+      <c r="I179">
+        <v>20</v>
+      </c>
+      <c r="J179"/>
+      <c r="K179"/>
+      <c r="L179">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="s">
+        <v>209</v>
+      </c>
+      <c r="B180" t="s">
+        <v>210</v>
+      </c>
+      <c r="C180" t="s">
+        <v>205</v>
+      </c>
+      <c r="D180">
+        <v>93</v>
+      </c>
+      <c r="E180" t="s">
+        <v>206</v>
+      </c>
+      <c r="F180" s="2">
+        <v>45777.752291666664</v>
+      </c>
+      <c r="G180" t="s">
+        <v>15</v>
+      </c>
+      <c r="H180" t="s">
+        <v>211</v>
+      </c>
+      <c r="I180">
+        <v>16</v>
+      </c>
+      <c r="J180"/>
+      <c r="K180"/>
+      <c r="L180">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="s">
+        <v>212</v>
+      </c>
+      <c r="B181" t="s">
+        <v>213</v>
+      </c>
+      <c r="C181" t="s">
+        <v>205</v>
+      </c>
+      <c r="D181">
+        <v>55</v>
+      </c>
+      <c r="E181" t="s">
+        <v>206</v>
+      </c>
+      <c r="F181" s="2">
+        <v>44426</v>
+      </c>
+      <c r="G181" t="s">
+        <v>15</v>
+      </c>
+      <c r="H181" t="s">
+        <v>74</v>
+      </c>
+      <c r="I181">
+        <v>2</v>
+      </c>
+      <c r="J181"/>
+      <c r="K181"/>
+      <c r="L181">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="s">
+        <v>214</v>
+      </c>
+      <c r="B182" t="s">
+        <v>215</v>
+      </c>
+      <c r="C182" t="s">
+        <v>216</v>
+      </c>
+      <c r="D182">
+        <v>2160</v>
+      </c>
+      <c r="E182" t="s">
+        <v>217</v>
+      </c>
+      <c r="F182" s="2">
+        <v>46265.869062499994</v>
+      </c>
+      <c r="G182" t="s">
+        <v>15</v>
+      </c>
+      <c r="H182" t="s">
+        <v>16</v>
+      </c>
+      <c r="I182"/>
+      <c r="J182"/>
+      <c r="K182"/>
+      <c r="L182">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="s">
+        <v>164</v>
+      </c>
+      <c r="B183" t="s">
+        <v>165</v>
+      </c>
+      <c r="C183" t="s">
+        <v>216</v>
+      </c>
+      <c r="D183">
+        <v>300</v>
+      </c>
+      <c r="E183" t="s">
+        <v>217</v>
+      </c>
+      <c r="F183" s="2">
+        <v>46266.533495370371</v>
+      </c>
+      <c r="G183" t="s">
+        <v>15</v>
+      </c>
+      <c r="H183" t="s">
+        <v>16</v>
+      </c>
+      <c r="I183"/>
+      <c r="J183"/>
+      <c r="K183"/>
+      <c r="L183">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="s">
+        <v>156</v>
+      </c>
+      <c r="B184" t="s">
+        <v>157</v>
+      </c>
+      <c r="C184" t="s">
+        <v>216</v>
+      </c>
+      <c r="D184">
+        <v>4608</v>
+      </c>
+      <c r="E184" t="s">
+        <v>217</v>
+      </c>
+      <c r="F184" s="2">
+        <v>46266</v>
+      </c>
+      <c r="G184" t="s">
+        <v>15</v>
+      </c>
+      <c r="H184" t="s">
+        <v>16</v>
+      </c>
+      <c r="I184"/>
+      <c r="J184"/>
+      <c r="K184"/>
+      <c r="L184">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="s">
+        <v>218</v>
+      </c>
+      <c r="B185" t="s">
+        <v>219</v>
+      </c>
+      <c r="C185" t="s">
+        <v>216</v>
+      </c>
+      <c r="D185">
+        <v>4320</v>
+      </c>
+      <c r="E185" t="s">
+        <v>217</v>
+      </c>
+      <c r="F185" s="2">
+        <v>46265.869062499994</v>
+      </c>
+      <c r="G185" t="s">
+        <v>15</v>
+      </c>
+      <c r="H185" t="s">
+        <v>16</v>
+      </c>
+      <c r="I185"/>
+      <c r="J185"/>
+      <c r="K185"/>
+      <c r="L185">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="s">
+        <v>220</v>
+      </c>
+      <c r="B186" t="s">
+        <v>221</v>
+      </c>
+      <c r="C186" t="s">
+        <v>216</v>
+      </c>
+      <c r="D186">
+        <v>720</v>
+      </c>
+      <c r="E186" t="s">
+        <v>217</v>
+      </c>
+      <c r="F186" s="2">
+        <v>46266.710902777777</v>
+      </c>
+      <c r="G186" t="s">
+        <v>15</v>
+      </c>
+      <c r="H186" t="s">
+        <v>16</v>
+      </c>
+      <c r="I186"/>
+      <c r="J186"/>
+      <c r="K186"/>
+      <c r="L186">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="s">
+        <v>222</v>
+      </c>
+      <c r="B187" t="s">
+        <v>223</v>
+      </c>
+      <c r="C187" t="s">
+        <v>216</v>
+      </c>
+      <c r="D187">
+        <v>8560</v>
+      </c>
+      <c r="E187" t="s">
+        <v>217</v>
+      </c>
+      <c r="F187" s="2">
+        <v>46266</v>
+      </c>
+      <c r="G187" t="s">
+        <v>15</v>
+      </c>
+      <c r="H187" t="s">
+        <v>16</v>
+      </c>
+      <c r="I187"/>
+      <c r="J187"/>
+      <c r="K187"/>
+      <c r="L187">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="s">
+        <v>224</v>
+      </c>
+      <c r="B188" t="s">
+        <v>225</v>
+      </c>
+      <c r="C188" t="s">
+        <v>216</v>
+      </c>
+      <c r="D188">
+        <v>12720</v>
+      </c>
+      <c r="E188" t="s">
+        <v>217</v>
+      </c>
+      <c r="F188" s="2">
+        <v>46266.6146875</v>
+      </c>
+      <c r="G188" t="s">
+        <v>15</v>
+      </c>
+      <c r="H188" t="s">
+        <v>16</v>
+      </c>
+      <c r="I188"/>
+      <c r="J188"/>
+      <c r="K188"/>
+      <c r="L188">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="s">
+        <v>226</v>
+      </c>
+      <c r="B189" t="s">
+        <v>227</v>
+      </c>
+      <c r="C189" t="s">
+        <v>216</v>
+      </c>
+      <c r="D189">
+        <v>14850</v>
+      </c>
+      <c r="E189" t="s">
+        <v>217</v>
+      </c>
+      <c r="F189" s="2">
+        <v>46266.6146875</v>
+      </c>
+      <c r="G189" t="s">
+        <v>15</v>
+      </c>
+      <c r="H189" t="s">
+        <v>16</v>
+      </c>
+      <c r="I189"/>
+      <c r="J189"/>
+      <c r="K189"/>
+      <c r="L189">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="s">
+        <v>43</v>
+      </c>
+      <c r="B190" t="s">
+        <v>44</v>
+      </c>
+      <c r="C190" t="s">
+        <v>216</v>
+      </c>
+      <c r="D190">
+        <v>154</v>
+      </c>
+      <c r="E190" t="s">
+        <v>217</v>
+      </c>
+      <c r="F190" s="2">
+        <v>46266.6146875</v>
+      </c>
+      <c r="G190" t="s">
+        <v>15</v>
+      </c>
+      <c r="H190" t="s">
+        <v>45</v>
+      </c>
+      <c r="I190">
+        <v>440</v>
+      </c>
+      <c r="J190"/>
+      <c r="K190"/>
+      <c r="L190">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="s">
+        <v>156</v>
+      </c>
+      <c r="B191" t="s">
+        <v>157</v>
+      </c>
+      <c r="C191" t="s">
+        <v>228</v>
+      </c>
+      <c r="D191">
+        <v>310176</v>
+      </c>
+      <c r="E191" t="s">
+        <v>229</v>
+      </c>
+      <c r="F191" s="2">
+        <v>46266.9621875</v>
+      </c>
+      <c r="G191" t="s">
+        <v>15</v>
+      </c>
+      <c r="H191" t="s">
+        <v>16</v>
+      </c>
+      <c r="I191"/>
+      <c r="J191"/>
+      <c r="K191"/>
+      <c r="L191">
+        <v>2286</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="s">
+        <v>150</v>
+      </c>
+      <c r="B192" t="s">
+        <v>151</v>
+      </c>
+      <c r="C192" t="s">
+        <v>228</v>
+      </c>
+      <c r="D192">
+        <v>105600</v>
+      </c>
+      <c r="E192" t="s">
+        <v>229</v>
+      </c>
+      <c r="F192" s="2">
+        <v>46267.140914351847</v>
+      </c>
+      <c r="G192" t="s">
+        <v>15</v>
+      </c>
+      <c r="H192" t="s">
+        <v>16</v>
+      </c>
+      <c r="I192"/>
+      <c r="J192"/>
+      <c r="K192"/>
+      <c r="L192">
+        <v>1771</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="s">
+        <v>154</v>
+      </c>
+      <c r="B193" t="s">
+        <v>155</v>
+      </c>
+      <c r="C193" t="s">
+        <v>228</v>
+      </c>
+      <c r="D193">
+        <v>316800</v>
+      </c>
+      <c r="E193" t="s">
+        <v>229</v>
+      </c>
+      <c r="F193" s="2">
+        <v>46266.951736111107</v>
+      </c>
+      <c r="G193" t="s">
+        <v>15</v>
+      </c>
+      <c r="H193" t="s">
+        <v>16</v>
+      </c>
+      <c r="I193"/>
+      <c r="J193"/>
+      <c r="K193"/>
+      <c r="L193">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="s">
+        <v>43</v>
+      </c>
+      <c r="B194" t="s">
+        <v>44</v>
+      </c>
+      <c r="C194" t="s">
+        <v>228</v>
+      </c>
+      <c r="D194">
+        <v>1760</v>
+      </c>
+      <c r="E194" t="s">
+        <v>229</v>
+      </c>
+      <c r="F194" s="2">
+        <v>46267.140914351847</v>
+      </c>
+      <c r="G194" t="s">
+        <v>15</v>
+      </c>
+      <c r="H194" t="s">
+        <v>45</v>
+      </c>
+      <c r="I194">
+        <v>440</v>
+      </c>
+      <c r="J194"/>
+      <c r="K194"/>
+      <c r="L194">
+        <v>4960</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="s">
+        <v>46</v>
+      </c>
+      <c r="B195" t="s">
+        <v>47</v>
+      </c>
+      <c r="C195" t="s">
+        <v>228</v>
+      </c>
+      <c r="D195">
+        <v>155</v>
+      </c>
+      <c r="E195" t="s">
+        <v>229</v>
+      </c>
+      <c r="F195" s="2">
+        <v>46267.140914351847</v>
+      </c>
+      <c r="G195" t="s">
+        <v>15</v>
+      </c>
+      <c r="H195" t="s">
+        <v>45</v>
+      </c>
+      <c r="I195">
+        <v>250</v>
+      </c>
+      <c r="J195"/>
+      <c r="K195"/>
+      <c r="L195">
+        <v>4329</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="s">
+        <v>64</v>
+      </c>
+      <c r="B196" t="s">
+        <v>65</v>
+      </c>
+      <c r="C196" t="s">
+        <v>228</v>
+      </c>
+      <c r="D196">
+        <v>38</v>
+      </c>
+      <c r="E196" t="s">
+        <v>229</v>
+      </c>
+      <c r="F196" s="2">
+        <v>46266.951736111107</v>
+      </c>
+      <c r="G196" t="s">
+        <v>15</v>
+      </c>
+      <c r="H196" t="s">
+        <v>45</v>
+      </c>
+      <c r="I196">
+        <v>250</v>
+      </c>
+      <c r="J196"/>
+      <c r="K196"/>
+      <c r="L196">
+        <v>2470</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="s">
+        <v>43</v>
+      </c>
+      <c r="B197" t="s">
+        <v>44</v>
+      </c>
+      <c r="C197" t="s">
+        <v>230</v>
+      </c>
+      <c r="D197">
+        <v>1912</v>
+      </c>
+      <c r="E197" t="s">
+        <v>231</v>
+      </c>
+      <c r="F197" s="2">
+        <v>46267.378159722219</v>
+      </c>
+      <c r="G197" t="s">
+        <v>15</v>
+      </c>
+      <c r="H197" t="s">
+        <v>45</v>
+      </c>
+      <c r="I197">
+        <v>440</v>
+      </c>
+      <c r="J197"/>
+      <c r="K197"/>
+      <c r="L197">
+        <v>3143</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="s">
+        <v>46</v>
+      </c>
+      <c r="B198" t="s">
+        <v>47</v>
+      </c>
+      <c r="C198" t="s">
+        <v>230</v>
+      </c>
+      <c r="D198">
+        <v>107</v>
+      </c>
+      <c r="E198" t="s">
+        <v>231</v>
+      </c>
+      <c r="F198" s="2">
+        <v>46267.378159722219</v>
+      </c>
+      <c r="G198" t="s">
+        <v>15</v>
+      </c>
+      <c r="H198" t="s">
+        <v>45</v>
+      </c>
+      <c r="I198">
+        <v>250</v>
+      </c>
+      <c r="J198"/>
+      <c r="K198"/>
+      <c r="L198">
+        <v>2760</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="s">
+        <v>64</v>
+      </c>
+      <c r="B199" t="s">
+        <v>65</v>
+      </c>
+      <c r="C199" t="s">
+        <v>230</v>
+      </c>
+      <c r="D199">
+        <v>63</v>
+      </c>
+      <c r="E199" t="s">
+        <v>231</v>
+      </c>
+      <c r="F199" s="2">
+        <v>46267.378159722219</v>
+      </c>
+      <c r="G199" t="s">
+        <v>15</v>
+      </c>
+      <c r="H199" t="s">
+        <v>45</v>
+      </c>
+      <c r="I199">
+        <v>250</v>
+      </c>
+      <c r="J199"/>
+      <c r="K199"/>
+      <c r="L199">
+        <v>1128</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="s">
+        <v>72</v>
+      </c>
+      <c r="B200" t="s">
+        <v>73</v>
+      </c>
+      <c r="C200" t="s">
+        <v>230</v>
+      </c>
+      <c r="D200">
+        <v>30</v>
+      </c>
+      <c r="E200" t="s">
+        <v>231</v>
+      </c>
+      <c r="F200" s="2">
+        <v>46267.3690162037</v>
+      </c>
+      <c r="G200" t="s">
+        <v>15</v>
+      </c>
+      <c r="H200" t="s">
+        <v>74</v>
+      </c>
+      <c r="I200">
+        <v>5000</v>
+      </c>
+      <c r="J200"/>
+      <c r="K200"/>
+      <c r="L200">
+        <v>1330</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="s">
+        <v>232</v>
+      </c>
+      <c r="B201" t="s">
+        <v>233</v>
+      </c>
+      <c r="C201" t="s">
+        <v>234</v>
+      </c>
+      <c r="D201">
+        <v>1000000</v>
+      </c>
+      <c r="E201" t="s">
+        <v>235</v>
+      </c>
+      <c r="F201" s="2">
+        <v>46235</v>
+      </c>
+      <c r="G201" t="s">
+        <v>236</v>
+      </c>
+      <c r="H201" t="s">
+        <v>237</v>
+      </c>
+      <c r="I201">
+        <v>1000000</v>
+      </c>
+      <c r="J201"/>
+      <c r="K201"/>
+      <c r="L201">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="s">
+        <v>238</v>
+      </c>
+      <c r="B202" t="s">
+        <v>239</v>
+      </c>
+      <c r="C202" t="s">
+        <v>240</v>
+      </c>
+      <c r="D202">
+        <v>5060000</v>
+      </c>
+      <c r="E202" t="s">
+        <v>241</v>
+      </c>
+      <c r="F202" s="2">
+        <v>46239</v>
+      </c>
+      <c r="G202" t="s">
+        <v>236</v>
+      </c>
+      <c r="H202" t="s">
+        <v>237</v>
+      </c>
+      <c r="I202">
+        <v>5060000</v>
+      </c>
+      <c r="J202"/>
+      <c r="K202"/>
+      <c r="L202">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="s">
+        <v>242</v>
+      </c>
+      <c r="B203" t="s">
+        <v>243</v>
+      </c>
+      <c r="C203" t="s">
+        <v>240</v>
+      </c>
+      <c r="D203">
+        <v>2439100</v>
+      </c>
+      <c r="E203" t="s">
+        <v>241</v>
+      </c>
+      <c r="F203" s="2">
+        <v>46235</v>
+      </c>
+      <c r="G203" t="s">
+        <v>236</v>
+      </c>
+      <c r="H203" t="s">
+        <v>237</v>
+      </c>
+      <c r="I203">
+        <v>800000</v>
+      </c>
+      <c r="J203"/>
+      <c r="K203"/>
+      <c r="L203">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="s">
+        <v>244</v>
+      </c>
+      <c r="B204" t="s">
+        <v>245</v>
+      </c>
+      <c r="C204" t="s">
+        <v>240</v>
+      </c>
+      <c r="D204">
+        <v>880000</v>
+      </c>
+      <c r="E204" t="s">
+        <v>241</v>
+      </c>
+      <c r="F204" s="2">
+        <v>46235</v>
+      </c>
+      <c r="G204" t="s">
+        <v>236</v>
+      </c>
+      <c r="H204" t="s">
+        <v>237</v>
+      </c>
+      <c r="I204">
+        <v>880000</v>
+      </c>
+      <c r="J204"/>
+      <c r="K204"/>
+      <c r="L204">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="s">
+        <v>246</v>
+      </c>
+      <c r="B205" t="s">
+        <v>247</v>
+      </c>
+      <c r="C205" t="s">
+        <v>240</v>
+      </c>
+      <c r="D205">
+        <v>104000</v>
+      </c>
+      <c r="E205" t="s">
+        <v>241</v>
+      </c>
+      <c r="F205" s="2">
+        <v>46258</v>
+      </c>
+      <c r="G205" t="s">
+        <v>236</v>
+      </c>
+      <c r="H205" t="s">
+        <v>237</v>
+      </c>
+      <c r="I205">
+        <v>52000</v>
+      </c>
+      <c r="J205"/>
+      <c r="K205"/>
+      <c r="L205">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="s">
+        <v>248</v>
+      </c>
+      <c r="B206" t="s">
+        <v>249</v>
+      </c>
+      <c r="C206" t="s">
+        <v>250</v>
+      </c>
+      <c r="D206">
+        <v>3</v>
+      </c>
+      <c r="E206" t="s">
+        <v>251</v>
+      </c>
+      <c r="F206" s="2">
+        <v>46262.311388888884</v>
+      </c>
+      <c r="G206" t="s">
+        <v>252</v>
+      </c>
+      <c r="H206" t="s">
+        <v>74</v>
+      </c>
+      <c r="I206">
+        <v>2</v>
+      </c>
+      <c r="J206"/>
+      <c r="K206"/>
+      <c r="L206">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="s">
+        <v>253</v>
+      </c>
+      <c r="B207" t="s">
+        <v>254</v>
+      </c>
+      <c r="C207" t="s">
+        <v>250</v>
+      </c>
+      <c r="D207">
+        <v>2</v>
+      </c>
+      <c r="E207" t="s">
+        <v>251</v>
+      </c>
+      <c r="F207" s="2">
+        <v>46261.675902777773</v>
+      </c>
+      <c r="G207" t="s">
+        <v>15</v>
+      </c>
+      <c r="H207" t="s">
+        <v>255</v>
+      </c>
+      <c r="I207">
+        <v>20</v>
+      </c>
+      <c r="J207"/>
+      <c r="K207"/>
+      <c r="L207">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="s">
+        <v>180</v>
+      </c>
+      <c r="B208" t="s">
+        <v>181</v>
+      </c>
+      <c r="C208" t="s">
+        <v>256</v>
+      </c>
+      <c r="D208">
+        <v>10000</v>
+      </c>
+      <c r="E208" t="s">
+        <v>257</v>
+      </c>
+      <c r="F208" s="2">
+        <v>46267.406504629631</v>
+      </c>
+      <c r="G208" t="s">
+        <v>15</v>
+      </c>
+      <c r="H208" t="s">
+        <v>113</v>
+      </c>
+      <c r="I208">
+        <v>15000</v>
+      </c>
+      <c r="J208"/>
+      <c r="K208"/>
+      <c r="L208">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="s">
+        <v>111</v>
+      </c>
+      <c r="B209" t="s">
+        <v>112</v>
+      </c>
+      <c r="C209" t="s">
+        <v>256</v>
+      </c>
+      <c r="D209">
+        <v>10000</v>
+      </c>
+      <c r="E209" t="s">
+        <v>257</v>
+      </c>
+      <c r="F209" s="2">
+        <v>46267.406504629631</v>
+      </c>
+      <c r="G209" t="s">
+        <v>15</v>
+      </c>
+      <c r="H209" t="s">
+        <v>113</v>
+      </c>
+      <c r="I209">
+        <v>60000</v>
+      </c>
+      <c r="J209"/>
+      <c r="K209"/>
+      <c r="L209">
+        <v>960</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="s">
+        <v>258</v>
+      </c>
+      <c r="B210" t="s">
+        <v>259</v>
+      </c>
+      <c r="C210" t="s">
+        <v>256</v>
+      </c>
+      <c r="D210">
+        <v>10000</v>
+      </c>
+      <c r="E210" t="s">
+        <v>257</v>
+      </c>
+      <c r="F210" s="2">
+        <v>46267.406504629631</v>
+      </c>
+      <c r="G210" t="s">
+        <v>15</v>
+      </c>
+      <c r="H210" t="s">
+        <v>113</v>
+      </c>
+      <c r="I210">
+        <v>10000</v>
+      </c>
+      <c r="J210"/>
+      <c r="K210"/>
+      <c r="L210">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="s">
+        <v>260</v>
+      </c>
+      <c r="B211" t="s">
+        <v>261</v>
+      </c>
+      <c r="C211" t="s">
+        <v>256</v>
+      </c>
+      <c r="D211">
+        <v>4200</v>
+      </c>
+      <c r="E211" t="s">
+        <v>257</v>
+      </c>
+      <c r="F211" s="2">
+        <v>46267.406504629631</v>
+      </c>
+      <c r="G211" t="s">
+        <v>15</v>
+      </c>
+      <c r="H211" t="s">
+        <v>118</v>
+      </c>
+      <c r="I211"/>
+      <c r="J211"/>
+      <c r="K211"/>
+      <c r="L211">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="s">
+        <v>140</v>
+      </c>
+      <c r="B212" t="s">
+        <v>141</v>
+      </c>
+      <c r="C212" t="s">
+        <v>256</v>
+      </c>
+      <c r="D212">
+        <v>1920</v>
+      </c>
+      <c r="E212" t="s">
+        <v>257</v>
+      </c>
+      <c r="F212" s="2">
+        <v>46267.406504629631</v>
+      </c>
+      <c r="G212" t="s">
+        <v>15</v>
+      </c>
+      <c r="H212" t="s">
+        <v>118</v>
+      </c>
+      <c r="I212"/>
+      <c r="J212"/>
+      <c r="K212"/>
+      <c r="L212">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="s">
+        <v>262</v>
+      </c>
+      <c r="B213" t="s">
+        <v>263</v>
+      </c>
+      <c r="C213" t="s">
+        <v>256</v>
+      </c>
+      <c r="D213">
+        <v>2400</v>
+      </c>
+      <c r="E213" t="s">
+        <v>257</v>
+      </c>
+      <c r="F213" s="2">
+        <v>46267.406504629631</v>
+      </c>
+      <c r="G213" t="s">
+        <v>15</v>
+      </c>
+      <c r="H213" t="s">
+        <v>118</v>
+      </c>
+      <c r="I213"/>
+      <c r="J213"/>
+      <c r="K213"/>
+      <c r="L213">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="s">
+        <v>246</v>
+      </c>
+      <c r="B214" t="s">
+        <v>247</v>
+      </c>
+      <c r="C214" t="s">
+        <v>264</v>
+      </c>
+      <c r="D214">
+        <v>104000</v>
+      </c>
+      <c r="E214" t="s">
+        <v>265</v>
+      </c>
+      <c r="F214" s="2">
+        <v>46235</v>
+      </c>
+      <c r="G214" t="s">
+        <v>236</v>
+      </c>
+      <c r="H214" t="s">
+        <v>237</v>
+      </c>
+      <c r="I214">
+        <v>52000</v>
+      </c>
+      <c r="J214"/>
+      <c r="K214"/>
+      <c r="L214">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="s">
+        <v>266</v>
+      </c>
+      <c r="B215" t="s">
+        <v>267</v>
+      </c>
+      <c r="C215" t="s">
+        <v>268</v>
+      </c>
+      <c r="D215">
+        <v>23400</v>
+      </c>
+      <c r="E215" t="s">
+        <v>269</v>
+      </c>
+      <c r="F215" s="2">
+        <v>46266</v>
+      </c>
+      <c r="G215" t="s">
+        <v>15</v>
+      </c>
+      <c r="H215" t="s">
+        <v>16</v>
+      </c>
+      <c r="I215"/>
+      <c r="J215"/>
+      <c r="K215"/>
+      <c r="L215">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="s">
+        <v>270</v>
+      </c>
+      <c r="B216" t="s">
+        <v>271</v>
+      </c>
+      <c r="C216" t="s">
+        <v>272</v>
+      </c>
+      <c r="D216">
+        <v>520</v>
+      </c>
+      <c r="E216" t="s">
+        <v>273</v>
+      </c>
+      <c r="F216" s="2">
+        <v>46265.37394675926</v>
+      </c>
+      <c r="G216" t="s">
+        <v>236</v>
+      </c>
+      <c r="H216" t="s">
+        <v>274</v>
+      </c>
+      <c r="I216">
+        <v>520</v>
+      </c>
+      <c r="J216"/>
+      <c r="K216"/>
+      <c r="L216">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="s">
+        <v>275</v>
+      </c>
+      <c r="B217" t="s">
+        <v>276</v>
+      </c>
+      <c r="C217" t="s">
+        <v>272</v>
+      </c>
+      <c r="D217">
+        <v>5000</v>
+      </c>
+      <c r="E217" t="s">
+        <v>273</v>
+      </c>
+      <c r="F217" s="2">
+        <v>46265.37394675926</v>
+      </c>
+      <c r="G217" t="s">
+        <v>236</v>
+      </c>
+      <c r="H217" t="s">
+        <v>274</v>
+      </c>
+      <c r="I217">
+        <v>5000</v>
+      </c>
+      <c r="J217"/>
+      <c r="K217"/>
+      <c r="L217">
         <v>412</v>
       </c>
     </row>

--- a/Inventarios.xlsx
+++ b/Inventarios.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheets>
-    <sheet name="Inventarios" sheetId="1" r:id="R7e08819919b54cf7"/>
+    <sheet name="Inventarios" sheetId="1" r:id="R6e6546b951ec46d1"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="243" xml:space="preserve">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="249" xml:space="preserve">
   <si>
     <t>codigo_articulo</t>
   </si>
@@ -43,21 +43,42 @@
     <t>consecutivo</t>
   </si>
   <si>
+    <t>112301</t>
+  </si>
+  <si>
+    <t>HUEVO L X 30 PET</t>
+  </si>
+  <si>
+    <t>VT1</t>
+  </si>
+  <si>
+    <t>TAT BUCARAMANGA - INVENTARIO TRANSITO</t>
+  </si>
+  <si>
+    <t>UN</t>
+  </si>
+  <si>
+    <t>HU</t>
+  </si>
+  <si>
+    <t>114357</t>
+  </si>
+  <si>
+    <t>HUEVO L X 12 PET CAJA X 120 PV.</t>
+  </si>
+  <si>
+    <t>114379</t>
+  </si>
+  <si>
+    <t>HUEVO L X 30 PET CAJA X 300 PV.</t>
+  </si>
+  <si>
     <t>142111</t>
   </si>
   <si>
     <t>BARRA DE PROTEINA 50 GR ARANDANO DISPLAY X 4 CAJA X 48</t>
   </si>
   <si>
-    <t>VT1</t>
-  </si>
-  <si>
-    <t>TAT BUCARAMANGA - INVENTARIO TRANSITO</t>
-  </si>
-  <si>
-    <t>UN</t>
-  </si>
-  <si>
     <t>BP</t>
   </si>
   <si>
@@ -73,25 +94,154 @@
     <t>HUEVO XL X 15 PET CAJA X 300.</t>
   </si>
   <si>
-    <t>VT2</t>
-  </si>
-  <si>
-    <t>TAT CALI - INVENTARIO TRANSITO</t>
-  </si>
-  <si>
-    <t>HU</t>
-  </si>
-  <si>
-    <t>114379</t>
-  </si>
-  <si>
-    <t>HUEVO L X 30 PET CAJA X 300 PV.</t>
-  </si>
-  <si>
-    <t>13421</t>
-  </si>
-  <si>
-    <t>HUEVO A X 30 CARTON GRIS AMARRADO - ALKOSTO.</t>
+    <t>VT3</t>
+  </si>
+  <si>
+    <t>TAT MEDELLIN - INVENTARIO TRANSITO</t>
+  </si>
+  <si>
+    <t>112271</t>
+  </si>
+  <si>
+    <t>HUEVO XL X 15 PET CAJA X 300 - TAT</t>
+  </si>
+  <si>
+    <t>112379</t>
+  </si>
+  <si>
+    <t>HUEVO L X 30 PET CAJA X 300</t>
+  </si>
+  <si>
+    <t>152384</t>
+  </si>
+  <si>
+    <t>HUEVO L X 15 PAGUE 14 PET CAJA X 300.</t>
+  </si>
+  <si>
+    <t>2110202</t>
+  </si>
+  <si>
+    <t>HUEVO XL X 30 CARTON VERDE CANASTA</t>
+  </si>
+  <si>
+    <t>2110217</t>
+  </si>
+  <si>
+    <t>HUEVO XL X 30 CARTON VERDE AMARRADO SIN ETIQUETA CANASTA</t>
+  </si>
+  <si>
+    <t>2110302</t>
+  </si>
+  <si>
+    <t>HUEVO L X 30 CARTON VERDE CANASTA</t>
+  </si>
+  <si>
+    <t>2110317</t>
+  </si>
+  <si>
+    <t>HUEVO L X 30 CARTON VERDE AMARRADO SIN ETIQUETA CANASTA</t>
+  </si>
+  <si>
+    <t>2110402</t>
+  </si>
+  <si>
+    <t>HUEVO M X 30 CARTON VERDE CANASTA</t>
+  </si>
+  <si>
+    <t>AFCA022</t>
+  </si>
+  <si>
+    <t>CANASTA KIKES 63  X 32 X  23</t>
+  </si>
+  <si>
+    <t>AF</t>
+  </si>
+  <si>
+    <t>AFES013</t>
+  </si>
+  <si>
+    <t>ESTIBAS OVOID 124CM X 65CM</t>
+  </si>
+  <si>
+    <t>AFSE003</t>
+  </si>
+  <si>
+    <t>SEPARADORES OVOID DE 124CM X 66CM</t>
+  </si>
+  <si>
+    <t>MDGA105</t>
+  </si>
+  <si>
+    <t>GANGHO METÁLICO LAMINA CAL14 COLD ROLLED BRAZOS 5.2CM P/CANASTA OVOID</t>
+  </si>
+  <si>
+    <t>MD</t>
+  </si>
+  <si>
+    <t>VT4</t>
+  </si>
+  <si>
+    <t>TAT BARRANQUILLA - INVENTARIO TRANSITO</t>
+  </si>
+  <si>
+    <t>2110403</t>
+  </si>
+  <si>
+    <t>HUEVO M X30 CARTON VERDE AMARRADO CANASTA</t>
+  </si>
+  <si>
+    <t>2152388</t>
+  </si>
+  <si>
+    <t>HUEVO L X 15 PAGUE 14 PET EN CANASTA.</t>
+  </si>
+  <si>
+    <t>VT41</t>
+  </si>
+  <si>
+    <t>TAT CARTAGENA - INVENTARIO TRANSITO</t>
+  </si>
+  <si>
+    <t>2110303</t>
+  </si>
+  <si>
+    <t>HUEVO L X30 CARTON VERDE AMARRADO CANASTA</t>
+  </si>
+  <si>
+    <t>VT43</t>
+  </si>
+  <si>
+    <t>TAT VALLEDUPAR - INVENTARIO TRANSITO</t>
+  </si>
+  <si>
+    <t>VT49</t>
+  </si>
+  <si>
+    <t>MONTERIA - INVENTARIO EN TRANSITO OPERADOR</t>
+  </si>
+  <si>
+    <t>VT52</t>
+  </si>
+  <si>
+    <t>TAT BOGOTA - VT52</t>
+  </si>
+  <si>
+    <t>112357</t>
+  </si>
+  <si>
+    <t>HUEVO L X 12 PET CAJA X 120</t>
+  </si>
+  <si>
+    <t>13359</t>
+  </si>
+  <si>
+    <t>HUEVO AA X 30 BAND GRIS AMARRADO ALAT CAJA X 300</t>
+  </si>
+  <si>
+    <t>13469</t>
+  </si>
+  <si>
+    <t>HUEVO A X 300 BAND GRIS CAJA AMARR EXITO.</t>
   </si>
   <si>
     <t>2010102</t>
@@ -100,28 +250,10 @@
     <t>HUEVO YUMBO X20 CARTON VERDE CANASTA.</t>
   </si>
   <si>
-    <t>2110202</t>
-  </si>
-  <si>
-    <t>HUEVO XL X 30 CARTON VERDE CANASTA</t>
-  </si>
-  <si>
-    <t>2110217</t>
-  </si>
-  <si>
-    <t>HUEVO XL X 30 CARTON VERDE AMARRADO SIN ETIQUETA CANASTA</t>
-  </si>
-  <si>
-    <t>2110302</t>
-  </si>
-  <si>
-    <t>HUEVO L X 30 CARTON VERDE CANASTA</t>
-  </si>
-  <si>
-    <t>2110317</t>
-  </si>
-  <si>
-    <t>HUEVO L X 30 CARTON VERDE AMARRADO SIN ETIQUETA CANASTA</t>
+    <t>VT59</t>
+  </si>
+  <si>
+    <t>TAT BOGOTA - VT59</t>
   </si>
   <si>
     <t>2112207</t>
@@ -130,76 +262,238 @@
     <t>HUEVO XL X 15 PET CANASTA</t>
   </si>
   <si>
-    <t>2152388</t>
-  </si>
-  <si>
-    <t>HUEVO L X 15 PAGUE 14 PET EN CANASTA.</t>
-  </si>
-  <si>
-    <t>AFCA022</t>
-  </si>
-  <si>
-    <t>CANASTA KIKES 63  X 32 X  23</t>
-  </si>
-  <si>
-    <t>AF</t>
-  </si>
-  <si>
-    <t>AFES013</t>
-  </si>
-  <si>
-    <t>ESTIBAS OVOID 124CM X 65CM</t>
-  </si>
-  <si>
-    <t>AFSE003</t>
-  </si>
-  <si>
-    <t>SEPARADORES OVOID DE 124CM X 66CM</t>
-  </si>
-  <si>
-    <t>VT3</t>
-  </si>
-  <si>
-    <t>TAT MEDELLIN - INVENTARIO TRANSITO</t>
-  </si>
-  <si>
-    <t>112271</t>
-  </si>
-  <si>
-    <t>HUEVO XL X 15 PET CAJA X 300 - TAT</t>
-  </si>
-  <si>
-    <t>112379</t>
-  </si>
-  <si>
-    <t>HUEVO L X 30 PET CAJA X 300</t>
-  </si>
-  <si>
-    <t>152384</t>
-  </si>
-  <si>
-    <t>HUEVO L X 15 PAGUE 14 PET CAJA X 300.</t>
-  </si>
-  <si>
-    <t>2110402</t>
-  </si>
-  <si>
-    <t>HUEVO M X 30 CARTON VERDE CANASTA</t>
-  </si>
-  <si>
-    <t>MDGA105</t>
-  </si>
-  <si>
-    <t>GANGHO METÁLICO LAMINA CAL14 COLD ROLLED BRAZOS 5.2CM P/CANASTA OVOID</t>
-  </si>
-  <si>
-    <t>MD</t>
-  </si>
-  <si>
-    <t>VT4</t>
-  </si>
-  <si>
-    <t>TAT BARRANQUILLA - INVENTARIO TRANSITO</t>
+    <t>VT6</t>
+  </si>
+  <si>
+    <t>TAT PASTO - INVENTARIO TRANSITO</t>
+  </si>
+  <si>
+    <t>2013322</t>
+  </si>
+  <si>
+    <t>HUEVO AA X 30 BAND GRIS AMARRADO TAPA VERDE ALAT CANASTA</t>
+  </si>
+  <si>
+    <t>VT7</t>
+  </si>
+  <si>
+    <t>TAT CUCUTA - INVENTARIO TRANSITO</t>
+  </si>
+  <si>
+    <t>2013419</t>
+  </si>
+  <si>
+    <t>HUEVO A X 30 CARTON GRIS AMARRADO SOL NACIENTE CANASTA.</t>
+  </si>
+  <si>
+    <t>EECA006</t>
+  </si>
+  <si>
+    <t>CAJA REGULAR X300 EMPAQUE PET</t>
+  </si>
+  <si>
+    <t>VTAL06</t>
+  </si>
+  <si>
+    <t>EMPAQUES ALKA 1 TRANSITO</t>
+  </si>
+  <si>
+    <t>EE</t>
+  </si>
+  <si>
+    <t>EMET014</t>
+  </si>
+  <si>
+    <t>ETIQUETA COD  BARRA HUEVO A ROJO X 30 D1</t>
+  </si>
+  <si>
+    <t>EM</t>
+  </si>
+  <si>
+    <t>PTET101</t>
+  </si>
+  <si>
+    <t>ETIQUETA PET X 15 XL</t>
+  </si>
+  <si>
+    <t>PT</t>
+  </si>
+  <si>
+    <t>13358</t>
+  </si>
+  <si>
+    <t>HUEVO AA ROJO X 288 CARTON GRIS CAJA-EN DOCENERA-SOL NACIENT.</t>
+  </si>
+  <si>
+    <t>VTBO</t>
+  </si>
+  <si>
+    <t>CENTRO DE EMPAQUES BOGOTA -INVENTARIO TRANSITO</t>
+  </si>
+  <si>
+    <t>2410401</t>
+  </si>
+  <si>
+    <t>HUEVO CE X 30 CARTON GRIS CANASTA</t>
+  </si>
+  <si>
+    <t>VTBQ</t>
+  </si>
+  <si>
+    <t>BARRANQUILLA - INVENTARIO TRANSITO</t>
+  </si>
+  <si>
+    <t>114268</t>
+  </si>
+  <si>
+    <t>HUEVO XL X 15 PET CAJA X 300 PV.</t>
+  </si>
+  <si>
+    <t>2010301</t>
+  </si>
+  <si>
+    <t>HUEVO AA X30 CARTON GRIS CANASTA.</t>
+  </si>
+  <si>
+    <t>2010501</t>
+  </si>
+  <si>
+    <t>HUEVO B X30 CARTON GRIS CANASTA.</t>
+  </si>
+  <si>
+    <t>13324</t>
+  </si>
+  <si>
+    <t>HUEVO AA X 30 BAND GRIS AMARRADO TAPA VERDE ALAT - ESTIBADO</t>
+  </si>
+  <si>
+    <t>VTCA</t>
+  </si>
+  <si>
+    <t>CENTRO DE EMPAQUES CALI-INVENTARIO TRANSITO</t>
+  </si>
+  <si>
+    <t>EMES005</t>
+  </si>
+  <si>
+    <t>ESQUINERO DE CARTON 85 X 14 CM</t>
+  </si>
+  <si>
+    <t>VTEM03</t>
+  </si>
+  <si>
+    <t>EMPAQUES MEDELLIN TRANSITO</t>
+  </si>
+  <si>
+    <t>EMTB001</t>
+  </si>
+  <si>
+    <t>TAPA PARA BANDEJA GRIS</t>
+  </si>
+  <si>
+    <t>EMTB002</t>
+  </si>
+  <si>
+    <t>TAPA PARA BANDEJA VERDE KIKES</t>
+  </si>
+  <si>
+    <t>VTEMBO</t>
+  </si>
+  <si>
+    <t>EMPAQUES BOGOTA TRANSITO</t>
+  </si>
+  <si>
+    <t>EMBA001</t>
+  </si>
+  <si>
+    <t>BANDEJA HUEVO X 30 SPCCO GRIS</t>
+  </si>
+  <si>
+    <t>VTEMBQ</t>
+  </si>
+  <si>
+    <t>EMPAQUES BARRANQUILLA TRANSITO</t>
+  </si>
+  <si>
+    <t>EMET01</t>
+  </si>
+  <si>
+    <t>ETIQUETA COD DE BARRA HUEVO M X 30 - K</t>
+  </si>
+  <si>
+    <t>EMBA006</t>
+  </si>
+  <si>
+    <t>BANDEJA HUEVO X 30 SUPERIOR O UNIVERSAL GRIS</t>
+  </si>
+  <si>
+    <t>VTEMMO</t>
+  </si>
+  <si>
+    <t>EMPAQUES MONTERIA TRANSITO</t>
+  </si>
+  <si>
+    <t>EMBA010</t>
+  </si>
+  <si>
+    <t>BANDEJA HUEVO X 30 SPCCO VERDE</t>
+  </si>
+  <si>
+    <t>EMLA002</t>
+  </si>
+  <si>
+    <t>LAMINA CARTON 60X90</t>
+  </si>
+  <si>
+    <t>VTEMT3</t>
+  </si>
+  <si>
+    <t>VIRTUAL EMPAQUE TAT MEDELLIN</t>
+  </si>
+  <si>
+    <t>VTEMT42</t>
+  </si>
+  <si>
+    <t>VIRTUAL EMPAQUE TAT SANTAMARTA</t>
+  </si>
+  <si>
+    <t>DOCL002</t>
+  </si>
+  <si>
+    <t>CAMISETA LANILLA VERDE TALLA M</t>
+  </si>
+  <si>
+    <t>VTEMT6</t>
+  </si>
+  <si>
+    <t>VIRTUAL EMPAQUE TAT PASTO</t>
+  </si>
+  <si>
+    <t>DO</t>
+  </si>
+  <si>
+    <t>DOCP003</t>
+  </si>
+  <si>
+    <t>CAMISETA POLO VERDE TALLA L</t>
+  </si>
+  <si>
+    <t>DOPJ003</t>
+  </si>
+  <si>
+    <t>PANTALON JEAN CABALLERO TALLA 32</t>
+  </si>
+  <si>
+    <t>10601</t>
+  </si>
+  <si>
+    <t>HUEVO C X30 CARTON GRIS</t>
+  </si>
+  <si>
+    <t>VTKI</t>
+  </si>
+  <si>
+    <t>BODEGA KIKES - INVENTARIO TRANSITO</t>
   </si>
   <si>
     <t>2114268</t>
@@ -208,154 +502,37 @@
     <t>HUEVO XL X 15 PET CANASTA X 180 PV</t>
   </si>
   <si>
-    <t>2114357</t>
-  </si>
-  <si>
-    <t>HUEVO L X 12 PET CANASTA X 144 PV</t>
-  </si>
-  <si>
-    <t>2114379</t>
-  </si>
-  <si>
-    <t>HUEVO L X 30 PET CANASTA X 180 PV</t>
-  </si>
-  <si>
-    <t>VT41</t>
-  </si>
-  <si>
-    <t>TAT CARTAGENA - INVENTARIO TRANSITO</t>
-  </si>
-  <si>
-    <t>114357</t>
-  </si>
-  <si>
-    <t>HUEVO L X 12 PET CAJA X 120 PV.</t>
-  </si>
-  <si>
-    <t>2110303</t>
-  </si>
-  <si>
-    <t>HUEVO L X30 CARTON VERDE AMARRADO CANASTA</t>
-  </si>
-  <si>
-    <t>VT42</t>
-  </si>
-  <si>
-    <t>TAT SANTAMARTA - INVENTARIO TRANSITO</t>
-  </si>
-  <si>
-    <t>2013561</t>
-  </si>
-  <si>
-    <t>HUEVO B X 30 BAND GRIS AMARRADO CANASTA - OLIMPICA</t>
-  </si>
-  <si>
-    <t>VT49</t>
-  </si>
-  <si>
-    <t>MONTERIA - INVENTARIO EN TRANSITO OPERADOR</t>
-  </si>
-  <si>
-    <t>VT52</t>
-  </si>
-  <si>
-    <t>TAT BOGOTA - VT52</t>
-  </si>
-  <si>
-    <t>13560</t>
-  </si>
-  <si>
-    <t>HUEVO B X 300 BANDEJA GRIS CAJA AMARRADO - OLIMPICA</t>
-  </si>
-  <si>
-    <t>152281</t>
-  </si>
-  <si>
-    <t>HUEVO XL X 15 PAGUE 14 PET CAJA X 300</t>
-  </si>
-  <si>
-    <t>VT59</t>
-  </si>
-  <si>
-    <t>TAT BOGOTA - VT59</t>
-  </si>
-  <si>
-    <t>VT6</t>
-  </si>
-  <si>
-    <t>TAT PASTO - INVENTARIO TRANSITO</t>
-  </si>
-  <si>
-    <t>VT7</t>
-  </si>
-  <si>
-    <t>TAT CUCUTA - INVENTARIO TRANSITO</t>
-  </si>
-  <si>
-    <t>2013322</t>
-  </si>
-  <si>
-    <t>HUEVO AA X 30 BAND GRIS AMARRADO TAPA VERDE ALAT CANASTA</t>
-  </si>
-  <si>
-    <t>VTBE</t>
-  </si>
-  <si>
-    <t>BODEGA BELLAVISTA - INVENTARIO TRANSITO</t>
-  </si>
-  <si>
-    <t>13358</t>
-  </si>
-  <si>
-    <t>HUEVO AA ROJO X 288 CARTON GRIS CAJA-EN DOCENERA-SOL NACIENT.</t>
-  </si>
-  <si>
-    <t>VTBO</t>
-  </si>
-  <si>
-    <t>CENTRO DE EMPAQUES BOGOTA -INVENTARIO TRANSITO</t>
-  </si>
-  <si>
-    <t>2410401</t>
-  </si>
-  <si>
-    <t>HUEVO CE X 30 CARTON GRIS CANASTA</t>
-  </si>
-  <si>
-    <t>VTBQ</t>
-  </si>
-  <si>
-    <t>BARRANQUILLA - INVENTARIO TRANSITO</t>
-  </si>
-  <si>
-    <t>2010301</t>
-  </si>
-  <si>
-    <t>HUEVO AA X30 CARTON GRIS CANASTA.</t>
-  </si>
-  <si>
-    <t>2010401</t>
-  </si>
-  <si>
-    <t>HUEVO A X30 CARTON GRIS CANASTA.</t>
-  </si>
-  <si>
-    <t>2010501</t>
-  </si>
-  <si>
-    <t>HUEVO B X30 CARTON GRIS CANASTA.</t>
-  </si>
-  <si>
-    <t>13324</t>
-  </si>
-  <si>
-    <t>HUEVO AA X 30 BAND GRIS AMARRADO TAPA VERDE ALAT - ESTIBADO</t>
-  </si>
-  <si>
-    <t>VTCA</t>
-  </si>
-  <si>
-    <t>CENTRO DE EMPAQUES CALI-INVENTARIO TRANSITO</t>
+    <t>AFES00</t>
+  </si>
+  <si>
+    <t>ESTIBA DE MADERA 120 CM X100 CM   X 9 TACOS</t>
+  </si>
+  <si>
+    <t>ENES014</t>
+  </si>
+  <si>
+    <t>ESTIBA TIPO EXPORTACION 120 CMS X 100CMS</t>
+  </si>
+  <si>
+    <t>EN</t>
+  </si>
+  <si>
+    <t>MDES002</t>
+  </si>
+  <si>
+    <t>ESTIBAS PLASTICAS</t>
+  </si>
+  <si>
+    <t>VTKIGT</t>
+  </si>
+  <si>
+    <t>BODEGA EVENTUALIDAD ALMACENAMIENTO- INVENTARIO TRA</t>
+  </si>
+  <si>
+    <t>13419</t>
+  </si>
+  <si>
+    <t>HUEVO A X 30 CARTON GRIS AMARRADO SOL NACIENTE.</t>
   </si>
   <si>
     <t>13420</t>
@@ -364,31 +541,46 @@
     <t>HUEVO A X 30 BAND GRIS AMARRADO SOL NACIENTE - ESTIBADO</t>
   </si>
   <si>
-    <t>EMES005</t>
-  </si>
-  <si>
-    <t>ESQUINERO DE CARTON 85 X 14 CM</t>
-  </si>
-  <si>
-    <t>VTEM03</t>
-  </si>
-  <si>
-    <t>EMPAQUES MEDELLIN TRANSITO</t>
-  </si>
-  <si>
-    <t>EM</t>
-  </si>
-  <si>
-    <t>EMTB001</t>
-  </si>
-  <si>
-    <t>TAPA PARA BANDEJA GRIS</t>
-  </si>
-  <si>
-    <t>EMTB002</t>
-  </si>
-  <si>
-    <t>TAPA PARA BANDEJA VERDE KIKES</t>
+    <t>13461</t>
+  </si>
+  <si>
+    <t>HUEVO A X 30 BAND GRIS AMARRADO - OLIMPICA</t>
+  </si>
+  <si>
+    <t>13561</t>
+  </si>
+  <si>
+    <t>HUEVO B X 30 BAND GRIS AMARRADO - OLIMPICA</t>
+  </si>
+  <si>
+    <t>VTLZEM</t>
+  </si>
+  <si>
+    <t>EMPAQUES LANZA TRANSITO</t>
+  </si>
+  <si>
+    <t>EMET031</t>
+  </si>
+  <si>
+    <t>ETIQUETA ADHESIVA BLANCA 100 MM X 50 MM - ZEBRA</t>
+  </si>
+  <si>
+    <t>EMET050</t>
+  </si>
+  <si>
+    <t>ETIQUETA COD BARRA HUEVO B X 30 - BUENASOS</t>
+  </si>
+  <si>
+    <t>EMET123</t>
+  </si>
+  <si>
+    <t>ETIQUETA COD DE BARRA HUEVO L X 30 - FS</t>
+  </si>
+  <si>
+    <t>EMSU001</t>
+  </si>
+  <si>
+    <t>SUJETADOR PLASTIFLECHA 8MM NYLON DOBLE TT CAJA X 10.000 UNID</t>
   </si>
   <si>
     <t>EMZU004</t>
@@ -400,201 +592,6 @@
     <t>RL</t>
   </si>
   <si>
-    <t>EMET014</t>
-  </si>
-  <si>
-    <t>ETIQUETA COD  BARRA HUEVO A ROJO X 30 D1</t>
-  </si>
-  <si>
-    <t>VTEMBO</t>
-  </si>
-  <si>
-    <t>EMPAQUES BOGOTA TRANSITO</t>
-  </si>
-  <si>
-    <t>EMSU001</t>
-  </si>
-  <si>
-    <t>SUJETADOR PLASTIFLECHA 8MM NYLON DOBLE TT CAJA X 10.000 UNID</t>
-  </si>
-  <si>
-    <t>VTEMBQ</t>
-  </si>
-  <si>
-    <t>EMPAQUES BARRANQUILLA TRANSITO</t>
-  </si>
-  <si>
-    <t>EMET01</t>
-  </si>
-  <si>
-    <t>ETIQUETA COD DE BARRA HUEVO M X 30 - K</t>
-  </si>
-  <si>
-    <t>EMBA006</t>
-  </si>
-  <si>
-    <t>BANDEJA HUEVO X 30 SUPERIOR O UNIVERSAL GRIS</t>
-  </si>
-  <si>
-    <t>VTEMMO</t>
-  </si>
-  <si>
-    <t>EMPAQUES MONTERIA TRANSITO</t>
-  </si>
-  <si>
-    <t>EMBA010</t>
-  </si>
-  <si>
-    <t>BANDEJA HUEVO X 30 SPCCO VERDE</t>
-  </si>
-  <si>
-    <t>EMLA002</t>
-  </si>
-  <si>
-    <t>LAMINA CARTON 60X90</t>
-  </si>
-  <si>
-    <t>VTEMT3</t>
-  </si>
-  <si>
-    <t>VIRTUAL EMPAQUE TAT MEDELLIN</t>
-  </si>
-  <si>
-    <t>VTEMT42</t>
-  </si>
-  <si>
-    <t>VIRTUAL EMPAQUE TAT SANTAMARTA</t>
-  </si>
-  <si>
-    <t>DOCL002</t>
-  </si>
-  <si>
-    <t>CAMISETA LANILLA VERDE TALLA M</t>
-  </si>
-  <si>
-    <t>VTEMT6</t>
-  </si>
-  <si>
-    <t>VIRTUAL EMPAQUE TAT PASTO</t>
-  </si>
-  <si>
-    <t>DO</t>
-  </si>
-  <si>
-    <t>DOCP003</t>
-  </si>
-  <si>
-    <t>CAMISETA POLO VERDE TALLA L</t>
-  </si>
-  <si>
-    <t>DOPJ003</t>
-  </si>
-  <si>
-    <t>PANTALON JEAN CABALLERO TALLA 32</t>
-  </si>
-  <si>
-    <t>VTEMT7</t>
-  </si>
-  <si>
-    <t>VIRTUAL EMPAQUE TAT CUCUTA</t>
-  </si>
-  <si>
-    <t>10601</t>
-  </si>
-  <si>
-    <t>HUEVO C X30 CARTON GRIS</t>
-  </si>
-  <si>
-    <t>VTKI</t>
-  </si>
-  <si>
-    <t>BODEGA KIKES - INVENTARIO TRANSITO</t>
-  </si>
-  <si>
-    <t>AFES00</t>
-  </si>
-  <si>
-    <t>ESTIBA DE MADERA 120 CM X100 CM   X 9 TACOS</t>
-  </si>
-  <si>
-    <t>ENES014</t>
-  </si>
-  <si>
-    <t>ESTIBA TIPO EXPORTACION 120 CMS X 100CMS</t>
-  </si>
-  <si>
-    <t>EN</t>
-  </si>
-  <si>
-    <t>MDES002</t>
-  </si>
-  <si>
-    <t>ESTIBAS PLASTICAS</t>
-  </si>
-  <si>
-    <t>VTKIGT</t>
-  </si>
-  <si>
-    <t>BODEGA EVENTUALIDAD ALMACENAMIENTO- INVENTARIO TRA</t>
-  </si>
-  <si>
-    <t>13419</t>
-  </si>
-  <si>
-    <t>HUEVO A X 30 CARTON GRIS AMARRADO SOL NACIENTE.</t>
-  </si>
-  <si>
-    <t>13457</t>
-  </si>
-  <si>
-    <t>HUEVO A ROJO X 240 CARTON GRIS CAJA AMARRADO SOL NACIENTE.</t>
-  </si>
-  <si>
-    <t>13524</t>
-  </si>
-  <si>
-    <t>HUEVO B X 240 BANDEJA GRIS CAJA AMARRADO BUENASOS.</t>
-  </si>
-  <si>
-    <t>EECA006</t>
-  </si>
-  <si>
-    <t>CAJA REGULAR X300 EMPAQUE PET</t>
-  </si>
-  <si>
-    <t>VTLZEM</t>
-  </si>
-  <si>
-    <t>EMPAQUES LANZA TRANSITO</t>
-  </si>
-  <si>
-    <t>EE</t>
-  </si>
-  <si>
-    <t>EMET031</t>
-  </si>
-  <si>
-    <t>ETIQUETA ADHESIVA BLANCA 100 MM X 50 MM - ZEBRA</t>
-  </si>
-  <si>
-    <t>EMET050</t>
-  </si>
-  <si>
-    <t>ETIQUETA COD BARRA HUEVO B X 30 - BUENASOS</t>
-  </si>
-  <si>
-    <t>EMET123</t>
-  </si>
-  <si>
-    <t>ETIQUETA COD DE BARRA HUEVO L X 30 - FS</t>
-  </si>
-  <si>
-    <t>112357</t>
-  </si>
-  <si>
-    <t>HUEVO L X 12 PET CAJA X 120</t>
-  </si>
-  <si>
     <t>VTME</t>
   </si>
   <si>
@@ -661,43 +658,64 @@
     <t>FOSFATO MONOCALCICO MCP PHOSPHEA</t>
   </si>
   <si>
+    <t>EMAG003</t>
+  </si>
+  <si>
+    <t>AGUJA LIVIANA METALICA PARA PISTOLA SUJETADORA X 5 UND</t>
+  </si>
+  <si>
+    <t>VTPL01</t>
+  </si>
+  <si>
+    <t>ALMACEN - PALMAS TRANSITO</t>
+  </si>
+  <si>
+    <t>PQ</t>
+  </si>
+  <si>
+    <t>LABO05</t>
+  </si>
+  <si>
+    <t>BOLSA  CIERRE HERMETICO 8X8 C2 ROJA CARLIXPLAST</t>
+  </si>
+  <si>
+    <t>LA</t>
+  </si>
+  <si>
     <t>MDKI027</t>
   </si>
   <si>
     <t>KIT-71 ANILLOS INTERMEDIO HIDROLAVADORA  WS-171/ W-913 / W-9</t>
   </si>
   <si>
-    <t>VTPL01</t>
-  </si>
-  <si>
-    <t>ALMACEN - PALMAS TRANSITO</t>
-  </si>
-  <si>
     <t>KI</t>
   </si>
   <si>
+    <t>UPRO005</t>
+  </si>
+  <si>
+    <t>ROTULO ADHESIVO REDONDO VERDE-AMARILLO-ROJO</t>
+  </si>
+  <si>
+    <t>UP</t>
+  </si>
+  <si>
     <t>UPTA25</t>
   </si>
   <si>
     <t>TALON. RECIBOS DE CAJA MENOR</t>
   </si>
   <si>
-    <t>UP</t>
-  </si>
-  <si>
-    <t>VTPL06</t>
-  </si>
-  <si>
-    <t>EMPAQUES PALMAS TRANSITO</t>
-  </si>
-  <si>
-    <t>MAAM033</t>
-  </si>
-  <si>
-    <t>AMARRES PLASTICOS DE 8"</t>
-  </si>
-  <si>
-    <t>MA</t>
+    <t>UPTA39</t>
+  </si>
+  <si>
+    <t>TALON. ESTACION DE SERVICIO</t>
+  </si>
+  <si>
+    <t>UPTA51</t>
+  </si>
+  <si>
+    <t>TALON. CONTROL PESO</t>
   </si>
   <si>
     <t>VTPSM</t>
@@ -841,13 +859,13 @@
         <v>13</v>
       </c>
       <c r="D2">
-        <v>480</v>
+        <v>4500</v>
       </c>
       <c r="E2" t="s">
         <v>14</v>
       </c>
       <c r="F2" s="2">
-        <v>46268.304270833331</v>
+        <v>46269.367534722223</v>
       </c>
       <c r="G2" t="s">
         <v>15</v>
@@ -859,7 +877,7 @@
       <c r="J2"/>
       <c r="K2"/>
       <c r="L2">
-        <v>19</v>
+        <v>182</v>
       </c>
     </row>
     <row r="3">
@@ -873,13 +891,13 @@
         <v>13</v>
       </c>
       <c r="D3">
-        <v>720</v>
+        <v>120</v>
       </c>
       <c r="E3" t="s">
         <v>14</v>
       </c>
       <c r="F3" s="2">
-        <v>46268.304270833331</v>
+        <v>46269.354363425926</v>
       </c>
       <c r="G3" t="s">
         <v>15</v>
@@ -891,7 +909,7 @@
       <c r="J3"/>
       <c r="K3"/>
       <c r="L3">
-        <v>19</v>
+        <v>595</v>
       </c>
     </row>
     <row r="4">
@@ -902,48 +920,48 @@
         <v>20</v>
       </c>
       <c r="C4" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="D4">
-        <v>3000</v>
+        <v>900</v>
       </c>
       <c r="E4" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="F4" s="2">
-        <v>46267.956423611111</v>
+        <v>46269.354363425926</v>
       </c>
       <c r="G4" t="s">
         <v>15</v>
       </c>
       <c r="H4" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="I4"/>
       <c r="J4"/>
       <c r="K4"/>
       <c r="L4">
-        <v>2159</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B5" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C5" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="D5">
-        <v>11400</v>
+        <v>480</v>
       </c>
       <c r="E5" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="F5" s="2">
-        <v>46267.702060185184</v>
+        <v>46268.304270833331</v>
       </c>
       <c r="G5" t="s">
         <v>15</v>
@@ -955,27 +973,27 @@
       <c r="J5"/>
       <c r="K5"/>
       <c r="L5">
-        <v>1052</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="D6">
-        <v>41400</v>
+        <v>720</v>
       </c>
       <c r="E6" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="F6" s="2">
-        <v>46267.702060185184</v>
+        <v>46268.304270833331</v>
       </c>
       <c r="G6" t="s">
         <v>15</v>
@@ -987,39 +1005,39 @@
       <c r="J6"/>
       <c r="K6"/>
       <c r="L6">
-        <v>298</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
+        <v>26</v>
+      </c>
+      <c r="B7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" t="s">
         <v>28</v>
       </c>
-      <c r="B7" t="s">
+      <c r="D7">
+        <v>18000</v>
+      </c>
+      <c r="E7" t="s">
         <v>29</v>
       </c>
-      <c r="C7" t="s">
-        <v>21</v>
-      </c>
-      <c r="D7">
-        <v>4320</v>
-      </c>
-      <c r="E7" t="s">
-        <v>22</v>
-      </c>
       <c r="F7" s="2">
-        <v>46267.956423611111</v>
+        <v>46268.971550925926</v>
       </c>
       <c r="G7" t="s">
         <v>15</v>
       </c>
       <c r="H7" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="I7"/>
       <c r="J7"/>
       <c r="K7"/>
       <c r="L7">
-        <v>1435</v>
+        <v>2925</v>
       </c>
     </row>
     <row r="8">
@@ -1030,28 +1048,28 @@
         <v>31</v>
       </c>
       <c r="C8" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="D8">
-        <v>222480</v>
+        <v>9000</v>
       </c>
       <c r="E8" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="F8" s="2">
-        <v>46267</v>
+        <v>46268.971550925926</v>
       </c>
       <c r="G8" t="s">
         <v>15</v>
       </c>
       <c r="H8" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="I8"/>
       <c r="J8"/>
       <c r="K8"/>
       <c r="L8">
-        <v>2220</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="9">
@@ -1062,28 +1080,28 @@
         <v>33</v>
       </c>
       <c r="C9" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="D9">
-        <v>21120</v>
+        <v>18000</v>
       </c>
       <c r="E9" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="F9" s="2">
-        <v>46267.956423611111</v>
+        <v>46268.971550925926</v>
       </c>
       <c r="G9" t="s">
         <v>15</v>
       </c>
       <c r="H9" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="I9"/>
       <c r="J9"/>
       <c r="K9"/>
       <c r="L9">
-        <v>641</v>
+        <v>2699</v>
       </c>
     </row>
     <row r="10">
@@ -1094,28 +1112,28 @@
         <v>35</v>
       </c>
       <c r="C10" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="D10">
-        <v>34560</v>
+        <v>6000</v>
       </c>
       <c r="E10" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="F10" s="2">
-        <v>46267.956423611111</v>
+        <v>46268.971550925926</v>
       </c>
       <c r="G10" t="s">
         <v>15</v>
       </c>
       <c r="H10" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="I10"/>
       <c r="J10"/>
       <c r="K10"/>
       <c r="L10">
-        <v>2035</v>
+        <v>1623</v>
       </c>
     </row>
     <row r="11">
@@ -1126,28 +1144,28 @@
         <v>37</v>
       </c>
       <c r="C11" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="D11">
-        <v>3960</v>
+        <v>182160</v>
       </c>
       <c r="E11" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="F11" s="2">
-        <v>46267.956423611111</v>
+        <v>46268.971550925926</v>
       </c>
       <c r="G11" t="s">
         <v>15</v>
       </c>
       <c r="H11" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="I11"/>
       <c r="J11"/>
       <c r="K11"/>
       <c r="L11">
-        <v>781</v>
+        <v>2872</v>
       </c>
     </row>
     <row r="12">
@@ -1158,28 +1176,28 @@
         <v>39</v>
       </c>
       <c r="C12" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="D12">
-        <v>3960</v>
+        <v>15840</v>
       </c>
       <c r="E12" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="F12" s="2">
-        <v>46267.956423611111</v>
+        <v>46268.971550925926</v>
       </c>
       <c r="G12" t="s">
         <v>15</v>
       </c>
       <c r="H12" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="I12"/>
       <c r="J12"/>
       <c r="K12"/>
       <c r="L12">
-        <v>271</v>
+        <v>811</v>
       </c>
     </row>
     <row r="13">
@@ -1190,28 +1208,28 @@
         <v>41</v>
       </c>
       <c r="C13" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="D13">
-        <v>1800</v>
+        <v>42240</v>
       </c>
       <c r="E13" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="F13" s="2">
-        <v>46267.956423611111</v>
+        <v>46268.666701388887</v>
       </c>
       <c r="G13" t="s">
         <v>15</v>
       </c>
       <c r="H13" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="I13"/>
       <c r="J13"/>
       <c r="K13"/>
       <c r="L13">
-        <v>389</v>
+        <v>2389</v>
       </c>
     </row>
     <row r="14">
@@ -1222,130 +1240,128 @@
         <v>43</v>
       </c>
       <c r="C14" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="D14">
-        <v>1646</v>
+        <v>3960</v>
       </c>
       <c r="E14" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="F14" s="2">
-        <v>46267</v>
+        <v>46268.971550925926</v>
       </c>
       <c r="G14" t="s">
         <v>15</v>
       </c>
       <c r="H14" t="s">
-        <v>44</v>
-      </c>
-      <c r="I14">
-        <v>440</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="I14"/>
       <c r="J14"/>
       <c r="K14"/>
       <c r="L14">
-        <v>3250</v>
+        <v>839</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
+        <v>44</v>
+      </c>
+      <c r="B15" t="s">
         <v>45</v>
       </c>
-      <c r="B15" t="s">
-        <v>46</v>
-      </c>
       <c r="C15" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="D15">
-        <v>60</v>
+        <v>21120</v>
       </c>
       <c r="E15" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="F15" s="2">
-        <v>46267</v>
+        <v>46268.971550925926</v>
       </c>
       <c r="G15" t="s">
         <v>15</v>
       </c>
       <c r="H15" t="s">
-        <v>44</v>
-      </c>
-      <c r="I15">
-        <v>250</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="I15"/>
       <c r="J15"/>
       <c r="K15"/>
       <c r="L15">
-        <v>2810</v>
+        <v>1621</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
+        <v>46</v>
+      </c>
+      <c r="B16" t="s">
         <v>47</v>
       </c>
-      <c r="B16" t="s">
+      <c r="C16" t="s">
+        <v>28</v>
+      </c>
+      <c r="D16">
+        <v>1430</v>
+      </c>
+      <c r="E16" t="s">
+        <v>29</v>
+      </c>
+      <c r="F16" s="2">
+        <v>46268.971550925926</v>
+      </c>
+      <c r="G16" t="s">
+        <v>15</v>
+      </c>
+      <c r="H16" t="s">
         <v>48</v>
       </c>
-      <c r="C16" t="s">
-        <v>21</v>
-      </c>
-      <c r="D16">
-        <v>18</v>
-      </c>
-      <c r="E16" t="s">
-        <v>22</v>
-      </c>
-      <c r="F16" s="2">
-        <v>46267.956423611111</v>
-      </c>
-      <c r="G16" t="s">
-        <v>15</v>
-      </c>
-      <c r="H16" t="s">
-        <v>44</v>
-      </c>
       <c r="I16">
-        <v>250</v>
+        <v>440</v>
       </c>
       <c r="J16"/>
       <c r="K16"/>
       <c r="L16">
-        <v>291</v>
+        <v>4170</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>19</v>
+        <v>49</v>
       </c>
       <c r="B17" t="s">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="C17" t="s">
-        <v>49</v>
+        <v>28</v>
       </c>
       <c r="D17">
-        <v>21000</v>
+        <v>72</v>
       </c>
       <c r="E17" t="s">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="F17" s="2">
-        <v>46267</v>
+        <v>46268.971550925926</v>
       </c>
       <c r="G17" t="s">
         <v>15</v>
       </c>
       <c r="H17" t="s">
-        <v>23</v>
-      </c>
-      <c r="I17"/>
+        <v>48</v>
+      </c>
+      <c r="I17">
+        <v>250</v>
+      </c>
       <c r="J17"/>
       <c r="K17"/>
       <c r="L17">
-        <v>2923</v>
+        <v>3629</v>
       </c>
     </row>
     <row r="18">
@@ -1356,28 +1372,30 @@
         <v>52</v>
       </c>
       <c r="C18" t="s">
-        <v>49</v>
+        <v>28</v>
       </c>
       <c r="D18">
-        <v>6000</v>
+        <v>34</v>
       </c>
       <c r="E18" t="s">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="F18" s="2">
-        <v>46267</v>
+        <v>46268.971550925926</v>
       </c>
       <c r="G18" t="s">
         <v>15</v>
       </c>
       <c r="H18" t="s">
-        <v>23</v>
-      </c>
-      <c r="I18"/>
+        <v>48</v>
+      </c>
+      <c r="I18">
+        <v>250</v>
+      </c>
       <c r="J18"/>
       <c r="K18"/>
       <c r="L18">
-        <v>1095</v>
+        <v>2443</v>
       </c>
     </row>
     <row r="19">
@@ -1388,314 +1406,314 @@
         <v>54</v>
       </c>
       <c r="C19" t="s">
-        <v>49</v>
+        <v>28</v>
       </c>
       <c r="D19">
-        <v>33000</v>
+        <v>68</v>
       </c>
       <c r="E19" t="s">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="F19" s="2">
-        <v>46267</v>
+        <v>46268.971550925926</v>
       </c>
       <c r="G19" t="s">
         <v>15</v>
       </c>
       <c r="H19" t="s">
-        <v>23</v>
-      </c>
-      <c r="I19"/>
+        <v>55</v>
+      </c>
+      <c r="I19">
+        <v>5000</v>
+      </c>
       <c r="J19"/>
       <c r="K19"/>
       <c r="L19">
-        <v>2697</v>
+        <v>2501</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>55</v>
+        <v>26</v>
       </c>
       <c r="B20" t="s">
+        <v>27</v>
+      </c>
+      <c r="C20" t="s">
         <v>56</v>
       </c>
-      <c r="C20" t="s">
-        <v>49</v>
-      </c>
       <c r="D20">
-        <v>9000</v>
+        <v>3600</v>
       </c>
       <c r="E20" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="F20" s="2">
-        <v>46267</v>
+        <v>46268.933564814812</v>
       </c>
       <c r="G20" t="s">
         <v>15</v>
       </c>
       <c r="H20" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="I20"/>
       <c r="J20"/>
       <c r="K20"/>
       <c r="L20">
-        <v>1621</v>
+        <v>638</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="B21" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="C21" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="D21">
-        <v>5280</v>
+        <v>5400</v>
       </c>
       <c r="E21" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="F21" s="2">
-        <v>46267</v>
+        <v>46268.933564814812</v>
       </c>
       <c r="G21" t="s">
         <v>15</v>
       </c>
       <c r="H21" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="I21"/>
       <c r="J21"/>
       <c r="K21"/>
       <c r="L21">
-        <v>505</v>
+        <v>618</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="B22" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="C22" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="D22">
-        <v>181260</v>
+        <v>211680</v>
       </c>
       <c r="E22" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="F22" s="2">
-        <v>46268.146782407406</v>
+        <v>46268.968541666662</v>
       </c>
       <c r="G22" t="s">
         <v>15</v>
       </c>
       <c r="H22" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="I22"/>
       <c r="J22"/>
       <c r="K22"/>
       <c r="L22">
-        <v>2868</v>
+        <v>2047</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="B23" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="C23" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="D23">
-        <v>21120</v>
+        <v>3960</v>
       </c>
       <c r="E23" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="F23" s="2">
-        <v>46267</v>
+        <v>46267.836053240739</v>
       </c>
       <c r="G23" t="s">
         <v>15</v>
       </c>
       <c r="H23" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="I23"/>
       <c r="J23"/>
       <c r="K23"/>
       <c r="L23">
-        <v>809</v>
+        <v>431</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="B24" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="C24" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="D24">
-        <v>1800</v>
+        <v>501120</v>
       </c>
       <c r="E24" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="F24" s="2">
-        <v>46267</v>
+        <v>46268.933564814812</v>
       </c>
       <c r="G24" t="s">
         <v>15</v>
       </c>
       <c r="H24" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="I24"/>
       <c r="J24"/>
       <c r="K24"/>
       <c r="L24">
-        <v>837</v>
+        <v>2739</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
+        <v>58</v>
+      </c>
+      <c r="B25" t="s">
+        <v>59</v>
+      </c>
+      <c r="C25" t="s">
+        <v>56</v>
+      </c>
+      <c r="D25">
+        <v>7920</v>
+      </c>
+      <c r="E25" t="s">
         <v>57</v>
       </c>
-      <c r="B25" t="s">
-        <v>58</v>
-      </c>
-      <c r="C25" t="s">
-        <v>49</v>
-      </c>
-      <c r="D25">
-        <v>10560</v>
-      </c>
-      <c r="E25" t="s">
-        <v>50</v>
-      </c>
       <c r="F25" s="2">
-        <v>46267</v>
+        <v>46268.933564814812</v>
       </c>
       <c r="G25" t="s">
         <v>15</v>
       </c>
       <c r="H25" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="I25"/>
       <c r="J25"/>
       <c r="K25"/>
       <c r="L25">
-        <v>1619</v>
+        <v>663</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="B26" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="C26" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="D26">
-        <v>1281</v>
+        <v>27720</v>
       </c>
       <c r="E26" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="F26" s="2">
-        <v>46268.146782407406</v>
+        <v>46268.933564814812</v>
       </c>
       <c r="G26" t="s">
         <v>15</v>
       </c>
       <c r="H26" t="s">
-        <v>44</v>
-      </c>
-      <c r="I26">
-        <v>440</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="I26"/>
       <c r="J26"/>
       <c r="K26"/>
       <c r="L26">
-        <v>4164</v>
+        <v>481</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B27" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C27" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="D27">
-        <v>50</v>
+        <v>3190</v>
       </c>
       <c r="E27" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="F27" s="2">
-        <v>46268.146782407406</v>
+        <v>46268.968541666662</v>
       </c>
       <c r="G27" t="s">
         <v>15</v>
       </c>
       <c r="H27" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="I27">
-        <v>250</v>
+        <v>440</v>
       </c>
       <c r="J27"/>
       <c r="K27"/>
       <c r="L27">
-        <v>3624</v>
+        <v>3415</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B28" t="s">
+        <v>50</v>
+      </c>
+      <c r="C28" t="s">
+        <v>56</v>
+      </c>
+      <c r="D28">
+        <v>205</v>
+      </c>
+      <c r="E28" t="s">
+        <v>57</v>
+      </c>
+      <c r="F28" s="2">
+        <v>46268.968541666662</v>
+      </c>
+      <c r="G28" t="s">
+        <v>15</v>
+      </c>
+      <c r="H28" t="s">
         <v>48</v>
-      </c>
-      <c r="C28" t="s">
-        <v>49</v>
-      </c>
-      <c r="D28">
-        <v>16</v>
-      </c>
-      <c r="E28" t="s">
-        <v>50</v>
-      </c>
-      <c r="F28" s="2">
-        <v>46267</v>
-      </c>
-      <c r="G28" t="s">
-        <v>15</v>
-      </c>
-      <c r="H28" t="s">
-        <v>44</v>
       </c>
       <c r="I28">
         <v>250</v>
@@ -1703,953 +1721,961 @@
       <c r="J28"/>
       <c r="K28"/>
       <c r="L28">
-        <v>2439</v>
+        <v>2676</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="B29" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="C29" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="D29">
-        <v>32</v>
+        <v>98</v>
       </c>
       <c r="E29" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="F29" s="2">
-        <v>46267</v>
+        <v>46268.968541666662</v>
       </c>
       <c r="G29" t="s">
         <v>15</v>
       </c>
       <c r="H29" t="s">
-        <v>61</v>
+        <v>48</v>
       </c>
       <c r="I29">
-        <v>5000</v>
+        <v>250</v>
       </c>
       <c r="J29"/>
       <c r="K29"/>
       <c r="L29">
-        <v>2499</v>
+        <v>2035</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>19</v>
+        <v>53</v>
       </c>
       <c r="B30" t="s">
-        <v>20</v>
+        <v>54</v>
       </c>
       <c r="C30" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D30">
-        <v>1800</v>
+        <v>68</v>
       </c>
       <c r="E30" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="F30" s="2">
-        <v>46267.836053240739</v>
+        <v>46268.968541666662</v>
       </c>
       <c r="G30" t="s">
         <v>15</v>
       </c>
       <c r="H30" t="s">
-        <v>23</v>
-      </c>
-      <c r="I30"/>
+        <v>55</v>
+      </c>
+      <c r="I30">
+        <v>5000</v>
+      </c>
       <c r="J30"/>
       <c r="K30"/>
       <c r="L30">
-        <v>637</v>
+        <v>2132</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>53</v>
+        <v>32</v>
       </c>
       <c r="B31" t="s">
-        <v>54</v>
+        <v>33</v>
       </c>
       <c r="C31" t="s">
         <v>62</v>
       </c>
       <c r="D31">
-        <v>2700</v>
+        <v>9000</v>
       </c>
       <c r="E31" t="s">
         <v>63</v>
       </c>
       <c r="F31" s="2">
-        <v>46267.836053240739</v>
+        <v>46267.90347222222</v>
       </c>
       <c r="G31" t="s">
         <v>15</v>
       </c>
       <c r="H31" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="I31"/>
       <c r="J31"/>
       <c r="K31"/>
       <c r="L31">
-        <v>617</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="B32" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="C32" t="s">
         <v>62</v>
       </c>
       <c r="D32">
-        <v>254880</v>
+        <v>52800</v>
       </c>
       <c r="E32" t="s">
         <v>63</v>
       </c>
       <c r="F32" s="2">
-        <v>46267.836053240739</v>
+        <v>46267.90347222222</v>
       </c>
       <c r="G32" t="s">
         <v>15</v>
       </c>
       <c r="H32" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="I32"/>
       <c r="J32"/>
       <c r="K32"/>
       <c r="L32">
-        <v>2044</v>
+        <v>785</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>36</v>
+        <v>64</v>
       </c>
       <c r="B33" t="s">
-        <v>37</v>
+        <v>65</v>
       </c>
       <c r="C33" t="s">
         <v>62</v>
       </c>
       <c r="D33">
-        <v>3960</v>
+        <v>7920</v>
       </c>
       <c r="E33" t="s">
         <v>63</v>
       </c>
       <c r="F33" s="2">
-        <v>46267.836053240739</v>
+        <v>46267.90347222222</v>
       </c>
       <c r="G33" t="s">
         <v>15</v>
       </c>
       <c r="H33" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="I33"/>
       <c r="J33"/>
       <c r="K33"/>
       <c r="L33">
-        <v>431</v>
+        <v>505</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="B34" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="C34" t="s">
         <v>62</v>
       </c>
       <c r="D34">
-        <v>574080</v>
+        <v>525360</v>
       </c>
       <c r="E34" t="s">
         <v>63</v>
       </c>
       <c r="F34" s="2">
-        <v>46267.986909722218</v>
+        <v>46269.269594907404</v>
       </c>
       <c r="G34" t="s">
         <v>15</v>
       </c>
       <c r="H34" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="I34"/>
       <c r="J34"/>
       <c r="K34"/>
       <c r="L34">
-        <v>2735</v>
+        <v>3179</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="B35" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="C35" t="s">
         <v>62</v>
       </c>
       <c r="D35">
-        <v>1800</v>
+        <v>23760</v>
       </c>
       <c r="E35" t="s">
         <v>63</v>
       </c>
       <c r="F35" s="2">
-        <v>46267.839490740742</v>
+        <v>46267.90347222222</v>
       </c>
       <c r="G35" t="s">
         <v>15</v>
       </c>
       <c r="H35" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="I35"/>
       <c r="J35"/>
       <c r="K35"/>
       <c r="L35">
-        <v>63</v>
+        <v>311</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>66</v>
+        <v>46</v>
       </c>
       <c r="B36" t="s">
-        <v>67</v>
+        <v>47</v>
       </c>
       <c r="C36" t="s">
         <v>62</v>
       </c>
       <c r="D36">
-        <v>864</v>
+        <v>2585</v>
       </c>
       <c r="E36" t="s">
         <v>63</v>
       </c>
       <c r="F36" s="2">
-        <v>46267.839490740742</v>
+        <v>46269.269594907404</v>
       </c>
       <c r="G36" t="s">
         <v>15</v>
       </c>
       <c r="H36" t="s">
-        <v>23</v>
-      </c>
-      <c r="I36"/>
+        <v>48</v>
+      </c>
+      <c r="I36">
+        <v>440</v>
+      </c>
       <c r="J36"/>
       <c r="K36"/>
       <c r="L36">
-        <v>63</v>
+        <v>4007</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>68</v>
+        <v>49</v>
       </c>
       <c r="B37" t="s">
-        <v>69</v>
+        <v>50</v>
       </c>
       <c r="C37" t="s">
         <v>62</v>
       </c>
       <c r="D37">
-        <v>6300</v>
+        <v>126</v>
       </c>
       <c r="E37" t="s">
         <v>63</v>
       </c>
       <c r="F37" s="2">
-        <v>46267.839490740742</v>
+        <v>46269.269594907404</v>
       </c>
       <c r="G37" t="s">
         <v>15</v>
       </c>
       <c r="H37" t="s">
-        <v>23</v>
-      </c>
-      <c r="I37"/>
+        <v>48</v>
+      </c>
+      <c r="I37">
+        <v>250</v>
+      </c>
       <c r="J37"/>
       <c r="K37"/>
       <c r="L37">
-        <v>61</v>
+        <v>3095</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="B38" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="C38" t="s">
         <v>62</v>
       </c>
       <c r="D38">
-        <v>15840</v>
+        <v>62</v>
       </c>
       <c r="E38" t="s">
         <v>63</v>
       </c>
       <c r="F38" s="2">
-        <v>46268.24083333333</v>
+        <v>46268.754050925927</v>
       </c>
       <c r="G38" t="s">
         <v>15</v>
       </c>
       <c r="H38" t="s">
-        <v>23</v>
-      </c>
-      <c r="I38"/>
+        <v>48</v>
+      </c>
+      <c r="I38">
+        <v>250</v>
+      </c>
       <c r="J38"/>
       <c r="K38"/>
       <c r="L38">
-        <v>480</v>
+        <v>1753</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="B39" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="C39" t="s">
         <v>62</v>
       </c>
       <c r="D39">
-        <v>3615</v>
+        <v>54</v>
       </c>
       <c r="E39" t="s">
         <v>63</v>
       </c>
       <c r="F39" s="2">
-        <v>46268.24083333333</v>
+        <v>46269.269594907404</v>
       </c>
       <c r="G39" t="s">
         <v>15</v>
       </c>
       <c r="H39" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="I39">
-        <v>440</v>
+        <v>5000</v>
       </c>
       <c r="J39"/>
       <c r="K39"/>
       <c r="L39">
-        <v>3408</v>
+        <v>2126</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
+        <v>44</v>
+      </c>
+      <c r="B40" t="s">
         <v>45</v>
       </c>
-      <c r="B40" t="s">
-        <v>46</v>
-      </c>
       <c r="C40" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="D40">
-        <v>234</v>
+        <v>213840</v>
       </c>
       <c r="E40" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="F40" s="2">
-        <v>46267.986909722218</v>
+        <v>46268.602719907409</v>
       </c>
       <c r="G40" t="s">
         <v>15</v>
       </c>
       <c r="H40" t="s">
-        <v>44</v>
-      </c>
-      <c r="I40">
-        <v>250</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="I40"/>
       <c r="J40"/>
       <c r="K40"/>
       <c r="L40">
-        <v>2670</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="B41" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="C41" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="D41">
-        <v>91</v>
+        <v>2700</v>
       </c>
       <c r="E41" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="F41" s="2">
-        <v>46267.986909722218</v>
+        <v>46268.602719907409</v>
       </c>
       <c r="G41" t="s">
         <v>15</v>
       </c>
       <c r="H41" t="s">
-        <v>44</v>
-      </c>
-      <c r="I41">
-        <v>250</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="I41"/>
       <c r="J41"/>
       <c r="K41"/>
       <c r="L41">
-        <v>2031</v>
+        <v>227</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>59</v>
+        <v>46</v>
       </c>
       <c r="B42" t="s">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="C42" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="D42">
-        <v>70</v>
+        <v>906</v>
       </c>
       <c r="E42" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="F42" s="2">
-        <v>46267.986909722218</v>
+        <v>46268.602719907409</v>
       </c>
       <c r="G42" t="s">
         <v>15</v>
       </c>
       <c r="H42" t="s">
-        <v>61</v>
+        <v>48</v>
       </c>
       <c r="I42">
-        <v>5000</v>
+        <v>440</v>
       </c>
       <c r="J42"/>
       <c r="K42"/>
       <c r="L42">
-        <v>2129</v>
+        <v>1443</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="B43" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="C43" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="D43">
-        <v>9000</v>
+        <v>48</v>
       </c>
       <c r="E43" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="F43" s="2">
-        <v>46267.90347222222</v>
+        <v>46268.602719907409</v>
       </c>
       <c r="G43" t="s">
         <v>15</v>
       </c>
       <c r="H43" t="s">
-        <v>23</v>
-      </c>
-      <c r="I43"/>
+        <v>48</v>
+      </c>
+      <c r="I43">
+        <v>250</v>
+      </c>
       <c r="J43"/>
       <c r="K43"/>
       <c r="L43">
-        <v>1185</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>72</v>
+        <v>51</v>
       </c>
       <c r="B44" t="s">
-        <v>73</v>
+        <v>52</v>
       </c>
       <c r="C44" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="D44">
-        <v>120</v>
+        <v>24</v>
       </c>
       <c r="E44" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="F44" s="2">
-        <v>46268.3452662037</v>
+        <v>46268.602719907409</v>
       </c>
       <c r="G44" t="s">
         <v>15</v>
       </c>
       <c r="H44" t="s">
-        <v>23</v>
-      </c>
-      <c r="I44"/>
+        <v>48</v>
+      </c>
+      <c r="I44">
+        <v>250</v>
+      </c>
       <c r="J44"/>
       <c r="K44"/>
       <c r="L44">
-        <v>609</v>
+        <v>155</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="B45" t="s">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="C45" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D45">
-        <v>600</v>
+        <v>10560</v>
       </c>
       <c r="E45" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F45" s="2">
-        <v>46268.3452662037</v>
+        <v>46267</v>
       </c>
       <c r="G45" t="s">
         <v>15</v>
       </c>
       <c r="H45" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="I45"/>
       <c r="J45"/>
       <c r="K45"/>
       <c r="L45">
-        <v>1026</v>
+        <v>443</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="C46" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D46">
-        <v>52800</v>
+        <v>416640</v>
       </c>
       <c r="E46" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F46" s="2">
-        <v>46267.90347222222</v>
+        <v>46268</v>
       </c>
       <c r="G46" t="s">
         <v>15</v>
       </c>
       <c r="H46" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="I46"/>
       <c r="J46"/>
       <c r="K46"/>
       <c r="L46">
-        <v>785</v>
+        <v>911</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="B47" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="C47" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D47">
-        <v>7920</v>
+        <v>1800</v>
       </c>
       <c r="E47" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F47" s="2">
-        <v>46267.90347222222</v>
+        <v>46267</v>
       </c>
       <c r="G47" t="s">
         <v>15</v>
       </c>
       <c r="H47" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="I47"/>
       <c r="J47"/>
       <c r="K47"/>
       <c r="L47">
-        <v>505</v>
+        <v>95</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="B48" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="C48" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D48">
-        <v>379440</v>
+        <v>1790</v>
       </c>
       <c r="E48" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F48" s="2">
-        <v>46267.90347222222</v>
+        <v>46268</v>
       </c>
       <c r="G48" t="s">
         <v>15</v>
       </c>
       <c r="H48" t="s">
-        <v>23</v>
-      </c>
-      <c r="I48"/>
+        <v>48</v>
+      </c>
+      <c r="I48">
+        <v>440</v>
+      </c>
       <c r="J48"/>
       <c r="K48"/>
       <c r="L48">
-        <v>3173</v>
+        <v>981</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="B49" t="s">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="C49" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D49">
-        <v>3420</v>
+        <v>84</v>
       </c>
       <c r="E49" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F49" s="2">
-        <v>46267.700127314813</v>
+        <v>46268</v>
       </c>
       <c r="G49" t="s">
         <v>15</v>
       </c>
       <c r="H49" t="s">
-        <v>23</v>
-      </c>
-      <c r="I49"/>
+        <v>48</v>
+      </c>
+      <c r="I49">
+        <v>250</v>
+      </c>
       <c r="J49"/>
       <c r="K49"/>
       <c r="L49">
-        <v>53</v>
+        <v>831</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>66</v>
+        <v>51</v>
       </c>
       <c r="B50" t="s">
-        <v>67</v>
+        <v>52</v>
       </c>
       <c r="C50" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D50">
-        <v>1008</v>
+        <v>38</v>
       </c>
       <c r="E50" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F50" s="2">
-        <v>46267.700127314813</v>
+        <v>46268</v>
       </c>
       <c r="G50" t="s">
         <v>15</v>
       </c>
       <c r="H50" t="s">
-        <v>23</v>
-      </c>
-      <c r="I50"/>
+        <v>48</v>
+      </c>
+      <c r="I50">
+        <v>250</v>
+      </c>
       <c r="J50"/>
       <c r="K50"/>
       <c r="L50">
-        <v>41</v>
+        <v>640</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
+        <v>53</v>
+      </c>
+      <c r="B51" t="s">
+        <v>54</v>
+      </c>
+      <c r="C51" t="s">
         <v>68</v>
       </c>
-      <c r="B51" t="s">
+      <c r="D51">
+        <v>84</v>
+      </c>
+      <c r="E51" t="s">
         <v>69</v>
       </c>
-      <c r="C51" t="s">
-        <v>70</v>
-      </c>
-      <c r="D51">
-        <v>5760</v>
-      </c>
-      <c r="E51" t="s">
-        <v>71</v>
-      </c>
       <c r="F51" s="2">
-        <v>46267.700127314813</v>
+        <v>46268</v>
       </c>
       <c r="G51" t="s">
         <v>15</v>
       </c>
       <c r="H51" t="s">
-        <v>23</v>
-      </c>
-      <c r="I51"/>
+        <v>55</v>
+      </c>
+      <c r="I51">
+        <v>5000</v>
+      </c>
       <c r="J51"/>
       <c r="K51"/>
       <c r="L51">
-        <v>49</v>
+        <v>535</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="B52" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="C52" t="s">
         <v>70</v>
       </c>
       <c r="D52">
-        <v>23760</v>
+        <v>3000</v>
       </c>
       <c r="E52" t="s">
         <v>71</v>
       </c>
       <c r="F52" s="2">
-        <v>46267.90347222222</v>
+        <v>46269.263831018514</v>
       </c>
       <c r="G52" t="s">
         <v>15</v>
       </c>
       <c r="H52" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="I52"/>
       <c r="J52"/>
       <c r="K52"/>
       <c r="L52">
-        <v>311</v>
+        <v>3712</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>42</v>
+        <v>72</v>
       </c>
       <c r="B53" t="s">
-        <v>43</v>
+        <v>73</v>
       </c>
       <c r="C53" t="s">
         <v>70</v>
       </c>
       <c r="D53">
-        <v>2035</v>
+        <v>1680</v>
       </c>
       <c r="E53" t="s">
         <v>71</v>
       </c>
       <c r="F53" s="2">
-        <v>46267.90347222222</v>
+        <v>46269.263831018514</v>
       </c>
       <c r="G53" t="s">
         <v>15</v>
       </c>
       <c r="H53" t="s">
-        <v>44</v>
-      </c>
-      <c r="I53">
-        <v>440</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="I53"/>
       <c r="J53"/>
       <c r="K53"/>
       <c r="L53">
-        <v>4000</v>
+        <v>2376</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="B54" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="C54" t="s">
         <v>70</v>
       </c>
       <c r="D54">
-        <v>90</v>
+        <v>15000</v>
       </c>
       <c r="E54" t="s">
         <v>71</v>
       </c>
       <c r="F54" s="2">
-        <v>46267.90347222222</v>
+        <v>46269.263831018514</v>
       </c>
       <c r="G54" t="s">
         <v>15</v>
       </c>
       <c r="H54" t="s">
-        <v>44</v>
-      </c>
-      <c r="I54">
-        <v>250</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="I54"/>
       <c r="J54"/>
       <c r="K54"/>
       <c r="L54">
-        <v>3091</v>
+        <v>4709</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>47</v>
+        <v>74</v>
       </c>
       <c r="B55" t="s">
-        <v>48</v>
+        <v>75</v>
       </c>
       <c r="C55" t="s">
         <v>70</v>
       </c>
       <c r="D55">
-        <v>38</v>
+        <v>2700</v>
       </c>
       <c r="E55" t="s">
         <v>71</v>
       </c>
       <c r="F55" s="2">
-        <v>46267.90347222222</v>
+        <v>46268.827592592592</v>
       </c>
       <c r="G55" t="s">
         <v>15</v>
       </c>
       <c r="H55" t="s">
-        <v>44</v>
-      </c>
-      <c r="I55">
-        <v>250</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="I55"/>
       <c r="J55"/>
       <c r="K55"/>
       <c r="L55">
-        <v>1752</v>
+        <v>171</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="B56" t="s">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="C56" t="s">
         <v>70</v>
       </c>
       <c r="D56">
-        <v>18</v>
+        <v>9300</v>
       </c>
       <c r="E56" t="s">
         <v>71</v>
       </c>
       <c r="F56" s="2">
-        <v>46267.70177083333</v>
+        <v>46268.827592592592</v>
       </c>
       <c r="G56" t="s">
         <v>15</v>
       </c>
       <c r="H56" t="s">
-        <v>61</v>
-      </c>
-      <c r="I56">
-        <v>5000</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="I56"/>
       <c r="J56"/>
       <c r="K56"/>
       <c r="L56">
-        <v>2122</v>
+        <v>143</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>55</v>
+        <v>34</v>
       </c>
       <c r="B57" t="s">
-        <v>56</v>
+        <v>35</v>
       </c>
       <c r="C57" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="D57">
-        <v>3000</v>
+        <v>6000</v>
       </c>
       <c r="E57" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="F57" s="2">
-        <v>46267.87195601852</v>
+        <v>46269.263831018514</v>
       </c>
       <c r="G57" t="s">
         <v>15</v>
       </c>
       <c r="H57" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="I57"/>
       <c r="J57"/>
       <c r="K57"/>
       <c r="L57">
-        <v>919</v>
+        <v>2123</v>
       </c>
     </row>
     <row r="58">
@@ -2660,214 +2686,214 @@
         <v>79</v>
       </c>
       <c r="C58" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="D58">
-        <v>21960</v>
+        <v>8520</v>
       </c>
       <c r="E58" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="F58" s="2">
-        <v>46267.87195601852</v>
+        <v>46269.263831018514</v>
       </c>
       <c r="G58" t="s">
         <v>15</v>
       </c>
       <c r="H58" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="I58"/>
       <c r="J58"/>
       <c r="K58"/>
       <c r="L58">
-        <v>45</v>
+        <v>1609</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>57</v>
+        <v>36</v>
       </c>
       <c r="B59" t="s">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="C59" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="D59">
-        <v>170160</v>
+        <v>79200</v>
       </c>
       <c r="E59" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="F59" s="2">
-        <v>46267.87195601852</v>
+        <v>46269.263831018514</v>
       </c>
       <c r="G59" t="s">
         <v>15</v>
       </c>
       <c r="H59" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="I59"/>
       <c r="J59"/>
       <c r="K59"/>
       <c r="L59">
-        <v>1731</v>
+        <v>3712</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>64</v>
+        <v>38</v>
       </c>
       <c r="B60" t="s">
-        <v>65</v>
+        <v>39</v>
       </c>
       <c r="C60" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="D60">
-        <v>180</v>
+        <v>79200</v>
       </c>
       <c r="E60" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="F60" s="2">
-        <v>46267.869479166664</v>
+        <v>46269.263831018514</v>
       </c>
       <c r="G60" t="s">
         <v>15</v>
       </c>
       <c r="H60" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="I60"/>
       <c r="J60"/>
       <c r="K60"/>
       <c r="L60">
-        <v>49</v>
+        <v>1193</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>66</v>
+        <v>40</v>
       </c>
       <c r="B61" t="s">
-        <v>67</v>
+        <v>41</v>
       </c>
       <c r="C61" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="D61">
-        <v>288</v>
+        <v>69360</v>
       </c>
       <c r="E61" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="F61" s="2">
-        <v>46267.869479166664</v>
+        <v>46269.263831018514</v>
       </c>
       <c r="G61" t="s">
         <v>15</v>
       </c>
       <c r="H61" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="I61"/>
       <c r="J61"/>
       <c r="K61"/>
       <c r="L61">
-        <v>39</v>
+        <v>2821</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>68</v>
+        <v>42</v>
       </c>
       <c r="B62" t="s">
-        <v>69</v>
+        <v>43</v>
       </c>
       <c r="C62" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="D62">
-        <v>720</v>
+        <v>7920</v>
       </c>
       <c r="E62" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="F62" s="2">
-        <v>46267.869479166664</v>
+        <v>46269.263831018514</v>
       </c>
       <c r="G62" t="s">
         <v>15</v>
       </c>
       <c r="H62" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="I62"/>
       <c r="J62"/>
       <c r="K62"/>
       <c r="L62">
-        <v>49</v>
+        <v>829</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="B63" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="C63" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="D63">
-        <v>3240</v>
+        <v>21120</v>
       </c>
       <c r="E63" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="F63" s="2">
-        <v>46267.87195601852</v>
+        <v>46269.263831018514</v>
       </c>
       <c r="G63" t="s">
         <v>15</v>
       </c>
       <c r="H63" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="I63"/>
       <c r="J63"/>
       <c r="K63"/>
       <c r="L63">
-        <v>243</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="B64" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="C64" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="D64">
-        <v>856</v>
+        <v>1592</v>
       </c>
       <c r="E64" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="F64" s="2">
-        <v>46267.87195601852</v>
+        <v>46269.263831018514</v>
       </c>
       <c r="G64" t="s">
         <v>15</v>
       </c>
       <c r="H64" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="I64">
         <v>440</v>
@@ -2875,33 +2901,33 @@
       <c r="J64"/>
       <c r="K64"/>
       <c r="L64">
-        <v>2056</v>
+        <v>5391</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B65" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C65" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="D65">
+        <v>112</v>
+      </c>
+      <c r="E65" t="s">
+        <v>71</v>
+      </c>
+      <c r="F65" s="2">
+        <v>46269.263831018514</v>
+      </c>
+      <c r="G65" t="s">
+        <v>15</v>
+      </c>
+      <c r="H65" t="s">
         <v>48</v>
-      </c>
-      <c r="E65" t="s">
-        <v>77</v>
-      </c>
-      <c r="F65" s="2">
-        <v>46267.87195601852</v>
-      </c>
-      <c r="G65" t="s">
-        <v>15</v>
-      </c>
-      <c r="H65" t="s">
-        <v>44</v>
       </c>
       <c r="I65">
         <v>250</v>
@@ -2909,33 +2935,33 @@
       <c r="J65"/>
       <c r="K65"/>
       <c r="L65">
-        <v>1717</v>
+        <v>4693</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="B66" t="s">
+        <v>52</v>
+      </c>
+      <c r="C66" t="s">
+        <v>70</v>
+      </c>
+      <c r="D66">
+        <v>72</v>
+      </c>
+      <c r="E66" t="s">
+        <v>71</v>
+      </c>
+      <c r="F66" s="2">
+        <v>46269.263831018514</v>
+      </c>
+      <c r="G66" t="s">
+        <v>15</v>
+      </c>
+      <c r="H66" t="s">
         <v>48</v>
-      </c>
-      <c r="C66" t="s">
-        <v>76</v>
-      </c>
-      <c r="D66">
-        <v>24</v>
-      </c>
-      <c r="E66" t="s">
-        <v>77</v>
-      </c>
-      <c r="F66" s="2">
-        <v>46267.87195601852</v>
-      </c>
-      <c r="G66" t="s">
-        <v>15</v>
-      </c>
-      <c r="H66" t="s">
-        <v>44</v>
       </c>
       <c r="I66">
         <v>250</v>
@@ -2943,33 +2969,33 @@
       <c r="J66"/>
       <c r="K66"/>
       <c r="L66">
-        <v>1033</v>
+        <v>2662</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="B67" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="C67" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="D67">
-        <v>48</v>
+        <v>90</v>
       </c>
       <c r="E67" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="F67" s="2">
-        <v>46267.87195601852</v>
+        <v>46269.263831018514</v>
       </c>
       <c r="G67" t="s">
         <v>15</v>
       </c>
       <c r="H67" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="I67">
         <v>5000</v>
@@ -2977,71 +3003,71 @@
       <c r="J67"/>
       <c r="K67"/>
       <c r="L67">
-        <v>1215</v>
+        <v>3606</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B68" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C68" t="s">
         <v>80</v>
       </c>
       <c r="D68">
-        <v>10560</v>
+        <v>39600</v>
       </c>
       <c r="E68" t="s">
         <v>81</v>
       </c>
       <c r="F68" s="2">
-        <v>46267</v>
+        <v>46269.318287037036</v>
       </c>
       <c r="G68" t="s">
         <v>15</v>
       </c>
       <c r="H68" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="I68"/>
       <c r="J68"/>
       <c r="K68"/>
       <c r="L68">
-        <v>443</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="B69" t="s">
-        <v>58</v>
+        <v>39</v>
       </c>
       <c r="C69" t="s">
         <v>80</v>
       </c>
       <c r="D69">
-        <v>210720</v>
+        <v>15840</v>
       </c>
       <c r="E69" t="s">
         <v>81</v>
       </c>
       <c r="F69" s="2">
-        <v>46267</v>
+        <v>46269.318287037036</v>
       </c>
       <c r="G69" t="s">
         <v>15</v>
       </c>
       <c r="H69" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="I69"/>
       <c r="J69"/>
       <c r="K69"/>
       <c r="L69">
-        <v>910</v>
+        <v>655</v>
       </c>
     </row>
     <row r="70">
@@ -3055,649 +3081,649 @@
         <v>80</v>
       </c>
       <c r="D70">
-        <v>1800</v>
+        <v>21120</v>
       </c>
       <c r="E70" t="s">
         <v>81</v>
       </c>
       <c r="F70" s="2">
-        <v>46267</v>
+        <v>46269.318287037036</v>
       </c>
       <c r="G70" t="s">
         <v>15</v>
       </c>
       <c r="H70" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="I70"/>
       <c r="J70"/>
       <c r="K70"/>
       <c r="L70">
-        <v>95</v>
+        <v>973</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B71" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C71" t="s">
         <v>80</v>
       </c>
       <c r="D71">
-        <v>932</v>
+        <v>1200</v>
       </c>
       <c r="E71" t="s">
         <v>81</v>
       </c>
       <c r="F71" s="2">
-        <v>46268.352233796293</v>
+        <v>46268.937754629631</v>
       </c>
       <c r="G71" t="s">
         <v>15</v>
       </c>
       <c r="H71" t="s">
-        <v>44</v>
-      </c>
-      <c r="I71">
-        <v>440</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="I71"/>
       <c r="J71"/>
       <c r="K71"/>
       <c r="L71">
-        <v>980</v>
+        <v>497</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>45</v>
+        <v>82</v>
       </c>
       <c r="B72" t="s">
-        <v>46</v>
+        <v>83</v>
       </c>
       <c r="C72" t="s">
         <v>80</v>
       </c>
       <c r="D72">
-        <v>40</v>
+        <v>360</v>
       </c>
       <c r="E72" t="s">
         <v>81</v>
       </c>
       <c r="F72" s="2">
-        <v>46268.352233796293</v>
+        <v>46269.318287037036</v>
       </c>
       <c r="G72" t="s">
         <v>15</v>
       </c>
       <c r="H72" t="s">
-        <v>44</v>
-      </c>
-      <c r="I72">
-        <v>250</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="I72"/>
       <c r="J72"/>
       <c r="K72"/>
       <c r="L72">
-        <v>830</v>
+        <v>145</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="B73" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="C73" t="s">
         <v>80</v>
       </c>
       <c r="D73">
-        <v>18</v>
+        <v>900</v>
       </c>
       <c r="E73" t="s">
         <v>81</v>
       </c>
       <c r="F73" s="2">
-        <v>46267</v>
+        <v>46269.318287037036</v>
       </c>
       <c r="G73" t="s">
         <v>15</v>
       </c>
       <c r="H73" t="s">
-        <v>44</v>
-      </c>
-      <c r="I73">
-        <v>250</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="I73"/>
       <c r="J73"/>
       <c r="K73"/>
       <c r="L73">
-        <v>639</v>
+        <v>163</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>59</v>
+        <v>46</v>
       </c>
       <c r="B74" t="s">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="C74" t="s">
         <v>80</v>
       </c>
       <c r="D74">
-        <v>40</v>
+        <v>452</v>
       </c>
       <c r="E74" t="s">
         <v>81</v>
       </c>
       <c r="F74" s="2">
-        <v>46268.352233796293</v>
+        <v>46269.318287037036</v>
       </c>
       <c r="G74" t="s">
         <v>15</v>
       </c>
       <c r="H74" t="s">
-        <v>61</v>
+        <v>48</v>
       </c>
       <c r="I74">
-        <v>5000</v>
+        <v>440</v>
       </c>
       <c r="J74"/>
       <c r="K74"/>
       <c r="L74">
-        <v>534</v>
+        <v>1379</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B75" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C75" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D75">
-        <v>6000</v>
+        <v>86</v>
       </c>
       <c r="E75" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="F75" s="2">
-        <v>46268.101493055554</v>
+        <v>46268.937754629631</v>
       </c>
       <c r="G75" t="s">
         <v>15</v>
       </c>
       <c r="H75" t="s">
-        <v>23</v>
-      </c>
-      <c r="I75"/>
+        <v>48</v>
+      </c>
+      <c r="I75">
+        <v>250</v>
+      </c>
       <c r="J75"/>
       <c r="K75"/>
       <c r="L75">
-        <v>1027</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>24</v>
+        <v>51</v>
       </c>
       <c r="B76" t="s">
-        <v>25</v>
+        <v>52</v>
       </c>
       <c r="C76" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D76">
-        <v>30000</v>
+        <v>40</v>
       </c>
       <c r="E76" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="F76" s="2">
-        <v>46267.851805555554</v>
+        <v>46268.937754629631</v>
       </c>
       <c r="G76" t="s">
         <v>15</v>
       </c>
       <c r="H76" t="s">
-        <v>23</v>
-      </c>
-      <c r="I76"/>
+        <v>48</v>
+      </c>
+      <c r="I76">
+        <v>250</v>
+      </c>
       <c r="J76"/>
       <c r="K76"/>
       <c r="L76">
-        <v>1811</v>
+        <v>701</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s">
+        <v>30</v>
+      </c>
+      <c r="B77" t="s">
+        <v>31</v>
+      </c>
+      <c r="C77" t="s">
         <v>84</v>
       </c>
-      <c r="B77" t="s">
+      <c r="D77">
+        <v>3000</v>
+      </c>
+      <c r="E77" t="s">
         <v>85</v>
       </c>
-      <c r="C77" t="s">
-        <v>82</v>
-      </c>
-      <c r="D77">
-        <v>300</v>
-      </c>
-      <c r="E77" t="s">
-        <v>83</v>
-      </c>
       <c r="F77" s="2">
-        <v>46265.79105324074</v>
+        <v>46268.807349537034</v>
       </c>
       <c r="G77" t="s">
         <v>15</v>
       </c>
       <c r="H77" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="I77"/>
       <c r="J77"/>
       <c r="K77"/>
       <c r="L77">
-        <v>25</v>
+        <v>131</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>86</v>
+        <v>36</v>
       </c>
       <c r="B78" t="s">
-        <v>87</v>
+        <v>37</v>
       </c>
       <c r="C78" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D78">
-        <v>9000</v>
+        <v>63360</v>
       </c>
       <c r="E78" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F78" s="2">
-        <v>46267.90357638889</v>
+        <v>46268.807349537034</v>
       </c>
       <c r="G78" t="s">
         <v>15</v>
       </c>
       <c r="H78" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="I78"/>
       <c r="J78"/>
       <c r="K78"/>
       <c r="L78">
-        <v>201</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="B79" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="C79" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D79">
-        <v>26400</v>
+        <v>76796</v>
       </c>
       <c r="E79" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F79" s="2">
-        <v>46267.90357638889</v>
+        <v>46268.807349537034</v>
       </c>
       <c r="G79" t="s">
         <v>15</v>
       </c>
       <c r="H79" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="I79"/>
       <c r="J79"/>
       <c r="K79"/>
       <c r="L79">
-        <v>2120</v>
+        <v>2825</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="B80" t="s">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="C80" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D80">
-        <v>5280</v>
+        <v>15840</v>
       </c>
       <c r="E80" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F80" s="2">
-        <v>46268.101493055554</v>
+        <v>46268.807349537034</v>
       </c>
       <c r="G80" t="s">
         <v>15</v>
       </c>
       <c r="H80" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="I80"/>
       <c r="J80"/>
       <c r="K80"/>
       <c r="L80">
-        <v>1607</v>
+        <v>429</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="B81" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="C81" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D81">
-        <v>188460</v>
+        <v>2923</v>
       </c>
       <c r="E81" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F81" s="2">
-        <v>46267.90357638889</v>
+        <v>46268.807349537034</v>
       </c>
       <c r="G81" t="s">
         <v>15</v>
       </c>
       <c r="H81" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="I81"/>
       <c r="J81"/>
       <c r="K81"/>
       <c r="L81">
-        <v>3709</v>
+        <v>798</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>32</v>
+        <v>60</v>
       </c>
       <c r="B82" t="s">
-        <v>33</v>
+        <v>61</v>
       </c>
       <c r="C82" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D82">
-        <v>5760</v>
+        <v>7920</v>
       </c>
       <c r="E82" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F82" s="2">
-        <v>46268.101493055554</v>
+        <v>46268.807349537034</v>
       </c>
       <c r="G82" t="s">
         <v>15</v>
       </c>
       <c r="H82" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="I82"/>
       <c r="J82"/>
       <c r="K82"/>
       <c r="L82">
-        <v>1191</v>
+        <v>203</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="B83" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="C83" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D83">
-        <v>198720</v>
+        <v>816</v>
       </c>
       <c r="E83" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F83" s="2">
-        <v>46267.90357638889</v>
+        <v>46268.807349537034</v>
       </c>
       <c r="G83" t="s">
         <v>15</v>
       </c>
       <c r="H83" t="s">
-        <v>23</v>
-      </c>
-      <c r="I83"/>
+        <v>48</v>
+      </c>
+      <c r="I83">
+        <v>440</v>
+      </c>
       <c r="J83"/>
       <c r="K83"/>
       <c r="L83">
-        <v>2819</v>
+        <v>3073</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="B84" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="C84" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D84">
-        <v>7920</v>
+        <v>38</v>
       </c>
       <c r="E84" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F84" s="2">
-        <v>46267.90357638889</v>
+        <v>46268.807349537034</v>
       </c>
       <c r="G84" t="s">
         <v>15</v>
       </c>
       <c r="H84" t="s">
-        <v>23</v>
-      </c>
-      <c r="I84"/>
+        <v>48</v>
+      </c>
+      <c r="I84">
+        <v>250</v>
+      </c>
       <c r="J84"/>
       <c r="K84"/>
       <c r="L84">
-        <v>827</v>
+        <v>2791</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="B85" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="C85" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D85">
-        <v>10643</v>
+        <v>19</v>
       </c>
       <c r="E85" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F85" s="2">
-        <v>46267.90357638889</v>
+        <v>46268.807349537034</v>
       </c>
       <c r="G85" t="s">
         <v>15</v>
       </c>
       <c r="H85" t="s">
-        <v>23</v>
-      </c>
-      <c r="I85"/>
+        <v>48</v>
+      </c>
+      <c r="I85">
+        <v>250</v>
+      </c>
       <c r="J85"/>
       <c r="K85"/>
       <c r="L85">
-        <v>1105</v>
+        <v>343</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>42</v>
+        <v>86</v>
       </c>
       <c r="B86" t="s">
-        <v>43</v>
+        <v>87</v>
       </c>
       <c r="C86" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="D86">
-        <v>2056</v>
+        <v>86400</v>
       </c>
       <c r="E86" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="F86" s="2">
-        <v>46268.101493055554</v>
+        <v>46268</v>
       </c>
       <c r="G86" t="s">
         <v>15</v>
       </c>
       <c r="H86" t="s">
-        <v>44</v>
-      </c>
-      <c r="I86">
-        <v>440</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="I86"/>
       <c r="J86"/>
       <c r="K86"/>
       <c r="L86">
-        <v>5388</v>
+        <v>237</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>45</v>
+        <v>90</v>
       </c>
       <c r="B87" t="s">
-        <v>46</v>
+        <v>91</v>
       </c>
       <c r="C87" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="D87">
-        <v>118</v>
+        <v>69840</v>
       </c>
       <c r="E87" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="F87" s="2">
-        <v>46268.101493055554</v>
+        <v>46268.866793981477</v>
       </c>
       <c r="G87" t="s">
         <v>15</v>
       </c>
       <c r="H87" t="s">
-        <v>44</v>
-      </c>
-      <c r="I87">
-        <v>250</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="I87"/>
       <c r="J87"/>
       <c r="K87"/>
       <c r="L87">
-        <v>4690</v>
+        <v>331</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="s">
+        <v>46</v>
+      </c>
+      <c r="B88" t="s">
         <v>47</v>
       </c>
-      <c r="B88" t="s">
+      <c r="C88" t="s">
+        <v>88</v>
+      </c>
+      <c r="D88">
+        <v>868</v>
+      </c>
+      <c r="E88" t="s">
+        <v>89</v>
+      </c>
+      <c r="F88" s="2">
+        <v>46268</v>
+      </c>
+      <c r="G88" t="s">
+        <v>15</v>
+      </c>
+      <c r="H88" t="s">
         <v>48</v>
       </c>
-      <c r="C88" t="s">
-        <v>82</v>
-      </c>
-      <c r="D88">
-        <v>66</v>
-      </c>
-      <c r="E88" t="s">
-        <v>83</v>
-      </c>
-      <c r="F88" s="2">
-        <v>46268.101493055554</v>
-      </c>
-      <c r="G88" t="s">
-        <v>15</v>
-      </c>
-      <c r="H88" t="s">
-        <v>44</v>
-      </c>
       <c r="I88">
-        <v>250</v>
+        <v>440</v>
       </c>
       <c r="J88"/>
       <c r="K88"/>
       <c r="L88">
-        <v>2660</v>
+        <v>2304</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="B89" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="C89" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="D89">
-        <v>53</v>
+        <v>35</v>
       </c>
       <c r="E89" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="F89" s="2">
-        <v>46268.101493055554</v>
+        <v>46268</v>
       </c>
       <c r="G89" t="s">
         <v>15</v>
       </c>
       <c r="H89" t="s">
-        <v>61</v>
+        <v>48</v>
       </c>
       <c r="I89">
-        <v>5000</v>
+        <v>250</v>
       </c>
       <c r="J89"/>
       <c r="K89"/>
       <c r="L89">
-        <v>3604</v>
+        <v>1872</v>
       </c>
     </row>
     <row r="90">
@@ -3711,2247 +3737,2251 @@
         <v>88</v>
       </c>
       <c r="D90">
-        <v>12000</v>
+        <v>10</v>
       </c>
       <c r="E90" t="s">
         <v>89</v>
       </c>
       <c r="F90" s="2">
-        <v>46267.870520833334</v>
+        <v>46268</v>
       </c>
       <c r="G90" t="s">
         <v>15</v>
       </c>
       <c r="H90" t="s">
-        <v>23</v>
-      </c>
-      <c r="I90"/>
+        <v>48</v>
+      </c>
+      <c r="I90">
+        <v>250</v>
+      </c>
       <c r="J90"/>
       <c r="K90"/>
       <c r="L90">
-        <v>180</v>
+        <v>953</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>28</v>
+        <v>53</v>
       </c>
       <c r="B91" t="s">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="C91" t="s">
         <v>88</v>
       </c>
       <c r="D91">
-        <v>9762</v>
+        <v>23</v>
       </c>
       <c r="E91" t="s">
         <v>89</v>
       </c>
       <c r="F91" s="2">
-        <v>46267.870520833334</v>
+        <v>46268</v>
       </c>
       <c r="G91" t="s">
         <v>15</v>
       </c>
       <c r="H91" t="s">
-        <v>23</v>
-      </c>
-      <c r="I91"/>
+        <v>55</v>
+      </c>
+      <c r="I91">
+        <v>5000</v>
+      </c>
       <c r="J91"/>
       <c r="K91"/>
       <c r="L91">
-        <v>670</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s">
-        <v>30</v>
+        <v>92</v>
       </c>
       <c r="B92" t="s">
-        <v>31</v>
+        <v>93</v>
       </c>
       <c r="C92" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="D92">
-        <v>68400</v>
+        <v>500</v>
       </c>
       <c r="E92" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="F92" s="2">
-        <v>46267.870520833334</v>
+        <v>46269.304409722223</v>
       </c>
       <c r="G92" t="s">
         <v>15</v>
       </c>
       <c r="H92" t="s">
-        <v>23</v>
-      </c>
-      <c r="I92"/>
+        <v>96</v>
+      </c>
+      <c r="I92">
+        <v>400</v>
+      </c>
       <c r="J92"/>
       <c r="K92"/>
       <c r="L92">
-        <v>1152</v>
+        <v>1864</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="s">
-        <v>32</v>
+        <v>97</v>
       </c>
       <c r="B93" t="s">
-        <v>33</v>
+        <v>98</v>
       </c>
       <c r="C93" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="D93">
-        <v>15840</v>
+        <v>20000</v>
       </c>
       <c r="E93" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="F93" s="2">
-        <v>46267.870520833334</v>
+        <v>46269.324178240742</v>
       </c>
       <c r="G93" t="s">
         <v>15</v>
       </c>
       <c r="H93" t="s">
-        <v>23</v>
-      </c>
-      <c r="I93"/>
+        <v>99</v>
+      </c>
+      <c r="I93">
+        <v>60000</v>
+      </c>
       <c r="J93"/>
       <c r="K93"/>
       <c r="L93">
-        <v>652</v>
+        <v>866</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s">
-        <v>34</v>
+        <v>100</v>
       </c>
       <c r="B94" t="s">
-        <v>35</v>
+        <v>101</v>
       </c>
       <c r="C94" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="D94">
-        <v>48000</v>
+        <v>30000</v>
       </c>
       <c r="E94" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="F94" s="2">
-        <v>46267.870520833334</v>
+        <v>46269.304409722223</v>
       </c>
       <c r="G94" t="s">
         <v>15</v>
       </c>
       <c r="H94" t="s">
-        <v>23</v>
-      </c>
-      <c r="I94"/>
+        <v>102</v>
+      </c>
+      <c r="I94">
+        <v>76613</v>
+      </c>
       <c r="J94"/>
       <c r="K94"/>
       <c r="L94">
-        <v>970</v>
+        <v>1287</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="s">
-        <v>36</v>
+        <v>103</v>
       </c>
       <c r="B95" t="s">
-        <v>37</v>
+        <v>104</v>
       </c>
       <c r="C95" t="s">
-        <v>88</v>
+        <v>105</v>
       </c>
       <c r="D95">
-        <v>1800</v>
+        <v>36576</v>
       </c>
       <c r="E95" t="s">
-        <v>89</v>
+        <v>106</v>
       </c>
       <c r="F95" s="2">
-        <v>46267.870520833334</v>
+        <v>46268.938796296294</v>
       </c>
       <c r="G95" t="s">
         <v>15</v>
       </c>
       <c r="H95" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="I95"/>
       <c r="J95"/>
       <c r="K95"/>
       <c r="L95">
-        <v>403</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="s">
-        <v>38</v>
+        <v>107</v>
       </c>
       <c r="B96" t="s">
-        <v>39</v>
+        <v>108</v>
       </c>
       <c r="C96" t="s">
-        <v>88</v>
+        <v>105</v>
       </c>
       <c r="D96">
-        <v>180</v>
+        <v>275520</v>
       </c>
       <c r="E96" t="s">
-        <v>89</v>
+        <v>106</v>
       </c>
       <c r="F96" s="2">
-        <v>46267.870520833334</v>
+        <v>46269.317430555551</v>
       </c>
       <c r="G96" t="s">
         <v>15</v>
       </c>
       <c r="H96" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="I96"/>
       <c r="J96"/>
       <c r="K96"/>
       <c r="L96">
-        <v>143</v>
+        <v>183</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="B97" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="C97" t="s">
-        <v>88</v>
+        <v>105</v>
       </c>
       <c r="D97">
-        <v>360</v>
+        <v>1148</v>
       </c>
       <c r="E97" t="s">
-        <v>89</v>
+        <v>106</v>
       </c>
       <c r="F97" s="2">
-        <v>46267.870520833334</v>
+        <v>46269.317430555551</v>
       </c>
       <c r="G97" t="s">
         <v>15</v>
       </c>
       <c r="H97" t="s">
-        <v>23</v>
-      </c>
-      <c r="I97"/>
+        <v>48</v>
+      </c>
+      <c r="I97">
+        <v>440</v>
+      </c>
       <c r="J97"/>
       <c r="K97"/>
       <c r="L97">
-        <v>161</v>
+        <v>4327</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="B98" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="C98" t="s">
-        <v>88</v>
+        <v>109</v>
       </c>
       <c r="D98">
-        <v>807</v>
+        <v>1200</v>
       </c>
       <c r="E98" t="s">
-        <v>89</v>
+        <v>110</v>
       </c>
       <c r="F98" s="2">
-        <v>46267.870520833334</v>
+        <v>46268.969259259255</v>
       </c>
       <c r="G98" t="s">
         <v>15</v>
       </c>
       <c r="H98" t="s">
-        <v>44</v>
-      </c>
-      <c r="I98">
-        <v>440</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="I98"/>
       <c r="J98"/>
       <c r="K98"/>
       <c r="L98">
-        <v>1376</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s">
-        <v>45</v>
+        <v>72</v>
       </c>
       <c r="B99" t="s">
-        <v>46</v>
+        <v>73</v>
       </c>
       <c r="C99" t="s">
-        <v>88</v>
+        <v>109</v>
       </c>
       <c r="D99">
-        <v>84</v>
+        <v>120</v>
       </c>
       <c r="E99" t="s">
-        <v>89</v>
+        <v>110</v>
       </c>
       <c r="F99" s="2">
-        <v>46267.351400462961</v>
+        <v>46268.969259259255</v>
       </c>
       <c r="G99" t="s">
         <v>15</v>
       </c>
       <c r="H99" t="s">
-        <v>44</v>
-      </c>
-      <c r="I99">
-        <v>250</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="I99"/>
       <c r="J99"/>
       <c r="K99"/>
       <c r="L99">
-        <v>1093</v>
+        <v>910</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="s">
-        <v>47</v>
+        <v>111</v>
       </c>
       <c r="B100" t="s">
-        <v>48</v>
+        <v>112</v>
       </c>
       <c r="C100" t="s">
-        <v>88</v>
+        <v>109</v>
       </c>
       <c r="D100">
-        <v>42</v>
+        <v>1200</v>
       </c>
       <c r="E100" t="s">
-        <v>89</v>
+        <v>110</v>
       </c>
       <c r="F100" s="2">
-        <v>46267.351400462961</v>
+        <v>46268</v>
       </c>
       <c r="G100" t="s">
         <v>15</v>
       </c>
       <c r="H100" t="s">
-        <v>44</v>
-      </c>
-      <c r="I100">
-        <v>250</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="I100"/>
       <c r="J100"/>
       <c r="K100"/>
       <c r="L100">
-        <v>699</v>
+        <v>265</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="s">
-        <v>59</v>
+        <v>17</v>
       </c>
       <c r="B101" t="s">
-        <v>60</v>
+        <v>18</v>
       </c>
       <c r="C101" t="s">
-        <v>88</v>
+        <v>109</v>
       </c>
       <c r="D101">
-        <v>80</v>
+        <v>840</v>
       </c>
       <c r="E101" t="s">
-        <v>89</v>
+        <v>110</v>
       </c>
       <c r="F101" s="2">
-        <v>46266.849386574075</v>
+        <v>46268</v>
       </c>
       <c r="G101" t="s">
         <v>15</v>
       </c>
       <c r="H101" t="s">
-        <v>61</v>
-      </c>
-      <c r="I101">
-        <v>5000</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="I101"/>
       <c r="J101"/>
       <c r="K101"/>
       <c r="L101">
-        <v>737</v>
+        <v>245</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="s">
-        <v>57</v>
+        <v>19</v>
       </c>
       <c r="B102" t="s">
-        <v>58</v>
+        <v>20</v>
       </c>
       <c r="C102" t="s">
-        <v>90</v>
+        <v>109</v>
       </c>
       <c r="D102">
-        <v>43</v>
+        <v>1800</v>
       </c>
       <c r="E102" t="s">
-        <v>91</v>
+        <v>110</v>
       </c>
       <c r="F102" s="2">
-        <v>46267.691504629627</v>
+        <v>46268</v>
       </c>
       <c r="G102" t="s">
         <v>15</v>
       </c>
       <c r="H102" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="I102"/>
       <c r="J102"/>
       <c r="K102"/>
       <c r="L102">
-        <v>797</v>
+        <v>273</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="s">
-        <v>55</v>
+        <v>103</v>
       </c>
       <c r="B103" t="s">
-        <v>56</v>
+        <v>104</v>
       </c>
       <c r="C103" t="s">
-        <v>92</v>
+        <v>109</v>
       </c>
       <c r="D103">
-        <v>3000</v>
+        <v>72864</v>
       </c>
       <c r="E103" t="s">
-        <v>93</v>
+        <v>110</v>
       </c>
       <c r="F103" s="2">
-        <v>46267.911319444444</v>
+        <v>46269.326041666667</v>
       </c>
       <c r="G103" t="s">
         <v>15</v>
       </c>
       <c r="H103" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="I103"/>
       <c r="J103"/>
       <c r="K103"/>
       <c r="L103">
-        <v>957</v>
+        <v>1817</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="s">
-        <v>94</v>
+        <v>113</v>
       </c>
       <c r="B104" t="s">
-        <v>95</v>
+        <v>114</v>
       </c>
       <c r="C104" t="s">
-        <v>92</v>
+        <v>109</v>
       </c>
       <c r="D104">
-        <v>86400</v>
+        <v>211200</v>
       </c>
       <c r="E104" t="s">
-        <v>93</v>
+        <v>110</v>
       </c>
       <c r="F104" s="2">
-        <v>46267.763101851851</v>
+        <v>46269.326041666667</v>
       </c>
       <c r="G104" t="s">
         <v>15</v>
       </c>
       <c r="H104" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="I104"/>
       <c r="J104"/>
       <c r="K104"/>
       <c r="L104">
-        <v>235</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="s">
-        <v>34</v>
+        <v>115</v>
       </c>
       <c r="B105" t="s">
-        <v>35</v>
+        <v>116</v>
       </c>
       <c r="C105" t="s">
-        <v>92</v>
+        <v>109</v>
       </c>
       <c r="D105">
-        <v>135600</v>
+        <v>284028</v>
       </c>
       <c r="E105" t="s">
-        <v>93</v>
+        <v>110</v>
       </c>
       <c r="F105" s="2">
-        <v>46267.911319444444</v>
+        <v>46268.934386574074</v>
       </c>
       <c r="G105" t="s">
         <v>15</v>
       </c>
       <c r="H105" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="I105"/>
       <c r="J105"/>
       <c r="K105"/>
       <c r="L105">
-        <v>1647</v>
+        <v>5122</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="s">
-        <v>36</v>
+        <v>107</v>
       </c>
       <c r="B106" t="s">
-        <v>37</v>
+        <v>108</v>
       </c>
       <c r="C106" t="s">
-        <v>92</v>
+        <v>109</v>
       </c>
       <c r="D106">
-        <v>9720</v>
+        <v>195360</v>
       </c>
       <c r="E106" t="s">
-        <v>93</v>
+        <v>110</v>
       </c>
       <c r="F106" s="2">
-        <v>46267.911319444444</v>
+        <v>46268.854108796295</v>
       </c>
       <c r="G106" t="s">
         <v>15</v>
       </c>
       <c r="H106" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="I106"/>
       <c r="J106"/>
       <c r="K106"/>
       <c r="L106">
-        <v>665</v>
+        <v>102</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="B107" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="C107" t="s">
-        <v>92</v>
+        <v>109</v>
       </c>
       <c r="D107">
-        <v>43200</v>
+        <v>2878</v>
       </c>
       <c r="E107" t="s">
-        <v>93</v>
+        <v>110</v>
       </c>
       <c r="F107" s="2">
-        <v>46267.911319444444</v>
+        <v>46269.326041666667</v>
       </c>
       <c r="G107" t="s">
         <v>15</v>
       </c>
       <c r="H107" t="s">
-        <v>23</v>
-      </c>
-      <c r="I107"/>
+        <v>48</v>
+      </c>
+      <c r="I107">
+        <v>440</v>
+      </c>
       <c r="J107"/>
       <c r="K107"/>
       <c r="L107">
-        <v>1443</v>
+        <v>9083</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="B108" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="C108" t="s">
-        <v>92</v>
+        <v>109</v>
       </c>
       <c r="D108">
-        <v>900</v>
+        <v>94</v>
       </c>
       <c r="E108" t="s">
-        <v>93</v>
+        <v>110</v>
       </c>
       <c r="F108" s="2">
-        <v>46267.911319444444</v>
+        <v>46269.326041666667</v>
       </c>
       <c r="G108" t="s">
         <v>15</v>
       </c>
       <c r="H108" t="s">
-        <v>23</v>
-      </c>
-      <c r="I108"/>
+        <v>48</v>
+      </c>
+      <c r="I108">
+        <v>250</v>
+      </c>
       <c r="J108"/>
       <c r="K108"/>
       <c r="L108">
-        <v>223</v>
+        <v>6369</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="B109" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="C109" t="s">
-        <v>92</v>
+        <v>109</v>
       </c>
       <c r="D109">
-        <v>6480</v>
+        <v>47</v>
       </c>
       <c r="E109" t="s">
-        <v>93</v>
+        <v>110</v>
       </c>
       <c r="F109" s="2">
-        <v>46267.911319444444</v>
+        <v>46268.854108796295</v>
       </c>
       <c r="G109" t="s">
         <v>15</v>
       </c>
       <c r="H109" t="s">
-        <v>23</v>
-      </c>
-      <c r="I109"/>
+        <v>48</v>
+      </c>
+      <c r="I109">
+        <v>250</v>
+      </c>
       <c r="J109"/>
       <c r="K109"/>
       <c r="L109">
-        <v>343</v>
+        <v>5171</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="s">
-        <v>42</v>
+        <v>117</v>
       </c>
       <c r="B110" t="s">
-        <v>43</v>
+        <v>118</v>
       </c>
       <c r="C110" t="s">
-        <v>92</v>
+        <v>119</v>
       </c>
       <c r="D110">
-        <v>1320</v>
+        <v>1800</v>
       </c>
       <c r="E110" t="s">
-        <v>93</v>
+        <v>120</v>
       </c>
       <c r="F110" s="2">
-        <v>46268.323009259257</v>
+        <v>46269.301168981481</v>
       </c>
       <c r="G110" t="s">
         <v>15</v>
       </c>
       <c r="H110" t="s">
-        <v>44</v>
-      </c>
-      <c r="I110">
-        <v>440</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="I110"/>
       <c r="J110"/>
       <c r="K110"/>
       <c r="L110">
-        <v>2300</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="s">
-        <v>45</v>
+        <v>121</v>
       </c>
       <c r="B111" t="s">
-        <v>46</v>
+        <v>122</v>
       </c>
       <c r="C111" t="s">
-        <v>92</v>
+        <v>123</v>
       </c>
       <c r="D111">
-        <v>66</v>
+        <v>800</v>
       </c>
       <c r="E111" t="s">
-        <v>93</v>
+        <v>124</v>
       </c>
       <c r="F111" s="2">
-        <v>46268.323009259257</v>
+        <v>46269.2324537037</v>
       </c>
       <c r="G111" t="s">
         <v>15</v>
       </c>
       <c r="H111" t="s">
-        <v>44</v>
+        <v>99</v>
       </c>
       <c r="I111">
-        <v>250</v>
+        <v>793</v>
       </c>
       <c r="J111"/>
       <c r="K111"/>
       <c r="L111">
-        <v>1868</v>
+        <v>383</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="s">
-        <v>47</v>
+        <v>97</v>
       </c>
       <c r="B112" t="s">
-        <v>48</v>
+        <v>98</v>
       </c>
       <c r="C112" t="s">
-        <v>92</v>
+        <v>123</v>
       </c>
       <c r="D112">
-        <v>22</v>
+        <v>20000</v>
       </c>
       <c r="E112" t="s">
-        <v>93</v>
+        <v>124</v>
       </c>
       <c r="F112" s="2">
-        <v>46267.911319444444</v>
+        <v>46268.826527777775</v>
       </c>
       <c r="G112" t="s">
         <v>15</v>
       </c>
       <c r="H112" t="s">
-        <v>44</v>
+        <v>99</v>
       </c>
       <c r="I112">
-        <v>250</v>
+        <v>60000</v>
       </c>
       <c r="J112"/>
       <c r="K112"/>
       <c r="L112">
-        <v>951</v>
+        <v>137</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="s">
-        <v>59</v>
+        <v>125</v>
       </c>
       <c r="B113" t="s">
-        <v>60</v>
+        <v>126</v>
       </c>
       <c r="C113" t="s">
-        <v>92</v>
+        <v>123</v>
       </c>
       <c r="D113">
-        <v>100.92</v>
+        <v>22313</v>
       </c>
       <c r="E113" t="s">
-        <v>93</v>
+        <v>124</v>
       </c>
       <c r="F113" s="2">
-        <v>46268.323009259257</v>
+        <v>46269.2324537037</v>
       </c>
       <c r="G113" t="s">
         <v>15</v>
       </c>
       <c r="H113" t="s">
-        <v>61</v>
+        <v>99</v>
       </c>
       <c r="I113">
-        <v>5000</v>
+        <v>55020</v>
       </c>
       <c r="J113"/>
       <c r="K113"/>
       <c r="L113">
-        <v>1211</v>
+        <v>2134</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="s">
-        <v>45</v>
+        <v>127</v>
       </c>
       <c r="B114" t="s">
-        <v>46</v>
+        <v>128</v>
       </c>
       <c r="C114" t="s">
-        <v>96</v>
+        <v>123</v>
       </c>
       <c r="D114">
-        <v>192</v>
+        <v>6720</v>
       </c>
       <c r="E114" t="s">
-        <v>97</v>
+        <v>124</v>
       </c>
       <c r="F114" s="2">
-        <v>46267.798773148148</v>
+        <v>46269.2324537037</v>
       </c>
       <c r="G114" t="s">
         <v>15</v>
       </c>
       <c r="H114" t="s">
-        <v>44</v>
+        <v>99</v>
       </c>
       <c r="I114">
-        <v>250</v>
+        <v>30100</v>
       </c>
       <c r="J114"/>
       <c r="K114"/>
       <c r="L114">
-        <v>4128</v>
+        <v>596</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="s">
+        <v>97</v>
+      </c>
+      <c r="B115" t="s">
         <v>98</v>
       </c>
-      <c r="B115" t="s">
+      <c r="C115" t="s">
+        <v>129</v>
+      </c>
+      <c r="D115">
+        <v>20000</v>
+      </c>
+      <c r="E115" t="s">
+        <v>130</v>
+      </c>
+      <c r="F115" s="2">
+        <v>46268.939097222217</v>
+      </c>
+      <c r="G115" t="s">
+        <v>15</v>
+      </c>
+      <c r="H115" t="s">
         <v>99</v>
       </c>
-      <c r="C115" t="s">
-        <v>100</v>
-      </c>
-      <c r="D115">
-        <v>109728</v>
-      </c>
-      <c r="E115" t="s">
-        <v>101</v>
-      </c>
-      <c r="F115" s="2">
-        <v>46267.808645833335</v>
-      </c>
-      <c r="G115" t="s">
-        <v>15</v>
-      </c>
-      <c r="H115" t="s">
-        <v>23</v>
-      </c>
-      <c r="I115"/>
+      <c r="I115">
+        <v>60000</v>
+      </c>
       <c r="J115"/>
       <c r="K115"/>
       <c r="L115">
-        <v>1483</v>
+        <v>111</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="s">
-        <v>102</v>
+        <v>131</v>
       </c>
       <c r="B116" t="s">
-        <v>103</v>
+        <v>132</v>
       </c>
       <c r="C116" t="s">
-        <v>100</v>
+        <v>133</v>
       </c>
       <c r="D116">
-        <v>782640</v>
+        <v>2240</v>
       </c>
       <c r="E116" t="s">
-        <v>101</v>
+        <v>134</v>
       </c>
       <c r="F116" s="2">
-        <v>46267.872013888889</v>
+        <v>46268.972465277773</v>
       </c>
       <c r="G116" t="s">
         <v>15</v>
       </c>
       <c r="H116" t="s">
-        <v>23</v>
-      </c>
-      <c r="I116"/>
+        <v>99</v>
+      </c>
+      <c r="I116">
+        <v>5040</v>
+      </c>
       <c r="J116"/>
       <c r="K116"/>
       <c r="L116">
-        <v>179</v>
+        <v>908</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="s">
-        <v>42</v>
+        <v>121</v>
       </c>
       <c r="B117" t="s">
-        <v>43</v>
+        <v>122</v>
       </c>
       <c r="C117" t="s">
-        <v>100</v>
+        <v>133</v>
       </c>
       <c r="D117">
-        <v>3261</v>
+        <v>1600</v>
       </c>
       <c r="E117" t="s">
-        <v>101</v>
+        <v>134</v>
       </c>
       <c r="F117" s="2">
-        <v>46267.872013888889</v>
+        <v>46268.972465277773</v>
       </c>
       <c r="G117" t="s">
         <v>15</v>
       </c>
       <c r="H117" t="s">
-        <v>44</v>
+        <v>99</v>
       </c>
       <c r="I117">
-        <v>440</v>
+        <v>793</v>
       </c>
       <c r="J117"/>
       <c r="K117"/>
       <c r="L117">
-        <v>4323</v>
+        <v>157</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="s">
-        <v>45</v>
+        <v>135</v>
       </c>
       <c r="B118" t="s">
-        <v>46</v>
+        <v>136</v>
       </c>
       <c r="C118" t="s">
-        <v>100</v>
+        <v>133</v>
       </c>
       <c r="D118">
-        <v>128</v>
+        <v>600</v>
       </c>
       <c r="E118" t="s">
-        <v>101</v>
+        <v>134</v>
       </c>
       <c r="F118" s="2">
-        <v>46267.872013888889</v>
+        <v>46267.859270833331</v>
       </c>
       <c r="G118" t="s">
         <v>15</v>
       </c>
       <c r="H118" t="s">
-        <v>44</v>
+        <v>99</v>
       </c>
       <c r="I118">
-        <v>250</v>
+        <v>15000</v>
       </c>
       <c r="J118"/>
       <c r="K118"/>
       <c r="L118">
-        <v>4013</v>
+        <v>5</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="s">
-        <v>47</v>
+        <v>137</v>
       </c>
       <c r="B119" t="s">
-        <v>48</v>
+        <v>138</v>
       </c>
       <c r="C119" t="s">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="D119">
-        <v>40</v>
+        <v>2940</v>
       </c>
       <c r="E119" t="s">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="F119" s="2">
-        <v>46267.872013888889</v>
+        <v>46268</v>
       </c>
       <c r="G119" t="s">
         <v>15</v>
       </c>
       <c r="H119" t="s">
-        <v>44</v>
+        <v>99</v>
       </c>
       <c r="I119">
-        <v>250</v>
+        <v>4480</v>
       </c>
       <c r="J119"/>
       <c r="K119"/>
       <c r="L119">
-        <v>1424</v>
+        <v>44</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="s">
-        <v>59</v>
+        <v>141</v>
       </c>
       <c r="B120" t="s">
-        <v>60</v>
+        <v>142</v>
       </c>
       <c r="C120" t="s">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="D120">
-        <v>32</v>
+        <v>4480</v>
       </c>
       <c r="E120" t="s">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="F120" s="2">
-        <v>46267.872013888889</v>
+        <v>46268</v>
       </c>
       <c r="G120" t="s">
         <v>15</v>
       </c>
       <c r="H120" t="s">
-        <v>61</v>
+        <v>99</v>
       </c>
       <c r="I120">
-        <v>5000</v>
+        <v>33600</v>
       </c>
       <c r="J120"/>
       <c r="K120"/>
       <c r="L120">
-        <v>2557</v>
+        <v>90</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="s">
-        <v>98</v>
+        <v>121</v>
       </c>
       <c r="B121" t="s">
+        <v>122</v>
+      </c>
+      <c r="C121" t="s">
+        <v>139</v>
+      </c>
+      <c r="D121">
+        <v>900</v>
+      </c>
+      <c r="E121" t="s">
+        <v>140</v>
+      </c>
+      <c r="F121" s="2">
+        <v>46268</v>
+      </c>
+      <c r="G121" t="s">
+        <v>15</v>
+      </c>
+      <c r="H121" t="s">
         <v>99</v>
       </c>
-      <c r="C121" t="s">
-        <v>104</v>
-      </c>
-      <c r="D121">
-        <v>145728</v>
-      </c>
-      <c r="E121" t="s">
-        <v>105</v>
-      </c>
-      <c r="F121" s="2">
-        <v>46267.841446759259</v>
-      </c>
-      <c r="G121" t="s">
-        <v>15</v>
-      </c>
-      <c r="H121" t="s">
-        <v>23</v>
-      </c>
-      <c r="I121"/>
+      <c r="I121">
+        <v>793</v>
+      </c>
       <c r="J121"/>
       <c r="K121"/>
       <c r="L121">
-        <v>1814</v>
+        <v>114</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="s">
-        <v>106</v>
+        <v>143</v>
       </c>
       <c r="B122" t="s">
-        <v>107</v>
+        <v>144</v>
       </c>
       <c r="C122" t="s">
-        <v>104</v>
+        <v>139</v>
       </c>
       <c r="D122">
-        <v>168960</v>
+        <v>220</v>
       </c>
       <c r="E122" t="s">
-        <v>105</v>
+        <v>140</v>
       </c>
       <c r="F122" s="2">
-        <v>46267.879085648143</v>
+        <v>46267</v>
       </c>
       <c r="G122" t="s">
         <v>15</v>
       </c>
       <c r="H122" t="s">
-        <v>23</v>
-      </c>
-      <c r="I122"/>
+        <v>99</v>
+      </c>
+      <c r="I122">
+        <v>173</v>
+      </c>
       <c r="J122"/>
       <c r="K122"/>
       <c r="L122">
-        <v>1323</v>
+        <v>107</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="s">
-        <v>108</v>
+        <v>125</v>
       </c>
       <c r="B123" t="s">
-        <v>109</v>
+        <v>126</v>
       </c>
       <c r="C123" t="s">
-        <v>104</v>
+        <v>139</v>
       </c>
       <c r="D123">
-        <v>51840</v>
+        <v>4480</v>
       </c>
       <c r="E123" t="s">
-        <v>105</v>
+        <v>140</v>
       </c>
       <c r="F123" s="2">
-        <v>46266.850347222222</v>
+        <v>46268</v>
       </c>
       <c r="G123" t="s">
         <v>15</v>
       </c>
       <c r="H123" t="s">
-        <v>23</v>
-      </c>
-      <c r="I123"/>
+        <v>99</v>
+      </c>
+      <c r="I123">
+        <v>55020</v>
+      </c>
       <c r="J123"/>
       <c r="K123"/>
       <c r="L123">
-        <v>1875</v>
+        <v>250</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="s">
-        <v>110</v>
+        <v>143</v>
       </c>
       <c r="B124" t="s">
-        <v>111</v>
+        <v>144</v>
       </c>
       <c r="C124" t="s">
-        <v>104</v>
+        <v>145</v>
       </c>
       <c r="D124">
-        <v>362880</v>
+        <v>400</v>
       </c>
       <c r="E124" t="s">
-        <v>105</v>
+        <v>146</v>
       </c>
       <c r="F124" s="2">
-        <v>46267.974745370368</v>
+        <v>45185</v>
       </c>
       <c r="G124" t="s">
         <v>15</v>
       </c>
       <c r="H124" t="s">
-        <v>23</v>
-      </c>
-      <c r="I124"/>
+        <v>99</v>
+      </c>
+      <c r="I124">
+        <v>173</v>
+      </c>
       <c r="J124"/>
       <c r="K124"/>
       <c r="L124">
-        <v>5118</v>
+        <v>1</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="s">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="B125" t="s">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="C125" t="s">
-        <v>104</v>
+        <v>147</v>
       </c>
       <c r="D125">
-        <v>40320</v>
+        <v>1120</v>
       </c>
       <c r="E125" t="s">
-        <v>105</v>
+        <v>148</v>
       </c>
       <c r="F125" s="2">
-        <v>46267.879085648143</v>
+        <v>46267.903784722221</v>
       </c>
       <c r="G125" t="s">
         <v>15</v>
       </c>
       <c r="H125" t="s">
-        <v>23</v>
-      </c>
-      <c r="I125"/>
+        <v>99</v>
+      </c>
+      <c r="I125">
+        <v>33600</v>
+      </c>
       <c r="J125"/>
       <c r="K125"/>
       <c r="L125">
-        <v>101</v>
+        <v>74</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="s">
-        <v>42</v>
+        <v>135</v>
       </c>
       <c r="B126" t="s">
-        <v>43</v>
+        <v>136</v>
       </c>
       <c r="C126" t="s">
-        <v>104</v>
+        <v>147</v>
       </c>
       <c r="D126">
-        <v>2600</v>
+        <v>1000</v>
       </c>
       <c r="E126" t="s">
-        <v>105</v>
+        <v>148</v>
       </c>
       <c r="F126" s="2">
-        <v>46267.974745370368</v>
+        <v>46267.872303240736</v>
       </c>
       <c r="G126" t="s">
         <v>15</v>
       </c>
       <c r="H126" t="s">
-        <v>44</v>
+        <v>99</v>
       </c>
       <c r="I126">
-        <v>440</v>
+        <v>15000</v>
       </c>
       <c r="J126"/>
       <c r="K126"/>
       <c r="L126">
-        <v>9076</v>
+        <v>21</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="s">
-        <v>45</v>
+        <v>149</v>
       </c>
       <c r="B127" t="s">
-        <v>46</v>
+        <v>150</v>
       </c>
       <c r="C127" t="s">
-        <v>104</v>
+        <v>151</v>
       </c>
       <c r="D127">
-        <v>84</v>
+        <v>1</v>
       </c>
       <c r="E127" t="s">
-        <v>105</v>
+        <v>152</v>
       </c>
       <c r="F127" s="2">
-        <v>46267.974745370368</v>
+        <v>46265.788981481477</v>
       </c>
       <c r="G127" t="s">
         <v>15</v>
       </c>
       <c r="H127" t="s">
-        <v>44</v>
+        <v>153</v>
       </c>
       <c r="I127">
-        <v>250</v>
+        <v>12</v>
       </c>
       <c r="J127"/>
       <c r="K127"/>
       <c r="L127">
-        <v>6366</v>
+        <v>14</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="s">
-        <v>47</v>
+        <v>154</v>
       </c>
       <c r="B128" t="s">
-        <v>48</v>
+        <v>155</v>
       </c>
       <c r="C128" t="s">
-        <v>104</v>
+        <v>151</v>
       </c>
       <c r="D128">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="E128" t="s">
-        <v>105</v>
+        <v>152</v>
       </c>
       <c r="F128" s="2">
-        <v>46267.974745370368</v>
+        <v>46265.776967592588</v>
       </c>
       <c r="G128" t="s">
         <v>15</v>
       </c>
       <c r="H128" t="s">
-        <v>44</v>
+        <v>153</v>
       </c>
       <c r="I128">
-        <v>250</v>
+        <v>45</v>
       </c>
       <c r="J128"/>
       <c r="K128"/>
       <c r="L128">
-        <v>5169</v>
+        <v>11</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="s">
-        <v>59</v>
+        <v>156</v>
       </c>
       <c r="B129" t="s">
+        <v>157</v>
+      </c>
+      <c r="C129" t="s">
+        <v>151</v>
+      </c>
+      <c r="D129">
+        <v>1</v>
+      </c>
+      <c r="E129" t="s">
+        <v>152</v>
+      </c>
+      <c r="F129" s="2">
+        <v>46265.788981481477</v>
+      </c>
+      <c r="G129" t="s">
+        <v>15</v>
+      </c>
+      <c r="H129" t="s">
+        <v>153</v>
+      </c>
+      <c r="I129">
         <v>60</v>
-      </c>
-      <c r="C129" t="s">
-        <v>104</v>
-      </c>
-      <c r="D129">
-        <v>2</v>
-      </c>
-      <c r="E129" t="s">
-        <v>105</v>
-      </c>
-      <c r="F129" s="2">
-        <v>46267.858657407407</v>
-      </c>
-      <c r="G129" t="s">
-        <v>15</v>
-      </c>
-      <c r="H129" t="s">
-        <v>61</v>
-      </c>
-      <c r="I129">
-        <v>5000</v>
       </c>
       <c r="J129"/>
       <c r="K129"/>
       <c r="L129">
-        <v>2977</v>
+        <v>19</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="s">
-        <v>112</v>
+        <v>141</v>
       </c>
       <c r="B130" t="s">
-        <v>113</v>
+        <v>142</v>
       </c>
       <c r="C130" t="s">
-        <v>114</v>
+        <v>151</v>
       </c>
       <c r="D130">
-        <v>1800</v>
+        <v>280</v>
       </c>
       <c r="E130" t="s">
-        <v>115</v>
+        <v>152</v>
       </c>
       <c r="F130" s="2">
-        <v>46267.969629629624</v>
+        <v>46261.786122685182</v>
       </c>
       <c r="G130" t="s">
         <v>15</v>
       </c>
       <c r="H130" t="s">
-        <v>23</v>
-      </c>
-      <c r="I130"/>
+        <v>99</v>
+      </c>
+      <c r="I130">
+        <v>33600</v>
+      </c>
       <c r="J130"/>
       <c r="K130"/>
       <c r="L130">
-        <v>1002</v>
+        <v>167</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="s">
-        <v>116</v>
+        <v>158</v>
       </c>
       <c r="B131" t="s">
-        <v>117</v>
+        <v>159</v>
       </c>
       <c r="C131" t="s">
-        <v>114</v>
+        <v>160</v>
       </c>
       <c r="D131">
-        <v>900</v>
+        <v>39040</v>
       </c>
       <c r="E131" t="s">
-        <v>115</v>
+        <v>161</v>
       </c>
       <c r="F131" s="2">
-        <v>46267.712511574071</v>
+        <v>46267.720879629625</v>
       </c>
       <c r="G131" t="s">
         <v>15</v>
       </c>
       <c r="H131" t="s">
-        <v>23</v>
-      </c>
-      <c r="I131"/>
+        <v>16</v>
+      </c>
+      <c r="I131">
+        <v>0</v>
+      </c>
       <c r="J131"/>
       <c r="K131"/>
       <c r="L131">
-        <v>1429</v>
+        <v>1386</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="s">
-        <v>118</v>
+        <v>162</v>
       </c>
       <c r="B132" t="s">
-        <v>119</v>
+        <v>163</v>
       </c>
       <c r="C132" t="s">
-        <v>120</v>
+        <v>160</v>
       </c>
       <c r="D132">
-        <v>1233</v>
+        <v>180</v>
       </c>
       <c r="E132" t="s">
-        <v>121</v>
+        <v>161</v>
       </c>
       <c r="F132" s="2">
-        <v>46268.104074074072</v>
+        <v>46268.594189814816</v>
       </c>
       <c r="G132" t="s">
         <v>15</v>
       </c>
       <c r="H132" t="s">
-        <v>122</v>
-      </c>
-      <c r="I132">
-        <v>793</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="I132"/>
       <c r="J132"/>
       <c r="K132"/>
       <c r="L132">
-        <v>380</v>
+        <v>9</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="s">
-        <v>123</v>
+        <v>164</v>
       </c>
       <c r="B133" t="s">
-        <v>124</v>
+        <v>165</v>
       </c>
       <c r="C133" t="s">
-        <v>120</v>
+        <v>160</v>
       </c>
       <c r="D133">
-        <v>8960</v>
+        <v>186</v>
       </c>
       <c r="E133" t="s">
-        <v>121</v>
+        <v>161</v>
       </c>
       <c r="F133" s="2">
-        <v>46268.224583333329</v>
+        <v>44946.553055555552</v>
       </c>
       <c r="G133" t="s">
         <v>15</v>
       </c>
       <c r="H133" t="s">
-        <v>122</v>
+        <v>48</v>
       </c>
       <c r="I133">
-        <v>13440</v>
+        <v>20</v>
       </c>
       <c r="J133"/>
       <c r="K133"/>
       <c r="L133">
-        <v>2129</v>
+        <v>2</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="s">
-        <v>125</v>
+        <v>166</v>
       </c>
       <c r="B134" t="s">
-        <v>126</v>
+        <v>167</v>
       </c>
       <c r="C134" t="s">
-        <v>120</v>
+        <v>160</v>
       </c>
       <c r="D134">
-        <v>13440</v>
+        <v>93</v>
       </c>
       <c r="E134" t="s">
-        <v>121</v>
+        <v>161</v>
       </c>
       <c r="F134" s="2">
-        <v>46268.1030787037</v>
+        <v>45777.752291666664</v>
       </c>
       <c r="G134" t="s">
         <v>15</v>
       </c>
       <c r="H134" t="s">
-        <v>122</v>
+        <v>168</v>
       </c>
       <c r="I134">
-        <v>8960</v>
+        <v>16</v>
       </c>
       <c r="J134"/>
       <c r="K134"/>
       <c r="L134">
-        <v>593</v>
+        <v>7</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="s">
-        <v>127</v>
+        <v>169</v>
       </c>
       <c r="B135" t="s">
-        <v>128</v>
+        <v>170</v>
       </c>
       <c r="C135" t="s">
-        <v>120</v>
+        <v>160</v>
       </c>
       <c r="D135">
-        <v>4</v>
+        <v>55</v>
       </c>
       <c r="E135" t="s">
-        <v>121</v>
+        <v>161</v>
       </c>
       <c r="F135" s="2">
-        <v>46267.983576388884</v>
+        <v>44426</v>
       </c>
       <c r="G135" t="s">
-        <v>129</v>
+        <v>15</v>
       </c>
       <c r="H135" t="s">
-        <v>122</v>
+        <v>55</v>
       </c>
       <c r="I135">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="J135"/>
       <c r="K135"/>
       <c r="L135">
-        <v>32</v>
+        <v>5</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="s">
-        <v>130</v>
+        <v>117</v>
       </c>
       <c r="B136" t="s">
-        <v>131</v>
+        <v>118</v>
       </c>
       <c r="C136" t="s">
-        <v>132</v>
+        <v>171</v>
       </c>
       <c r="D136">
-        <v>30000</v>
+        <v>600</v>
       </c>
       <c r="E136" t="s">
-        <v>133</v>
+        <v>172</v>
       </c>
       <c r="F136" s="2">
-        <v>46267.809710648144</v>
+        <v>46268.846284722218</v>
       </c>
       <c r="G136" t="s">
         <v>15</v>
       </c>
       <c r="H136" t="s">
-        <v>122</v>
-      </c>
-      <c r="I136">
-        <v>60000</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="I136"/>
       <c r="J136"/>
       <c r="K136"/>
       <c r="L136">
-        <v>109</v>
+        <v>418</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="s">
-        <v>134</v>
+        <v>103</v>
       </c>
       <c r="B137" t="s">
-        <v>135</v>
+        <v>104</v>
       </c>
       <c r="C137" t="s">
-        <v>132</v>
+        <v>171</v>
       </c>
       <c r="D137">
-        <v>20000</v>
+        <v>576</v>
       </c>
       <c r="E137" t="s">
-        <v>133</v>
+        <v>172</v>
       </c>
       <c r="F137" s="2">
-        <v>46267.87232638889</v>
+        <v>46268.846284722218</v>
       </c>
       <c r="G137" t="s">
         <v>15</v>
       </c>
       <c r="H137" t="s">
-        <v>122</v>
-      </c>
-      <c r="I137">
-        <v>290000</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="I137"/>
       <c r="J137"/>
       <c r="K137"/>
       <c r="L137">
-        <v>14</v>
+        <v>438</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="s">
-        <v>118</v>
+        <v>173</v>
       </c>
       <c r="B138" t="s">
-        <v>119</v>
+        <v>174</v>
       </c>
       <c r="C138" t="s">
-        <v>136</v>
+        <v>171</v>
       </c>
       <c r="D138">
-        <v>1200</v>
+        <v>2160</v>
       </c>
       <c r="E138" t="s">
-        <v>137</v>
+        <v>172</v>
       </c>
       <c r="F138" s="2">
-        <v>46267.975081018514</v>
+        <v>46267.751342592594</v>
       </c>
       <c r="G138" t="s">
         <v>15</v>
       </c>
       <c r="H138" t="s">
-        <v>122</v>
-      </c>
-      <c r="I138">
-        <v>793</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="I138"/>
       <c r="J138"/>
       <c r="K138"/>
       <c r="L138">
-        <v>154</v>
+        <v>51</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="s">
-        <v>138</v>
+        <v>175</v>
       </c>
       <c r="B139" t="s">
-        <v>139</v>
+        <v>176</v>
       </c>
       <c r="C139" t="s">
-        <v>136</v>
+        <v>171</v>
       </c>
       <c r="D139">
         <v>600</v>
       </c>
       <c r="E139" t="s">
-        <v>137</v>
+        <v>172</v>
       </c>
       <c r="F139" s="2">
-        <v>46267.859270833331</v>
+        <v>46268.821967592594</v>
       </c>
       <c r="G139" t="s">
         <v>15</v>
       </c>
       <c r="H139" t="s">
-        <v>122</v>
-      </c>
-      <c r="I139">
-        <v>15000</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="I139"/>
       <c r="J139"/>
       <c r="K139"/>
       <c r="L139">
-        <v>5</v>
+        <v>532</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="s">
-        <v>140</v>
+        <v>177</v>
       </c>
       <c r="B140" t="s">
-        <v>141</v>
+        <v>178</v>
       </c>
       <c r="C140" t="s">
-        <v>142</v>
+        <v>171</v>
       </c>
       <c r="D140">
-        <v>1680</v>
+        <v>9624</v>
       </c>
       <c r="E140" t="s">
-        <v>143</v>
+        <v>172</v>
       </c>
       <c r="F140" s="2">
-        <v>46267</v>
+        <v>46268.832696759258</v>
       </c>
       <c r="G140" t="s">
         <v>15</v>
       </c>
       <c r="H140" t="s">
-        <v>122</v>
-      </c>
-      <c r="I140">
-        <v>4480</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="I140"/>
       <c r="J140"/>
       <c r="K140"/>
       <c r="L140">
-        <v>43</v>
+        <v>27</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="s">
-        <v>144</v>
+        <v>179</v>
       </c>
       <c r="B141" t="s">
-        <v>145</v>
+        <v>180</v>
       </c>
       <c r="C141" t="s">
-        <v>142</v>
+        <v>171</v>
       </c>
       <c r="D141">
-        <v>2240</v>
+        <v>3276</v>
       </c>
       <c r="E141" t="s">
-        <v>143</v>
+        <v>172</v>
       </c>
       <c r="F141" s="2">
-        <v>46267</v>
+        <v>46268.832696759258</v>
       </c>
       <c r="G141" t="s">
         <v>15</v>
       </c>
       <c r="H141" t="s">
-        <v>122</v>
-      </c>
-      <c r="I141">
-        <v>8120</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="I141"/>
       <c r="J141"/>
       <c r="K141"/>
       <c r="L141">
-        <v>89</v>
+        <v>25</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="s">
-        <v>118</v>
+        <v>46</v>
       </c>
       <c r="B142" t="s">
-        <v>119</v>
+        <v>47</v>
       </c>
       <c r="C142" t="s">
-        <v>142</v>
+        <v>171</v>
       </c>
       <c r="D142">
-        <v>600</v>
+        <v>54</v>
       </c>
       <c r="E142" t="s">
-        <v>143</v>
+        <v>172</v>
       </c>
       <c r="F142" s="2">
-        <v>46267</v>
+        <v>46268.832696759258</v>
       </c>
       <c r="G142" t="s">
         <v>15</v>
       </c>
       <c r="H142" t="s">
-        <v>122</v>
+        <v>48</v>
       </c>
       <c r="I142">
-        <v>793</v>
+        <v>440</v>
       </c>
       <c r="J142"/>
       <c r="K142"/>
       <c r="L142">
-        <v>113</v>
+        <v>145</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="s">
-        <v>146</v>
+        <v>49</v>
       </c>
       <c r="B143" t="s">
-        <v>147</v>
+        <v>50</v>
       </c>
       <c r="C143" t="s">
-        <v>142</v>
+        <v>171</v>
       </c>
       <c r="D143">
-        <v>220</v>
+        <v>2</v>
       </c>
       <c r="E143" t="s">
-        <v>143</v>
+        <v>172</v>
       </c>
       <c r="F143" s="2">
-        <v>46267</v>
+        <v>46268.832696759258</v>
       </c>
       <c r="G143" t="s">
         <v>15</v>
       </c>
       <c r="H143" t="s">
-        <v>122</v>
+        <v>48</v>
       </c>
       <c r="I143">
-        <v>173</v>
+        <v>250</v>
       </c>
       <c r="J143"/>
       <c r="K143"/>
       <c r="L143">
-        <v>107</v>
+        <v>84</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="s">
-        <v>123</v>
+        <v>53</v>
       </c>
       <c r="B144" t="s">
-        <v>124</v>
+        <v>54</v>
       </c>
       <c r="C144" t="s">
-        <v>142</v>
+        <v>171</v>
       </c>
       <c r="D144">
-        <v>2240</v>
+        <v>5</v>
       </c>
       <c r="E144" t="s">
-        <v>143</v>
+        <v>172</v>
       </c>
       <c r="F144" s="2">
-        <v>46267</v>
+        <v>46268.832696759258</v>
       </c>
       <c r="G144" t="s">
         <v>15</v>
       </c>
       <c r="H144" t="s">
-        <v>122</v>
+        <v>55</v>
       </c>
       <c r="I144">
-        <v>13440</v>
+        <v>5000</v>
       </c>
       <c r="J144"/>
       <c r="K144"/>
       <c r="L144">
-        <v>249</v>
+        <v>46</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="s">
-        <v>146</v>
+        <v>121</v>
       </c>
       <c r="B145" t="s">
-        <v>147</v>
+        <v>122</v>
       </c>
       <c r="C145" t="s">
-        <v>148</v>
+        <v>181</v>
       </c>
       <c r="D145">
-        <v>400</v>
+        <v>2880</v>
       </c>
       <c r="E145" t="s">
-        <v>149</v>
+        <v>182</v>
       </c>
       <c r="F145" s="2">
-        <v>45185</v>
+        <v>46269.351180555554</v>
       </c>
       <c r="G145" t="s">
         <v>15</v>
       </c>
       <c r="H145" t="s">
-        <v>122</v>
+        <v>99</v>
       </c>
       <c r="I145">
-        <v>173</v>
+        <v>793</v>
       </c>
       <c r="J145"/>
       <c r="K145"/>
       <c r="L145">
-        <v>1</v>
+        <v>223</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="s">
-        <v>144</v>
+        <v>97</v>
       </c>
       <c r="B146" t="s">
-        <v>145</v>
+        <v>98</v>
       </c>
       <c r="C146" t="s">
-        <v>150</v>
+        <v>181</v>
       </c>
       <c r="D146">
-        <v>1120</v>
+        <v>10000</v>
       </c>
       <c r="E146" t="s">
-        <v>151</v>
+        <v>182</v>
       </c>
       <c r="F146" s="2">
-        <v>46267.903784722221</v>
+        <v>46267.591412037036</v>
       </c>
       <c r="G146" t="s">
         <v>15</v>
       </c>
       <c r="H146" t="s">
-        <v>122</v>
+        <v>99</v>
       </c>
       <c r="I146">
-        <v>8120</v>
+        <v>60000</v>
       </c>
       <c r="J146"/>
       <c r="K146"/>
       <c r="L146">
-        <v>74</v>
+        <v>923</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="s">
-        <v>138</v>
+        <v>183</v>
       </c>
       <c r="B147" t="s">
-        <v>139</v>
+        <v>184</v>
       </c>
       <c r="C147" t="s">
-        <v>150</v>
+        <v>181</v>
       </c>
       <c r="D147">
-        <v>1000</v>
+        <v>2500</v>
       </c>
       <c r="E147" t="s">
-        <v>151</v>
+        <v>182</v>
       </c>
       <c r="F147" s="2">
-        <v>46267.872303240736</v>
+        <v>46267.591412037036</v>
       </c>
       <c r="G147" t="s">
         <v>15</v>
       </c>
       <c r="H147" t="s">
-        <v>122</v>
+        <v>99</v>
       </c>
       <c r="I147">
-        <v>15000</v>
+        <v>40000</v>
       </c>
       <c r="J147"/>
       <c r="K147"/>
       <c r="L147">
-        <v>21</v>
+        <v>822</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="s">
-        <v>152</v>
+        <v>185</v>
       </c>
       <c r="B148" t="s">
-        <v>153</v>
+        <v>186</v>
       </c>
       <c r="C148" t="s">
-        <v>154</v>
+        <v>181</v>
       </c>
       <c r="D148">
-        <v>1</v>
+        <v>10000</v>
       </c>
       <c r="E148" t="s">
-        <v>155</v>
+        <v>182</v>
       </c>
       <c r="F148" s="2">
-        <v>46265.788981481477</v>
+        <v>46267.591412037036</v>
       </c>
       <c r="G148" t="s">
         <v>15</v>
       </c>
       <c r="H148" t="s">
-        <v>156</v>
+        <v>99</v>
       </c>
       <c r="I148">
-        <v>12</v>
+        <v>45000</v>
       </c>
       <c r="J148"/>
       <c r="K148"/>
       <c r="L148">
-        <v>14</v>
+        <v>319</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="s">
-        <v>157</v>
+        <v>187</v>
       </c>
       <c r="B149" t="s">
-        <v>158</v>
+        <v>188</v>
       </c>
       <c r="C149" t="s">
-        <v>154</v>
+        <v>181</v>
       </c>
       <c r="D149">
-        <v>1</v>
+        <v>5000</v>
       </c>
       <c r="E149" t="s">
-        <v>155</v>
+        <v>182</v>
       </c>
       <c r="F149" s="2">
-        <v>46265.776967592588</v>
+        <v>46267.591412037036</v>
       </c>
       <c r="G149" t="s">
         <v>15</v>
       </c>
       <c r="H149" t="s">
-        <v>156</v>
+        <v>99</v>
       </c>
       <c r="I149">
-        <v>45</v>
+        <v>5000</v>
       </c>
       <c r="J149"/>
       <c r="K149"/>
       <c r="L149">
-        <v>11</v>
+        <v>32</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="s">
-        <v>159</v>
+        <v>189</v>
       </c>
       <c r="B150" t="s">
-        <v>160</v>
+        <v>190</v>
       </c>
       <c r="C150" t="s">
-        <v>154</v>
+        <v>181</v>
       </c>
       <c r="D150">
-        <v>1</v>
+        <v>10000</v>
       </c>
       <c r="E150" t="s">
-        <v>155</v>
+        <v>182</v>
       </c>
       <c r="F150" s="2">
-        <v>46265.788981481477</v>
+        <v>46267.591412037036</v>
       </c>
       <c r="G150" t="s">
         <v>15</v>
       </c>
       <c r="H150" t="s">
-        <v>156</v>
+        <v>99</v>
       </c>
       <c r="I150">
-        <v>60</v>
+        <v>400000</v>
       </c>
       <c r="J150"/>
       <c r="K150"/>
       <c r="L150">
-        <v>19</v>
+        <v>963</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="B151" t="s">
-        <v>145</v>
+        <v>192</v>
       </c>
       <c r="C151" t="s">
-        <v>154</v>
+        <v>181</v>
       </c>
       <c r="D151">
-        <v>280</v>
+        <v>2</v>
       </c>
       <c r="E151" t="s">
-        <v>155</v>
+        <v>182</v>
       </c>
       <c r="F151" s="2">
-        <v>46261.786122685182</v>
+        <v>46267.591412037036</v>
       </c>
       <c r="G151" t="s">
-        <v>15</v>
+        <v>193</v>
       </c>
       <c r="H151" t="s">
-        <v>122</v>
+        <v>99</v>
       </c>
       <c r="I151">
-        <v>8120</v>
+        <v>30</v>
       </c>
       <c r="J151"/>
       <c r="K151"/>
       <c r="L151">
-        <v>167</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="s">
-        <v>144</v>
+        <v>72</v>
       </c>
       <c r="B152" t="s">
-        <v>145</v>
+        <v>73</v>
       </c>
       <c r="C152" t="s">
-        <v>161</v>
+        <v>194</v>
       </c>
       <c r="D152">
-        <v>420</v>
+        <v>36</v>
       </c>
       <c r="E152" t="s">
-        <v>162</v>
+        <v>195</v>
       </c>
       <c r="F152" s="2">
-        <v>46267.764189814814</v>
+        <v>46268.796597222223</v>
       </c>
       <c r="G152" t="s">
         <v>15</v>
       </c>
       <c r="H152" t="s">
-        <v>122</v>
-      </c>
-      <c r="I152">
-        <v>8120</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="I152"/>
       <c r="J152"/>
       <c r="K152"/>
       <c r="L152">
-        <v>131</v>
+        <v>166</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="s">
-        <v>146</v>
+        <v>196</v>
       </c>
       <c r="B153" t="s">
-        <v>147</v>
+        <v>197</v>
       </c>
       <c r="C153" t="s">
-        <v>161</v>
+        <v>194</v>
       </c>
       <c r="D153">
-        <v>260</v>
+        <v>300</v>
       </c>
       <c r="E153" t="s">
-        <v>162</v>
+        <v>195</v>
       </c>
       <c r="F153" s="2">
-        <v>46267.764189814814</v>
+        <v>46267.568553240737</v>
       </c>
       <c r="G153" t="s">
         <v>15</v>
       </c>
       <c r="H153" t="s">
-        <v>122</v>
-      </c>
-      <c r="I153">
-        <v>173</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="I153"/>
       <c r="J153"/>
       <c r="K153"/>
       <c r="L153">
-        <v>57</v>
+        <v>3</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="s">
-        <v>163</v>
+        <v>103</v>
       </c>
       <c r="B154" t="s">
-        <v>164</v>
+        <v>104</v>
       </c>
       <c r="C154" t="s">
-        <v>165</v>
+        <v>194</v>
       </c>
       <c r="D154">
-        <v>39040</v>
+        <v>237024</v>
       </c>
       <c r="E154" t="s">
-        <v>166</v>
+        <v>195</v>
       </c>
       <c r="F154" s="2">
-        <v>46267.720879629625</v>
+        <v>46268.940960648149</v>
       </c>
       <c r="G154" t="s">
         <v>15</v>
       </c>
       <c r="H154" t="s">
-        <v>23</v>
-      </c>
-      <c r="I154">
-        <v>0</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="I154"/>
       <c r="J154"/>
       <c r="K154"/>
       <c r="L154">
-        <v>1386</v>
+        <v>2296</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="s">
-        <v>42</v>
+        <v>113</v>
       </c>
       <c r="B155" t="s">
-        <v>43</v>
+        <v>114</v>
       </c>
       <c r="C155" t="s">
-        <v>165</v>
+        <v>194</v>
       </c>
       <c r="D155">
-        <v>330</v>
+        <v>274080</v>
       </c>
       <c r="E155" t="s">
-        <v>166</v>
+        <v>195</v>
       </c>
       <c r="F155" s="2">
-        <v>46267.923310185186</v>
+        <v>46269.231666666667</v>
       </c>
       <c r="G155" t="s">
         <v>15</v>
       </c>
       <c r="H155" t="s">
-        <v>44</v>
-      </c>
-      <c r="I155">
-        <v>440</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="I155"/>
       <c r="J155"/>
       <c r="K155"/>
       <c r="L155">
-        <v>11092</v>
+        <v>1777</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="s">
-        <v>167</v>
+        <v>46</v>
       </c>
       <c r="B156" t="s">
-        <v>168</v>
+        <v>47</v>
       </c>
       <c r="C156" t="s">
-        <v>165</v>
+        <v>194</v>
       </c>
       <c r="D156">
-        <v>186</v>
+        <v>1142</v>
       </c>
       <c r="E156" t="s">
-        <v>166</v>
+        <v>195</v>
       </c>
       <c r="F156" s="2">
-        <v>44946.553055555552</v>
+        <v>46269.231666666667</v>
       </c>
       <c r="G156" t="s">
         <v>15</v>
       </c>
       <c r="H156" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="I156">
-        <v>20</v>
+        <v>440</v>
       </c>
       <c r="J156"/>
       <c r="K156"/>
       <c r="L156">
-        <v>2</v>
+        <v>4968</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B157" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C157" t="s">
-        <v>165</v>
+        <v>194</v>
       </c>
       <c r="D157">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="E157" t="s">
-        <v>166</v>
+        <v>195</v>
       </c>
       <c r="F157" s="2">
-        <v>46267.923310185186</v>
+        <v>46269.231666666667</v>
       </c>
       <c r="G157" t="s">
         <v>15</v>
       </c>
       <c r="H157" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="I157">
         <v>250</v>
@@ -5959,1543 +5989,817 @@
       <c r="J157"/>
       <c r="K157"/>
       <c r="L157">
-        <v>8748</v>
+        <v>4341</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="s">
-        <v>169</v>
+        <v>51</v>
       </c>
       <c r="B158" t="s">
-        <v>170</v>
+        <v>52</v>
       </c>
       <c r="C158" t="s">
-        <v>165</v>
+        <v>194</v>
       </c>
       <c r="D158">
-        <v>93</v>
+        <v>20</v>
       </c>
       <c r="E158" t="s">
-        <v>166</v>
+        <v>195</v>
       </c>
       <c r="F158" s="2">
-        <v>45777.752291666664</v>
+        <v>46269.231666666667</v>
       </c>
       <c r="G158" t="s">
         <v>15</v>
       </c>
       <c r="H158" t="s">
-        <v>171</v>
+        <v>48</v>
       </c>
       <c r="I158">
-        <v>16</v>
+        <v>250</v>
       </c>
       <c r="J158"/>
       <c r="K158"/>
       <c r="L158">
-        <v>7</v>
+        <v>2476</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="s">
-        <v>172</v>
+        <v>53</v>
       </c>
       <c r="B159" t="s">
-        <v>173</v>
+        <v>54</v>
       </c>
       <c r="C159" t="s">
-        <v>165</v>
+        <v>194</v>
       </c>
       <c r="D159">
+        <v>36</v>
+      </c>
+      <c r="E159" t="s">
+        <v>195</v>
+      </c>
+      <c r="F159" s="2">
+        <v>46268.900347222218</v>
+      </c>
+      <c r="G159" t="s">
+        <v>15</v>
+      </c>
+      <c r="H159" t="s">
         <v>55</v>
       </c>
-      <c r="E159" t="s">
-        <v>166</v>
-      </c>
-      <c r="F159" s="2">
-        <v>44426</v>
-      </c>
-      <c r="G159" t="s">
-        <v>15</v>
-      </c>
-      <c r="H159" t="s">
-        <v>61</v>
-      </c>
       <c r="I159">
-        <v>2</v>
+        <v>5000</v>
       </c>
       <c r="J159"/>
       <c r="K159"/>
       <c r="L159">
-        <v>5</v>
+        <v>2629</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="s">
-        <v>59</v>
+        <v>113</v>
       </c>
       <c r="B160" t="s">
-        <v>60</v>
+        <v>114</v>
       </c>
       <c r="C160" t="s">
-        <v>165</v>
+        <v>198</v>
       </c>
       <c r="D160">
-        <v>7</v>
+        <v>95040</v>
       </c>
       <c r="E160" t="s">
-        <v>166</v>
+        <v>199</v>
       </c>
       <c r="F160" s="2">
-        <v>46267.720879629625</v>
+        <v>46267</v>
       </c>
       <c r="G160" t="s">
         <v>15</v>
       </c>
       <c r="H160" t="s">
-        <v>61</v>
-      </c>
-      <c r="I160">
-        <v>5000</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="I160"/>
       <c r="J160"/>
       <c r="K160"/>
       <c r="L160">
-        <v>2484</v>
+        <v>357</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="B161" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="C161" t="s">
-        <v>174</v>
+        <v>198</v>
       </c>
       <c r="D161">
-        <v>300</v>
+        <v>84480</v>
       </c>
       <c r="E161" t="s">
-        <v>175</v>
+        <v>199</v>
       </c>
       <c r="F161" s="2">
-        <v>46266.533495370371</v>
+        <v>46267</v>
       </c>
       <c r="G161" t="s">
         <v>15</v>
       </c>
       <c r="H161" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="I161"/>
       <c r="J161"/>
       <c r="K161"/>
       <c r="L161">
-        <v>417</v>
+        <v>39</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="s">
-        <v>98</v>
+        <v>46</v>
       </c>
       <c r="B162" t="s">
-        <v>99</v>
+        <v>47</v>
       </c>
       <c r="C162" t="s">
-        <v>174</v>
+        <v>198</v>
       </c>
       <c r="D162">
-        <v>576</v>
+        <v>748</v>
       </c>
       <c r="E162" t="s">
-        <v>175</v>
+        <v>199</v>
       </c>
       <c r="F162" s="2">
-        <v>46267.749340277776</v>
+        <v>46267</v>
       </c>
       <c r="G162" t="s">
         <v>15</v>
       </c>
       <c r="H162" t="s">
-        <v>23</v>
-      </c>
-      <c r="I162"/>
+        <v>48</v>
+      </c>
+      <c r="I162">
+        <v>440</v>
+      </c>
       <c r="J162"/>
       <c r="K162"/>
       <c r="L162">
-        <v>436</v>
+        <v>1570</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="s">
-        <v>176</v>
+        <v>49</v>
       </c>
       <c r="B163" t="s">
-        <v>177</v>
+        <v>50</v>
       </c>
       <c r="C163" t="s">
-        <v>174</v>
+        <v>198</v>
       </c>
       <c r="D163">
-        <v>2160</v>
+        <v>34</v>
       </c>
       <c r="E163" t="s">
-        <v>175</v>
+        <v>199</v>
       </c>
       <c r="F163" s="2">
-        <v>46267.751342592594</v>
+        <v>46267</v>
       </c>
       <c r="G163" t="s">
         <v>15</v>
       </c>
       <c r="H163" t="s">
-        <v>23</v>
-      </c>
-      <c r="I163"/>
+        <v>48</v>
+      </c>
+      <c r="I163">
+        <v>250</v>
+      </c>
       <c r="J163"/>
       <c r="K163"/>
       <c r="L163">
-        <v>51</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="s">
-        <v>116</v>
+        <v>51</v>
       </c>
       <c r="B164" t="s">
-        <v>117</v>
+        <v>52</v>
       </c>
       <c r="C164" t="s">
-        <v>174</v>
+        <v>198</v>
       </c>
       <c r="D164">
-        <v>300</v>
+        <v>17</v>
       </c>
       <c r="E164" t="s">
-        <v>175</v>
+        <v>199</v>
       </c>
       <c r="F164" s="2">
-        <v>46267.858819444446</v>
+        <v>46267</v>
       </c>
       <c r="G164" t="s">
         <v>15</v>
       </c>
       <c r="H164" t="s">
-        <v>23</v>
-      </c>
-      <c r="I164"/>
+        <v>48</v>
+      </c>
+      <c r="I164">
+        <v>250</v>
+      </c>
       <c r="J164"/>
       <c r="K164"/>
       <c r="L164">
-        <v>531</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="s">
-        <v>178</v>
+        <v>53</v>
       </c>
       <c r="B165" t="s">
-        <v>179</v>
+        <v>54</v>
       </c>
       <c r="C165" t="s">
-        <v>174</v>
+        <v>198</v>
       </c>
       <c r="D165">
-        <v>720</v>
+        <v>34</v>
       </c>
       <c r="E165" t="s">
-        <v>175</v>
+        <v>199</v>
       </c>
       <c r="F165" s="2">
-        <v>46266.710902777777</v>
+        <v>46267</v>
       </c>
       <c r="G165" t="s">
         <v>15</v>
       </c>
       <c r="H165" t="s">
-        <v>23</v>
-      </c>
-      <c r="I165"/>
+        <v>55</v>
+      </c>
+      <c r="I165">
+        <v>5000</v>
+      </c>
       <c r="J165"/>
       <c r="K165"/>
       <c r="L165">
-        <v>1</v>
+        <v>764</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="s">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="B166" t="s">
-        <v>181</v>
+        <v>201</v>
       </c>
       <c r="C166" t="s">
-        <v>174</v>
+        <v>202</v>
       </c>
       <c r="D166">
-        <v>1440</v>
+        <v>1000000</v>
       </c>
       <c r="E166" t="s">
-        <v>175</v>
+        <v>203</v>
       </c>
       <c r="F166" s="2">
-        <v>46267.986307870371</v>
+        <v>46235</v>
       </c>
       <c r="G166" t="s">
-        <v>15</v>
+        <v>204</v>
       </c>
       <c r="H166" t="s">
-        <v>23</v>
-      </c>
-      <c r="I166"/>
+        <v>205</v>
+      </c>
+      <c r="I166">
+        <v>1000000</v>
+      </c>
       <c r="J166"/>
       <c r="K166"/>
       <c r="L166">
-        <v>385</v>
+        <v>49</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="s">
-        <v>182</v>
+        <v>206</v>
       </c>
       <c r="B167" t="s">
-        <v>183</v>
+        <v>207</v>
       </c>
       <c r="C167" t="s">
-        <v>184</v>
+        <v>208</v>
       </c>
       <c r="D167">
-        <v>800</v>
+        <v>5060000</v>
       </c>
       <c r="E167" t="s">
-        <v>185</v>
+        <v>209</v>
       </c>
       <c r="F167" s="2">
-        <v>46268.339062499996</v>
+        <v>46239</v>
       </c>
       <c r="G167" t="s">
-        <v>15</v>
+        <v>204</v>
       </c>
       <c r="H167" t="s">
-        <v>186</v>
+        <v>205</v>
       </c>
       <c r="I167">
-        <v>884</v>
+        <v>5060000</v>
       </c>
       <c r="J167"/>
       <c r="K167"/>
       <c r="L167">
-        <v>1609</v>
+        <v>157</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="s">
-        <v>130</v>
+        <v>210</v>
       </c>
       <c r="B168" t="s">
-        <v>131</v>
+        <v>211</v>
       </c>
       <c r="C168" t="s">
-        <v>184</v>
+        <v>208</v>
       </c>
       <c r="D168">
-        <v>10000</v>
+        <v>2439100</v>
       </c>
       <c r="E168" t="s">
-        <v>185</v>
+        <v>209</v>
       </c>
       <c r="F168" s="2">
-        <v>46267.591412037036</v>
+        <v>46235</v>
       </c>
       <c r="G168" t="s">
-        <v>15</v>
+        <v>204</v>
       </c>
       <c r="H168" t="s">
-        <v>122</v>
+        <v>205</v>
       </c>
       <c r="I168">
-        <v>60000</v>
+        <v>800000</v>
       </c>
       <c r="J168"/>
       <c r="K168"/>
       <c r="L168">
-        <v>923</v>
+        <v>54</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="s">
-        <v>187</v>
+        <v>212</v>
       </c>
       <c r="B169" t="s">
-        <v>188</v>
+        <v>213</v>
       </c>
       <c r="C169" t="s">
-        <v>184</v>
+        <v>208</v>
       </c>
       <c r="D169">
-        <v>2500</v>
+        <v>880000</v>
       </c>
       <c r="E169" t="s">
-        <v>185</v>
+        <v>209</v>
       </c>
       <c r="F169" s="2">
-        <v>46267.591412037036</v>
+        <v>46235</v>
       </c>
       <c r="G169" t="s">
-        <v>15</v>
+        <v>204</v>
       </c>
       <c r="H169" t="s">
-        <v>122</v>
+        <v>205</v>
       </c>
       <c r="I169">
-        <v>35000</v>
+        <v>880000</v>
       </c>
       <c r="J169"/>
       <c r="K169"/>
       <c r="L169">
-        <v>822</v>
+        <v>43</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="s">
-        <v>189</v>
+        <v>214</v>
       </c>
       <c r="B170" t="s">
-        <v>190</v>
+        <v>215</v>
       </c>
       <c r="C170" t="s">
-        <v>184</v>
+        <v>208</v>
       </c>
       <c r="D170">
-        <v>10000</v>
+        <v>104000</v>
       </c>
       <c r="E170" t="s">
-        <v>185</v>
+        <v>209</v>
       </c>
       <c r="F170" s="2">
-        <v>46267.591412037036</v>
+        <v>46258</v>
       </c>
       <c r="G170" t="s">
-        <v>15</v>
+        <v>204</v>
       </c>
       <c r="H170" t="s">
-        <v>122</v>
+        <v>205</v>
       </c>
       <c r="I170">
-        <v>45000</v>
+        <v>52000</v>
       </c>
       <c r="J170"/>
       <c r="K170"/>
       <c r="L170">
-        <v>319</v>
+        <v>53</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="s">
-        <v>191</v>
+        <v>216</v>
       </c>
       <c r="B171" t="s">
-        <v>192</v>
+        <v>217</v>
       </c>
       <c r="C171" t="s">
-        <v>184</v>
+        <v>218</v>
       </c>
       <c r="D171">
-        <v>5000</v>
+        <v>2</v>
       </c>
       <c r="E171" t="s">
-        <v>185</v>
+        <v>219</v>
       </c>
       <c r="F171" s="2">
-        <v>46267.591412037036</v>
+        <v>46268.56618055555</v>
       </c>
       <c r="G171" t="s">
-        <v>15</v>
+        <v>220</v>
       </c>
       <c r="H171" t="s">
-        <v>122</v>
+        <v>99</v>
       </c>
       <c r="I171">
-        <v>5000</v>
+        <v>2</v>
       </c>
       <c r="J171"/>
       <c r="K171"/>
       <c r="L171">
-        <v>32</v>
+        <v>1</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="s">
-        <v>134</v>
+        <v>221</v>
       </c>
       <c r="B172" t="s">
-        <v>135</v>
+        <v>222</v>
       </c>
       <c r="C172" t="s">
-        <v>184</v>
+        <v>218</v>
       </c>
       <c r="D172">
-        <v>10000</v>
+        <v>300</v>
       </c>
       <c r="E172" t="s">
-        <v>185</v>
+        <v>219</v>
       </c>
       <c r="F172" s="2">
-        <v>46267.591412037036</v>
+        <v>46268.65243055555</v>
       </c>
       <c r="G172" t="s">
         <v>15</v>
       </c>
       <c r="H172" t="s">
-        <v>122</v>
+        <v>223</v>
       </c>
       <c r="I172">
-        <v>290000</v>
+        <v>300</v>
       </c>
       <c r="J172"/>
       <c r="K172"/>
       <c r="L172">
-        <v>963</v>
+        <v>3</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="s">
-        <v>127</v>
+        <v>224</v>
       </c>
       <c r="B173" t="s">
-        <v>128</v>
+        <v>225</v>
       </c>
       <c r="C173" t="s">
-        <v>184</v>
+        <v>218</v>
       </c>
       <c r="D173">
+        <v>3</v>
+      </c>
+      <c r="E173" t="s">
+        <v>219</v>
+      </c>
+      <c r="F173" s="2">
+        <v>46262.311388888884</v>
+      </c>
+      <c r="G173" t="s">
+        <v>226</v>
+      </c>
+      <c r="H173" t="s">
+        <v>55</v>
+      </c>
+      <c r="I173">
         <v>2</v>
-      </c>
-      <c r="E173" t="s">
-        <v>185</v>
-      </c>
-      <c r="F173" s="2">
-        <v>46267.591412037036</v>
-      </c>
-      <c r="G173" t="s">
-        <v>129</v>
-      </c>
-      <c r="H173" t="s">
-        <v>122</v>
-      </c>
-      <c r="I173">
-        <v>30</v>
       </c>
       <c r="J173"/>
       <c r="K173"/>
       <c r="L173">
-        <v>1061</v>
+        <v>1</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="s">
-        <v>193</v>
+        <v>227</v>
       </c>
       <c r="B174" t="s">
-        <v>194</v>
+        <v>228</v>
       </c>
       <c r="C174" t="s">
-        <v>195</v>
+        <v>218</v>
       </c>
       <c r="D174">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="E174" t="s">
-        <v>196</v>
+        <v>219</v>
       </c>
       <c r="F174" s="2">
-        <v>46267.568553240737</v>
+        <v>46268.664467592593</v>
       </c>
       <c r="G174" t="s">
         <v>15</v>
       </c>
       <c r="H174" t="s">
-        <v>23</v>
-      </c>
-      <c r="I174"/>
+        <v>229</v>
+      </c>
+      <c r="I174">
+        <v>1</v>
+      </c>
       <c r="J174"/>
       <c r="K174"/>
       <c r="L174">
-        <v>165</v>
+        <v>1</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="s">
-        <v>197</v>
+        <v>230</v>
       </c>
       <c r="B175" t="s">
-        <v>198</v>
+        <v>231</v>
       </c>
       <c r="C175" t="s">
-        <v>195</v>
+        <v>218</v>
       </c>
       <c r="D175">
-        <v>300</v>
+        <v>17</v>
       </c>
       <c r="E175" t="s">
-        <v>196</v>
+        <v>219</v>
       </c>
       <c r="F175" s="2">
-        <v>46267.568553240737</v>
+        <v>46268.665104166663</v>
       </c>
       <c r="G175" t="s">
         <v>15</v>
       </c>
       <c r="H175" t="s">
-        <v>23</v>
-      </c>
-      <c r="I175"/>
+        <v>229</v>
+      </c>
+      <c r="I175">
+        <v>20</v>
+      </c>
       <c r="J175"/>
       <c r="K175"/>
       <c r="L175">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="s">
-        <v>98</v>
+        <v>232</v>
       </c>
       <c r="B176" t="s">
-        <v>99</v>
+        <v>233</v>
       </c>
       <c r="C176" t="s">
-        <v>195</v>
+        <v>218</v>
       </c>
       <c r="D176">
-        <v>127584</v>
+        <v>20</v>
       </c>
       <c r="E176" t="s">
-        <v>196</v>
+        <v>219</v>
       </c>
       <c r="F176" s="2">
-        <v>46268.106261574074</v>
+        <v>46268.656412037039</v>
       </c>
       <c r="G176" t="s">
         <v>15</v>
       </c>
       <c r="H176" t="s">
-        <v>23</v>
-      </c>
-      <c r="I176"/>
+        <v>229</v>
+      </c>
+      <c r="I176">
+        <v>20</v>
+      </c>
       <c r="J176"/>
       <c r="K176"/>
       <c r="L176">
-        <v>2290</v>
+        <v>1</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="s">
-        <v>106</v>
+        <v>234</v>
       </c>
       <c r="B177" t="s">
-        <v>107</v>
+        <v>235</v>
       </c>
       <c r="C177" t="s">
-        <v>195</v>
+        <v>218</v>
       </c>
       <c r="D177">
-        <v>316800</v>
+        <v>8</v>
       </c>
       <c r="E177" t="s">
-        <v>196</v>
+        <v>219</v>
       </c>
       <c r="F177" s="2">
-        <v>46268.22378472222</v>
+        <v>46268.655486111107</v>
       </c>
       <c r="G177" t="s">
         <v>15</v>
       </c>
       <c r="H177" t="s">
-        <v>23</v>
-      </c>
-      <c r="I177"/>
+        <v>229</v>
+      </c>
+      <c r="I177">
+        <v>11</v>
+      </c>
       <c r="J177"/>
       <c r="K177"/>
       <c r="L177">
-        <v>1773</v>
+        <v>7</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="s">
-        <v>102</v>
+        <v>214</v>
       </c>
       <c r="B178" t="s">
-        <v>103</v>
+        <v>215</v>
       </c>
       <c r="C178" t="s">
-        <v>195</v>
+        <v>236</v>
       </c>
       <c r="D178">
-        <v>289920</v>
+        <v>104000</v>
       </c>
       <c r="E178" t="s">
-        <v>196</v>
+        <v>237</v>
       </c>
       <c r="F178" s="2">
-        <v>46268.22378472222</v>
+        <v>46235</v>
       </c>
       <c r="G178" t="s">
-        <v>15</v>
+        <v>204</v>
       </c>
       <c r="H178" t="s">
-        <v>23</v>
-      </c>
-      <c r="I178"/>
+        <v>205</v>
+      </c>
+      <c r="I178">
+        <v>52000</v>
+      </c>
       <c r="J178"/>
       <c r="K178"/>
       <c r="L178">
-        <v>198</v>
+        <v>47</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="s">
-        <v>42</v>
+        <v>238</v>
       </c>
       <c r="B179" t="s">
-        <v>43</v>
+        <v>239</v>
       </c>
       <c r="C179" t="s">
-        <v>195</v>
+        <v>240</v>
       </c>
       <c r="D179">
-        <v>2528</v>
+        <v>82407</v>
       </c>
       <c r="E179" t="s">
-        <v>196</v>
+        <v>241</v>
       </c>
       <c r="F179" s="2">
-        <v>46268.22378472222</v>
+        <v>46268</v>
       </c>
       <c r="G179" t="s">
         <v>15</v>
       </c>
       <c r="H179" t="s">
-        <v>44</v>
-      </c>
-      <c r="I179">
-        <v>440</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="I179"/>
       <c r="J179"/>
       <c r="K179"/>
       <c r="L179">
-        <v>4963</v>
+        <v>554</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="s">
-        <v>45</v>
+        <v>242</v>
       </c>
       <c r="B180" t="s">
-        <v>46</v>
+        <v>243</v>
       </c>
       <c r="C180" t="s">
-        <v>195</v>
+        <v>244</v>
       </c>
       <c r="D180">
-        <v>154</v>
+        <v>1040</v>
       </c>
       <c r="E180" t="s">
-        <v>196</v>
+        <v>245</v>
       </c>
       <c r="F180" s="2">
-        <v>46268.22378472222</v>
+        <v>46268.533379629625</v>
       </c>
       <c r="G180" t="s">
-        <v>15</v>
+        <v>204</v>
       </c>
       <c r="H180" t="s">
-        <v>44</v>
+        <v>246</v>
       </c>
       <c r="I180">
-        <v>250</v>
+        <v>520</v>
       </c>
       <c r="J180"/>
       <c r="K180"/>
       <c r="L180">
-        <v>4335</v>
+        <v>52</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="s">
-        <v>47</v>
+        <v>247</v>
       </c>
       <c r="B181" t="s">
-        <v>48</v>
+        <v>248</v>
       </c>
       <c r="C181" t="s">
-        <v>195</v>
+        <v>244</v>
       </c>
       <c r="D181">
-        <v>62</v>
+        <v>10000</v>
       </c>
       <c r="E181" t="s">
-        <v>196</v>
+        <v>245</v>
       </c>
       <c r="F181" s="2">
-        <v>46268.22378472222</v>
+        <v>46268.533379629625</v>
       </c>
       <c r="G181" t="s">
-        <v>15</v>
+        <v>204</v>
       </c>
       <c r="H181" t="s">
-        <v>44</v>
+        <v>246</v>
       </c>
       <c r="I181">
-        <v>250</v>
+        <v>5000</v>
       </c>
       <c r="J181"/>
       <c r="K181"/>
       <c r="L181">
-        <v>2473</v>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="s">
-        <v>106</v>
-      </c>
-      <c r="B182" t="s">
-        <v>107</v>
-      </c>
-      <c r="C182" t="s">
-        <v>199</v>
-      </c>
-      <c r="D182">
-        <v>95040</v>
-      </c>
-      <c r="E182" t="s">
-        <v>200</v>
-      </c>
-      <c r="F182" s="2">
-        <v>46267</v>
-      </c>
-      <c r="G182" t="s">
-        <v>15</v>
-      </c>
-      <c r="H182" t="s">
-        <v>23</v>
-      </c>
-      <c r="I182"/>
-      <c r="J182"/>
-      <c r="K182"/>
-      <c r="L182">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="s">
-        <v>102</v>
-      </c>
-      <c r="B183" t="s">
-        <v>103</v>
-      </c>
-      <c r="C183" t="s">
-        <v>199</v>
-      </c>
-      <c r="D183">
-        <v>84480</v>
-      </c>
-      <c r="E183" t="s">
-        <v>200</v>
-      </c>
-      <c r="F183" s="2">
-        <v>46267</v>
-      </c>
-      <c r="G183" t="s">
-        <v>15</v>
-      </c>
-      <c r="H183" t="s">
-        <v>23</v>
-      </c>
-      <c r="I183"/>
-      <c r="J183"/>
-      <c r="K183"/>
-      <c r="L183">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" t="s">
-        <v>42</v>
-      </c>
-      <c r="B184" t="s">
-        <v>43</v>
-      </c>
-      <c r="C184" t="s">
-        <v>199</v>
-      </c>
-      <c r="D184">
-        <v>748</v>
-      </c>
-      <c r="E184" t="s">
-        <v>200</v>
-      </c>
-      <c r="F184" s="2">
-        <v>46267</v>
-      </c>
-      <c r="G184" t="s">
-        <v>15</v>
-      </c>
-      <c r="H184" t="s">
-        <v>44</v>
-      </c>
-      <c r="I184">
-        <v>440</v>
-      </c>
-      <c r="J184"/>
-      <c r="K184"/>
-      <c r="L184">
-        <v>1570</v>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="s">
-        <v>45</v>
-      </c>
-      <c r="B185" t="s">
-        <v>46</v>
-      </c>
-      <c r="C185" t="s">
-        <v>199</v>
-      </c>
-      <c r="D185">
-        <v>34</v>
-      </c>
-      <c r="E185" t="s">
-        <v>200</v>
-      </c>
-      <c r="F185" s="2">
-        <v>46267</v>
-      </c>
-      <c r="G185" t="s">
-        <v>15</v>
-      </c>
-      <c r="H185" t="s">
-        <v>44</v>
-      </c>
-      <c r="I185">
-        <v>250</v>
-      </c>
-      <c r="J185"/>
-      <c r="K185"/>
-      <c r="L185">
-        <v>1146</v>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" t="s">
-        <v>47</v>
-      </c>
-      <c r="B186" t="s">
-        <v>48</v>
-      </c>
-      <c r="C186" t="s">
-        <v>199</v>
-      </c>
-      <c r="D186">
-        <v>17</v>
-      </c>
-      <c r="E186" t="s">
-        <v>200</v>
-      </c>
-      <c r="F186" s="2">
-        <v>46267</v>
-      </c>
-      <c r="G186" t="s">
-        <v>15</v>
-      </c>
-      <c r="H186" t="s">
-        <v>44</v>
-      </c>
-      <c r="I186">
-        <v>250</v>
-      </c>
-      <c r="J186"/>
-      <c r="K186"/>
-      <c r="L186">
-        <v>1019</v>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" t="s">
-        <v>59</v>
-      </c>
-      <c r="B187" t="s">
-        <v>60</v>
-      </c>
-      <c r="C187" t="s">
-        <v>199</v>
-      </c>
-      <c r="D187">
-        <v>34</v>
-      </c>
-      <c r="E187" t="s">
-        <v>200</v>
-      </c>
-      <c r="F187" s="2">
-        <v>46267</v>
-      </c>
-      <c r="G187" t="s">
-        <v>15</v>
-      </c>
-      <c r="H187" t="s">
-        <v>61</v>
-      </c>
-      <c r="I187">
-        <v>5000</v>
-      </c>
-      <c r="J187"/>
-      <c r="K187"/>
-      <c r="L187">
-        <v>764</v>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" t="s">
-        <v>201</v>
-      </c>
-      <c r="B188" t="s">
-        <v>202</v>
-      </c>
-      <c r="C188" t="s">
-        <v>203</v>
-      </c>
-      <c r="D188">
-        <v>1000000</v>
-      </c>
-      <c r="E188" t="s">
-        <v>204</v>
-      </c>
-      <c r="F188" s="2">
-        <v>46235</v>
-      </c>
-      <c r="G188" t="s">
-        <v>205</v>
-      </c>
-      <c r="H188" t="s">
-        <v>206</v>
-      </c>
-      <c r="I188">
-        <v>1000000</v>
-      </c>
-      <c r="J188"/>
-      <c r="K188"/>
-      <c r="L188">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="s">
-        <v>207</v>
-      </c>
-      <c r="B189" t="s">
-        <v>208</v>
-      </c>
-      <c r="C189" t="s">
-        <v>209</v>
-      </c>
-      <c r="D189">
-        <v>5060000</v>
-      </c>
-      <c r="E189" t="s">
-        <v>210</v>
-      </c>
-      <c r="F189" s="2">
-        <v>46239</v>
-      </c>
-      <c r="G189" t="s">
-        <v>205</v>
-      </c>
-      <c r="H189" t="s">
-        <v>206</v>
-      </c>
-      <c r="I189">
-        <v>5060000</v>
-      </c>
-      <c r="J189"/>
-      <c r="K189"/>
-      <c r="L189">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" t="s">
-        <v>211</v>
-      </c>
-      <c r="B190" t="s">
-        <v>212</v>
-      </c>
-      <c r="C190" t="s">
-        <v>209</v>
-      </c>
-      <c r="D190">
-        <v>2439100</v>
-      </c>
-      <c r="E190" t="s">
-        <v>210</v>
-      </c>
-      <c r="F190" s="2">
-        <v>46235</v>
-      </c>
-      <c r="G190" t="s">
-        <v>205</v>
-      </c>
-      <c r="H190" t="s">
-        <v>206</v>
-      </c>
-      <c r="I190">
-        <v>800000</v>
-      </c>
-      <c r="J190"/>
-      <c r="K190"/>
-      <c r="L190">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" t="s">
-        <v>213</v>
-      </c>
-      <c r="B191" t="s">
-        <v>214</v>
-      </c>
-      <c r="C191" t="s">
-        <v>209</v>
-      </c>
-      <c r="D191">
-        <v>880000</v>
-      </c>
-      <c r="E191" t="s">
-        <v>210</v>
-      </c>
-      <c r="F191" s="2">
-        <v>46235</v>
-      </c>
-      <c r="G191" t="s">
-        <v>205</v>
-      </c>
-      <c r="H191" t="s">
-        <v>206</v>
-      </c>
-      <c r="I191">
-        <v>880000</v>
-      </c>
-      <c r="J191"/>
-      <c r="K191"/>
-      <c r="L191">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" t="s">
-        <v>215</v>
-      </c>
-      <c r="B192" t="s">
-        <v>216</v>
-      </c>
-      <c r="C192" t="s">
-        <v>209</v>
-      </c>
-      <c r="D192">
-        <v>104000</v>
-      </c>
-      <c r="E192" t="s">
-        <v>210</v>
-      </c>
-      <c r="F192" s="2">
-        <v>46258</v>
-      </c>
-      <c r="G192" t="s">
-        <v>205</v>
-      </c>
-      <c r="H192" t="s">
-        <v>206</v>
-      </c>
-      <c r="I192">
-        <v>52000</v>
-      </c>
-      <c r="J192"/>
-      <c r="K192"/>
-      <c r="L192">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" t="s">
-        <v>217</v>
-      </c>
-      <c r="B193" t="s">
-        <v>218</v>
-      </c>
-      <c r="C193" t="s">
-        <v>219</v>
-      </c>
-      <c r="D193">
-        <v>3</v>
-      </c>
-      <c r="E193" t="s">
-        <v>220</v>
-      </c>
-      <c r="F193" s="2">
-        <v>46262.311388888884</v>
-      </c>
-      <c r="G193" t="s">
-        <v>221</v>
-      </c>
-      <c r="H193" t="s">
-        <v>61</v>
-      </c>
-      <c r="I193">
-        <v>2</v>
-      </c>
-      <c r="J193"/>
-      <c r="K193"/>
-      <c r="L193">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" t="s">
-        <v>222</v>
-      </c>
-      <c r="B194" t="s">
-        <v>223</v>
-      </c>
-      <c r="C194" t="s">
-        <v>219</v>
-      </c>
-      <c r="D194">
-        <v>2</v>
-      </c>
-      <c r="E194" t="s">
-        <v>220</v>
-      </c>
-      <c r="F194" s="2">
-        <v>46261.675902777773</v>
-      </c>
-      <c r="G194" t="s">
-        <v>15</v>
-      </c>
-      <c r="H194" t="s">
-        <v>224</v>
-      </c>
-      <c r="I194">
-        <v>20</v>
-      </c>
-      <c r="J194"/>
-      <c r="K194"/>
-      <c r="L194">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" t="s">
-        <v>118</v>
-      </c>
-      <c r="B195" t="s">
-        <v>119</v>
-      </c>
-      <c r="C195" t="s">
-        <v>225</v>
-      </c>
-      <c r="D195">
-        <v>2700</v>
-      </c>
-      <c r="E195" t="s">
-        <v>226</v>
-      </c>
-      <c r="F195" s="2">
-        <v>46268.327569444446</v>
-      </c>
-      <c r="G195" t="s">
-        <v>15</v>
-      </c>
-      <c r="H195" t="s">
-        <v>122</v>
-      </c>
-      <c r="I195">
-        <v>793</v>
-      </c>
-      <c r="J195"/>
-      <c r="K195"/>
-      <c r="L195">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" t="s">
-        <v>130</v>
-      </c>
-      <c r="B196" t="s">
-        <v>131</v>
-      </c>
-      <c r="C196" t="s">
-        <v>225</v>
-      </c>
-      <c r="D196">
-        <v>20000</v>
-      </c>
-      <c r="E196" t="s">
-        <v>226</v>
-      </c>
-      <c r="F196" s="2">
-        <v>46268.327569444446</v>
-      </c>
-      <c r="G196" t="s">
-        <v>15</v>
-      </c>
-      <c r="H196" t="s">
-        <v>122</v>
-      </c>
-      <c r="I196">
-        <v>60000</v>
-      </c>
-      <c r="J196"/>
-      <c r="K196"/>
-      <c r="L196">
-        <v>962</v>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" t="s">
-        <v>187</v>
-      </c>
-      <c r="B197" t="s">
-        <v>188</v>
-      </c>
-      <c r="C197" t="s">
-        <v>225</v>
-      </c>
-      <c r="D197">
-        <v>5000</v>
-      </c>
-      <c r="E197" t="s">
-        <v>226</v>
-      </c>
-      <c r="F197" s="2">
-        <v>46268.327569444446</v>
-      </c>
-      <c r="G197" t="s">
-        <v>15</v>
-      </c>
-      <c r="H197" t="s">
-        <v>122</v>
-      </c>
-      <c r="I197">
-        <v>35000</v>
-      </c>
-      <c r="J197"/>
-      <c r="K197"/>
-      <c r="L197">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" t="s">
-        <v>146</v>
-      </c>
-      <c r="B198" t="s">
-        <v>147</v>
-      </c>
-      <c r="C198" t="s">
-        <v>225</v>
-      </c>
-      <c r="D198">
-        <v>1000</v>
-      </c>
-      <c r="E198" t="s">
-        <v>226</v>
-      </c>
-      <c r="F198" s="2">
-        <v>46268.327569444446</v>
-      </c>
-      <c r="G198" t="s">
-        <v>15</v>
-      </c>
-      <c r="H198" t="s">
-        <v>122</v>
-      </c>
-      <c r="I198">
-        <v>173</v>
-      </c>
-      <c r="J198"/>
-      <c r="K198"/>
-      <c r="L198">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" t="s">
-        <v>227</v>
-      </c>
-      <c r="B199" t="s">
-        <v>228</v>
-      </c>
-      <c r="C199" t="s">
-        <v>225</v>
-      </c>
-      <c r="D199">
-        <v>500</v>
-      </c>
-      <c r="E199" t="s">
-        <v>226</v>
-      </c>
-      <c r="F199" s="2">
-        <v>46268.327569444446</v>
-      </c>
-      <c r="G199" t="s">
-        <v>15</v>
-      </c>
-      <c r="H199" t="s">
-        <v>229</v>
-      </c>
-      <c r="I199">
-        <v>11</v>
-      </c>
-      <c r="J199"/>
-      <c r="K199"/>
-      <c r="L199">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" t="s">
-        <v>215</v>
-      </c>
-      <c r="B200" t="s">
-        <v>216</v>
-      </c>
-      <c r="C200" t="s">
-        <v>230</v>
-      </c>
-      <c r="D200">
-        <v>104000</v>
-      </c>
-      <c r="E200" t="s">
-        <v>231</v>
-      </c>
-      <c r="F200" s="2">
-        <v>46235</v>
-      </c>
-      <c r="G200" t="s">
-        <v>205</v>
-      </c>
-      <c r="H200" t="s">
-        <v>206</v>
-      </c>
-      <c r="I200">
-        <v>52000</v>
-      </c>
-      <c r="J200"/>
-      <c r="K200"/>
-      <c r="L200">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" t="s">
-        <v>232</v>
-      </c>
-      <c r="B201" t="s">
-        <v>233</v>
-      </c>
-      <c r="C201" t="s">
-        <v>234</v>
-      </c>
-      <c r="D201">
-        <v>49200</v>
-      </c>
-      <c r="E201" t="s">
-        <v>235</v>
-      </c>
-      <c r="F201" s="2">
-        <v>46267</v>
-      </c>
-      <c r="G201" t="s">
-        <v>15</v>
-      </c>
-      <c r="H201" t="s">
-        <v>23</v>
-      </c>
-      <c r="I201"/>
-      <c r="J201"/>
-      <c r="K201"/>
-      <c r="L201">
-        <v>552</v>
-      </c>
-    </row>
-    <row r="202">
-      <c r="A202" t="s">
-        <v>236</v>
-      </c>
-      <c r="B202" t="s">
-        <v>237</v>
-      </c>
-      <c r="C202" t="s">
-        <v>238</v>
-      </c>
-      <c r="D202">
-        <v>520</v>
-      </c>
-      <c r="E202" t="s">
-        <v>239</v>
-      </c>
-      <c r="F202" s="2">
-        <v>46265.37394675926</v>
-      </c>
-      <c r="G202" t="s">
-        <v>205</v>
-      </c>
-      <c r="H202" t="s">
-        <v>240</v>
-      </c>
-      <c r="I202">
-        <v>520</v>
-      </c>
-      <c r="J202"/>
-      <c r="K202"/>
-      <c r="L202">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" t="s">
-        <v>241</v>
-      </c>
-      <c r="B203" t="s">
-        <v>242</v>
-      </c>
-      <c r="C203" t="s">
-        <v>238</v>
-      </c>
-      <c r="D203">
-        <v>5000</v>
-      </c>
-      <c r="E203" t="s">
-        <v>239</v>
-      </c>
-      <c r="F203" s="2">
-        <v>46265.37394675926</v>
-      </c>
-      <c r="G203" t="s">
-        <v>205</v>
-      </c>
-      <c r="H203" t="s">
-        <v>240</v>
-      </c>
-      <c r="I203">
-        <v>5000</v>
-      </c>
-      <c r="J203"/>
-      <c r="K203"/>
-      <c r="L203">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
   </sheetData>

--- a/Inventarios.xlsx
+++ b/Inventarios.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheets>
-    <sheet name="Inventarios" sheetId="1" r:id="R6e6546b951ec46d1"/>
+    <sheet name="Inventarios" sheetId="1" r:id="R4fc03b847b5f4bc0"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="249" xml:space="preserve">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="244" xml:space="preserve">
   <si>
     <t>codigo_articulo</t>
   </si>
@@ -43,10 +43,10 @@
     <t>consecutivo</t>
   </si>
   <si>
-    <t>112301</t>
-  </si>
-  <si>
-    <t>HUEVO L X 30 PET</t>
+    <t>142111</t>
+  </si>
+  <si>
+    <t>BARRA DE PROTEINA 50 GR ARANDANO DISPLAY X 4 CAJA X 48</t>
   </si>
   <si>
     <t>VT1</t>
@@ -58,70 +58,214 @@
     <t>UN</t>
   </si>
   <si>
+    <t>BP</t>
+  </si>
+  <si>
+    <t>143241</t>
+  </si>
+  <si>
+    <t>BARRA DE PROTEINA 30 GR CHOCOLATE DISPLAY X 6 CAJA X 72</t>
+  </si>
+  <si>
+    <t>2110202</t>
+  </si>
+  <si>
+    <t>HUEVO XL X 30 CARTON VERDE CANASTA</t>
+  </si>
+  <si>
+    <t>VT3</t>
+  </si>
+  <si>
+    <t>TAT MEDELLIN - INVENTARIO TRANSITO</t>
+  </si>
+  <si>
     <t>HU</t>
   </si>
   <si>
+    <t>AFCA022</t>
+  </si>
+  <si>
+    <t>CANASTA KIKES 63  X 32 X  23</t>
+  </si>
+  <si>
+    <t>AF</t>
+  </si>
+  <si>
+    <t>AFES013</t>
+  </si>
+  <si>
+    <t>ESTIBAS OVOID 124CM X 65CM</t>
+  </si>
+  <si>
+    <t>AFSE003</t>
+  </si>
+  <si>
+    <t>SEPARADORES OVOID DE 124CM X 66CM</t>
+  </si>
+  <si>
+    <t>MDGA105</t>
+  </si>
+  <si>
+    <t>GANGHO METÁLICO LAMINA CAL14 COLD ROLLED BRAZOS 5.2CM P/CANASTA OVOID</t>
+  </si>
+  <si>
+    <t>MD</t>
+  </si>
+  <si>
+    <t>110316</t>
+  </si>
+  <si>
+    <t>HUEVO L X30 CARTON VERDE CON ETIQUETA</t>
+  </si>
+  <si>
+    <t>VT36</t>
+  </si>
+  <si>
+    <t>PEREIRA - INVENTARIO TRANSITO OPERADOR</t>
+  </si>
+  <si>
+    <t>112357</t>
+  </si>
+  <si>
+    <t>HUEVO L X 12 PET CAJA X 120</t>
+  </si>
+  <si>
+    <t>152281</t>
+  </si>
+  <si>
+    <t>HUEVO XL X 15 PAGUE 14 PET CAJA X 300</t>
+  </si>
+  <si>
+    <t>152382</t>
+  </si>
+  <si>
+    <t>HUEVO L X 30 PAGUE 28 PET CAJA X 300</t>
+  </si>
+  <si>
+    <t>112268</t>
+  </si>
+  <si>
+    <t>HUEVO XL X 15 PET CAJA X 300.</t>
+  </si>
+  <si>
+    <t>VT4</t>
+  </si>
+  <si>
+    <t>TAT BARRANQUILLA - INVENTARIO TRANSITO</t>
+  </si>
+  <si>
+    <t>112379</t>
+  </si>
+  <si>
+    <t>HUEVO L X 30 PET CAJA X 300</t>
+  </si>
+  <si>
+    <t>114268</t>
+  </si>
+  <si>
+    <t>HUEVO XL X 15 PET CAJA X 300 PV.</t>
+  </si>
+  <si>
+    <t>114379</t>
+  </si>
+  <si>
+    <t>HUEVO L X 30 PET CAJA X 300 PV.</t>
+  </si>
+  <si>
+    <t>2110302</t>
+  </si>
+  <si>
+    <t>HUEVO L X 30 CARTON VERDE CANASTA</t>
+  </si>
+  <si>
+    <t>2110317</t>
+  </si>
+  <si>
+    <t>HUEVO L X 30 CARTON VERDE AMARRADO SIN ETIQUETA CANASTA</t>
+  </si>
+  <si>
+    <t>2110402</t>
+  </si>
+  <si>
+    <t>HUEVO M X 30 CARTON VERDE CANASTA</t>
+  </si>
+  <si>
+    <t>2110403</t>
+  </si>
+  <si>
+    <t>HUEVO M X30 CARTON VERDE AMARRADO CANASTA</t>
+  </si>
+  <si>
+    <t>2114268</t>
+  </si>
+  <si>
+    <t>HUEVO XL X 15 PET CANASTA X 180 PV</t>
+  </si>
+  <si>
+    <t>2114357</t>
+  </si>
+  <si>
+    <t>HUEVO L X 12 PET CANASTA X 144 PV</t>
+  </si>
+  <si>
+    <t>2114379</t>
+  </si>
+  <si>
+    <t>HUEVO L X 30 PET CANASTA X 180 PV</t>
+  </si>
+  <si>
+    <t>VT41</t>
+  </si>
+  <si>
+    <t>TAT CARTAGENA - INVENTARIO TRANSITO</t>
+  </si>
+  <si>
+    <t>2152388</t>
+  </si>
+  <si>
+    <t>HUEVO L X 15 PAGUE 14 PET EN CANASTA.</t>
+  </si>
+  <si>
+    <t>VT42</t>
+  </si>
+  <si>
+    <t>TAT SANTAMARTA - INVENTARIO TRANSITO</t>
+  </si>
+  <si>
     <t>114357</t>
   </si>
   <si>
     <t>HUEVO L X 12 PET CAJA X 120 PV.</t>
   </si>
   <si>
-    <t>114379</t>
-  </si>
-  <si>
-    <t>HUEVO L X 30 PET CAJA X 300 PV.</t>
-  </si>
-  <si>
-    <t>142111</t>
-  </si>
-  <si>
-    <t>BARRA DE PROTEINA 50 GR ARANDANO DISPLAY X 4 CAJA X 48</t>
-  </si>
-  <si>
-    <t>BP</t>
-  </si>
-  <si>
-    <t>143241</t>
-  </si>
-  <si>
-    <t>BARRA DE PROTEINA 30 GR CHOCOLATE DISPLAY X 6 CAJA X 72</t>
-  </si>
-  <si>
-    <t>112268</t>
-  </si>
-  <si>
-    <t>HUEVO XL X 15 PET CAJA X 300.</t>
-  </si>
-  <si>
-    <t>VT3</t>
-  </si>
-  <si>
-    <t>TAT MEDELLIN - INVENTARIO TRANSITO</t>
-  </si>
-  <si>
-    <t>112271</t>
-  </si>
-  <si>
-    <t>HUEVO XL X 15 PET CAJA X 300 - TAT</t>
-  </si>
-  <si>
-    <t>112379</t>
-  </si>
-  <si>
-    <t>HUEVO L X 30 PET CAJA X 300</t>
-  </si>
-  <si>
     <t>152384</t>
   </si>
   <si>
     <t>HUEVO L X 15 PAGUE 14 PET CAJA X 300.</t>
   </si>
   <si>
-    <t>2110202</t>
-  </si>
-  <si>
-    <t>HUEVO XL X 30 CARTON VERDE CANASTA</t>
+    <t>VT49</t>
+  </si>
+  <si>
+    <t>MONTERIA - INVENTARIO EN TRANSITO OPERADOR</t>
+  </si>
+  <si>
+    <t>VT52</t>
+  </si>
+  <si>
+    <t>TAT BOGOTA - VT52</t>
+  </si>
+  <si>
+    <t>VT59</t>
+  </si>
+  <si>
+    <t>TAT BOGOTA - VT59</t>
+  </si>
+  <si>
+    <t>2010102</t>
+  </si>
+  <si>
+    <t>HUEVO YUMBO X20 CARTON VERDE CANASTA.</t>
   </si>
   <si>
     <t>2110217</t>
@@ -130,132 +274,6 @@
     <t>HUEVO XL X 30 CARTON VERDE AMARRADO SIN ETIQUETA CANASTA</t>
   </si>
   <si>
-    <t>2110302</t>
-  </si>
-  <si>
-    <t>HUEVO L X 30 CARTON VERDE CANASTA</t>
-  </si>
-  <si>
-    <t>2110317</t>
-  </si>
-  <si>
-    <t>HUEVO L X 30 CARTON VERDE AMARRADO SIN ETIQUETA CANASTA</t>
-  </si>
-  <si>
-    <t>2110402</t>
-  </si>
-  <si>
-    <t>HUEVO M X 30 CARTON VERDE CANASTA</t>
-  </si>
-  <si>
-    <t>AFCA022</t>
-  </si>
-  <si>
-    <t>CANASTA KIKES 63  X 32 X  23</t>
-  </si>
-  <si>
-    <t>AF</t>
-  </si>
-  <si>
-    <t>AFES013</t>
-  </si>
-  <si>
-    <t>ESTIBAS OVOID 124CM X 65CM</t>
-  </si>
-  <si>
-    <t>AFSE003</t>
-  </si>
-  <si>
-    <t>SEPARADORES OVOID DE 124CM X 66CM</t>
-  </si>
-  <si>
-    <t>MDGA105</t>
-  </si>
-  <si>
-    <t>GANGHO METÁLICO LAMINA CAL14 COLD ROLLED BRAZOS 5.2CM P/CANASTA OVOID</t>
-  </si>
-  <si>
-    <t>MD</t>
-  </si>
-  <si>
-    <t>VT4</t>
-  </si>
-  <si>
-    <t>TAT BARRANQUILLA - INVENTARIO TRANSITO</t>
-  </si>
-  <si>
-    <t>2110403</t>
-  </si>
-  <si>
-    <t>HUEVO M X30 CARTON VERDE AMARRADO CANASTA</t>
-  </si>
-  <si>
-    <t>2152388</t>
-  </si>
-  <si>
-    <t>HUEVO L X 15 PAGUE 14 PET EN CANASTA.</t>
-  </si>
-  <si>
-    <t>VT41</t>
-  </si>
-  <si>
-    <t>TAT CARTAGENA - INVENTARIO TRANSITO</t>
-  </si>
-  <si>
-    <t>2110303</t>
-  </si>
-  <si>
-    <t>HUEVO L X30 CARTON VERDE AMARRADO CANASTA</t>
-  </si>
-  <si>
-    <t>VT43</t>
-  </si>
-  <si>
-    <t>TAT VALLEDUPAR - INVENTARIO TRANSITO</t>
-  </si>
-  <si>
-    <t>VT49</t>
-  </si>
-  <si>
-    <t>MONTERIA - INVENTARIO EN TRANSITO OPERADOR</t>
-  </si>
-  <si>
-    <t>VT52</t>
-  </si>
-  <si>
-    <t>TAT BOGOTA - VT52</t>
-  </si>
-  <si>
-    <t>112357</t>
-  </si>
-  <si>
-    <t>HUEVO L X 12 PET CAJA X 120</t>
-  </si>
-  <si>
-    <t>13359</t>
-  </si>
-  <si>
-    <t>HUEVO AA X 30 BAND GRIS AMARRADO ALAT CAJA X 300</t>
-  </si>
-  <si>
-    <t>13469</t>
-  </si>
-  <si>
-    <t>HUEVO A X 300 BAND GRIS CAJA AMARR EXITO.</t>
-  </si>
-  <si>
-    <t>2010102</t>
-  </si>
-  <si>
-    <t>HUEVO YUMBO X20 CARTON VERDE CANASTA.</t>
-  </si>
-  <si>
-    <t>VT59</t>
-  </si>
-  <si>
-    <t>TAT BOGOTA - VT59</t>
-  </si>
-  <si>
     <t>2112207</t>
   </si>
   <si>
@@ -268,22 +286,19 @@
     <t>TAT PASTO - INVENTARIO TRANSITO</t>
   </si>
   <si>
-    <t>2013322</t>
-  </si>
-  <si>
-    <t>HUEVO AA X 30 BAND GRIS AMARRADO TAPA VERDE ALAT CANASTA</t>
-  </si>
-  <si>
-    <t>VT7</t>
-  </si>
-  <si>
-    <t>TAT CUCUTA - INVENTARIO TRANSITO</t>
-  </si>
-  <si>
-    <t>2013419</t>
-  </si>
-  <si>
-    <t>HUEVO A X 30 CARTON GRIS AMARRADO SOL NACIENTE CANASTA.</t>
+    <t>UPCI07</t>
+  </si>
+  <si>
+    <t>CINTA EMPAQUE 48MM X 100M REF. 305 3M</t>
+  </si>
+  <si>
+    <t>VTAL06</t>
+  </si>
+  <si>
+    <t>EMPAQUES ALKA 1 TRANSITO</t>
+  </si>
+  <si>
+    <t>UP</t>
   </si>
   <si>
     <t>EECA006</t>
@@ -292,10 +307,10 @@
     <t>CAJA REGULAR X300 EMPAQUE PET</t>
   </si>
   <si>
-    <t>VTAL06</t>
-  </si>
-  <si>
-    <t>EMPAQUES ALKA 1 TRANSITO</t>
+    <t>VTALBKA2</t>
+  </si>
+  <si>
+    <t>EMPAQUES ALKA 2 TRANSITO</t>
   </si>
   <si>
     <t>EE</t>
@@ -310,15 +325,48 @@
     <t>EM</t>
   </si>
   <si>
-    <t>PTET101</t>
-  </si>
-  <si>
-    <t>ETIQUETA PET X 15 XL</t>
+    <t>EMET031</t>
+  </si>
+  <si>
+    <t>ETIQUETA ADHESIVA BLANCA 100 MM X 50 MM - ZEBRA</t>
+  </si>
+  <si>
+    <t>EMZU004</t>
+  </si>
+  <si>
+    <t>ZUNCHO ANCHO 5 MM 7.500 MTS</t>
+  </si>
+  <si>
+    <t>RL</t>
+  </si>
+  <si>
+    <t>PTEM049</t>
+  </si>
+  <si>
+    <t>EMPAQUE PET X 15 XL ETIQUETADO</t>
   </si>
   <si>
     <t>PT</t>
   </si>
   <si>
+    <t>EMBA025</t>
+  </si>
+  <si>
+    <t>BANDEJA HUEVO 12 GRIS SOL NACIENTE</t>
+  </si>
+  <si>
+    <t>VTBC</t>
+  </si>
+  <si>
+    <t>EMPAQUES BELLAVISTA TRANSITO</t>
+  </si>
+  <si>
+    <t>VTBE</t>
+  </si>
+  <si>
+    <t>BODEGA BELLAVISTA - INVENTARIO TRANSITO</t>
+  </si>
+  <si>
     <t>13358</t>
   </si>
   <si>
@@ -331,6 +379,12 @@
     <t>CENTRO DE EMPAQUES BOGOTA -INVENTARIO TRANSITO</t>
   </si>
   <si>
+    <t>2010301</t>
+  </si>
+  <si>
+    <t>HUEVO AA X30 CARTON GRIS CANASTA.</t>
+  </si>
+  <si>
     <t>2410401</t>
   </si>
   <si>
@@ -343,18 +397,6 @@
     <t>BARRANQUILLA - INVENTARIO TRANSITO</t>
   </si>
   <si>
-    <t>114268</t>
-  </si>
-  <si>
-    <t>HUEVO XL X 15 PET CAJA X 300 PV.</t>
-  </si>
-  <si>
-    <t>2010301</t>
-  </si>
-  <si>
-    <t>HUEVO AA X30 CARTON GRIS CANASTA.</t>
-  </si>
-  <si>
     <t>2010501</t>
   </si>
   <si>
@@ -373,10 +415,10 @@
     <t>CENTRO DE EMPAQUES CALI-INVENTARIO TRANSITO</t>
   </si>
   <si>
-    <t>EMES005</t>
-  </si>
-  <si>
-    <t>ESQUINERO DE CARTON 85 X 14 CM</t>
+    <t>EMBA001</t>
+  </si>
+  <si>
+    <t>BANDEJA HUEVO X 30 SPCCO GRIS</t>
   </si>
   <si>
     <t>VTEM03</t>
@@ -385,16 +427,22 @@
     <t>EMPAQUES MEDELLIN TRANSITO</t>
   </si>
   <si>
+    <t>EMBA008</t>
+  </si>
+  <si>
+    <t>BANDEJA HUEVO X 30 EXTRA VERDE</t>
+  </si>
+  <si>
     <t>EMTB001</t>
   </si>
   <si>
     <t>TAPA PARA BANDEJA GRIS</t>
   </si>
   <si>
-    <t>EMTB002</t>
-  </si>
-  <si>
-    <t>TAPA PARA BANDEJA VERDE KIKES</t>
+    <t>EMBA007</t>
+  </si>
+  <si>
+    <t>BANDEJA HUEVO X 30 EXTRA GRIS</t>
   </si>
   <si>
     <t>VTEMBO</t>
@@ -403,58 +451,73 @@
     <t>EMPAQUES BOGOTA TRANSITO</t>
   </si>
   <si>
-    <t>EMBA001</t>
-  </si>
-  <si>
-    <t>BANDEJA HUEVO X 30 SPCCO GRIS</t>
-  </si>
-  <si>
     <t>VTEMBQ</t>
   </si>
   <si>
     <t>EMPAQUES BARRANQUILLA TRANSITO</t>
   </si>
   <si>
+    <t>EMLA002</t>
+  </si>
+  <si>
+    <t>LAMINA CARTON 60X90</t>
+  </si>
+  <si>
+    <t>VTEMT3</t>
+  </si>
+  <si>
+    <t>VIRTUAL EMPAQUE TAT MEDELLIN</t>
+  </si>
+  <si>
+    <t>DOCH084</t>
+  </si>
+  <si>
+    <t>CHALECO VERDE TAT BOLSILLO FRONTAL TALLA XL</t>
+  </si>
+  <si>
+    <t>VTEMT42</t>
+  </si>
+  <si>
+    <t>VIRTUAL EMPAQUE TAT SANTAMARTA</t>
+  </si>
+  <si>
+    <t>DO</t>
+  </si>
+  <si>
+    <t>DOCP004</t>
+  </si>
+  <si>
+    <t>CAMISETA POLO VERDE TALLA XL</t>
+  </si>
+  <si>
+    <t>EMBA010</t>
+  </si>
+  <si>
+    <t>BANDEJA HUEVO X 30 SPCCO VERDE</t>
+  </si>
+  <si>
     <t>EMET01</t>
   </si>
   <si>
     <t>ETIQUETA COD DE BARRA HUEVO M X 30 - K</t>
   </si>
   <si>
-    <t>EMBA006</t>
-  </si>
-  <si>
-    <t>BANDEJA HUEVO X 30 SUPERIOR O UNIVERSAL GRIS</t>
-  </si>
-  <si>
-    <t>VTEMMO</t>
-  </si>
-  <si>
-    <t>EMPAQUES MONTERIA TRANSITO</t>
-  </si>
-  <si>
-    <t>EMBA010</t>
-  </si>
-  <si>
-    <t>BANDEJA HUEVO X 30 SPCCO VERDE</t>
-  </si>
-  <si>
-    <t>EMLA002</t>
-  </si>
-  <si>
-    <t>LAMINA CARTON 60X90</t>
-  </si>
-  <si>
-    <t>VTEMT3</t>
-  </si>
-  <si>
-    <t>VIRTUAL EMPAQUE TAT MEDELLIN</t>
-  </si>
-  <si>
-    <t>VTEMT42</t>
-  </si>
-  <si>
-    <t>VIRTUAL EMPAQUE TAT SANTAMARTA</t>
+    <t>VTEMT52</t>
+  </si>
+  <si>
+    <t>VIRTUAL EMPAQUE TAT BOGOTA NORTE</t>
+  </si>
+  <si>
+    <t>EMET02</t>
+  </si>
+  <si>
+    <t>ETIQUETA COD DE BARRA HUEVO L X 30 - K</t>
+  </si>
+  <si>
+    <t>EMSU001</t>
+  </si>
+  <si>
+    <t>SUJETADOR PLASTIFLECHA 8MM NYLON DOBLE TT CAJA X 10.000 UNID</t>
   </si>
   <si>
     <t>DOCL002</t>
@@ -469,9 +532,6 @@
     <t>VIRTUAL EMPAQUE TAT PASTO</t>
   </si>
   <si>
-    <t>DO</t>
-  </si>
-  <si>
     <t>DOCP003</t>
   </si>
   <si>
@@ -484,22 +544,16 @@
     <t>PANTALON JEAN CABALLERO TALLA 32</t>
   </si>
   <si>
-    <t>10601</t>
-  </si>
-  <si>
-    <t>HUEVO C X30 CARTON GRIS</t>
-  </si>
-  <si>
     <t>VTKI</t>
   </si>
   <si>
     <t>BODEGA KIKES - INVENTARIO TRANSITO</t>
   </si>
   <si>
-    <t>2114268</t>
-  </si>
-  <si>
-    <t>HUEVO XL X 15 PET CANASTA X 180 PV</t>
+    <t>274001</t>
+  </si>
+  <si>
+    <t>HUEVO BAJA ROTACION CANASTA</t>
   </si>
   <si>
     <t>AFES00</t>
@@ -523,10 +577,40 @@
     <t>ESTIBAS PLASTICAS</t>
   </si>
   <si>
-    <t>VTKIGT</t>
-  </si>
-  <si>
-    <t>BODEGA EVENTUALIDAD ALMACENAMIENTO- INVENTARIO TRA</t>
+    <t>VTLZEM</t>
+  </si>
+  <si>
+    <t>EMPAQUES LANZA TRANSITO</t>
+  </si>
+  <si>
+    <t>EMCA019</t>
+  </si>
+  <si>
+    <t>CAJA DOCENERA SOL NACIENTE NEGRA</t>
+  </si>
+  <si>
+    <t>EMET050</t>
+  </si>
+  <si>
+    <t>ETIQUETA COD BARRA HUEVO B X 30 - BUENASOS</t>
+  </si>
+  <si>
+    <t>PTEM029</t>
+  </si>
+  <si>
+    <t>EMPAQUE PET X 30 UNIDADES BASE ACEBRI</t>
+  </si>
+  <si>
+    <t>VTME</t>
+  </si>
+  <si>
+    <t>CENTRO DE EMPAQUES MEDELLIN -INVENTARIO TRANSITO</t>
+  </si>
+  <si>
+    <t>114365</t>
+  </si>
+  <si>
+    <t>HUEVO L X 15 PET CAJA X 300 PV.</t>
   </si>
   <si>
     <t>13419</t>
@@ -535,81 +619,6 @@
     <t>HUEVO A X 30 CARTON GRIS AMARRADO SOL NACIENTE.</t>
   </si>
   <si>
-    <t>13420</t>
-  </si>
-  <si>
-    <t>HUEVO A X 30 BAND GRIS AMARRADO SOL NACIENTE - ESTIBADO</t>
-  </si>
-  <si>
-    <t>13461</t>
-  </si>
-  <si>
-    <t>HUEVO A X 30 BAND GRIS AMARRADO - OLIMPICA</t>
-  </si>
-  <si>
-    <t>13561</t>
-  </si>
-  <si>
-    <t>HUEVO B X 30 BAND GRIS AMARRADO - OLIMPICA</t>
-  </si>
-  <si>
-    <t>VTLZEM</t>
-  </si>
-  <si>
-    <t>EMPAQUES LANZA TRANSITO</t>
-  </si>
-  <si>
-    <t>EMET031</t>
-  </si>
-  <si>
-    <t>ETIQUETA ADHESIVA BLANCA 100 MM X 50 MM - ZEBRA</t>
-  </si>
-  <si>
-    <t>EMET050</t>
-  </si>
-  <si>
-    <t>ETIQUETA COD BARRA HUEVO B X 30 - BUENASOS</t>
-  </si>
-  <si>
-    <t>EMET123</t>
-  </si>
-  <si>
-    <t>ETIQUETA COD DE BARRA HUEVO L X 30 - FS</t>
-  </si>
-  <si>
-    <t>EMSU001</t>
-  </si>
-  <si>
-    <t>SUJETADOR PLASTIFLECHA 8MM NYLON DOBLE TT CAJA X 10.000 UNID</t>
-  </si>
-  <si>
-    <t>EMZU004</t>
-  </si>
-  <si>
-    <t>ZUNCHO ANCHO 5 MM 7.500 MTS</t>
-  </si>
-  <si>
-    <t>RL</t>
-  </si>
-  <si>
-    <t>VTME</t>
-  </si>
-  <si>
-    <t>CENTRO DE EMPAQUES MEDELLIN -INVENTARIO TRANSITO</t>
-  </si>
-  <si>
-    <t>114365</t>
-  </si>
-  <si>
-    <t>HUEVO L X 15 PET CAJA X 300 PV.</t>
-  </si>
-  <si>
-    <t>VTMO</t>
-  </si>
-  <si>
-    <t>CENTRO DE EMPAQUES MONTERIA-INVENTARIO TRANSITO</t>
-  </si>
-  <si>
     <t>MA0101</t>
   </si>
   <si>
@@ -628,10 +637,10 @@
     <t>MI</t>
   </si>
   <si>
-    <t>MA0001</t>
-  </si>
-  <si>
-    <t>MAIZ AMARILLO AMERICANO</t>
+    <t>MA0041</t>
+  </si>
+  <si>
+    <t>TORTA DE SOYA AMERICANA</t>
   </si>
   <si>
     <t>VTPBU</t>
@@ -640,18 +649,6 @@
     <t>TRANSITO VIRTUAL PUERTO BUENAVENTURA</t>
   </si>
   <si>
-    <t>MA0041</t>
-  </si>
-  <si>
-    <t>TORTA DE SOYA AMERICANA</t>
-  </si>
-  <si>
-    <t>MA0056</t>
-  </si>
-  <si>
-    <t>FRIJOL SOYA AMERICANO CRUDO</t>
-  </si>
-  <si>
     <t>MI0502</t>
   </si>
   <si>
@@ -682,22 +679,10 @@
     <t>LA</t>
   </si>
   <si>
-    <t>MDKI027</t>
-  </si>
-  <si>
-    <t>KIT-71 ANILLOS INTERMEDIO HIDROLAVADORA  WS-171/ W-913 / W-9</t>
-  </si>
-  <si>
-    <t>KI</t>
-  </si>
-  <si>
     <t>UPRO005</t>
   </si>
   <si>
     <t>ROTULO ADHESIVO REDONDO VERDE-AMARILLO-ROJO</t>
-  </si>
-  <si>
-    <t>UP</t>
   </si>
   <si>
     <t>UPTA25</t>
@@ -859,13 +844,13 @@
         <v>13</v>
       </c>
       <c r="D2">
-        <v>4500</v>
+        <v>480</v>
       </c>
       <c r="E2" t="s">
         <v>14</v>
       </c>
       <c r="F2" s="2">
-        <v>46269.367534722223</v>
+        <v>46268.304270833331</v>
       </c>
       <c r="G2" t="s">
         <v>15</v>
@@ -877,7 +862,7 @@
       <c r="J2"/>
       <c r="K2"/>
       <c r="L2">
-        <v>182</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3">
@@ -891,13 +876,13 @@
         <v>13</v>
       </c>
       <c r="D3">
-        <v>120</v>
+        <v>720</v>
       </c>
       <c r="E3" t="s">
         <v>14</v>
       </c>
       <c r="F3" s="2">
-        <v>46269.354363425926</v>
+        <v>46268.304270833331</v>
       </c>
       <c r="G3" t="s">
         <v>15</v>
@@ -909,7 +894,7 @@
       <c r="J3"/>
       <c r="K3"/>
       <c r="L3">
-        <v>595</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4">
@@ -920,2342 +905,2342 @@
         <v>20</v>
       </c>
       <c r="C4" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="D4">
-        <v>900</v>
+        <v>186480</v>
       </c>
       <c r="E4" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F4" s="2">
-        <v>46269.354363425926</v>
+        <v>46272.131469907406</v>
       </c>
       <c r="G4" t="s">
         <v>15</v>
       </c>
       <c r="H4" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="I4"/>
       <c r="J4"/>
       <c r="K4"/>
       <c r="L4">
-        <v>1376</v>
+        <v>2878</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5" t="s">
         <v>21</v>
       </c>
-      <c r="B5" t="s">
+      <c r="D5">
+        <v>1036</v>
+      </c>
+      <c r="E5" t="s">
         <v>22</v>
       </c>
-      <c r="C5" t="s">
-        <v>13</v>
-      </c>
-      <c r="D5">
-        <v>480</v>
-      </c>
-      <c r="E5" t="s">
-        <v>14</v>
-      </c>
       <c r="F5" s="2">
-        <v>46268.304270833331</v>
+        <v>46272.131469907406</v>
       </c>
       <c r="G5" t="s">
         <v>15</v>
       </c>
       <c r="H5" t="s">
-        <v>23</v>
-      </c>
-      <c r="I5"/>
+        <v>26</v>
+      </c>
+      <c r="I5">
+        <v>440</v>
+      </c>
       <c r="J5"/>
       <c r="K5"/>
       <c r="L5">
-        <v>19</v>
+        <v>4184</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B6" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C6" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="D6">
-        <v>720</v>
+        <v>50</v>
       </c>
       <c r="E6" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F6" s="2">
-        <v>46268.304270833331</v>
+        <v>46272.131469907406</v>
       </c>
       <c r="G6" t="s">
         <v>15</v>
       </c>
       <c r="H6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I6"/>
+        <v>26</v>
+      </c>
+      <c r="I6">
+        <v>250</v>
+      </c>
       <c r="J6"/>
       <c r="K6"/>
       <c r="L6">
-        <v>19</v>
+        <v>3642</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
+        <v>29</v>
+      </c>
+      <c r="B7" t="s">
+        <v>30</v>
+      </c>
+      <c r="C7" t="s">
+        <v>21</v>
+      </c>
+      <c r="D7">
+        <v>20</v>
+      </c>
+      <c r="E7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F7" s="2">
+        <v>46272.131469907406</v>
+      </c>
+      <c r="G7" t="s">
+        <v>15</v>
+      </c>
+      <c r="H7" t="s">
         <v>26</v>
       </c>
-      <c r="B7" t="s">
-        <v>27</v>
-      </c>
-      <c r="C7" t="s">
-        <v>28</v>
-      </c>
-      <c r="D7">
-        <v>18000</v>
-      </c>
-      <c r="E7" t="s">
-        <v>29</v>
-      </c>
-      <c r="F7" s="2">
-        <v>46268.971550925926</v>
-      </c>
-      <c r="G7" t="s">
-        <v>15</v>
-      </c>
-      <c r="H7" t="s">
-        <v>16</v>
-      </c>
-      <c r="I7"/>
+      <c r="I7">
+        <v>250</v>
+      </c>
       <c r="J7"/>
       <c r="K7"/>
       <c r="L7">
-        <v>2925</v>
+        <v>2453</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B8" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C8" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="D8">
-        <v>9000</v>
+        <v>68</v>
       </c>
       <c r="E8" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="F8" s="2">
-        <v>46268.971550925926</v>
+        <v>46272.055289351847</v>
       </c>
       <c r="G8" t="s">
         <v>15</v>
       </c>
       <c r="H8" t="s">
-        <v>16</v>
-      </c>
-      <c r="I8"/>
+        <v>33</v>
+      </c>
+      <c r="I8">
+        <v>5000</v>
+      </c>
       <c r="J8"/>
       <c r="K8"/>
       <c r="L8">
-        <v>1097</v>
+        <v>2507</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B9" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C9" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="D9">
-        <v>18000</v>
+        <v>9000</v>
       </c>
       <c r="E9" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="F9" s="2">
-        <v>46268.971550925926</v>
+        <v>46270.754479166666</v>
       </c>
       <c r="G9" t="s">
         <v>15</v>
       </c>
       <c r="H9" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="I9"/>
       <c r="J9"/>
       <c r="K9"/>
       <c r="L9">
-        <v>2699</v>
+        <v>694</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="B10" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C10" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="D10">
-        <v>6000</v>
+        <v>120</v>
       </c>
       <c r="E10" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="F10" s="2">
-        <v>46268.971550925926</v>
+        <v>46270.754479166666</v>
       </c>
       <c r="G10" t="s">
         <v>15</v>
       </c>
       <c r="H10" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="I10"/>
       <c r="J10"/>
       <c r="K10"/>
       <c r="L10">
-        <v>1623</v>
+        <v>387</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
+        <v>40</v>
+      </c>
+      <c r="B11" t="s">
+        <v>41</v>
+      </c>
+      <c r="C11" t="s">
         <v>36</v>
       </c>
-      <c r="B11" t="s">
+      <c r="D11">
+        <v>1500</v>
+      </c>
+      <c r="E11" t="s">
         <v>37</v>
       </c>
-      <c r="C11" t="s">
-        <v>28</v>
-      </c>
-      <c r="D11">
-        <v>182160</v>
-      </c>
-      <c r="E11" t="s">
-        <v>29</v>
-      </c>
       <c r="F11" s="2">
-        <v>46268.971550925926</v>
+        <v>46270.754479166666</v>
       </c>
       <c r="G11" t="s">
         <v>15</v>
       </c>
       <c r="H11" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="I11"/>
       <c r="J11"/>
       <c r="K11"/>
       <c r="L11">
-        <v>2872</v>
+        <v>171</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B12" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="C12" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="D12">
-        <v>15840</v>
+        <v>3000</v>
       </c>
       <c r="E12" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="F12" s="2">
-        <v>46268.971550925926</v>
+        <v>46270.754479166666</v>
       </c>
       <c r="G12" t="s">
         <v>15</v>
       </c>
       <c r="H12" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="I12"/>
       <c r="J12"/>
       <c r="K12"/>
       <c r="L12">
-        <v>811</v>
+        <v>219</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="B13" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="C13" t="s">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="D13">
-        <v>42240</v>
+        <v>2700</v>
       </c>
       <c r="E13" t="s">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="F13" s="2">
-        <v>46268.666701388887</v>
+        <v>46271.421747685185</v>
       </c>
       <c r="G13" t="s">
         <v>15</v>
       </c>
       <c r="H13" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="I13"/>
       <c r="J13"/>
       <c r="K13"/>
       <c r="L13">
-        <v>2389</v>
+        <v>641</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="B14" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="C14" t="s">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="D14">
-        <v>3960</v>
+        <v>2400</v>
       </c>
       <c r="E14" t="s">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="F14" s="2">
-        <v>46268.971550925926</v>
+        <v>46271.421747685185</v>
       </c>
       <c r="G14" t="s">
         <v>15</v>
       </c>
       <c r="H14" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="I14"/>
       <c r="J14"/>
       <c r="K14"/>
       <c r="L14">
-        <v>839</v>
+        <v>621</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="B15" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="C15" t="s">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="D15">
-        <v>21120</v>
+        <v>600</v>
       </c>
       <c r="E15" t="s">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="F15" s="2">
-        <v>46268.971550925926</v>
+        <v>46270.866620370369</v>
       </c>
       <c r="G15" t="s">
         <v>15</v>
       </c>
       <c r="H15" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="I15"/>
       <c r="J15"/>
       <c r="K15"/>
       <c r="L15">
-        <v>1621</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
+        <v>52</v>
+      </c>
+      <c r="B16" t="s">
+        <v>53</v>
+      </c>
+      <c r="C16" t="s">
         <v>46</v>
       </c>
-      <c r="B16" t="s">
+      <c r="D16">
+        <v>3600</v>
+      </c>
+      <c r="E16" t="s">
         <v>47</v>
       </c>
-      <c r="C16" t="s">
-        <v>28</v>
-      </c>
-      <c r="D16">
-        <v>1430</v>
-      </c>
-      <c r="E16" t="s">
-        <v>29</v>
-      </c>
       <c r="F16" s="2">
-        <v>46268.971550925926</v>
+        <v>46270.866620370369</v>
       </c>
       <c r="G16" t="s">
         <v>15</v>
       </c>
       <c r="H16" t="s">
-        <v>48</v>
-      </c>
-      <c r="I16">
-        <v>440</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="I16"/>
       <c r="J16"/>
       <c r="K16"/>
       <c r="L16">
-        <v>4170</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>49</v>
+        <v>19</v>
       </c>
       <c r="B17" t="s">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="C17" t="s">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="D17">
-        <v>72</v>
+        <v>1800</v>
       </c>
       <c r="E17" t="s">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="F17" s="2">
-        <v>46268.971550925926</v>
+        <v>46270.916134259256</v>
       </c>
       <c r="G17" t="s">
         <v>15</v>
       </c>
       <c r="H17" t="s">
-        <v>48</v>
-      </c>
-      <c r="I17">
-        <v>250</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="I17"/>
       <c r="J17"/>
       <c r="K17"/>
       <c r="L17">
-        <v>3629</v>
+        <v>235</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B18" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C18" t="s">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="D18">
-        <v>34</v>
+        <v>163200</v>
       </c>
       <c r="E18" t="s">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="F18" s="2">
-        <v>46268.971550925926</v>
+        <v>46272.294212962959</v>
       </c>
       <c r="G18" t="s">
         <v>15</v>
       </c>
       <c r="H18" t="s">
-        <v>48</v>
-      </c>
-      <c r="I18">
-        <v>250</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="I18"/>
       <c r="J18"/>
       <c r="K18"/>
       <c r="L18">
-        <v>2443</v>
+        <v>2052</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="B19" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C19" t="s">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="D19">
-        <v>68</v>
+        <v>7920</v>
       </c>
       <c r="E19" t="s">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="F19" s="2">
-        <v>46268.971550925926</v>
+        <v>46272.294791666667</v>
       </c>
       <c r="G19" t="s">
         <v>15</v>
       </c>
       <c r="H19" t="s">
-        <v>55</v>
-      </c>
-      <c r="I19">
-        <v>5000</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="I19"/>
       <c r="J19"/>
       <c r="K19"/>
       <c r="L19">
-        <v>2501</v>
+        <v>435</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>26</v>
+        <v>58</v>
       </c>
       <c r="B20" t="s">
-        <v>27</v>
+        <v>59</v>
       </c>
       <c r="C20" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="D20">
-        <v>3600</v>
+        <v>496320</v>
       </c>
       <c r="E20" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="F20" s="2">
-        <v>46268.933564814812</v>
+        <v>46272.294791666667</v>
       </c>
       <c r="G20" t="s">
         <v>15</v>
       </c>
       <c r="H20" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="I20"/>
       <c r="J20"/>
       <c r="K20"/>
       <c r="L20">
-        <v>638</v>
+        <v>2747</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>32</v>
+        <v>60</v>
       </c>
       <c r="B21" t="s">
-        <v>33</v>
+        <v>61</v>
       </c>
       <c r="C21" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="D21">
-        <v>5400</v>
+        <v>1800</v>
       </c>
       <c r="E21" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="F21" s="2">
-        <v>46268.933564814812</v>
+        <v>46271.421747685185</v>
       </c>
       <c r="G21" t="s">
         <v>15</v>
       </c>
       <c r="H21" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="I21"/>
       <c r="J21"/>
       <c r="K21"/>
       <c r="L21">
-        <v>618</v>
+        <v>665</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>40</v>
+        <v>62</v>
       </c>
       <c r="B22" t="s">
-        <v>41</v>
+        <v>63</v>
       </c>
       <c r="C22" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="D22">
-        <v>211680</v>
+        <v>4320</v>
       </c>
       <c r="E22" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="F22" s="2">
-        <v>46268.968541666662</v>
+        <v>46270.867384259254</v>
       </c>
       <c r="G22" t="s">
         <v>15</v>
       </c>
       <c r="H22" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="I22"/>
       <c r="J22"/>
       <c r="K22"/>
       <c r="L22">
-        <v>2047</v>
+        <v>65</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>42</v>
+        <v>64</v>
       </c>
       <c r="B23" t="s">
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="C23" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="D23">
-        <v>3960</v>
+        <v>720</v>
       </c>
       <c r="E23" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="F23" s="2">
-        <v>46267.836053240739</v>
+        <v>46270.867384259254</v>
       </c>
       <c r="G23" t="s">
         <v>15</v>
       </c>
       <c r="H23" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="I23"/>
       <c r="J23"/>
       <c r="K23"/>
       <c r="L23">
-        <v>431</v>
+        <v>65</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>44</v>
+        <v>66</v>
       </c>
       <c r="B24" t="s">
-        <v>45</v>
+        <v>67</v>
       </c>
       <c r="C24" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="D24">
-        <v>501120</v>
+        <v>13500</v>
       </c>
       <c r="E24" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="F24" s="2">
-        <v>46268.933564814812</v>
+        <v>46270.867384259254</v>
       </c>
       <c r="G24" t="s">
         <v>15</v>
       </c>
       <c r="H24" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="I24"/>
       <c r="J24"/>
       <c r="K24"/>
       <c r="L24">
-        <v>2739</v>
+        <v>63</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>58</v>
+        <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>59</v>
+        <v>25</v>
       </c>
       <c r="C25" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="D25">
-        <v>7920</v>
+        <v>2916</v>
       </c>
       <c r="E25" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="F25" s="2">
-        <v>46268.933564814812</v>
+        <v>46272.294791666667</v>
       </c>
       <c r="G25" t="s">
         <v>15</v>
       </c>
       <c r="H25" t="s">
-        <v>16</v>
-      </c>
-      <c r="I25"/>
+        <v>26</v>
+      </c>
+      <c r="I25">
+        <v>440</v>
+      </c>
       <c r="J25"/>
       <c r="K25"/>
       <c r="L25">
-        <v>663</v>
+        <v>3429</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>60</v>
+        <v>27</v>
       </c>
       <c r="B26" t="s">
-        <v>61</v>
+        <v>28</v>
       </c>
       <c r="C26" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="D26">
-        <v>27720</v>
+        <v>159</v>
       </c>
       <c r="E26" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="F26" s="2">
-        <v>46268.933564814812</v>
+        <v>46272.294791666667</v>
       </c>
       <c r="G26" t="s">
         <v>15</v>
       </c>
       <c r="H26" t="s">
-        <v>16</v>
-      </c>
-      <c r="I26"/>
+        <v>26</v>
+      </c>
+      <c r="I26">
+        <v>250</v>
+      </c>
       <c r="J26"/>
       <c r="K26"/>
       <c r="L26">
-        <v>481</v>
+        <v>2687</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
+        <v>29</v>
+      </c>
+      <c r="B27" t="s">
+        <v>30</v>
+      </c>
+      <c r="C27" t="s">
         <v>46</v>
       </c>
-      <c r="B27" t="s">
+      <c r="D27">
+        <v>70</v>
+      </c>
+      <c r="E27" t="s">
         <v>47</v>
       </c>
-      <c r="C27" t="s">
-        <v>56</v>
-      </c>
-      <c r="D27">
-        <v>3190</v>
-      </c>
-      <c r="E27" t="s">
-        <v>57</v>
-      </c>
       <c r="F27" s="2">
-        <v>46268.968541666662</v>
+        <v>46272.294791666667</v>
       </c>
       <c r="G27" t="s">
         <v>15</v>
       </c>
       <c r="H27" t="s">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="I27">
-        <v>440</v>
+        <v>250</v>
       </c>
       <c r="J27"/>
       <c r="K27"/>
       <c r="L27">
-        <v>3415</v>
+        <v>2046</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="B28" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="C28" t="s">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="D28">
-        <v>205</v>
+        <v>1200</v>
       </c>
       <c r="E28" t="s">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="F28" s="2">
-        <v>46268.968541666662</v>
+        <v>46271.344166666662</v>
       </c>
       <c r="G28" t="s">
         <v>15</v>
       </c>
       <c r="H28" t="s">
-        <v>48</v>
-      </c>
-      <c r="I28">
-        <v>250</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="I28"/>
       <c r="J28"/>
       <c r="K28"/>
       <c r="L28">
-        <v>2676</v>
+        <v>819</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B29" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C29" t="s">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="D29">
-        <v>98</v>
+        <v>9000</v>
       </c>
       <c r="E29" t="s">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="F29" s="2">
-        <v>46268.968541666662</v>
+        <v>46271.344166666662</v>
       </c>
       <c r="G29" t="s">
         <v>15</v>
       </c>
       <c r="H29" t="s">
-        <v>48</v>
-      </c>
-      <c r="I29">
-        <v>250</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="I29"/>
       <c r="J29"/>
       <c r="K29"/>
       <c r="L29">
-        <v>2035</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B30" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C30" t="s">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="D30">
-        <v>68</v>
+        <v>1800</v>
       </c>
       <c r="E30" t="s">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="F30" s="2">
-        <v>46268.968541666662</v>
+        <v>46271.341539351852</v>
       </c>
       <c r="G30" t="s">
         <v>15</v>
       </c>
       <c r="H30" t="s">
-        <v>55</v>
-      </c>
-      <c r="I30">
-        <v>5000</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="I30"/>
       <c r="J30"/>
       <c r="K30"/>
       <c r="L30">
-        <v>2132</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="B31" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="C31" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="D31">
-        <v>9000</v>
+        <v>3300</v>
       </c>
       <c r="E31" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="F31" s="2">
-        <v>46267.90347222222</v>
+        <v>46271.341539351852</v>
       </c>
       <c r="G31" t="s">
         <v>15</v>
       </c>
       <c r="H31" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="I31"/>
       <c r="J31"/>
       <c r="K31"/>
       <c r="L31">
-        <v>1185</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="B32" t="s">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="C32" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="D32">
-        <v>52800</v>
+        <v>84480</v>
       </c>
       <c r="E32" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="F32" s="2">
-        <v>46267.90347222222</v>
+        <v>46271.344166666662</v>
       </c>
       <c r="G32" t="s">
         <v>15</v>
       </c>
       <c r="H32" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="I32"/>
       <c r="J32"/>
       <c r="K32"/>
       <c r="L32">
-        <v>785</v>
+        <v>787</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="B33" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="C33" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="D33">
-        <v>7920</v>
+        <v>694080</v>
       </c>
       <c r="E33" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="F33" s="2">
-        <v>46267.90347222222</v>
+        <v>46271.344166666662</v>
       </c>
       <c r="G33" t="s">
         <v>15</v>
       </c>
       <c r="H33" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="I33"/>
       <c r="J33"/>
       <c r="K33"/>
       <c r="L33">
-        <v>505</v>
+        <v>3185</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>44</v>
+        <v>62</v>
       </c>
       <c r="B34" t="s">
-        <v>45</v>
+        <v>63</v>
       </c>
       <c r="C34" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="D34">
-        <v>525360</v>
+        <v>8640</v>
       </c>
       <c r="E34" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="F34" s="2">
-        <v>46269.269594907404</v>
+        <v>46271.343009259261</v>
       </c>
       <c r="G34" t="s">
         <v>15</v>
       </c>
       <c r="H34" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="I34"/>
       <c r="J34"/>
       <c r="K34"/>
       <c r="L34">
-        <v>3179</v>
+        <v>55</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="B35" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="C35" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="D35">
-        <v>23760</v>
+        <v>1152</v>
       </c>
       <c r="E35" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="F35" s="2">
-        <v>46267.90347222222</v>
+        <v>46271.343009259261</v>
       </c>
       <c r="G35" t="s">
         <v>15</v>
       </c>
       <c r="H35" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="I35"/>
       <c r="J35"/>
       <c r="K35"/>
       <c r="L35">
-        <v>311</v>
+        <v>43</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="B36" t="s">
-        <v>47</v>
+        <v>67</v>
       </c>
       <c r="C36" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="D36">
-        <v>2585</v>
+        <v>23220</v>
       </c>
       <c r="E36" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="F36" s="2">
-        <v>46269.269594907404</v>
+        <v>46271.343009259261</v>
       </c>
       <c r="G36" t="s">
         <v>15</v>
       </c>
       <c r="H36" t="s">
-        <v>48</v>
-      </c>
-      <c r="I36">
-        <v>440</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="I36"/>
       <c r="J36"/>
       <c r="K36"/>
       <c r="L36">
-        <v>4007</v>
+        <v>51</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>49</v>
+        <v>70</v>
       </c>
       <c r="B37" t="s">
-        <v>50</v>
+        <v>71</v>
       </c>
       <c r="C37" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="D37">
-        <v>126</v>
+        <v>3780</v>
       </c>
       <c r="E37" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="F37" s="2">
-        <v>46269.269594907404</v>
+        <v>46271.344166666662</v>
       </c>
       <c r="G37" t="s">
         <v>15</v>
       </c>
       <c r="H37" t="s">
-        <v>48</v>
-      </c>
-      <c r="I37">
-        <v>250</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="I37"/>
       <c r="J37"/>
       <c r="K37"/>
       <c r="L37">
-        <v>3095</v>
+        <v>313</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>51</v>
+        <v>24</v>
       </c>
       <c r="B38" t="s">
-        <v>52</v>
+        <v>25</v>
       </c>
       <c r="C38" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="D38">
-        <v>62</v>
+        <v>3450</v>
       </c>
       <c r="E38" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="F38" s="2">
-        <v>46268.754050925927</v>
+        <v>46271.344166666662</v>
       </c>
       <c r="G38" t="s">
         <v>15</v>
       </c>
       <c r="H38" t="s">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="I38">
-        <v>250</v>
+        <v>440</v>
       </c>
       <c r="J38"/>
       <c r="K38"/>
       <c r="L38">
-        <v>1753</v>
+        <v>4014</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>53</v>
+        <v>27</v>
       </c>
       <c r="B39" t="s">
-        <v>54</v>
+        <v>28</v>
       </c>
       <c r="C39" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="D39">
-        <v>54</v>
+        <v>160</v>
       </c>
       <c r="E39" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="F39" s="2">
-        <v>46269.269594907404</v>
+        <v>46271.344166666662</v>
       </c>
       <c r="G39" t="s">
         <v>15</v>
       </c>
       <c r="H39" t="s">
-        <v>55</v>
+        <v>26</v>
       </c>
       <c r="I39">
-        <v>5000</v>
+        <v>250</v>
       </c>
       <c r="J39"/>
       <c r="K39"/>
       <c r="L39">
-        <v>2126</v>
+        <v>3101</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="B40" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="C40" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D40">
-        <v>213840</v>
+        <v>80</v>
       </c>
       <c r="E40" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F40" s="2">
-        <v>46268.602719907409</v>
+        <v>46271.344166666662</v>
       </c>
       <c r="G40" t="s">
         <v>15</v>
       </c>
       <c r="H40" t="s">
-        <v>16</v>
-      </c>
-      <c r="I40"/>
+        <v>26</v>
+      </c>
+      <c r="I40">
+        <v>250</v>
+      </c>
       <c r="J40"/>
       <c r="K40"/>
       <c r="L40">
-        <v>1337</v>
+        <v>1757</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>60</v>
+        <v>31</v>
       </c>
       <c r="B41" t="s">
-        <v>61</v>
+        <v>32</v>
       </c>
       <c r="C41" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D41">
-        <v>2700</v>
+        <v>130</v>
       </c>
       <c r="E41" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F41" s="2">
-        <v>46268.602719907409</v>
+        <v>46271.344166666662</v>
       </c>
       <c r="G41" t="s">
         <v>15</v>
       </c>
       <c r="H41" t="s">
-        <v>16</v>
-      </c>
-      <c r="I41"/>
+        <v>33</v>
+      </c>
+      <c r="I41">
+        <v>5000</v>
+      </c>
       <c r="J41"/>
       <c r="K41"/>
       <c r="L41">
-        <v>227</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="B42" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C42" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="D42">
-        <v>906</v>
+        <v>2100</v>
       </c>
       <c r="E42" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="F42" s="2">
-        <v>46268.602719907409</v>
+        <v>46270.799803240741</v>
       </c>
       <c r="G42" t="s">
         <v>15</v>
       </c>
       <c r="H42" t="s">
-        <v>48</v>
-      </c>
-      <c r="I42">
-        <v>440</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="I42"/>
       <c r="J42"/>
       <c r="K42"/>
       <c r="L42">
-        <v>1443</v>
+        <v>582</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>49</v>
+        <v>74</v>
       </c>
       <c r="B43" t="s">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="C43" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="D43">
-        <v>48</v>
+        <v>720</v>
       </c>
       <c r="E43" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="F43" s="2">
-        <v>46268.602719907409</v>
+        <v>46270.799803240741</v>
       </c>
       <c r="G43" t="s">
         <v>15</v>
       </c>
       <c r="H43" t="s">
-        <v>48</v>
-      </c>
-      <c r="I43">
-        <v>250</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="I43"/>
       <c r="J43"/>
       <c r="K43"/>
       <c r="L43">
-        <v>1222</v>
+        <v>323</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B44" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C44" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="D44">
-        <v>24</v>
+        <v>9000</v>
       </c>
       <c r="E44" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="F44" s="2">
-        <v>46268.602719907409</v>
+        <v>46270.799803240741</v>
       </c>
       <c r="G44" t="s">
         <v>15</v>
       </c>
       <c r="H44" t="s">
-        <v>48</v>
-      </c>
-      <c r="I44">
-        <v>250</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="I44"/>
       <c r="J44"/>
       <c r="K44"/>
       <c r="L44">
-        <v>155</v>
+        <v>588</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>40</v>
+        <v>76</v>
       </c>
       <c r="B45" t="s">
-        <v>41</v>
+        <v>77</v>
       </c>
       <c r="C45" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D45">
-        <v>10560</v>
+        <v>1500</v>
       </c>
       <c r="E45" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="F45" s="2">
-        <v>46267</v>
+        <v>46270.802418981482</v>
       </c>
       <c r="G45" t="s">
         <v>15</v>
       </c>
       <c r="H45" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="I45"/>
       <c r="J45"/>
       <c r="K45"/>
       <c r="L45">
-        <v>443</v>
+        <v>921</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="B46" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="C46" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D46">
-        <v>416640</v>
+        <v>34560</v>
       </c>
       <c r="E46" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="F46" s="2">
-        <v>46268</v>
+        <v>46270.802418981482</v>
       </c>
       <c r="G46" t="s">
         <v>15</v>
       </c>
       <c r="H46" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="I46"/>
       <c r="J46"/>
       <c r="K46"/>
       <c r="L46">
-        <v>911</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B47" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C47" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D47">
-        <v>1800</v>
+        <v>156960</v>
       </c>
       <c r="E47" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="F47" s="2">
-        <v>46267</v>
+        <v>46270.802418981482</v>
       </c>
       <c r="G47" t="s">
         <v>15</v>
       </c>
       <c r="H47" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="I47"/>
       <c r="J47"/>
       <c r="K47"/>
       <c r="L47">
-        <v>95</v>
+        <v>1737</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>46</v>
+        <v>62</v>
       </c>
       <c r="B48" t="s">
-        <v>47</v>
+        <v>63</v>
       </c>
       <c r="C48" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D48">
-        <v>1790</v>
+        <v>2160</v>
       </c>
       <c r="E48" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="F48" s="2">
-        <v>46268</v>
+        <v>46270.800243055557</v>
       </c>
       <c r="G48" t="s">
         <v>15</v>
       </c>
       <c r="H48" t="s">
-        <v>48</v>
-      </c>
-      <c r="I48">
-        <v>440</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="I48"/>
       <c r="J48"/>
       <c r="K48"/>
       <c r="L48">
-        <v>981</v>
+        <v>51</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="B49" t="s">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="C49" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D49">
-        <v>84</v>
+        <v>576</v>
       </c>
       <c r="E49" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="F49" s="2">
-        <v>46268</v>
+        <v>46270.800243055557</v>
       </c>
       <c r="G49" t="s">
         <v>15</v>
       </c>
       <c r="H49" t="s">
-        <v>48</v>
-      </c>
-      <c r="I49">
-        <v>250</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="I49"/>
       <c r="J49"/>
       <c r="K49"/>
       <c r="L49">
-        <v>831</v>
+        <v>41</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="B50" t="s">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="C50" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D50">
-        <v>38</v>
+        <v>3420</v>
       </c>
       <c r="E50" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="F50" s="2">
-        <v>46268</v>
+        <v>46270.800243055557</v>
       </c>
       <c r="G50" t="s">
         <v>15</v>
       </c>
       <c r="H50" t="s">
-        <v>48</v>
-      </c>
-      <c r="I50">
-        <v>250</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="I50"/>
       <c r="J50"/>
       <c r="K50"/>
       <c r="L50">
-        <v>640</v>
+        <v>51</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>53</v>
+        <v>24</v>
       </c>
       <c r="B51" t="s">
-        <v>54</v>
+        <v>25</v>
       </c>
       <c r="C51" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D51">
-        <v>84</v>
+        <v>833</v>
       </c>
       <c r="E51" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="F51" s="2">
-        <v>46268</v>
+        <v>46270.802418981482</v>
       </c>
       <c r="G51" t="s">
         <v>15</v>
       </c>
       <c r="H51" t="s">
-        <v>55</v>
+        <v>26</v>
       </c>
       <c r="I51">
-        <v>5000</v>
+        <v>440</v>
       </c>
       <c r="J51"/>
       <c r="K51"/>
       <c r="L51">
-        <v>535</v>
+        <v>2064</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
+        <v>27</v>
+      </c>
+      <c r="B52" t="s">
+        <v>28</v>
+      </c>
+      <c r="C52" t="s">
+        <v>72</v>
+      </c>
+      <c r="D52">
+        <v>48</v>
+      </c>
+      <c r="E52" t="s">
+        <v>73</v>
+      </c>
+      <c r="F52" s="2">
+        <v>46270.802418981482</v>
+      </c>
+      <c r="G52" t="s">
+        <v>15</v>
+      </c>
+      <c r="H52" t="s">
         <v>26</v>
       </c>
-      <c r="B52" t="s">
-        <v>27</v>
-      </c>
-      <c r="C52" t="s">
-        <v>70</v>
-      </c>
-      <c r="D52">
-        <v>3000</v>
-      </c>
-      <c r="E52" t="s">
-        <v>71</v>
-      </c>
-      <c r="F52" s="2">
-        <v>46269.263831018514</v>
-      </c>
-      <c r="G52" t="s">
-        <v>15</v>
-      </c>
-      <c r="H52" t="s">
-        <v>16</v>
-      </c>
-      <c r="I52"/>
+      <c r="I52">
+        <v>250</v>
+      </c>
       <c r="J52"/>
       <c r="K52"/>
       <c r="L52">
-        <v>3712</v>
+        <v>1721</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
+        <v>29</v>
+      </c>
+      <c r="B53" t="s">
+        <v>30</v>
+      </c>
+      <c r="C53" t="s">
         <v>72</v>
       </c>
-      <c r="B53" t="s">
+      <c r="D53">
+        <v>24</v>
+      </c>
+      <c r="E53" t="s">
         <v>73</v>
       </c>
-      <c r="C53" t="s">
-        <v>70</v>
-      </c>
-      <c r="D53">
-        <v>1680</v>
-      </c>
-      <c r="E53" t="s">
-        <v>71</v>
-      </c>
       <c r="F53" s="2">
-        <v>46269.263831018514</v>
+        <v>46270.802418981482</v>
       </c>
       <c r="G53" t="s">
         <v>15</v>
       </c>
       <c r="H53" t="s">
-        <v>16</v>
-      </c>
-      <c r="I53"/>
+        <v>26</v>
+      </c>
+      <c r="I53">
+        <v>250</v>
+      </c>
       <c r="J53"/>
       <c r="K53"/>
       <c r="L53">
-        <v>2376</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
+        <v>31</v>
+      </c>
+      <c r="B54" t="s">
         <v>32</v>
       </c>
-      <c r="B54" t="s">
+      <c r="C54" t="s">
+        <v>72</v>
+      </c>
+      <c r="D54">
+        <v>48</v>
+      </c>
+      <c r="E54" t="s">
+        <v>73</v>
+      </c>
+      <c r="F54" s="2">
+        <v>46270.802418981482</v>
+      </c>
+      <c r="G54" t="s">
+        <v>15</v>
+      </c>
+      <c r="H54" t="s">
         <v>33</v>
       </c>
-      <c r="C54" t="s">
-        <v>70</v>
-      </c>
-      <c r="D54">
-        <v>15000</v>
-      </c>
-      <c r="E54" t="s">
-        <v>71</v>
-      </c>
-      <c r="F54" s="2">
-        <v>46269.263831018514</v>
-      </c>
-      <c r="G54" t="s">
-        <v>15</v>
-      </c>
-      <c r="H54" t="s">
-        <v>16</v>
-      </c>
-      <c r="I54"/>
+      <c r="I54">
+        <v>5000</v>
+      </c>
       <c r="J54"/>
       <c r="K54"/>
       <c r="L54">
-        <v>4709</v>
+        <v>1219</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>74</v>
+        <v>24</v>
       </c>
       <c r="B55" t="s">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="C55" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="D55">
-        <v>2700</v>
+        <v>241</v>
       </c>
       <c r="E55" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="F55" s="2">
-        <v>46268.827592592592</v>
+        <v>46272.355497685181</v>
       </c>
       <c r="G55" t="s">
         <v>15</v>
       </c>
       <c r="H55" t="s">
-        <v>16</v>
-      </c>
-      <c r="I55"/>
+        <v>26</v>
+      </c>
+      <c r="I55">
+        <v>440</v>
+      </c>
       <c r="J55"/>
       <c r="K55"/>
       <c r="L55">
-        <v>171</v>
+        <v>984</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>76</v>
+        <v>27</v>
       </c>
       <c r="B56" t="s">
-        <v>77</v>
+        <v>28</v>
       </c>
       <c r="C56" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="D56">
-        <v>9300</v>
+        <v>11</v>
       </c>
       <c r="E56" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="F56" s="2">
-        <v>46268.827592592592</v>
+        <v>46272.355497685181</v>
       </c>
       <c r="G56" t="s">
         <v>15</v>
       </c>
       <c r="H56" t="s">
-        <v>16</v>
-      </c>
-      <c r="I56"/>
+        <v>26</v>
+      </c>
+      <c r="I56">
+        <v>250</v>
+      </c>
       <c r="J56"/>
       <c r="K56"/>
       <c r="L56">
-        <v>143</v>
+        <v>834</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B57" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C57" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="D57">
-        <v>6000</v>
+        <v>8</v>
       </c>
       <c r="E57" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="F57" s="2">
-        <v>46269.263831018514</v>
+        <v>46272.355497685181</v>
       </c>
       <c r="G57" t="s">
         <v>15</v>
       </c>
       <c r="H57" t="s">
-        <v>16</v>
-      </c>
-      <c r="I57"/>
+        <v>33</v>
+      </c>
+      <c r="I57">
+        <v>5000</v>
+      </c>
       <c r="J57"/>
       <c r="K57"/>
       <c r="L57">
-        <v>2123</v>
+        <v>538</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>78</v>
+        <v>44</v>
       </c>
       <c r="B58" t="s">
-        <v>79</v>
+        <v>45</v>
       </c>
       <c r="C58" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="D58">
-        <v>8520</v>
+        <v>300</v>
       </c>
       <c r="E58" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="F58" s="2">
-        <v>46269.263831018514</v>
+        <v>46272.207523148143</v>
       </c>
       <c r="G58" t="s">
         <v>15</v>
       </c>
       <c r="H58" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="I58"/>
       <c r="J58"/>
       <c r="K58"/>
       <c r="L58">
-        <v>1609</v>
+        <v>3718</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B59" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C59" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="D59">
-        <v>79200</v>
+        <v>120</v>
       </c>
       <c r="E59" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="F59" s="2">
-        <v>46269.263831018514</v>
+        <v>46272.207523148143</v>
       </c>
       <c r="G59" t="s">
         <v>15</v>
       </c>
       <c r="H59" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="I59"/>
       <c r="J59"/>
       <c r="K59"/>
       <c r="L59">
-        <v>3712</v>
+        <v>2381</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="B60" t="s">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="C60" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="D60">
-        <v>79200</v>
+        <v>59220</v>
       </c>
       <c r="E60" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="F60" s="2">
-        <v>46269.263831018514</v>
+        <v>46272.207523148143</v>
       </c>
       <c r="G60" t="s">
         <v>15</v>
       </c>
       <c r="H60" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="I60"/>
       <c r="J60"/>
       <c r="K60"/>
       <c r="L60">
-        <v>1193</v>
+        <v>3726</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="B61" t="s">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="C61" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="D61">
-        <v>69360</v>
+        <v>329</v>
       </c>
       <c r="E61" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="F61" s="2">
-        <v>46269.263831018514</v>
+        <v>46272.207523148143</v>
       </c>
       <c r="G61" t="s">
         <v>15</v>
       </c>
       <c r="H61" t="s">
-        <v>16</v>
-      </c>
-      <c r="I61"/>
+        <v>26</v>
+      </c>
+      <c r="I61">
+        <v>440</v>
+      </c>
       <c r="J61"/>
       <c r="K61"/>
       <c r="L61">
-        <v>2821</v>
+        <v>5401</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="B62" t="s">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="C62" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="D62">
-        <v>7920</v>
+        <v>41</v>
       </c>
       <c r="E62" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="F62" s="2">
-        <v>46269.263831018514</v>
+        <v>46272.207523148143</v>
       </c>
       <c r="G62" t="s">
         <v>15</v>
       </c>
       <c r="H62" t="s">
-        <v>16</v>
-      </c>
-      <c r="I62"/>
+        <v>26</v>
+      </c>
+      <c r="I62">
+        <v>250</v>
+      </c>
       <c r="J62"/>
       <c r="K62"/>
       <c r="L62">
-        <v>829</v>
+        <v>4703</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="B63" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="C63" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="D63">
-        <v>21120</v>
+        <v>32</v>
       </c>
       <c r="E63" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="F63" s="2">
-        <v>46269.263831018514</v>
+        <v>46272.207523148143</v>
       </c>
       <c r="G63" t="s">
         <v>15</v>
       </c>
       <c r="H63" t="s">
-        <v>16</v>
-      </c>
-      <c r="I63"/>
+        <v>26</v>
+      </c>
+      <c r="I63">
+        <v>250</v>
+      </c>
       <c r="J63"/>
       <c r="K63"/>
       <c r="L63">
-        <v>1107</v>
+        <v>2671</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="B64" t="s">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="C64" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="D64">
-        <v>1592</v>
+        <v>17</v>
       </c>
       <c r="E64" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="F64" s="2">
-        <v>46269.263831018514</v>
+        <v>46272.207523148143</v>
       </c>
       <c r="G64" t="s">
         <v>15</v>
       </c>
       <c r="H64" t="s">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="I64">
-        <v>440</v>
+        <v>5000</v>
       </c>
       <c r="J64"/>
       <c r="K64"/>
       <c r="L64">
-        <v>5391</v>
+        <v>3615</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="B65" t="s">
-        <v>50</v>
+        <v>77</v>
       </c>
       <c r="C65" t="s">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="D65">
-        <v>112</v>
+        <v>4800</v>
       </c>
       <c r="E65" t="s">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="F65" s="2">
-        <v>46269.263831018514</v>
+        <v>46270.780925925923</v>
       </c>
       <c r="G65" t="s">
         <v>15</v>
       </c>
       <c r="H65" t="s">
-        <v>48</v>
-      </c>
-      <c r="I65">
-        <v>250</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="I65"/>
       <c r="J65"/>
       <c r="K65"/>
       <c r="L65">
-        <v>4693</v>
+        <v>816</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>51</v>
+        <v>84</v>
       </c>
       <c r="B66" t="s">
-        <v>52</v>
+        <v>85</v>
       </c>
       <c r="C66" t="s">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="D66">
-        <v>72</v>
+        <v>3320</v>
       </c>
       <c r="E66" t="s">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="F66" s="2">
-        <v>46269.263831018514</v>
+        <v>46270.722499999996</v>
       </c>
       <c r="G66" t="s">
         <v>15</v>
       </c>
       <c r="H66" t="s">
-        <v>48</v>
-      </c>
-      <c r="I66">
-        <v>250</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="I66"/>
       <c r="J66"/>
       <c r="K66"/>
       <c r="L66">
-        <v>2662</v>
+        <v>673</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>53</v>
+        <v>19</v>
       </c>
       <c r="B67" t="s">
-        <v>54</v>
+        <v>20</v>
       </c>
       <c r="C67" t="s">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="D67">
-        <v>90</v>
+        <v>37440</v>
       </c>
       <c r="E67" t="s">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="F67" s="2">
-        <v>46269.263831018514</v>
+        <v>46270.722499999996</v>
       </c>
       <c r="G67" t="s">
         <v>15</v>
       </c>
       <c r="H67" t="s">
-        <v>55</v>
-      </c>
-      <c r="I67">
-        <v>5000</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="I67"/>
       <c r="J67"/>
       <c r="K67"/>
       <c r="L67">
-        <v>3606</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>36</v>
+        <v>86</v>
       </c>
       <c r="B68" t="s">
-        <v>37</v>
+        <v>87</v>
       </c>
       <c r="C68" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D68">
-        <v>39600</v>
+        <v>21120</v>
       </c>
       <c r="E68" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="F68" s="2">
-        <v>46269.318287037036</v>
+        <v>46270.780925925923</v>
       </c>
       <c r="G68" t="s">
         <v>15</v>
       </c>
       <c r="H68" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="I68"/>
       <c r="J68"/>
       <c r="K68"/>
       <c r="L68">
-        <v>1155</v>
+        <v>658</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="B69" t="s">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="C69" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D69">
-        <v>15840</v>
+        <v>27120</v>
       </c>
       <c r="E69" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="F69" s="2">
-        <v>46269.318287037036</v>
+        <v>46270.780925925923</v>
       </c>
       <c r="G69" t="s">
         <v>15</v>
       </c>
       <c r="H69" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="I69"/>
       <c r="J69"/>
       <c r="K69"/>
       <c r="L69">
-        <v>655</v>
+        <v>976</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="B70" t="s">
-        <v>41</v>
+        <v>59</v>
       </c>
       <c r="C70" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D70">
-        <v>21120</v>
+        <v>1200</v>
       </c>
       <c r="E70" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="F70" s="2">
-        <v>46269.318287037036</v>
+        <v>46270.780925925923</v>
       </c>
       <c r="G70" t="s">
         <v>15</v>
       </c>
       <c r="H70" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="I70"/>
       <c r="J70"/>
       <c r="K70"/>
       <c r="L70">
-        <v>973</v>
+        <v>499</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="B71" t="s">
-        <v>45</v>
+        <v>89</v>
       </c>
       <c r="C71" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D71">
-        <v>1200</v>
+        <v>900</v>
       </c>
       <c r="E71" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="F71" s="2">
-        <v>46268.937754629631</v>
+        <v>46270.286134259259</v>
       </c>
       <c r="G71" t="s">
         <v>15</v>
       </c>
       <c r="H71" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="I71"/>
       <c r="J71"/>
       <c r="K71"/>
       <c r="L71">
-        <v>497</v>
+        <v>147</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s">
+        <v>70</v>
+      </c>
+      <c r="B72" t="s">
+        <v>71</v>
+      </c>
+      <c r="C72" t="s">
         <v>82</v>
       </c>
-      <c r="B72" t="s">
+      <c r="D72">
+        <v>1800</v>
+      </c>
+      <c r="E72" t="s">
         <v>83</v>
       </c>
-      <c r="C72" t="s">
-        <v>80</v>
-      </c>
-      <c r="D72">
-        <v>360</v>
-      </c>
-      <c r="E72" t="s">
-        <v>81</v>
-      </c>
       <c r="F72" s="2">
-        <v>46269.318287037036</v>
+        <v>46270.780925925923</v>
       </c>
       <c r="G72" t="s">
         <v>15</v>
       </c>
       <c r="H72" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="I72"/>
       <c r="J72"/>
       <c r="K72"/>
       <c r="L72">
-        <v>145</v>
+        <v>165</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>60</v>
+        <v>24</v>
       </c>
       <c r="B73" t="s">
-        <v>61</v>
+        <v>25</v>
       </c>
       <c r="C73" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D73">
-        <v>900</v>
+        <v>545</v>
       </c>
       <c r="E73" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="F73" s="2">
-        <v>46269.318287037036</v>
+        <v>46270.780925925923</v>
       </c>
       <c r="G73" t="s">
         <v>15</v>
       </c>
       <c r="H73" t="s">
-        <v>16</v>
-      </c>
-      <c r="I73"/>
+        <v>26</v>
+      </c>
+      <c r="I73">
+        <v>440</v>
+      </c>
       <c r="J73"/>
       <c r="K73"/>
       <c r="L73">
-        <v>163</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>46</v>
+        <v>27</v>
       </c>
       <c r="B74" t="s">
-        <v>47</v>
+        <v>28</v>
       </c>
       <c r="C74" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D74">
-        <v>452</v>
+        <v>163</v>
       </c>
       <c r="E74" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="F74" s="2">
-        <v>46269.318287037036</v>
+        <v>46270.780925925923</v>
       </c>
       <c r="G74" t="s">
         <v>15</v>
       </c>
       <c r="H74" t="s">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="I74">
-        <v>440</v>
+        <v>250</v>
       </c>
       <c r="J74"/>
       <c r="K74"/>
       <c r="L74">
-        <v>1379</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="B75" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="C75" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D75">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="E75" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="F75" s="2">
-        <v>46268.937754629631</v>
+        <v>46270.780925925923</v>
       </c>
       <c r="G75" t="s">
         <v>15</v>
       </c>
       <c r="H75" t="s">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="I75">
         <v>250</v>
@@ -3263,2257 +3248,2275 @@
       <c r="J75"/>
       <c r="K75"/>
       <c r="L75">
-        <v>1095</v>
+        <v>705</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B76" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C76" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="D76">
-        <v>40</v>
+        <v>34560</v>
       </c>
       <c r="E76" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="F76" s="2">
-        <v>46268.937754629631</v>
+        <v>46270.694826388884</v>
       </c>
       <c r="G76" t="s">
         <v>15</v>
       </c>
       <c r="H76" t="s">
-        <v>48</v>
-      </c>
-      <c r="I76">
-        <v>250</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="I76"/>
       <c r="J76"/>
       <c r="K76"/>
       <c r="L76">
-        <v>701</v>
+        <v>2829</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>30</v>
+        <v>58</v>
       </c>
       <c r="B77" t="s">
-        <v>31</v>
+        <v>59</v>
       </c>
       <c r="C77" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="D77">
-        <v>3000</v>
+        <v>43</v>
       </c>
       <c r="E77" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="F77" s="2">
-        <v>46268.807349537034</v>
+        <v>46270.694826388884</v>
       </c>
       <c r="G77" t="s">
         <v>15</v>
       </c>
       <c r="H77" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="I77"/>
       <c r="J77"/>
       <c r="K77"/>
       <c r="L77">
-        <v>131</v>
+        <v>801</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>36</v>
+        <v>92</v>
       </c>
       <c r="B78" t="s">
-        <v>37</v>
+        <v>93</v>
       </c>
       <c r="C78" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="D78">
-        <v>63360</v>
+        <v>20</v>
       </c>
       <c r="E78" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="F78" s="2">
-        <v>46268.807349537034</v>
+        <v>46271.7280787037</v>
       </c>
       <c r="G78" t="s">
         <v>15</v>
       </c>
       <c r="H78" t="s">
-        <v>16</v>
-      </c>
-      <c r="I78"/>
+        <v>96</v>
+      </c>
+      <c r="I78">
+        <v>160</v>
+      </c>
       <c r="J78"/>
       <c r="K78"/>
       <c r="L78">
-        <v>1155</v>
+        <v>982</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>40</v>
+        <v>97</v>
       </c>
       <c r="B79" t="s">
-        <v>41</v>
+        <v>98</v>
       </c>
       <c r="C79" t="s">
-        <v>84</v>
+        <v>99</v>
       </c>
       <c r="D79">
-        <v>76796</v>
+        <v>500</v>
       </c>
       <c r="E79" t="s">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="F79" s="2">
-        <v>46268.807349537034</v>
+        <v>46272.324178240742</v>
       </c>
       <c r="G79" t="s">
         <v>15</v>
       </c>
       <c r="H79" t="s">
-        <v>16</v>
-      </c>
-      <c r="I79"/>
+        <v>101</v>
+      </c>
+      <c r="I79">
+        <v>400</v>
+      </c>
       <c r="J79"/>
       <c r="K79"/>
       <c r="L79">
-        <v>2825</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>42</v>
+        <v>102</v>
       </c>
       <c r="B80" t="s">
-        <v>43</v>
+        <v>103</v>
       </c>
       <c r="C80" t="s">
-        <v>84</v>
+        <v>99</v>
       </c>
       <c r="D80">
-        <v>15840</v>
+        <v>10000</v>
       </c>
       <c r="E80" t="s">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="F80" s="2">
-        <v>46268.807349537034</v>
+        <v>46272.324178240742</v>
       </c>
       <c r="G80" t="s">
         <v>15</v>
       </c>
       <c r="H80" t="s">
-        <v>16</v>
-      </c>
-      <c r="I80"/>
+        <v>104</v>
+      </c>
+      <c r="I80">
+        <v>60000</v>
+      </c>
       <c r="J80"/>
       <c r="K80"/>
       <c r="L80">
-        <v>429</v>
+        <v>617</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>44</v>
+        <v>105</v>
       </c>
       <c r="B81" t="s">
-        <v>45</v>
+        <v>106</v>
       </c>
       <c r="C81" t="s">
-        <v>84</v>
+        <v>99</v>
       </c>
       <c r="D81">
-        <v>2923</v>
+        <v>5000</v>
       </c>
       <c r="E81" t="s">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="F81" s="2">
-        <v>46268.807349537034</v>
+        <v>46272.324178240742</v>
       </c>
       <c r="G81" t="s">
         <v>15</v>
       </c>
       <c r="H81" t="s">
-        <v>16</v>
-      </c>
-      <c r="I81"/>
+        <v>104</v>
+      </c>
+      <c r="I81">
+        <v>40000</v>
+      </c>
       <c r="J81"/>
       <c r="K81"/>
       <c r="L81">
-        <v>798</v>
+        <v>426</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s">
+        <v>107</v>
+      </c>
+      <c r="B82" t="s">
+        <v>108</v>
+      </c>
+      <c r="C82" t="s">
+        <v>99</v>
+      </c>
+      <c r="D82">
+        <v>2</v>
+      </c>
+      <c r="E82" t="s">
+        <v>100</v>
+      </c>
+      <c r="F82" s="2">
+        <v>46272.324178240742</v>
+      </c>
+      <c r="G82" t="s">
+        <v>109</v>
+      </c>
+      <c r="H82" t="s">
+        <v>104</v>
+      </c>
+      <c r="I82">
         <v>60</v>
       </c>
-      <c r="B82" t="s">
-        <v>61</v>
-      </c>
-      <c r="C82" t="s">
-        <v>84</v>
-      </c>
-      <c r="D82">
-        <v>7920</v>
-      </c>
-      <c r="E82" t="s">
-        <v>85</v>
-      </c>
-      <c r="F82" s="2">
-        <v>46268.807349537034</v>
-      </c>
-      <c r="G82" t="s">
-        <v>15</v>
-      </c>
-      <c r="H82" t="s">
-        <v>16</v>
-      </c>
-      <c r="I82"/>
       <c r="J82"/>
       <c r="K82"/>
       <c r="L82">
-        <v>203</v>
+        <v>843</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>46</v>
+        <v>110</v>
       </c>
       <c r="B83" t="s">
-        <v>47</v>
+        <v>111</v>
       </c>
       <c r="C83" t="s">
-        <v>84</v>
+        <v>99</v>
       </c>
       <c r="D83">
-        <v>816</v>
+        <v>5600</v>
       </c>
       <c r="E83" t="s">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="F83" s="2">
-        <v>46268.807349537034</v>
+        <v>46272.324178240742</v>
       </c>
       <c r="G83" t="s">
         <v>15</v>
       </c>
       <c r="H83" t="s">
-        <v>48</v>
-      </c>
-      <c r="I83">
-        <v>440</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="I83"/>
       <c r="J83"/>
       <c r="K83"/>
       <c r="L83">
-        <v>3073</v>
+        <v>55</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>49</v>
+        <v>113</v>
       </c>
       <c r="B84" t="s">
-        <v>50</v>
+        <v>114</v>
       </c>
       <c r="C84" t="s">
-        <v>84</v>
+        <v>115</v>
       </c>
       <c r="D84">
-        <v>38</v>
+        <v>2100</v>
       </c>
       <c r="E84" t="s">
-        <v>85</v>
+        <v>116</v>
       </c>
       <c r="F84" s="2">
-        <v>46268.807349537034</v>
+        <v>46270.550451388888</v>
       </c>
       <c r="G84" t="s">
         <v>15</v>
       </c>
       <c r="H84" t="s">
-        <v>48</v>
+        <v>104</v>
       </c>
       <c r="I84">
-        <v>250</v>
+        <v>4200</v>
       </c>
       <c r="J84"/>
       <c r="K84"/>
       <c r="L84">
-        <v>2791</v>
+        <v>1883</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>51</v>
+        <v>24</v>
       </c>
       <c r="B85" t="s">
-        <v>52</v>
+        <v>25</v>
       </c>
       <c r="C85" t="s">
-        <v>84</v>
+        <v>117</v>
       </c>
       <c r="D85">
-        <v>19</v>
+        <v>8819</v>
       </c>
       <c r="E85" t="s">
-        <v>85</v>
+        <v>118</v>
       </c>
       <c r="F85" s="2">
-        <v>46268.807349537034</v>
+        <v>46271.368773148148</v>
       </c>
       <c r="G85" t="s">
         <v>15</v>
       </c>
       <c r="H85" t="s">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="I85">
-        <v>250</v>
+        <v>440</v>
       </c>
       <c r="J85"/>
       <c r="K85"/>
       <c r="L85">
-        <v>343</v>
+        <v>4314</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>86</v>
+        <v>27</v>
       </c>
       <c r="B86" t="s">
-        <v>87</v>
+        <v>28</v>
       </c>
       <c r="C86" t="s">
-        <v>88</v>
+        <v>117</v>
       </c>
       <c r="D86">
-        <v>86400</v>
+        <v>538</v>
       </c>
       <c r="E86" t="s">
-        <v>89</v>
+        <v>118</v>
       </c>
       <c r="F86" s="2">
-        <v>46268</v>
+        <v>46271.368773148148</v>
       </c>
       <c r="G86" t="s">
         <v>15</v>
       </c>
       <c r="H86" t="s">
-        <v>16</v>
-      </c>
-      <c r="I86"/>
+        <v>26</v>
+      </c>
+      <c r="I86">
+        <v>250</v>
+      </c>
       <c r="J86"/>
       <c r="K86"/>
       <c r="L86">
-        <v>237</v>
+        <v>4142</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>90</v>
+        <v>29</v>
       </c>
       <c r="B87" t="s">
-        <v>91</v>
+        <v>30</v>
       </c>
       <c r="C87" t="s">
-        <v>88</v>
+        <v>117</v>
       </c>
       <c r="D87">
-        <v>69840</v>
+        <v>231</v>
       </c>
       <c r="E87" t="s">
-        <v>89</v>
+        <v>118</v>
       </c>
       <c r="F87" s="2">
-        <v>46268.866793981477</v>
+        <v>46271.368773148148</v>
       </c>
       <c r="G87" t="s">
         <v>15</v>
       </c>
       <c r="H87" t="s">
-        <v>16</v>
-      </c>
-      <c r="I87"/>
+        <v>26</v>
+      </c>
+      <c r="I87">
+        <v>250</v>
+      </c>
       <c r="J87"/>
       <c r="K87"/>
       <c r="L87">
-        <v>331</v>
+        <v>2331</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="B88" t="s">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="C88" t="s">
-        <v>88</v>
+        <v>117</v>
       </c>
       <c r="D88">
-        <v>868</v>
+        <v>150</v>
       </c>
       <c r="E88" t="s">
-        <v>89</v>
+        <v>118</v>
       </c>
       <c r="F88" s="2">
-        <v>46268</v>
+        <v>46271.360972222217</v>
       </c>
       <c r="G88" t="s">
         <v>15</v>
       </c>
       <c r="H88" t="s">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="I88">
-        <v>440</v>
+        <v>5000</v>
       </c>
       <c r="J88"/>
       <c r="K88"/>
       <c r="L88">
-        <v>2304</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>49</v>
+        <v>119</v>
       </c>
       <c r="B89" t="s">
-        <v>50</v>
+        <v>120</v>
       </c>
       <c r="C89" t="s">
-        <v>88</v>
+        <v>121</v>
       </c>
       <c r="D89">
-        <v>35</v>
+        <v>182880</v>
       </c>
       <c r="E89" t="s">
-        <v>89</v>
+        <v>122</v>
       </c>
       <c r="F89" s="2">
-        <v>46268</v>
+        <v>46270.916168981479</v>
       </c>
       <c r="G89" t="s">
         <v>15</v>
       </c>
       <c r="H89" t="s">
-        <v>48</v>
-      </c>
-      <c r="I89">
-        <v>250</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="I89"/>
       <c r="J89"/>
       <c r="K89"/>
       <c r="L89">
-        <v>1872</v>
+        <v>1499</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="s">
-        <v>51</v>
+        <v>123</v>
       </c>
       <c r="B90" t="s">
-        <v>52</v>
+        <v>124</v>
       </c>
       <c r="C90" t="s">
-        <v>88</v>
+        <v>121</v>
       </c>
       <c r="D90">
-        <v>10</v>
+        <v>97920</v>
       </c>
       <c r="E90" t="s">
-        <v>89</v>
+        <v>122</v>
       </c>
       <c r="F90" s="2">
-        <v>46268</v>
+        <v>46270.916168981479</v>
       </c>
       <c r="G90" t="s">
         <v>15</v>
       </c>
       <c r="H90" t="s">
-        <v>48</v>
-      </c>
-      <c r="I90">
-        <v>250</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="I90"/>
       <c r="J90"/>
       <c r="K90"/>
       <c r="L90">
-        <v>953</v>
+        <v>1792</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>53</v>
+        <v>125</v>
       </c>
       <c r="B91" t="s">
-        <v>54</v>
+        <v>126</v>
       </c>
       <c r="C91" t="s">
-        <v>88</v>
+        <v>121</v>
       </c>
       <c r="D91">
-        <v>23</v>
+        <v>609600</v>
       </c>
       <c r="E91" t="s">
-        <v>89</v>
+        <v>122</v>
       </c>
       <c r="F91" s="2">
-        <v>46268</v>
+        <v>46270.78256944444</v>
       </c>
       <c r="G91" t="s">
         <v>15</v>
       </c>
       <c r="H91" t="s">
-        <v>55</v>
-      </c>
-      <c r="I91">
-        <v>5000</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="I91"/>
       <c r="J91"/>
       <c r="K91"/>
       <c r="L91">
-        <v>1214</v>
+        <v>190</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s">
-        <v>92</v>
+        <v>24</v>
       </c>
       <c r="B92" t="s">
-        <v>93</v>
+        <v>25</v>
       </c>
       <c r="C92" t="s">
-        <v>94</v>
+        <v>121</v>
       </c>
       <c r="D92">
-        <v>500</v>
+        <v>2948</v>
       </c>
       <c r="E92" t="s">
-        <v>95</v>
+        <v>122</v>
       </c>
       <c r="F92" s="2">
-        <v>46269.304409722223</v>
+        <v>46270.916168981479</v>
       </c>
       <c r="G92" t="s">
         <v>15</v>
       </c>
       <c r="H92" t="s">
-        <v>96</v>
+        <v>26</v>
       </c>
       <c r="I92">
-        <v>400</v>
+        <v>440</v>
       </c>
       <c r="J92"/>
       <c r="K92"/>
       <c r="L92">
-        <v>1864</v>
+        <v>4333</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="s">
-        <v>97</v>
+        <v>27</v>
       </c>
       <c r="B93" t="s">
-        <v>98</v>
+        <v>28</v>
       </c>
       <c r="C93" t="s">
-        <v>94</v>
+        <v>121</v>
       </c>
       <c r="D93">
-        <v>20000</v>
+        <v>46</v>
       </c>
       <c r="E93" t="s">
-        <v>95</v>
+        <v>122</v>
       </c>
       <c r="F93" s="2">
-        <v>46269.324178240742</v>
+        <v>46270.916168981479</v>
       </c>
       <c r="G93" t="s">
         <v>15</v>
       </c>
       <c r="H93" t="s">
-        <v>99</v>
+        <v>26</v>
       </c>
       <c r="I93">
-        <v>60000</v>
+        <v>250</v>
       </c>
       <c r="J93"/>
       <c r="K93"/>
       <c r="L93">
-        <v>866</v>
+        <v>4020</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s">
-        <v>100</v>
+        <v>31</v>
       </c>
       <c r="B94" t="s">
-        <v>101</v>
+        <v>32</v>
       </c>
       <c r="C94" t="s">
-        <v>94</v>
+        <v>121</v>
       </c>
       <c r="D94">
-        <v>30000</v>
+        <v>12</v>
       </c>
       <c r="E94" t="s">
-        <v>95</v>
+        <v>122</v>
       </c>
       <c r="F94" s="2">
-        <v>46269.304409722223</v>
+        <v>46270.916168981479</v>
       </c>
       <c r="G94" t="s">
         <v>15</v>
       </c>
       <c r="H94" t="s">
-        <v>102</v>
+        <v>33</v>
       </c>
       <c r="I94">
-        <v>76613</v>
+        <v>5000</v>
       </c>
       <c r="J94"/>
       <c r="K94"/>
       <c r="L94">
-        <v>1287</v>
+        <v>2561</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="s">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="B95" t="s">
-        <v>104</v>
+        <v>120</v>
       </c>
       <c r="C95" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="D95">
-        <v>36576</v>
+        <v>73152</v>
       </c>
       <c r="E95" t="s">
-        <v>106</v>
+        <v>128</v>
       </c>
       <c r="F95" s="2">
-        <v>46268.938796296294</v>
+        <v>46270.868113425924</v>
       </c>
       <c r="G95" t="s">
         <v>15</v>
       </c>
       <c r="H95" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="I95"/>
       <c r="J95"/>
       <c r="K95"/>
       <c r="L95">
-        <v>1487</v>
+        <v>1820</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="s">
-        <v>107</v>
+        <v>123</v>
       </c>
       <c r="B96" t="s">
-        <v>108</v>
+        <v>124</v>
       </c>
       <c r="C96" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="D96">
-        <v>275520</v>
+        <v>170880</v>
       </c>
       <c r="E96" t="s">
-        <v>106</v>
+        <v>128</v>
       </c>
       <c r="F96" s="2">
-        <v>46269.317430555551</v>
+        <v>46270.917337962965</v>
       </c>
       <c r="G96" t="s">
         <v>15</v>
       </c>
       <c r="H96" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="I96"/>
       <c r="J96"/>
       <c r="K96"/>
       <c r="L96">
-        <v>183</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="s">
-        <v>46</v>
+        <v>129</v>
       </c>
       <c r="B97" t="s">
-        <v>47</v>
+        <v>130</v>
       </c>
       <c r="C97" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="D97">
-        <v>1148</v>
+        <v>228000</v>
       </c>
       <c r="E97" t="s">
-        <v>106</v>
+        <v>128</v>
       </c>
       <c r="F97" s="2">
-        <v>46269.317430555551</v>
+        <v>46271.438125</v>
       </c>
       <c r="G97" t="s">
         <v>15</v>
       </c>
       <c r="H97" t="s">
-        <v>48</v>
-      </c>
-      <c r="I97">
-        <v>440</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="I97"/>
       <c r="J97"/>
       <c r="K97"/>
       <c r="L97">
-        <v>4327</v>
+        <v>5129</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s">
+        <v>24</v>
+      </c>
+      <c r="B98" t="s">
+        <v>25</v>
+      </c>
+      <c r="C98" t="s">
+        <v>127</v>
+      </c>
+      <c r="D98">
+        <v>1662</v>
+      </c>
+      <c r="E98" t="s">
+        <v>128</v>
+      </c>
+      <c r="F98" s="2">
+        <v>46271.438125</v>
+      </c>
+      <c r="G98" t="s">
+        <v>15</v>
+      </c>
+      <c r="H98" t="s">
         <v>26</v>
       </c>
-      <c r="B98" t="s">
-        <v>27</v>
-      </c>
-      <c r="C98" t="s">
-        <v>109</v>
-      </c>
-      <c r="D98">
-        <v>1200</v>
-      </c>
-      <c r="E98" t="s">
-        <v>110</v>
-      </c>
-      <c r="F98" s="2">
-        <v>46268.969259259255</v>
-      </c>
-      <c r="G98" t="s">
-        <v>15</v>
-      </c>
-      <c r="H98" t="s">
-        <v>16</v>
-      </c>
-      <c r="I98"/>
+      <c r="I98">
+        <v>440</v>
+      </c>
       <c r="J98"/>
       <c r="K98"/>
       <c r="L98">
-        <v>1358</v>
+        <v>9092</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s">
-        <v>72</v>
+        <v>27</v>
       </c>
       <c r="B99" t="s">
-        <v>73</v>
+        <v>28</v>
       </c>
       <c r="C99" t="s">
-        <v>109</v>
+        <v>127</v>
       </c>
       <c r="D99">
-        <v>120</v>
+        <v>22</v>
       </c>
       <c r="E99" t="s">
-        <v>110</v>
+        <v>128</v>
       </c>
       <c r="F99" s="2">
-        <v>46268.969259259255</v>
+        <v>46271.435810185183</v>
       </c>
       <c r="G99" t="s">
         <v>15</v>
       </c>
       <c r="H99" t="s">
-        <v>16</v>
-      </c>
-      <c r="I99"/>
+        <v>26</v>
+      </c>
+      <c r="I99">
+        <v>250</v>
+      </c>
       <c r="J99"/>
       <c r="K99"/>
       <c r="L99">
-        <v>910</v>
+        <v>6374</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="s">
-        <v>111</v>
+        <v>31</v>
       </c>
       <c r="B100" t="s">
-        <v>112</v>
+        <v>32</v>
       </c>
       <c r="C100" t="s">
-        <v>109</v>
+        <v>127</v>
       </c>
       <c r="D100">
-        <v>1200</v>
+        <v>6</v>
       </c>
       <c r="E100" t="s">
-        <v>110</v>
+        <v>128</v>
       </c>
       <c r="F100" s="2">
-        <v>46268</v>
+        <v>46270.868113425924</v>
       </c>
       <c r="G100" t="s">
         <v>15</v>
       </c>
       <c r="H100" t="s">
-        <v>16</v>
-      </c>
-      <c r="I100"/>
+        <v>33</v>
+      </c>
+      <c r="I100">
+        <v>5000</v>
+      </c>
       <c r="J100"/>
       <c r="K100"/>
       <c r="L100">
-        <v>265</v>
+        <v>2980</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="s">
-        <v>17</v>
+        <v>131</v>
       </c>
       <c r="B101" t="s">
-        <v>18</v>
+        <v>132</v>
       </c>
       <c r="C101" t="s">
-        <v>109</v>
+        <v>133</v>
       </c>
       <c r="D101">
-        <v>840</v>
+        <v>900</v>
       </c>
       <c r="E101" t="s">
-        <v>110</v>
+        <v>134</v>
       </c>
       <c r="F101" s="2">
-        <v>46268</v>
+        <v>46271.698958333334</v>
       </c>
       <c r="G101" t="s">
         <v>15</v>
       </c>
       <c r="H101" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="I101"/>
       <c r="J101"/>
       <c r="K101"/>
       <c r="L101">
-        <v>245</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="s">
-        <v>19</v>
+        <v>119</v>
       </c>
       <c r="B102" t="s">
-        <v>20</v>
+        <v>120</v>
       </c>
       <c r="C102" t="s">
-        <v>109</v>
+        <v>133</v>
       </c>
       <c r="D102">
-        <v>1800</v>
+        <v>576</v>
       </c>
       <c r="E102" t="s">
-        <v>110</v>
+        <v>134</v>
       </c>
       <c r="F102" s="2">
-        <v>46268</v>
+        <v>46271.687592592592</v>
       </c>
       <c r="G102" t="s">
         <v>15</v>
       </c>
       <c r="H102" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="I102"/>
       <c r="J102"/>
       <c r="K102"/>
       <c r="L102">
-        <v>273</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="s">
-        <v>103</v>
+        <v>135</v>
       </c>
       <c r="B103" t="s">
+        <v>136</v>
+      </c>
+      <c r="C103" t="s">
+        <v>137</v>
+      </c>
+      <c r="D103">
+        <v>3640</v>
+      </c>
+      <c r="E103" t="s">
+        <v>138</v>
+      </c>
+      <c r="F103" s="2">
+        <v>46270.942627314813</v>
+      </c>
+      <c r="G103" t="s">
+        <v>15</v>
+      </c>
+      <c r="H103" t="s">
         <v>104</v>
       </c>
-      <c r="C103" t="s">
-        <v>109</v>
-      </c>
-      <c r="D103">
-        <v>72864</v>
-      </c>
-      <c r="E103" t="s">
-        <v>110</v>
-      </c>
-      <c r="F103" s="2">
-        <v>46269.326041666667</v>
-      </c>
-      <c r="G103" t="s">
-        <v>15</v>
-      </c>
-      <c r="H103" t="s">
-        <v>16</v>
-      </c>
-      <c r="I103"/>
+      <c r="I103">
+        <v>49280</v>
+      </c>
       <c r="J103"/>
       <c r="K103"/>
       <c r="L103">
-        <v>1817</v>
+        <v>874</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="s">
-        <v>113</v>
+        <v>139</v>
       </c>
       <c r="B104" t="s">
-        <v>114</v>
+        <v>140</v>
       </c>
       <c r="C104" t="s">
-        <v>109</v>
+        <v>137</v>
       </c>
       <c r="D104">
-        <v>211200</v>
+        <v>600</v>
       </c>
       <c r="E104" t="s">
-        <v>110</v>
+        <v>138</v>
       </c>
       <c r="F104" s="2">
-        <v>46269.326041666667</v>
+        <v>46271.021747685183</v>
       </c>
       <c r="G104" t="s">
         <v>15</v>
       </c>
       <c r="H104" t="s">
-        <v>16</v>
-      </c>
-      <c r="I104"/>
+        <v>104</v>
+      </c>
+      <c r="I104">
+        <v>26880</v>
+      </c>
       <c r="J104"/>
       <c r="K104"/>
       <c r="L104">
-        <v>1326</v>
+        <v>369</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="s">
-        <v>115</v>
+        <v>141</v>
       </c>
       <c r="B105" t="s">
-        <v>116</v>
+        <v>142</v>
       </c>
       <c r="C105" t="s">
-        <v>109</v>
+        <v>137</v>
       </c>
       <c r="D105">
-        <v>284028</v>
+        <v>4480</v>
       </c>
       <c r="E105" t="s">
-        <v>110</v>
+        <v>138</v>
       </c>
       <c r="F105" s="2">
-        <v>46268.934386574074</v>
+        <v>46272.051979166667</v>
       </c>
       <c r="G105" t="s">
         <v>15</v>
       </c>
       <c r="H105" t="s">
-        <v>16</v>
-      </c>
-      <c r="I105"/>
+        <v>104</v>
+      </c>
+      <c r="I105">
+        <v>26880</v>
+      </c>
       <c r="J105"/>
       <c r="K105"/>
       <c r="L105">
-        <v>5122</v>
+        <v>2142</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="s">
-        <v>107</v>
+        <v>143</v>
       </c>
       <c r="B106" t="s">
-        <v>108</v>
+        <v>144</v>
       </c>
       <c r="C106" t="s">
-        <v>109</v>
+        <v>145</v>
       </c>
       <c r="D106">
-        <v>195360</v>
+        <v>600</v>
       </c>
       <c r="E106" t="s">
-        <v>110</v>
+        <v>146</v>
       </c>
       <c r="F106" s="2">
-        <v>46268.854108796295</v>
+        <v>46270.867384259254</v>
       </c>
       <c r="G106" t="s">
         <v>15</v>
       </c>
       <c r="H106" t="s">
-        <v>16</v>
-      </c>
-      <c r="I106"/>
+        <v>104</v>
+      </c>
+      <c r="I106">
+        <v>3840</v>
+      </c>
       <c r="J106"/>
       <c r="K106"/>
       <c r="L106">
-        <v>102</v>
+        <v>1</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="s">
-        <v>46</v>
+        <v>102</v>
       </c>
       <c r="B107" t="s">
-        <v>47</v>
+        <v>103</v>
       </c>
       <c r="C107" t="s">
-        <v>109</v>
+        <v>145</v>
       </c>
       <c r="D107">
-        <v>2878</v>
+        <v>30000</v>
       </c>
       <c r="E107" t="s">
-        <v>110</v>
+        <v>146</v>
       </c>
       <c r="F107" s="2">
-        <v>46269.326041666667</v>
+        <v>46270.7721412037</v>
       </c>
       <c r="G107" t="s">
         <v>15</v>
       </c>
       <c r="H107" t="s">
-        <v>48</v>
+        <v>104</v>
       </c>
       <c r="I107">
-        <v>440</v>
+        <v>60000</v>
       </c>
       <c r="J107"/>
       <c r="K107"/>
       <c r="L107">
-        <v>9083</v>
+        <v>115</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="s">
-        <v>49</v>
+        <v>141</v>
       </c>
       <c r="B108" t="s">
-        <v>50</v>
+        <v>142</v>
       </c>
       <c r="C108" t="s">
-        <v>109</v>
+        <v>145</v>
       </c>
       <c r="D108">
-        <v>94</v>
+        <v>6720</v>
       </c>
       <c r="E108" t="s">
-        <v>110</v>
+        <v>146</v>
       </c>
       <c r="F108" s="2">
-        <v>46269.326041666667</v>
+        <v>46270.765057870369</v>
       </c>
       <c r="G108" t="s">
         <v>15</v>
       </c>
       <c r="H108" t="s">
-        <v>48</v>
+        <v>104</v>
       </c>
       <c r="I108">
-        <v>250</v>
+        <v>26880</v>
       </c>
       <c r="J108"/>
       <c r="K108"/>
       <c r="L108">
-        <v>6369</v>
+        <v>319</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="s">
-        <v>51</v>
+        <v>141</v>
       </c>
       <c r="B109" t="s">
-        <v>52</v>
+        <v>142</v>
       </c>
       <c r="C109" t="s">
-        <v>109</v>
+        <v>147</v>
       </c>
       <c r="D109">
-        <v>47</v>
+        <v>2240</v>
       </c>
       <c r="E109" t="s">
-        <v>110</v>
+        <v>148</v>
       </c>
       <c r="F109" s="2">
-        <v>46268.854108796295</v>
+        <v>46271.740069444444</v>
       </c>
       <c r="G109" t="s">
         <v>15</v>
       </c>
       <c r="H109" t="s">
-        <v>48</v>
+        <v>104</v>
       </c>
       <c r="I109">
-        <v>250</v>
+        <v>26880</v>
       </c>
       <c r="J109"/>
       <c r="K109"/>
       <c r="L109">
-        <v>5171</v>
+        <v>920</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="s">
-        <v>117</v>
+        <v>149</v>
       </c>
       <c r="B110" t="s">
-        <v>118</v>
+        <v>150</v>
       </c>
       <c r="C110" t="s">
-        <v>119</v>
+        <v>151</v>
       </c>
       <c r="D110">
-        <v>1800</v>
+        <v>400</v>
       </c>
       <c r="E110" t="s">
-        <v>120</v>
+        <v>152</v>
       </c>
       <c r="F110" s="2">
-        <v>46269.301168981481</v>
+        <v>45185</v>
       </c>
       <c r="G110" t="s">
         <v>15</v>
       </c>
       <c r="H110" t="s">
-        <v>16</v>
-      </c>
-      <c r="I110"/>
+        <v>104</v>
+      </c>
+      <c r="I110">
+        <v>173</v>
+      </c>
       <c r="J110"/>
       <c r="K110"/>
       <c r="L110">
-        <v>1006</v>
+        <v>1</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="s">
-        <v>121</v>
+        <v>153</v>
       </c>
       <c r="B111" t="s">
-        <v>122</v>
+        <v>154</v>
       </c>
       <c r="C111" t="s">
-        <v>123</v>
+        <v>155</v>
       </c>
       <c r="D111">
-        <v>800</v>
+        <v>1</v>
       </c>
       <c r="E111" t="s">
-        <v>124</v>
+        <v>156</v>
       </c>
       <c r="F111" s="2">
-        <v>46269.2324537037</v>
+        <v>46269.612592592588</v>
       </c>
       <c r="G111" t="s">
         <v>15</v>
       </c>
       <c r="H111" t="s">
-        <v>99</v>
+        <v>157</v>
       </c>
       <c r="I111">
-        <v>793</v>
+        <v>1</v>
       </c>
       <c r="J111"/>
       <c r="K111"/>
       <c r="L111">
-        <v>383</v>
+        <v>11</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="s">
-        <v>97</v>
+        <v>158</v>
       </c>
       <c r="B112" t="s">
-        <v>98</v>
+        <v>159</v>
       </c>
       <c r="C112" t="s">
-        <v>123</v>
+        <v>155</v>
       </c>
       <c r="D112">
-        <v>20000</v>
+        <v>1</v>
       </c>
       <c r="E112" t="s">
-        <v>124</v>
+        <v>156</v>
       </c>
       <c r="F112" s="2">
-        <v>46268.826527777775</v>
+        <v>46269.612592592588</v>
       </c>
       <c r="G112" t="s">
         <v>15</v>
       </c>
       <c r="H112" t="s">
-        <v>99</v>
+        <v>157</v>
       </c>
       <c r="I112">
-        <v>60000</v>
+        <v>20</v>
       </c>
       <c r="J112"/>
       <c r="K112"/>
       <c r="L112">
-        <v>137</v>
+        <v>11</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="s">
-        <v>125</v>
+        <v>160</v>
       </c>
       <c r="B113" t="s">
-        <v>126</v>
+        <v>161</v>
       </c>
       <c r="C113" t="s">
-        <v>123</v>
+        <v>155</v>
       </c>
       <c r="D113">
-        <v>22313</v>
+        <v>1960</v>
       </c>
       <c r="E113" t="s">
-        <v>124</v>
+        <v>156</v>
       </c>
       <c r="F113" s="2">
-        <v>46269.2324537037</v>
+        <v>46269.655729166661</v>
       </c>
       <c r="G113" t="s">
         <v>15</v>
       </c>
       <c r="H113" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="I113">
-        <v>55020</v>
+        <v>35840</v>
       </c>
       <c r="J113"/>
       <c r="K113"/>
       <c r="L113">
-        <v>2134</v>
+        <v>75</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="s">
-        <v>127</v>
+        <v>162</v>
       </c>
       <c r="B114" t="s">
-        <v>128</v>
+        <v>163</v>
       </c>
       <c r="C114" t="s">
-        <v>123</v>
+        <v>155</v>
       </c>
       <c r="D114">
-        <v>6720</v>
+        <v>1800</v>
       </c>
       <c r="E114" t="s">
-        <v>124</v>
+        <v>156</v>
       </c>
       <c r="F114" s="2">
-        <v>46269.2324537037</v>
+        <v>46269.655729166661</v>
       </c>
       <c r="G114" t="s">
         <v>15</v>
       </c>
       <c r="H114" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="I114">
-        <v>30100</v>
+        <v>15000</v>
       </c>
       <c r="J114"/>
       <c r="K114"/>
       <c r="L114">
-        <v>596</v>
+        <v>22</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="s">
-        <v>97</v>
+        <v>139</v>
       </c>
       <c r="B115" t="s">
-        <v>98</v>
+        <v>140</v>
       </c>
       <c r="C115" t="s">
-        <v>129</v>
+        <v>164</v>
       </c>
       <c r="D115">
-        <v>20000</v>
+        <v>2560</v>
       </c>
       <c r="E115" t="s">
-        <v>130</v>
+        <v>165</v>
       </c>
       <c r="F115" s="2">
-        <v>46268.939097222217</v>
+        <v>46271.751493055555</v>
       </c>
       <c r="G115" t="s">
         <v>15</v>
       </c>
       <c r="H115" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="I115">
-        <v>60000</v>
+        <v>26880</v>
       </c>
       <c r="J115"/>
       <c r="K115"/>
       <c r="L115">
-        <v>111</v>
+        <v>432</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="s">
-        <v>131</v>
+        <v>166</v>
       </c>
       <c r="B116" t="s">
-        <v>132</v>
+        <v>167</v>
       </c>
       <c r="C116" t="s">
-        <v>133</v>
+        <v>164</v>
       </c>
       <c r="D116">
-        <v>2240</v>
+        <v>6000</v>
       </c>
       <c r="E116" t="s">
-        <v>134</v>
+        <v>165</v>
       </c>
       <c r="F116" s="2">
-        <v>46268.972465277773</v>
+        <v>46271.751493055555</v>
       </c>
       <c r="G116" t="s">
         <v>15</v>
       </c>
       <c r="H116" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="I116">
-        <v>5040</v>
+        <v>10000</v>
       </c>
       <c r="J116"/>
       <c r="K116"/>
       <c r="L116">
-        <v>908</v>
+        <v>139</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="s">
-        <v>121</v>
+        <v>168</v>
       </c>
       <c r="B117" t="s">
-        <v>122</v>
+        <v>169</v>
       </c>
       <c r="C117" t="s">
-        <v>133</v>
+        <v>164</v>
       </c>
       <c r="D117">
-        <v>1600</v>
+        <v>10000</v>
       </c>
       <c r="E117" t="s">
-        <v>134</v>
+        <v>165</v>
       </c>
       <c r="F117" s="2">
-        <v>46268.972465277773</v>
+        <v>46271.751493055555</v>
       </c>
       <c r="G117" t="s">
         <v>15</v>
       </c>
       <c r="H117" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="I117">
-        <v>793</v>
+        <v>400000</v>
       </c>
       <c r="J117"/>
       <c r="K117"/>
       <c r="L117">
-        <v>157</v>
+        <v>29</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="s">
-        <v>135</v>
+        <v>170</v>
       </c>
       <c r="B118" t="s">
-        <v>136</v>
+        <v>171</v>
       </c>
       <c r="C118" t="s">
-        <v>133</v>
+        <v>172</v>
       </c>
       <c r="D118">
-        <v>600</v>
+        <v>1</v>
       </c>
       <c r="E118" t="s">
-        <v>134</v>
+        <v>173</v>
       </c>
       <c r="F118" s="2">
-        <v>46267.859270833331</v>
+        <v>46265.788981481477</v>
       </c>
       <c r="G118" t="s">
         <v>15</v>
       </c>
       <c r="H118" t="s">
-        <v>99</v>
+        <v>157</v>
       </c>
       <c r="I118">
-        <v>15000</v>
+        <v>50</v>
       </c>
       <c r="J118"/>
       <c r="K118"/>
       <c r="L118">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="s">
-        <v>137</v>
+        <v>174</v>
       </c>
       <c r="B119" t="s">
-        <v>138</v>
+        <v>175</v>
       </c>
       <c r="C119" t="s">
-        <v>139</v>
+        <v>172</v>
       </c>
       <c r="D119">
-        <v>2940</v>
+        <v>1</v>
       </c>
       <c r="E119" t="s">
-        <v>140</v>
+        <v>173</v>
       </c>
       <c r="F119" s="2">
-        <v>46268</v>
+        <v>46265.776967592588</v>
       </c>
       <c r="G119" t="s">
         <v>15</v>
       </c>
       <c r="H119" t="s">
-        <v>99</v>
+        <v>157</v>
       </c>
       <c r="I119">
-        <v>4480</v>
+        <v>45</v>
       </c>
       <c r="J119"/>
       <c r="K119"/>
       <c r="L119">
-        <v>44</v>
+        <v>11</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="s">
-        <v>141</v>
+        <v>176</v>
       </c>
       <c r="B120" t="s">
-        <v>142</v>
+        <v>177</v>
       </c>
       <c r="C120" t="s">
-        <v>139</v>
+        <v>172</v>
       </c>
       <c r="D120">
-        <v>4480</v>
+        <v>1</v>
       </c>
       <c r="E120" t="s">
-        <v>140</v>
+        <v>173</v>
       </c>
       <c r="F120" s="2">
-        <v>46268</v>
+        <v>46265.788981481477</v>
       </c>
       <c r="G120" t="s">
         <v>15</v>
       </c>
       <c r="H120" t="s">
-        <v>99</v>
+        <v>157</v>
       </c>
       <c r="I120">
-        <v>33600</v>
+        <v>120</v>
       </c>
       <c r="J120"/>
       <c r="K120"/>
       <c r="L120">
-        <v>90</v>
+        <v>19</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="s">
-        <v>121</v>
+        <v>160</v>
       </c>
       <c r="B121" t="s">
-        <v>122</v>
+        <v>161</v>
       </c>
       <c r="C121" t="s">
-        <v>139</v>
+        <v>172</v>
       </c>
       <c r="D121">
-        <v>900</v>
+        <v>280</v>
       </c>
       <c r="E121" t="s">
-        <v>140</v>
+        <v>173</v>
       </c>
       <c r="F121" s="2">
-        <v>46268</v>
+        <v>46261.786122685182</v>
       </c>
       <c r="G121" t="s">
         <v>15</v>
       </c>
       <c r="H121" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="I121">
-        <v>793</v>
+        <v>35840</v>
       </c>
       <c r="J121"/>
       <c r="K121"/>
       <c r="L121">
-        <v>114</v>
+        <v>167</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="s">
-        <v>143</v>
+        <v>38</v>
       </c>
       <c r="B122" t="s">
-        <v>144</v>
+        <v>39</v>
       </c>
       <c r="C122" t="s">
-        <v>139</v>
+        <v>178</v>
       </c>
       <c r="D122">
-        <v>220</v>
+        <v>120</v>
       </c>
       <c r="E122" t="s">
-        <v>140</v>
+        <v>179</v>
       </c>
       <c r="F122" s="2">
-        <v>46267</v>
+        <v>46272.355543981481</v>
       </c>
       <c r="G122" t="s">
         <v>15</v>
       </c>
       <c r="H122" t="s">
-        <v>99</v>
-      </c>
-      <c r="I122">
-        <v>173</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="I122"/>
       <c r="J122"/>
       <c r="K122"/>
       <c r="L122">
-        <v>107</v>
+        <v>366</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="s">
-        <v>125</v>
+        <v>180</v>
       </c>
       <c r="B123" t="s">
-        <v>126</v>
+        <v>181</v>
       </c>
       <c r="C123" t="s">
-        <v>139</v>
+        <v>178</v>
       </c>
       <c r="D123">
-        <v>4480</v>
+        <v>48362</v>
       </c>
       <c r="E123" t="s">
-        <v>140</v>
+        <v>179</v>
       </c>
       <c r="F123" s="2">
-        <v>46268</v>
+        <v>46271.328287037039</v>
       </c>
       <c r="G123" t="s">
         <v>15</v>
       </c>
       <c r="H123" t="s">
-        <v>99</v>
-      </c>
-      <c r="I123">
-        <v>55020</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="I123"/>
       <c r="J123"/>
       <c r="K123"/>
       <c r="L123">
-        <v>250</v>
+        <v>11</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="s">
-        <v>143</v>
+        <v>24</v>
       </c>
       <c r="B124" t="s">
-        <v>144</v>
+        <v>25</v>
       </c>
       <c r="C124" t="s">
-        <v>145</v>
+        <v>178</v>
       </c>
       <c r="D124">
-        <v>400</v>
+        <v>5161</v>
       </c>
       <c r="E124" t="s">
-        <v>146</v>
+        <v>179</v>
       </c>
       <c r="F124" s="2">
-        <v>45185</v>
+        <v>46271.371979166666</v>
       </c>
       <c r="G124" t="s">
         <v>15</v>
       </c>
       <c r="H124" t="s">
-        <v>99</v>
+        <v>26</v>
       </c>
       <c r="I124">
-        <v>173</v>
+        <v>440</v>
       </c>
       <c r="J124"/>
       <c r="K124"/>
       <c r="L124">
-        <v>1</v>
+        <v>11127</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="s">
-        <v>141</v>
+        <v>182</v>
       </c>
       <c r="B125" t="s">
-        <v>142</v>
+        <v>183</v>
       </c>
       <c r="C125" t="s">
-        <v>147</v>
+        <v>178</v>
       </c>
       <c r="D125">
-        <v>1120</v>
+        <v>186</v>
       </c>
       <c r="E125" t="s">
-        <v>148</v>
+        <v>179</v>
       </c>
       <c r="F125" s="2">
-        <v>46267.903784722221</v>
+        <v>44946.553055555552</v>
       </c>
       <c r="G125" t="s">
         <v>15</v>
       </c>
       <c r="H125" t="s">
-        <v>99</v>
+        <v>26</v>
       </c>
       <c r="I125">
-        <v>33600</v>
+        <v>20</v>
       </c>
       <c r="J125"/>
       <c r="K125"/>
       <c r="L125">
-        <v>74</v>
+        <v>2</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="s">
-        <v>135</v>
+        <v>27</v>
       </c>
       <c r="B126" t="s">
-        <v>136</v>
+        <v>28</v>
       </c>
       <c r="C126" t="s">
-        <v>147</v>
+        <v>178</v>
       </c>
       <c r="D126">
-        <v>1000</v>
+        <v>172</v>
       </c>
       <c r="E126" t="s">
-        <v>148</v>
+        <v>179</v>
       </c>
       <c r="F126" s="2">
-        <v>46267.872303240736</v>
+        <v>46271.371979166666</v>
       </c>
       <c r="G126" t="s">
         <v>15</v>
       </c>
       <c r="H126" t="s">
-        <v>99</v>
+        <v>26</v>
       </c>
       <c r="I126">
-        <v>15000</v>
+        <v>250</v>
       </c>
       <c r="J126"/>
       <c r="K126"/>
       <c r="L126">
-        <v>21</v>
+        <v>8782</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="s">
-        <v>149</v>
+        <v>29</v>
       </c>
       <c r="B127" t="s">
-        <v>150</v>
+        <v>30</v>
       </c>
       <c r="C127" t="s">
-        <v>151</v>
+        <v>178</v>
       </c>
       <c r="D127">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="E127" t="s">
-        <v>152</v>
+        <v>179</v>
       </c>
       <c r="F127" s="2">
-        <v>46265.788981481477</v>
+        <v>46271.37054398148</v>
       </c>
       <c r="G127" t="s">
         <v>15</v>
       </c>
       <c r="H127" t="s">
-        <v>153</v>
+        <v>26</v>
       </c>
       <c r="I127">
-        <v>12</v>
+        <v>250</v>
       </c>
       <c r="J127"/>
       <c r="K127"/>
       <c r="L127">
-        <v>14</v>
+        <v>4287</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="s">
-        <v>154</v>
+        <v>184</v>
       </c>
       <c r="B128" t="s">
-        <v>155</v>
+        <v>185</v>
       </c>
       <c r="C128" t="s">
-        <v>151</v>
+        <v>178</v>
       </c>
       <c r="D128">
-        <v>1</v>
+        <v>93</v>
       </c>
       <c r="E128" t="s">
-        <v>152</v>
+        <v>179</v>
       </c>
       <c r="F128" s="2">
-        <v>46265.776967592588</v>
+        <v>45777.752291666664</v>
       </c>
       <c r="G128" t="s">
         <v>15</v>
       </c>
       <c r="H128" t="s">
-        <v>153</v>
+        <v>186</v>
       </c>
       <c r="I128">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="J128"/>
       <c r="K128"/>
       <c r="L128">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="s">
-        <v>156</v>
+        <v>187</v>
       </c>
       <c r="B129" t="s">
-        <v>157</v>
+        <v>188</v>
       </c>
       <c r="C129" t="s">
-        <v>151</v>
+        <v>178</v>
       </c>
       <c r="D129">
-        <v>1</v>
+        <v>55</v>
       </c>
       <c r="E129" t="s">
-        <v>152</v>
+        <v>179</v>
       </c>
       <c r="F129" s="2">
-        <v>46265.788981481477</v>
+        <v>44426</v>
       </c>
       <c r="G129" t="s">
         <v>15</v>
       </c>
       <c r="H129" t="s">
-        <v>153</v>
+        <v>33</v>
       </c>
       <c r="I129">
-        <v>60</v>
+        <v>2</v>
       </c>
       <c r="J129"/>
       <c r="K129"/>
       <c r="L129">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="s">
-        <v>141</v>
+        <v>31</v>
       </c>
       <c r="B130" t="s">
-        <v>142</v>
+        <v>32</v>
       </c>
       <c r="C130" t="s">
-        <v>151</v>
+        <v>178</v>
       </c>
       <c r="D130">
-        <v>280</v>
+        <v>50</v>
       </c>
       <c r="E130" t="s">
-        <v>152</v>
+        <v>179</v>
       </c>
       <c r="F130" s="2">
-        <v>46261.786122685182</v>
+        <v>46271.37054398148</v>
       </c>
       <c r="G130" t="s">
         <v>15</v>
       </c>
       <c r="H130" t="s">
-        <v>99</v>
+        <v>33</v>
       </c>
       <c r="I130">
-        <v>33600</v>
+        <v>5000</v>
       </c>
       <c r="J130"/>
       <c r="K130"/>
       <c r="L130">
-        <v>167</v>
+        <v>2494</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="s">
-        <v>158</v>
+        <v>97</v>
       </c>
       <c r="B131" t="s">
-        <v>159</v>
+        <v>98</v>
       </c>
       <c r="C131" t="s">
-        <v>160</v>
+        <v>189</v>
       </c>
       <c r="D131">
-        <v>39040</v>
+        <v>1200</v>
       </c>
       <c r="E131" t="s">
-        <v>161</v>
+        <v>190</v>
       </c>
       <c r="F131" s="2">
-        <v>46267.720879629625</v>
+        <v>46272.361030092594</v>
       </c>
       <c r="G131" t="s">
         <v>15</v>
       </c>
       <c r="H131" t="s">
-        <v>16</v>
+        <v>101</v>
       </c>
       <c r="I131">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="J131"/>
       <c r="K131"/>
       <c r="L131">
-        <v>1386</v>
+        <v>1611</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="s">
-        <v>162</v>
+        <v>191</v>
       </c>
       <c r="B132" t="s">
-        <v>163</v>
+        <v>192</v>
       </c>
       <c r="C132" t="s">
-        <v>160</v>
+        <v>189</v>
       </c>
       <c r="D132">
-        <v>180</v>
+        <v>260</v>
       </c>
       <c r="E132" t="s">
-        <v>161</v>
+        <v>190</v>
       </c>
       <c r="F132" s="2">
-        <v>46268.594189814816</v>
+        <v>46272.361030092594</v>
       </c>
       <c r="G132" t="s">
         <v>15</v>
       </c>
       <c r="H132" t="s">
-        <v>16</v>
-      </c>
-      <c r="I132"/>
+        <v>104</v>
+      </c>
+      <c r="I132">
+        <v>404</v>
+      </c>
       <c r="J132"/>
       <c r="K132"/>
       <c r="L132">
-        <v>9</v>
+        <v>419</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B133" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C133" t="s">
-        <v>160</v>
+        <v>189</v>
       </c>
       <c r="D133">
-        <v>186</v>
+        <v>2000</v>
       </c>
       <c r="E133" t="s">
-        <v>161</v>
+        <v>190</v>
       </c>
       <c r="F133" s="2">
-        <v>44946.553055555552</v>
+        <v>46272.361030092594</v>
       </c>
       <c r="G133" t="s">
         <v>15</v>
       </c>
       <c r="H133" t="s">
-        <v>48</v>
+        <v>104</v>
       </c>
       <c r="I133">
-        <v>20</v>
+        <v>15000</v>
       </c>
       <c r="J133"/>
       <c r="K133"/>
       <c r="L133">
-        <v>2</v>
+        <v>298</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="s">
-        <v>166</v>
+        <v>102</v>
       </c>
       <c r="B134" t="s">
-        <v>167</v>
+        <v>103</v>
       </c>
       <c r="C134" t="s">
-        <v>160</v>
+        <v>189</v>
       </c>
       <c r="D134">
-        <v>93</v>
+        <v>10000</v>
       </c>
       <c r="E134" t="s">
-        <v>161</v>
+        <v>190</v>
       </c>
       <c r="F134" s="2">
-        <v>45777.752291666664</v>
+        <v>46269</v>
       </c>
       <c r="G134" t="s">
         <v>15</v>
       </c>
       <c r="H134" t="s">
-        <v>168</v>
+        <v>104</v>
       </c>
       <c r="I134">
-        <v>16</v>
+        <v>60000</v>
       </c>
       <c r="J134"/>
       <c r="K134"/>
       <c r="L134">
-        <v>7</v>
+        <v>925</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="s">
-        <v>169</v>
+        <v>193</v>
       </c>
       <c r="B135" t="s">
-        <v>170</v>
+        <v>194</v>
       </c>
       <c r="C135" t="s">
-        <v>160</v>
+        <v>189</v>
       </c>
       <c r="D135">
-        <v>55</v>
+        <v>10000</v>
       </c>
       <c r="E135" t="s">
-        <v>161</v>
+        <v>190</v>
       </c>
       <c r="F135" s="2">
-        <v>44426</v>
+        <v>46269</v>
       </c>
       <c r="G135" t="s">
         <v>15</v>
       </c>
       <c r="H135" t="s">
-        <v>55</v>
+        <v>104</v>
       </c>
       <c r="I135">
-        <v>2</v>
+        <v>45000</v>
       </c>
       <c r="J135"/>
       <c r="K135"/>
       <c r="L135">
-        <v>5</v>
+        <v>321</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="B136" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="C136" t="s">
-        <v>171</v>
+        <v>189</v>
       </c>
       <c r="D136">
-        <v>600</v>
+        <v>2</v>
       </c>
       <c r="E136" t="s">
-        <v>172</v>
+        <v>190</v>
       </c>
       <c r="F136" s="2">
-        <v>46268.846284722218</v>
+        <v>46271.051990740736</v>
       </c>
       <c r="G136" t="s">
-        <v>15</v>
+        <v>109</v>
       </c>
       <c r="H136" t="s">
-        <v>16</v>
-      </c>
-      <c r="I136"/>
+        <v>104</v>
+      </c>
+      <c r="I136">
+        <v>60</v>
+      </c>
       <c r="J136"/>
       <c r="K136"/>
       <c r="L136">
-        <v>418</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="s">
-        <v>103</v>
+        <v>195</v>
       </c>
       <c r="B137" t="s">
-        <v>104</v>
+        <v>196</v>
       </c>
       <c r="C137" t="s">
-        <v>171</v>
+        <v>189</v>
       </c>
       <c r="D137">
-        <v>576</v>
+        <v>4000</v>
       </c>
       <c r="E137" t="s">
-        <v>172</v>
+        <v>190</v>
       </c>
       <c r="F137" s="2">
-        <v>46268.846284722218</v>
+        <v>46272.361030092594</v>
       </c>
       <c r="G137" t="s">
         <v>15</v>
       </c>
       <c r="H137" t="s">
-        <v>16</v>
-      </c>
-      <c r="I137"/>
+        <v>112</v>
+      </c>
+      <c r="I137">
+        <v>42080</v>
+      </c>
       <c r="J137"/>
       <c r="K137"/>
       <c r="L137">
-        <v>438</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="s">
-        <v>173</v>
+        <v>110</v>
       </c>
       <c r="B138" t="s">
-        <v>174</v>
+        <v>111</v>
       </c>
       <c r="C138" t="s">
-        <v>171</v>
+        <v>189</v>
       </c>
       <c r="D138">
-        <v>2160</v>
+        <v>4000</v>
       </c>
       <c r="E138" t="s">
-        <v>172</v>
+        <v>190</v>
       </c>
       <c r="F138" s="2">
-        <v>46267.751342592594</v>
+        <v>46272.361030092594</v>
       </c>
       <c r="G138" t="s">
         <v>15</v>
       </c>
       <c r="H138" t="s">
-        <v>16</v>
+        <v>112</v>
       </c>
       <c r="I138"/>
       <c r="J138"/>
       <c r="K138"/>
       <c r="L138">
-        <v>51</v>
+        <v>116</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="s">
-        <v>175</v>
+        <v>38</v>
       </c>
       <c r="B139" t="s">
-        <v>176</v>
+        <v>39</v>
       </c>
       <c r="C139" t="s">
-        <v>171</v>
+        <v>197</v>
       </c>
       <c r="D139">
-        <v>600</v>
+        <v>36</v>
       </c>
       <c r="E139" t="s">
-        <v>172</v>
+        <v>198</v>
       </c>
       <c r="F139" s="2">
-        <v>46268.821967592594</v>
+        <v>46268.796597222223</v>
       </c>
       <c r="G139" t="s">
         <v>15</v>
       </c>
       <c r="H139" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="I139"/>
       <c r="J139"/>
       <c r="K139"/>
       <c r="L139">
-        <v>532</v>
+        <v>166</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="s">
-        <v>177</v>
+        <v>199</v>
       </c>
       <c r="B140" t="s">
-        <v>178</v>
+        <v>200</v>
       </c>
       <c r="C140" t="s">
-        <v>171</v>
+        <v>197</v>
       </c>
       <c r="D140">
-        <v>9624</v>
+        <v>300</v>
       </c>
       <c r="E140" t="s">
-        <v>172</v>
+        <v>198</v>
       </c>
       <c r="F140" s="2">
-        <v>46268.832696759258</v>
+        <v>46267.568553240737</v>
       </c>
       <c r="G140" t="s">
         <v>15</v>
       </c>
       <c r="H140" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="I140"/>
       <c r="J140"/>
       <c r="K140"/>
       <c r="L140">
-        <v>27</v>
+        <v>3</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="s">
-        <v>179</v>
+        <v>119</v>
       </c>
       <c r="B141" t="s">
-        <v>180</v>
+        <v>120</v>
       </c>
       <c r="C141" t="s">
-        <v>171</v>
+        <v>197</v>
       </c>
       <c r="D141">
-        <v>3276</v>
+        <v>200736</v>
       </c>
       <c r="E141" t="s">
-        <v>172</v>
+        <v>198</v>
       </c>
       <c r="F141" s="2">
-        <v>46268.832696759258</v>
+        <v>46271.626504629625</v>
       </c>
       <c r="G141" t="s">
         <v>15</v>
       </c>
       <c r="H141" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="I141"/>
       <c r="J141"/>
       <c r="K141"/>
       <c r="L141">
-        <v>25</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="s">
-        <v>46</v>
+        <v>201</v>
       </c>
       <c r="B142" t="s">
-        <v>47</v>
+        <v>202</v>
       </c>
       <c r="C142" t="s">
-        <v>171</v>
+        <v>197</v>
       </c>
       <c r="D142">
-        <v>54</v>
+        <v>2160</v>
       </c>
       <c r="E142" t="s">
-        <v>172</v>
+        <v>198</v>
       </c>
       <c r="F142" s="2">
-        <v>46268.832696759258</v>
+        <v>46269.648263888885</v>
       </c>
       <c r="G142" t="s">
         <v>15</v>
       </c>
       <c r="H142" t="s">
-        <v>48</v>
-      </c>
-      <c r="I142">
-        <v>440</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="I142"/>
       <c r="J142"/>
       <c r="K142"/>
       <c r="L142">
-        <v>145</v>
+        <v>75</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="s">
-        <v>49</v>
+        <v>27</v>
       </c>
       <c r="B143" t="s">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="C143" t="s">
-        <v>171</v>
+        <v>197</v>
       </c>
       <c r="D143">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="E143" t="s">
-        <v>172</v>
+        <v>198</v>
       </c>
       <c r="F143" s="2">
-        <v>46268.832696759258</v>
+        <v>46272.054583333331</v>
       </c>
       <c r="G143" t="s">
         <v>15</v>
       </c>
       <c r="H143" t="s">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="I143">
         <v>250</v>
@@ -5521,1284 +5524,446 @@
       <c r="J143"/>
       <c r="K143"/>
       <c r="L143">
-        <v>84</v>
+        <v>4351</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="s">
-        <v>53</v>
+        <v>203</v>
       </c>
       <c r="B144" t="s">
-        <v>54</v>
+        <v>204</v>
       </c>
       <c r="C144" t="s">
-        <v>171</v>
+        <v>205</v>
       </c>
       <c r="D144">
-        <v>5</v>
+        <v>1000000</v>
       </c>
       <c r="E144" t="s">
-        <v>172</v>
+        <v>206</v>
       </c>
       <c r="F144" s="2">
-        <v>46268.832696759258</v>
+        <v>46235</v>
       </c>
       <c r="G144" t="s">
-        <v>15</v>
+        <v>207</v>
       </c>
       <c r="H144" t="s">
-        <v>55</v>
+        <v>208</v>
       </c>
       <c r="I144">
-        <v>5000</v>
+        <v>4880</v>
       </c>
       <c r="J144"/>
       <c r="K144"/>
       <c r="L144">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="s">
-        <v>121</v>
+        <v>209</v>
       </c>
       <c r="B145" t="s">
-        <v>122</v>
+        <v>210</v>
       </c>
       <c r="C145" t="s">
-        <v>181</v>
+        <v>211</v>
       </c>
       <c r="D145">
-        <v>2880</v>
+        <v>899100</v>
       </c>
       <c r="E145" t="s">
-        <v>182</v>
+        <v>212</v>
       </c>
       <c r="F145" s="2">
-        <v>46269.351180555554</v>
+        <v>46266</v>
       </c>
       <c r="G145" t="s">
-        <v>15</v>
+        <v>207</v>
       </c>
       <c r="H145" t="s">
-        <v>99</v>
+        <v>208</v>
       </c>
       <c r="I145">
-        <v>793</v>
+        <v>800000</v>
       </c>
       <c r="J145"/>
       <c r="K145"/>
       <c r="L145">
-        <v>223</v>
+        <v>55</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="s">
-        <v>97</v>
+        <v>213</v>
       </c>
       <c r="B146" t="s">
-        <v>98</v>
+        <v>214</v>
       </c>
       <c r="C146" t="s">
-        <v>181</v>
+        <v>211</v>
       </c>
       <c r="D146">
-        <v>10000</v>
+        <v>104000</v>
       </c>
       <c r="E146" t="s">
-        <v>182</v>
+        <v>212</v>
       </c>
       <c r="F146" s="2">
-        <v>46267.591412037036</v>
+        <v>46258</v>
       </c>
       <c r="G146" t="s">
-        <v>15</v>
+        <v>207</v>
       </c>
       <c r="H146" t="s">
-        <v>99</v>
+        <v>208</v>
       </c>
       <c r="I146">
-        <v>60000</v>
+        <v>52000</v>
       </c>
       <c r="J146"/>
       <c r="K146"/>
       <c r="L146">
-        <v>923</v>
+        <v>53</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="s">
-        <v>183</v>
+        <v>215</v>
       </c>
       <c r="B147" t="s">
-        <v>184</v>
+        <v>216</v>
       </c>
       <c r="C147" t="s">
-        <v>181</v>
+        <v>217</v>
       </c>
       <c r="D147">
-        <v>2500</v>
+        <v>2</v>
       </c>
       <c r="E147" t="s">
-        <v>182</v>
+        <v>218</v>
       </c>
       <c r="F147" s="2">
-        <v>46267.591412037036</v>
+        <v>46268.56618055555</v>
       </c>
       <c r="G147" t="s">
-        <v>15</v>
+        <v>219</v>
       </c>
       <c r="H147" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="I147">
-        <v>40000</v>
+        <v>2</v>
       </c>
       <c r="J147"/>
       <c r="K147"/>
       <c r="L147">
-        <v>822</v>
+        <v>1</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="s">
-        <v>185</v>
+        <v>220</v>
       </c>
       <c r="B148" t="s">
-        <v>186</v>
+        <v>221</v>
       </c>
       <c r="C148" t="s">
-        <v>181</v>
+        <v>217</v>
       </c>
       <c r="D148">
-        <v>10000</v>
+        <v>300</v>
       </c>
       <c r="E148" t="s">
-        <v>182</v>
+        <v>218</v>
       </c>
       <c r="F148" s="2">
-        <v>46267.591412037036</v>
+        <v>46268.65243055555</v>
       </c>
       <c r="G148" t="s">
         <v>15</v>
       </c>
       <c r="H148" t="s">
-        <v>99</v>
+        <v>222</v>
       </c>
       <c r="I148">
-        <v>45000</v>
+        <v>300</v>
       </c>
       <c r="J148"/>
       <c r="K148"/>
       <c r="L148">
-        <v>319</v>
+        <v>3</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="s">
-        <v>187</v>
+        <v>223</v>
       </c>
       <c r="B149" t="s">
-        <v>188</v>
+        <v>224</v>
       </c>
       <c r="C149" t="s">
-        <v>181</v>
+        <v>217</v>
       </c>
       <c r="D149">
-        <v>5000</v>
+        <v>1</v>
       </c>
       <c r="E149" t="s">
-        <v>182</v>
+        <v>218</v>
       </c>
       <c r="F149" s="2">
-        <v>46267.591412037036</v>
+        <v>46268.664467592593</v>
       </c>
       <c r="G149" t="s">
         <v>15</v>
       </c>
       <c r="H149" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="I149">
-        <v>5000</v>
+        <v>1</v>
       </c>
       <c r="J149"/>
       <c r="K149"/>
       <c r="L149">
-        <v>32</v>
+        <v>1</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="B150" t="s">
-        <v>190</v>
+        <v>226</v>
       </c>
       <c r="C150" t="s">
-        <v>181</v>
+        <v>217</v>
       </c>
       <c r="D150">
-        <v>10000</v>
+        <v>15</v>
       </c>
       <c r="E150" t="s">
-        <v>182</v>
+        <v>218</v>
       </c>
       <c r="F150" s="2">
-        <v>46267.591412037036</v>
+        <v>46269.483877314815</v>
       </c>
       <c r="G150" t="s">
         <v>15</v>
       </c>
       <c r="H150" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="I150">
-        <v>400000</v>
+        <v>20</v>
       </c>
       <c r="J150"/>
       <c r="K150"/>
       <c r="L150">
-        <v>963</v>
+        <v>5</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="s">
-        <v>191</v>
+        <v>227</v>
       </c>
       <c r="B151" t="s">
-        <v>192</v>
+        <v>228</v>
       </c>
       <c r="C151" t="s">
-        <v>181</v>
+        <v>217</v>
       </c>
       <c r="D151">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="E151" t="s">
-        <v>182</v>
+        <v>218</v>
       </c>
       <c r="F151" s="2">
-        <v>46267.591412037036</v>
+        <v>46268.656412037039</v>
       </c>
       <c r="G151" t="s">
-        <v>193</v>
+        <v>15</v>
       </c>
       <c r="H151" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="I151">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="J151"/>
       <c r="K151"/>
       <c r="L151">
-        <v>1061</v>
+        <v>1</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="s">
-        <v>72</v>
+        <v>229</v>
       </c>
       <c r="B152" t="s">
-        <v>73</v>
+        <v>230</v>
       </c>
       <c r="C152" t="s">
-        <v>194</v>
+        <v>217</v>
       </c>
       <c r="D152">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="E152" t="s">
-        <v>195</v>
+        <v>218</v>
       </c>
       <c r="F152" s="2">
-        <v>46268.796597222223</v>
+        <v>46268.655486111107</v>
       </c>
       <c r="G152" t="s">
         <v>15</v>
       </c>
       <c r="H152" t="s">
-        <v>16</v>
-      </c>
-      <c r="I152"/>
+        <v>96</v>
+      </c>
+      <c r="I152">
+        <v>11</v>
+      </c>
       <c r="J152"/>
       <c r="K152"/>
       <c r="L152">
-        <v>166</v>
+        <v>7</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="s">
-        <v>196</v>
+        <v>213</v>
       </c>
       <c r="B153" t="s">
-        <v>197</v>
+        <v>214</v>
       </c>
       <c r="C153" t="s">
-        <v>194</v>
+        <v>231</v>
       </c>
       <c r="D153">
-        <v>300</v>
+        <v>104000</v>
       </c>
       <c r="E153" t="s">
-        <v>195</v>
+        <v>232</v>
       </c>
       <c r="F153" s="2">
-        <v>46267.568553240737</v>
+        <v>46235</v>
       </c>
       <c r="G153" t="s">
-        <v>15</v>
+        <v>207</v>
       </c>
       <c r="H153" t="s">
-        <v>16</v>
-      </c>
-      <c r="I153"/>
+        <v>208</v>
+      </c>
+      <c r="I153">
+        <v>52000</v>
+      </c>
       <c r="J153"/>
       <c r="K153"/>
       <c r="L153">
-        <v>3</v>
+        <v>47</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="s">
-        <v>103</v>
+        <v>233</v>
       </c>
       <c r="B154" t="s">
-        <v>104</v>
+        <v>234</v>
       </c>
       <c r="C154" t="s">
-        <v>194</v>
+        <v>235</v>
       </c>
       <c r="D154">
-        <v>237024</v>
+        <v>127707</v>
       </c>
       <c r="E154" t="s">
-        <v>195</v>
+        <v>236</v>
       </c>
       <c r="F154" s="2">
-        <v>46268.940960648149</v>
+        <v>46270</v>
       </c>
       <c r="G154" t="s">
         <v>15</v>
       </c>
       <c r="H154" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="I154"/>
       <c r="J154"/>
       <c r="K154"/>
       <c r="L154">
-        <v>2296</v>
+        <v>556</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="s">
-        <v>113</v>
+        <v>237</v>
       </c>
       <c r="B155" t="s">
-        <v>114</v>
+        <v>238</v>
       </c>
       <c r="C155" t="s">
-        <v>194</v>
+        <v>239</v>
       </c>
       <c r="D155">
-        <v>274080</v>
+        <v>1040</v>
       </c>
       <c r="E155" t="s">
-        <v>195</v>
+        <v>240</v>
       </c>
       <c r="F155" s="2">
-        <v>46269.231666666667</v>
+        <v>46268.533379629625</v>
       </c>
       <c r="G155" t="s">
-        <v>15</v>
+        <v>207</v>
       </c>
       <c r="H155" t="s">
-        <v>16</v>
-      </c>
-      <c r="I155"/>
+        <v>241</v>
+      </c>
+      <c r="I155">
+        <v>520</v>
+      </c>
       <c r="J155"/>
       <c r="K155"/>
       <c r="L155">
-        <v>1777</v>
+        <v>52</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="s">
-        <v>46</v>
+        <v>242</v>
       </c>
       <c r="B156" t="s">
-        <v>47</v>
+        <v>243</v>
       </c>
       <c r="C156" t="s">
-        <v>194</v>
+        <v>239</v>
       </c>
       <c r="D156">
-        <v>1142</v>
+        <v>10000</v>
       </c>
       <c r="E156" t="s">
-        <v>195</v>
+        <v>240</v>
       </c>
       <c r="F156" s="2">
-        <v>46269.231666666667</v>
+        <v>46268.533379629625</v>
       </c>
       <c r="G156" t="s">
-        <v>15</v>
+        <v>207</v>
       </c>
       <c r="H156" t="s">
-        <v>48</v>
+        <v>241</v>
       </c>
       <c r="I156">
-        <v>440</v>
+        <v>5000</v>
       </c>
       <c r="J156"/>
       <c r="K156"/>
       <c r="L156">
-        <v>4968</v>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="s">
-        <v>49</v>
-      </c>
-      <c r="B157" t="s">
-        <v>50</v>
-      </c>
-      <c r="C157" t="s">
-        <v>194</v>
-      </c>
-      <c r="D157">
-        <v>88</v>
-      </c>
-      <c r="E157" t="s">
-        <v>195</v>
-      </c>
-      <c r="F157" s="2">
-        <v>46269.231666666667</v>
-      </c>
-      <c r="G157" t="s">
-        <v>15</v>
-      </c>
-      <c r="H157" t="s">
-        <v>48</v>
-      </c>
-      <c r="I157">
-        <v>250</v>
-      </c>
-      <c r="J157"/>
-      <c r="K157"/>
-      <c r="L157">
-        <v>4341</v>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="s">
-        <v>51</v>
-      </c>
-      <c r="B158" t="s">
-        <v>52</v>
-      </c>
-      <c r="C158" t="s">
-        <v>194</v>
-      </c>
-      <c r="D158">
-        <v>20</v>
-      </c>
-      <c r="E158" t="s">
-        <v>195</v>
-      </c>
-      <c r="F158" s="2">
-        <v>46269.231666666667</v>
-      </c>
-      <c r="G158" t="s">
-        <v>15</v>
-      </c>
-      <c r="H158" t="s">
-        <v>48</v>
-      </c>
-      <c r="I158">
-        <v>250</v>
-      </c>
-      <c r="J158"/>
-      <c r="K158"/>
-      <c r="L158">
-        <v>2476</v>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="s">
-        <v>53</v>
-      </c>
-      <c r="B159" t="s">
-        <v>54</v>
-      </c>
-      <c r="C159" t="s">
-        <v>194</v>
-      </c>
-      <c r="D159">
-        <v>36</v>
-      </c>
-      <c r="E159" t="s">
-        <v>195</v>
-      </c>
-      <c r="F159" s="2">
-        <v>46268.900347222218</v>
-      </c>
-      <c r="G159" t="s">
-        <v>15</v>
-      </c>
-      <c r="H159" t="s">
-        <v>55</v>
-      </c>
-      <c r="I159">
-        <v>5000</v>
-      </c>
-      <c r="J159"/>
-      <c r="K159"/>
-      <c r="L159">
-        <v>2629</v>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="s">
-        <v>113</v>
-      </c>
-      <c r="B160" t="s">
-        <v>114</v>
-      </c>
-      <c r="C160" t="s">
-        <v>198</v>
-      </c>
-      <c r="D160">
-        <v>95040</v>
-      </c>
-      <c r="E160" t="s">
-        <v>199</v>
-      </c>
-      <c r="F160" s="2">
-        <v>46267</v>
-      </c>
-      <c r="G160" t="s">
-        <v>15</v>
-      </c>
-      <c r="H160" t="s">
-        <v>16</v>
-      </c>
-      <c r="I160"/>
-      <c r="J160"/>
-      <c r="K160"/>
-      <c r="L160">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="s">
-        <v>107</v>
-      </c>
-      <c r="B161" t="s">
-        <v>108</v>
-      </c>
-      <c r="C161" t="s">
-        <v>198</v>
-      </c>
-      <c r="D161">
-        <v>84480</v>
-      </c>
-      <c r="E161" t="s">
-        <v>199</v>
-      </c>
-      <c r="F161" s="2">
-        <v>46267</v>
-      </c>
-      <c r="G161" t="s">
-        <v>15</v>
-      </c>
-      <c r="H161" t="s">
-        <v>16</v>
-      </c>
-      <c r="I161"/>
-      <c r="J161"/>
-      <c r="K161"/>
-      <c r="L161">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="s">
-        <v>46</v>
-      </c>
-      <c r="B162" t="s">
-        <v>47</v>
-      </c>
-      <c r="C162" t="s">
-        <v>198</v>
-      </c>
-      <c r="D162">
-        <v>748</v>
-      </c>
-      <c r="E162" t="s">
-        <v>199</v>
-      </c>
-      <c r="F162" s="2">
-        <v>46267</v>
-      </c>
-      <c r="G162" t="s">
-        <v>15</v>
-      </c>
-      <c r="H162" t="s">
-        <v>48</v>
-      </c>
-      <c r="I162">
-        <v>440</v>
-      </c>
-      <c r="J162"/>
-      <c r="K162"/>
-      <c r="L162">
-        <v>1570</v>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="s">
-        <v>49</v>
-      </c>
-      <c r="B163" t="s">
-        <v>50</v>
-      </c>
-      <c r="C163" t="s">
-        <v>198</v>
-      </c>
-      <c r="D163">
-        <v>34</v>
-      </c>
-      <c r="E163" t="s">
-        <v>199</v>
-      </c>
-      <c r="F163" s="2">
-        <v>46267</v>
-      </c>
-      <c r="G163" t="s">
-        <v>15</v>
-      </c>
-      <c r="H163" t="s">
-        <v>48</v>
-      </c>
-      <c r="I163">
-        <v>250</v>
-      </c>
-      <c r="J163"/>
-      <c r="K163"/>
-      <c r="L163">
-        <v>1146</v>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="s">
-        <v>51</v>
-      </c>
-      <c r="B164" t="s">
-        <v>52</v>
-      </c>
-      <c r="C164" t="s">
-        <v>198</v>
-      </c>
-      <c r="D164">
-        <v>17</v>
-      </c>
-      <c r="E164" t="s">
-        <v>199</v>
-      </c>
-      <c r="F164" s="2">
-        <v>46267</v>
-      </c>
-      <c r="G164" t="s">
-        <v>15</v>
-      </c>
-      <c r="H164" t="s">
-        <v>48</v>
-      </c>
-      <c r="I164">
-        <v>250</v>
-      </c>
-      <c r="J164"/>
-      <c r="K164"/>
-      <c r="L164">
-        <v>1019</v>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="s">
-        <v>53</v>
-      </c>
-      <c r="B165" t="s">
-        <v>54</v>
-      </c>
-      <c r="C165" t="s">
-        <v>198</v>
-      </c>
-      <c r="D165">
-        <v>34</v>
-      </c>
-      <c r="E165" t="s">
-        <v>199</v>
-      </c>
-      <c r="F165" s="2">
-        <v>46267</v>
-      </c>
-      <c r="G165" t="s">
-        <v>15</v>
-      </c>
-      <c r="H165" t="s">
-        <v>55</v>
-      </c>
-      <c r="I165">
-        <v>5000</v>
-      </c>
-      <c r="J165"/>
-      <c r="K165"/>
-      <c r="L165">
-        <v>764</v>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="s">
-        <v>200</v>
-      </c>
-      <c r="B166" t="s">
-        <v>201</v>
-      </c>
-      <c r="C166" t="s">
-        <v>202</v>
-      </c>
-      <c r="D166">
-        <v>1000000</v>
-      </c>
-      <c r="E166" t="s">
-        <v>203</v>
-      </c>
-      <c r="F166" s="2">
-        <v>46235</v>
-      </c>
-      <c r="G166" t="s">
-        <v>204</v>
-      </c>
-      <c r="H166" t="s">
-        <v>205</v>
-      </c>
-      <c r="I166">
-        <v>1000000</v>
-      </c>
-      <c r="J166"/>
-      <c r="K166"/>
-      <c r="L166">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="s">
-        <v>206</v>
-      </c>
-      <c r="B167" t="s">
-        <v>207</v>
-      </c>
-      <c r="C167" t="s">
-        <v>208</v>
-      </c>
-      <c r="D167">
-        <v>5060000</v>
-      </c>
-      <c r="E167" t="s">
-        <v>209</v>
-      </c>
-      <c r="F167" s="2">
-        <v>46239</v>
-      </c>
-      <c r="G167" t="s">
-        <v>204</v>
-      </c>
-      <c r="H167" t="s">
-        <v>205</v>
-      </c>
-      <c r="I167">
-        <v>5060000</v>
-      </c>
-      <c r="J167"/>
-      <c r="K167"/>
-      <c r="L167">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="s">
-        <v>210</v>
-      </c>
-      <c r="B168" t="s">
-        <v>211</v>
-      </c>
-      <c r="C168" t="s">
-        <v>208</v>
-      </c>
-      <c r="D168">
-        <v>2439100</v>
-      </c>
-      <c r="E168" t="s">
-        <v>209</v>
-      </c>
-      <c r="F168" s="2">
-        <v>46235</v>
-      </c>
-      <c r="G168" t="s">
-        <v>204</v>
-      </c>
-      <c r="H168" t="s">
-        <v>205</v>
-      </c>
-      <c r="I168">
-        <v>800000</v>
-      </c>
-      <c r="J168"/>
-      <c r="K168"/>
-      <c r="L168">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="s">
-        <v>212</v>
-      </c>
-      <c r="B169" t="s">
-        <v>213</v>
-      </c>
-      <c r="C169" t="s">
-        <v>208</v>
-      </c>
-      <c r="D169">
-        <v>880000</v>
-      </c>
-      <c r="E169" t="s">
-        <v>209</v>
-      </c>
-      <c r="F169" s="2">
-        <v>46235</v>
-      </c>
-      <c r="G169" t="s">
-        <v>204</v>
-      </c>
-      <c r="H169" t="s">
-        <v>205</v>
-      </c>
-      <c r="I169">
-        <v>880000</v>
-      </c>
-      <c r="J169"/>
-      <c r="K169"/>
-      <c r="L169">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="s">
-        <v>214</v>
-      </c>
-      <c r="B170" t="s">
-        <v>215</v>
-      </c>
-      <c r="C170" t="s">
-        <v>208</v>
-      </c>
-      <c r="D170">
-        <v>104000</v>
-      </c>
-      <c r="E170" t="s">
-        <v>209</v>
-      </c>
-      <c r="F170" s="2">
-        <v>46258</v>
-      </c>
-      <c r="G170" t="s">
-        <v>204</v>
-      </c>
-      <c r="H170" t="s">
-        <v>205</v>
-      </c>
-      <c r="I170">
-        <v>52000</v>
-      </c>
-      <c r="J170"/>
-      <c r="K170"/>
-      <c r="L170">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="s">
-        <v>216</v>
-      </c>
-      <c r="B171" t="s">
-        <v>217</v>
-      </c>
-      <c r="C171" t="s">
-        <v>218</v>
-      </c>
-      <c r="D171">
-        <v>2</v>
-      </c>
-      <c r="E171" t="s">
-        <v>219</v>
-      </c>
-      <c r="F171" s="2">
-        <v>46268.56618055555</v>
-      </c>
-      <c r="G171" t="s">
-        <v>220</v>
-      </c>
-      <c r="H171" t="s">
-        <v>99</v>
-      </c>
-      <c r="I171">
-        <v>2</v>
-      </c>
-      <c r="J171"/>
-      <c r="K171"/>
-      <c r="L171">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="s">
-        <v>221</v>
-      </c>
-      <c r="B172" t="s">
-        <v>222</v>
-      </c>
-      <c r="C172" t="s">
-        <v>218</v>
-      </c>
-      <c r="D172">
-        <v>300</v>
-      </c>
-      <c r="E172" t="s">
-        <v>219</v>
-      </c>
-      <c r="F172" s="2">
-        <v>46268.65243055555</v>
-      </c>
-      <c r="G172" t="s">
-        <v>15</v>
-      </c>
-      <c r="H172" t="s">
-        <v>223</v>
-      </c>
-      <c r="I172">
-        <v>300</v>
-      </c>
-      <c r="J172"/>
-      <c r="K172"/>
-      <c r="L172">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="s">
-        <v>224</v>
-      </c>
-      <c r="B173" t="s">
-        <v>225</v>
-      </c>
-      <c r="C173" t="s">
-        <v>218</v>
-      </c>
-      <c r="D173">
-        <v>3</v>
-      </c>
-      <c r="E173" t="s">
-        <v>219</v>
-      </c>
-      <c r="F173" s="2">
-        <v>46262.311388888884</v>
-      </c>
-      <c r="G173" t="s">
-        <v>226</v>
-      </c>
-      <c r="H173" t="s">
-        <v>55</v>
-      </c>
-      <c r="I173">
-        <v>2</v>
-      </c>
-      <c r="J173"/>
-      <c r="K173"/>
-      <c r="L173">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="s">
-        <v>227</v>
-      </c>
-      <c r="B174" t="s">
-        <v>228</v>
-      </c>
-      <c r="C174" t="s">
-        <v>218</v>
-      </c>
-      <c r="D174">
-        <v>1</v>
-      </c>
-      <c r="E174" t="s">
-        <v>219</v>
-      </c>
-      <c r="F174" s="2">
-        <v>46268.664467592593</v>
-      </c>
-      <c r="G174" t="s">
-        <v>15</v>
-      </c>
-      <c r="H174" t="s">
-        <v>229</v>
-      </c>
-      <c r="I174">
-        <v>1</v>
-      </c>
-      <c r="J174"/>
-      <c r="K174"/>
-      <c r="L174">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="s">
-        <v>230</v>
-      </c>
-      <c r="B175" t="s">
-        <v>231</v>
-      </c>
-      <c r="C175" t="s">
-        <v>218</v>
-      </c>
-      <c r="D175">
-        <v>17</v>
-      </c>
-      <c r="E175" t="s">
-        <v>219</v>
-      </c>
-      <c r="F175" s="2">
-        <v>46268.665104166663</v>
-      </c>
-      <c r="G175" t="s">
-        <v>15</v>
-      </c>
-      <c r="H175" t="s">
-        <v>229</v>
-      </c>
-      <c r="I175">
-        <v>20</v>
-      </c>
-      <c r="J175"/>
-      <c r="K175"/>
-      <c r="L175">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="s">
-        <v>232</v>
-      </c>
-      <c r="B176" t="s">
-        <v>233</v>
-      </c>
-      <c r="C176" t="s">
-        <v>218</v>
-      </c>
-      <c r="D176">
-        <v>20</v>
-      </c>
-      <c r="E176" t="s">
-        <v>219</v>
-      </c>
-      <c r="F176" s="2">
-        <v>46268.656412037039</v>
-      </c>
-      <c r="G176" t="s">
-        <v>15</v>
-      </c>
-      <c r="H176" t="s">
-        <v>229</v>
-      </c>
-      <c r="I176">
-        <v>20</v>
-      </c>
-      <c r="J176"/>
-      <c r="K176"/>
-      <c r="L176">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="s">
-        <v>234</v>
-      </c>
-      <c r="B177" t="s">
-        <v>235</v>
-      </c>
-      <c r="C177" t="s">
-        <v>218</v>
-      </c>
-      <c r="D177">
-        <v>8</v>
-      </c>
-      <c r="E177" t="s">
-        <v>219</v>
-      </c>
-      <c r="F177" s="2">
-        <v>46268.655486111107</v>
-      </c>
-      <c r="G177" t="s">
-        <v>15</v>
-      </c>
-      <c r="H177" t="s">
-        <v>229</v>
-      </c>
-      <c r="I177">
-        <v>11</v>
-      </c>
-      <c r="J177"/>
-      <c r="K177"/>
-      <c r="L177">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="s">
-        <v>214</v>
-      </c>
-      <c r="B178" t="s">
-        <v>215</v>
-      </c>
-      <c r="C178" t="s">
-        <v>236</v>
-      </c>
-      <c r="D178">
-        <v>104000</v>
-      </c>
-      <c r="E178" t="s">
-        <v>237</v>
-      </c>
-      <c r="F178" s="2">
-        <v>46235</v>
-      </c>
-      <c r="G178" t="s">
-        <v>204</v>
-      </c>
-      <c r="H178" t="s">
-        <v>205</v>
-      </c>
-      <c r="I178">
-        <v>52000</v>
-      </c>
-      <c r="J178"/>
-      <c r="K178"/>
-      <c r="L178">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" t="s">
-        <v>238</v>
-      </c>
-      <c r="B179" t="s">
-        <v>239</v>
-      </c>
-      <c r="C179" t="s">
-        <v>240</v>
-      </c>
-      <c r="D179">
-        <v>82407</v>
-      </c>
-      <c r="E179" t="s">
-        <v>241</v>
-      </c>
-      <c r="F179" s="2">
-        <v>46268</v>
-      </c>
-      <c r="G179" t="s">
-        <v>15</v>
-      </c>
-      <c r="H179" t="s">
-        <v>16</v>
-      </c>
-      <c r="I179"/>
-      <c r="J179"/>
-      <c r="K179"/>
-      <c r="L179">
-        <v>554</v>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="s">
-        <v>242</v>
-      </c>
-      <c r="B180" t="s">
-        <v>243</v>
-      </c>
-      <c r="C180" t="s">
-        <v>244</v>
-      </c>
-      <c r="D180">
-        <v>1040</v>
-      </c>
-      <c r="E180" t="s">
-        <v>245</v>
-      </c>
-      <c r="F180" s="2">
-        <v>46268.533379629625</v>
-      </c>
-      <c r="G180" t="s">
-        <v>204</v>
-      </c>
-      <c r="H180" t="s">
-        <v>246</v>
-      </c>
-      <c r="I180">
-        <v>520</v>
-      </c>
-      <c r="J180"/>
-      <c r="K180"/>
-      <c r="L180">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" t="s">
-        <v>247</v>
-      </c>
-      <c r="B181" t="s">
-        <v>248</v>
-      </c>
-      <c r="C181" t="s">
-        <v>244</v>
-      </c>
-      <c r="D181">
-        <v>10000</v>
-      </c>
-      <c r="E181" t="s">
-        <v>245</v>
-      </c>
-      <c r="F181" s="2">
-        <v>46268.533379629625</v>
-      </c>
-      <c r="G181" t="s">
-        <v>204</v>
-      </c>
-      <c r="H181" t="s">
-        <v>246</v>
-      </c>
-      <c r="I181">
-        <v>5000</v>
-      </c>
-      <c r="J181"/>
-      <c r="K181"/>
-      <c r="L181">
         <v>413</v>
       </c>
     </row>
